--- a/FNID_Area3_Operational_Workbook.xlsx
+++ b/FNID_Area3_Operational_Workbook.xlsx
@@ -55,6 +55,16 @@
     <sheet name="Form_CR2" sheetId="46" state="visible" r:id="rId46"/>
     <sheet name="Form_CR5" sheetId="47" state="visible" r:id="rId47"/>
     <sheet name="Form_CaseSummary" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet name="tbl_Personnel" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet name="tbl_Training" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet name="tbl_CourtDates" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet name="tbl_Arrests" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="tbl_Seizures" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet name="tbl_Warrants" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet name="tbl_Informants" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet name="tbl_DutyRoster" sheetId="56" state="visible" r:id="rId56"/>
+    <sheet name="tbl_CustodyTransfers" sheetId="57" state="visible" r:id="rId57"/>
+    <sheet name="tbl_SceneLog" sheetId="58" state="visible" r:id="rId58"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -201,7 +211,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -278,8 +288,13 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007030A0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -301,11 +316,27 @@
     <border>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="hair">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -443,6 +474,15 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="22" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -955,8 +995,8 @@
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="tbl_UnitPlans" displayName="tbl_UnitPlans" ref="A1:AC33" headerRowCount="1">
-  <autoFilter ref="A1:AC33"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="tbl_UnitPlans" displayName="tbl_UnitPlans" ref="A1:AC45" headerRowCount="1">
+  <autoFilter ref="A1:AC45"/>
   <tableColumns count="29">
     <tableColumn id="1" name="PlanID"/>
     <tableColumn id="2" name="Unit"/>
@@ -992,6 +1032,262 @@
 </table>
 </file>
 
+<file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="tbl_Personnel" displayName="tbl_Personnel" ref="A1:X6" headerRowCount="1">
+  <autoFilter ref="A1:X6"/>
+  <tableColumns count="24">
+    <tableColumn id="1" name="PersonnelID"/>
+    <tableColumn id="2" name="FullName"/>
+    <tableColumn id="3" name="Rank"/>
+    <tableColumn id="4" name="BadgeNo"/>
+    <tableColumn id="5" name="Unit"/>
+    <tableColumn id="6" name="Station"/>
+    <tableColumn id="7" name="DateOfEnlistment"/>
+    <tableColumn id="8" name="DatePostedToFNID"/>
+    <tableColumn id="9" name="CurrentRole"/>
+    <tableColumn id="10" name="Specialization"/>
+    <tableColumn id="11" name="Status"/>
+    <tableColumn id="12" name="Phone"/>
+    <tableColumn id="13" name="Email"/>
+    <tableColumn id="14" name="EmergencyContact"/>
+    <tableColumn id="15" name="QualificationsHeld"/>
+    <tableColumn id="16" name="LastTrainingDate"/>
+    <tableColumn id="17" name="NextTrainingDue"/>
+    <tableColumn id="18" name="PerformanceRating"/>
+    <tableColumn id="19" name="DisciplinaryFlag"/>
+    <tableColumn id="20" name="Notes"/>
+    <tableColumn id="21" name="CreatedBy"/>
+    <tableColumn id="22" name="CreatedDate"/>
+    <tableColumn id="23" name="LastUpdatedBy"/>
+    <tableColumn id="24" name="LastUpdatedDate"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="tbl_Training" displayName="tbl_Training" ref="A1:X6" headerRowCount="1">
+  <autoFilter ref="A1:X6"/>
+  <tableColumns count="24">
+    <tableColumn id="1" name="TrainingID"/>
+    <tableColumn id="2" name="Date"/>
+    <tableColumn id="3" name="CourseTitle"/>
+    <tableColumn id="4" name="TrainingType"/>
+    <tableColumn id="5" name="Trainer"/>
+    <tableColumn id="6" name="Location"/>
+    <tableColumn id="7" name="Duration_Hrs"/>
+    <tableColumn id="8" name="Attendees"/>
+    <tableColumn id="9" name="AttendeeNames"/>
+    <tableColumn id="10" name="CertificateIssued"/>
+    <tableColumn id="11" name="ExpiryDate"/>
+    <tableColumn id="12" name="LinkedUnit"/>
+    <tableColumn id="13" name="CostJMD"/>
+    <tableColumn id="14" name="FundingSource"/>
+    <tableColumn id="15" name="Outcome"/>
+    <tableColumn id="16" name="Notes"/>
+    <tableColumn id="17" name="CreatedBy"/>
+    <tableColumn id="18" name="CreatedDate"/>
+    <tableColumn id="19" name="LastUpdatedBy"/>
+    <tableColumn id="20" name="LastUpdatedDate"/>
+    <tableColumn id="21" name="Week"/>
+    <tableColumn id="22" name="Month"/>
+    <tableColumn id="23" name="Quarter"/>
+    <tableColumn id="24" name="Year"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="tbl_CourtDates" displayName="tbl_CourtDates" ref="A1:AG6" headerRowCount="1">
+  <autoFilter ref="A1:AG6"/>
+  <tableColumns count="33">
+    <tableColumn id="1" name="CourtID"/>
+    <tableColumn id="2" name="LinkedCaseID"/>
+    <tableColumn id="3" name="CourtName"/>
+    <tableColumn id="4" name="CourtType"/>
+    <tableColumn id="5" name="HearingDate"/>
+    <tableColumn id="6" name="HearingTime"/>
+    <tableColumn id="7" name="HearingType"/>
+    <tableColumn id="8" name="JudgeMagistrate"/>
+    <tableColumn id="9" name="Prosecutor"/>
+    <tableColumn id="10" name="DefenseAttorney"/>
+    <tableColumn id="11" name="Defendant"/>
+    <tableColumn id="12" name="ChargesSummary"/>
+    <tableColumn id="13" name="WitnessesRequired"/>
+    <tableColumn id="14" name="WitnessesAttended"/>
+    <tableColumn id="15" name="ExhibitsRequired"/>
+    <tableColumn id="16" name="Outcome"/>
+    <tableColumn id="17" name="AdjournmentReason"/>
+    <tableColumn id="18" name="NextHearingDate"/>
+    <tableColumn id="19" name="BailStatus"/>
+    <tableColumn id="20" name="BailAmount"/>
+    <tableColumn id="21" name="RemandStatus"/>
+    <tableColumn id="22" name="Verdict"/>
+    <tableColumn id="23" name="Sentence"/>
+    <tableColumn id="24" name="SentenceDate"/>
+    <tableColumn id="25" name="Notes"/>
+    <tableColumn id="26" name="CreatedBy"/>
+    <tableColumn id="27" name="CreatedDate"/>
+    <tableColumn id="28" name="LastUpdatedBy"/>
+    <tableColumn id="29" name="LastUpdatedDate"/>
+    <tableColumn id="30" name="Week"/>
+    <tableColumn id="31" name="Month"/>
+    <tableColumn id="32" name="Quarter"/>
+    <tableColumn id="33" name="Year"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="tbl_Arrests" displayName="tbl_Arrests" ref="A1:AG6" headerRowCount="1">
+  <autoFilter ref="A1:AG6"/>
+  <tableColumns count="33">
+    <tableColumn id="1" name="ArrestID"/>
+    <tableColumn id="2" name="LinkedOpsID"/>
+    <tableColumn id="3" name="LinkedCaseID"/>
+    <tableColumn id="4" name="ArrestDate"/>
+    <tableColumn id="5" name="ArrestTime"/>
+    <tableColumn id="6" name="ArrestLocation"/>
+    <tableColumn id="7" name="Parish"/>
+    <tableColumn id="8" name="Station"/>
+    <tableColumn id="9" name="SuspectName"/>
+    <tableColumn id="10" name="SuspectDOB"/>
+    <tableColumn id="11" name="SuspectAddress"/>
+    <tableColumn id="12" name="SuspectGender"/>
+    <tableColumn id="13" name="ChargeDescription"/>
+    <tableColumn id="14" name="OffenceType"/>
+    <tableColumn id="15" name="ArrestingOfficer"/>
+    <tableColumn id="16" name="ArrestingOfficerBadge"/>
+    <tableColumn id="17" name="CautionGiven"/>
+    <tableColumn id="18" name="RightsRead"/>
+    <tableColumn id="19" name="BailGranted"/>
+    <tableColumn id="20" name="BailAmount"/>
+    <tableColumn id="21" name="RemandFacility"/>
+    <tableColumn id="22" name="RemandDate"/>
+    <tableColumn id="23" name="CourtDate"/>
+    <tableColumn id="24" name="Status"/>
+    <tableColumn id="25" name="Notes"/>
+    <tableColumn id="26" name="CreatedBy"/>
+    <tableColumn id="27" name="CreatedDate"/>
+    <tableColumn id="28" name="LastUpdatedBy"/>
+    <tableColumn id="29" name="LastUpdatedDate"/>
+    <tableColumn id="30" name="Week"/>
+    <tableColumn id="31" name="Month"/>
+    <tableColumn id="32" name="Quarter"/>
+    <tableColumn id="33" name="Year"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="tbl_Seizures" displayName="tbl_Seizures" ref="A1:AC6" headerRowCount="1">
+  <autoFilter ref="A1:AC6"/>
+  <tableColumns count="29">
+    <tableColumn id="1" name="SeizureID"/>
+    <tableColumn id="2" name="LinkedOpsID"/>
+    <tableColumn id="3" name="LinkedCaseID"/>
+    <tableColumn id="4" name="LinkedArrestID"/>
+    <tableColumn id="5" name="SeizureDate"/>
+    <tableColumn id="6" name="SeizureLocation"/>
+    <tableColumn id="7" name="Parish"/>
+    <tableColumn id="8" name="ItemType"/>
+    <tableColumn id="9" name="ItemDescription"/>
+    <tableColumn id="10" name="Quantity"/>
+    <tableColumn id="11" name="UnitMeasure"/>
+    <tableColumn id="12" name="SerialNumber"/>
+    <tableColumn id="13" name="Make"/>
+    <tableColumn id="14" name="Model"/>
+    <tableColumn id="15" name="Calibre"/>
+    <tableColumn id="16" name="EstimatedValue"/>
+    <tableColumn id="17" name="LinkedExhibitID"/>
+    <tableColumn id="18" name="PhotoRef"/>
+    <tableColumn id="19" name="SeizedBy"/>
+    <tableColumn id="20" name="WitnessPresent"/>
+    <tableColumn id="21" name="Notes"/>
+    <tableColumn id="22" name="CreatedBy"/>
+    <tableColumn id="23" name="CreatedDate"/>
+    <tableColumn id="24" name="LastUpdatedBy"/>
+    <tableColumn id="25" name="LastUpdatedDate"/>
+    <tableColumn id="26" name="Week"/>
+    <tableColumn id="27" name="Month"/>
+    <tableColumn id="28" name="Quarter"/>
+    <tableColumn id="29" name="Year"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="28" name="tbl_Warrants" displayName="tbl_Warrants" ref="A1:Y6" headerRowCount="1">
+  <autoFilter ref="A1:Y6"/>
+  <tableColumns count="25">
+    <tableColumn id="1" name="WarrantID"/>
+    <tableColumn id="2" name="WarrantType"/>
+    <tableColumn id="3" name="LinkedCaseID"/>
+    <tableColumn id="4" name="LinkedLeadID"/>
+    <tableColumn id="5" name="LinkedOpsID"/>
+    <tableColumn id="6" name="ApplicationDate"/>
+    <tableColumn id="7" name="IssuedDate"/>
+    <tableColumn id="8" name="IssuedBy"/>
+    <tableColumn id="9" name="JP_Name"/>
+    <tableColumn id="10" name="Court"/>
+    <tableColumn id="11" name="TargetName"/>
+    <tableColumn id="12" name="TargetAddress"/>
+    <tableColumn id="13" name="Parish"/>
+    <tableColumn id="14" name="ValidUntil"/>
+    <tableColumn id="15" name="ExecutionDate"/>
+    <tableColumn id="16" name="ExecutedBy"/>
+    <tableColumn id="17" name="ExecutionOutcome"/>
+    <tableColumn id="18" name="ReturnToJP_Date"/>
+    <tableColumn id="19" name="ReturnToJP_By"/>
+    <tableColumn id="20" name="Status"/>
+    <tableColumn id="21" name="Notes"/>
+    <tableColumn id="22" name="CreatedBy"/>
+    <tableColumn id="23" name="CreatedDate"/>
+    <tableColumn id="24" name="LastUpdatedBy"/>
+    <tableColumn id="25" name="LastUpdatedDate"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table29.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="29" name="tbl_Informants" displayName="tbl_Informants" ref="A1:Y6" headerRowCount="1">
+  <autoFilter ref="A1:Y6"/>
+  <tableColumns count="25">
+    <tableColumn id="1" name="InformantID"/>
+    <tableColumn id="2" name="CodeName"/>
+    <tableColumn id="3" name="Handler"/>
+    <tableColumn id="4" name="HandlerBadge"/>
+    <tableColumn id="5" name="Unit"/>
+    <tableColumn id="6" name="RegistrationDate"/>
+    <tableColumn id="7" name="Credibility"/>
+    <tableColumn id="8" name="Parish"/>
+    <tableColumn id="9" name="Area_Coverage"/>
+    <tableColumn id="10" name="TotalTipsProvided"/>
+    <tableColumn id="11" name="TipsConvertedToCase"/>
+    <tableColumn id="12" name="TipsConvertedToOp"/>
+    <tableColumn id="13" name="ConversionRate"/>
+    <tableColumn id="14" name="LastContactDate"/>
+    <tableColumn id="15" name="NextContactDue"/>
+    <tableColumn id="16" name="PaymentsToDate"/>
+    <tableColumn id="17" name="LastPaymentDate"/>
+    <tableColumn id="18" name="LastPaymentAmount"/>
+    <tableColumn id="19" name="RiskToInformant"/>
+    <tableColumn id="20" name="Status"/>
+    <tableColumn id="21" name="Notes"/>
+    <tableColumn id="22" name="CreatedBy"/>
+    <tableColumn id="23" name="CreatedDate"/>
+    <tableColumn id="24" name="LastUpdatedBy"/>
+    <tableColumn id="25" name="LastUpdatedDate"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tbl_EvidenceUseMap" displayName="tbl_EvidenceUseMap" ref="A1:E12" headerRowCount="1">
   <autoFilter ref="A1:E12"/>
@@ -1001,6 +1297,109 @@
     <tableColumn id="3" name="CaseElement_Supported"/>
     <tableColumn id="4" name="LegalRequirement"/>
     <tableColumn id="5" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table30.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="30" name="tbl_DutyRoster" displayName="tbl_DutyRoster" ref="A1:W6" headerRowCount="1">
+  <autoFilter ref="A1:W6"/>
+  <tableColumns count="23">
+    <tableColumn id="1" name="RosterID"/>
+    <tableColumn id="2" name="Date"/>
+    <tableColumn id="3" name="ShiftType"/>
+    <tableColumn id="4" name="StartTime"/>
+    <tableColumn id="5" name="EndTime"/>
+    <tableColumn id="6" name="OfficerName"/>
+    <tableColumn id="7" name="Rank"/>
+    <tableColumn id="8" name="BadgeNo"/>
+    <tableColumn id="9" name="Unit"/>
+    <tableColumn id="10" name="Station"/>
+    <tableColumn id="11" name="Assignment"/>
+    <tableColumn id="12" name="PostLocation"/>
+    <tableColumn id="13" name="Supervisor"/>
+    <tableColumn id="14" name="OvertimeHrs"/>
+    <tableColumn id="15" name="LeaveType"/>
+    <tableColumn id="16" name="Replacement"/>
+    <tableColumn id="17" name="Notes"/>
+    <tableColumn id="18" name="CreatedBy"/>
+    <tableColumn id="19" name="CreatedDate"/>
+    <tableColumn id="20" name="Week"/>
+    <tableColumn id="21" name="Month"/>
+    <tableColumn id="22" name="Quarter"/>
+    <tableColumn id="23" name="Year"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table31.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="31" name="tbl_CustodyTransfers" displayName="tbl_CustodyTransfers" ref="A1:T6" headerRowCount="1">
+  <autoFilter ref="A1:T6"/>
+  <tableColumns count="20">
+    <tableColumn id="1" name="TransferID"/>
+    <tableColumn id="2" name="ExhibitID"/>
+    <tableColumn id="3" name="LinkedCaseID"/>
+    <tableColumn id="4" name="TransferDate"/>
+    <tableColumn id="5" name="TransferTime"/>
+    <tableColumn id="6" name="ReleasedBy"/>
+    <tableColumn id="7" name="ReleasedByRank"/>
+    <tableColumn id="8" name="ReleasedByBadge"/>
+    <tableColumn id="9" name="ReceivedBy"/>
+    <tableColumn id="10" name="ReceivedByRank"/>
+    <tableColumn id="11" name="ReceivedByBadge"/>
+    <tableColumn id="12" name="Purpose"/>
+    <tableColumn id="13" name="FromLocation"/>
+    <tableColumn id="14" name="ToLocation"/>
+    <tableColumn id="15" name="ConditionAtTransfer"/>
+    <tableColumn id="16" name="WitnessName"/>
+    <tableColumn id="17" name="WitnessBadge"/>
+    <tableColumn id="18" name="Notes"/>
+    <tableColumn id="19" name="CreatedBy"/>
+    <tableColumn id="20" name="CreatedDate"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table32.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="32" name="tbl_SceneLog" displayName="tbl_SceneLog" ref="A1:AG6" headerRowCount="1">
+  <autoFilter ref="A1:AG6"/>
+  <tableColumns count="33">
+    <tableColumn id="1" name="SceneID"/>
+    <tableColumn id="2" name="LinkedCaseID"/>
+    <tableColumn id="3" name="LinkedOpsID"/>
+    <tableColumn id="4" name="Date"/>
+    <tableColumn id="5" name="Time"/>
+    <tableColumn id="6" name="Location"/>
+    <tableColumn id="7" name="Parish"/>
+    <tableColumn id="8" name="GPS_Coordinates"/>
+    <tableColumn id="9" name="SceneType"/>
+    <tableColumn id="10" name="SceneOfficer"/>
+    <tableColumn id="11" name="Rank"/>
+    <tableColumn id="12" name="BadgeNo"/>
+    <tableColumn id="13" name="PhotosTaken"/>
+    <tableColumn id="14" name="VideoRecorded"/>
+    <tableColumn id="15" name="SketchDrawn"/>
+    <tableColumn id="16" name="GSR_Collected"/>
+    <tableColumn id="17" name="ShellCasingsFound"/>
+    <tableColumn id="18" name="ShellCasingCount"/>
+    <tableColumn id="19" name="BloodSamplesCollected"/>
+    <tableColumn id="20" name="FingerprintsLifted"/>
+    <tableColumn id="21" name="WeaponsFound"/>
+    <tableColumn id="22" name="WeaponDetails"/>
+    <tableColumn id="23" name="WitnessesAtScene"/>
+    <tableColumn id="24" name="WeatherConditions"/>
+    <tableColumn id="25" name="Lighting"/>
+    <tableColumn id="26" name="SceneSealedTime"/>
+    <tableColumn id="27" name="SceneReleasedTime"/>
+    <tableColumn id="28" name="OtherEvidenceNotes"/>
+    <tableColumn id="29" name="Notes"/>
+    <tableColumn id="30" name="CreatedBy"/>
+    <tableColumn id="31" name="CreatedDate"/>
+    <tableColumn id="32" name="LastUpdatedBy"/>
+    <tableColumn id="33" name="LastUpdatedDate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1464,7 +1863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1516,12 +1915,12 @@
           <t>Registry — Case Registration &amp; CR Tracking</t>
         </is>
       </c>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
+      <c r="C6" s="57" t="n"/>
+      <c r="D6" s="57" t="n"/>
+      <c r="E6" s="57" t="n"/>
+      <c r="F6" s="57" t="n"/>
+      <c r="G6" s="57" t="n"/>
+      <c r="H6" s="57" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -1534,12 +1933,12 @@
           <t>Investigations — Case Progress &amp; Reviews</t>
         </is>
       </c>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
+      <c r="C7" s="57" t="n"/>
+      <c r="D7" s="57" t="n"/>
+      <c r="E7" s="57" t="n"/>
+      <c r="F7" s="57" t="n"/>
+      <c r="G7" s="57" t="n"/>
+      <c r="H7" s="57" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -1552,12 +1951,12 @@
           <t>Operations — Ops Activity &amp; FCSI Tracking</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
+      <c r="C8" s="57" t="n"/>
+      <c r="D8" s="57" t="n"/>
+      <c r="E8" s="57" t="n"/>
+      <c r="F8" s="57" t="n"/>
+      <c r="G8" s="57" t="n"/>
+      <c r="H8" s="57" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -1570,12 +1969,12 @@
           <t>Intelligence — Lead Management &amp; Briefings</t>
         </is>
       </c>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
+      <c r="C9" s="57" t="n"/>
+      <c r="D9" s="57" t="n"/>
+      <c r="E9" s="57" t="n"/>
+      <c r="F9" s="57" t="n"/>
+      <c r="G9" s="57" t="n"/>
+      <c r="H9" s="57" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -1588,12 +1987,12 @@
           <t>Transport — Fleet, Usage, Fuel &amp; Maintenance</t>
         </is>
       </c>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
+      <c r="C10" s="57" t="n"/>
+      <c r="D10" s="57" t="n"/>
+      <c r="E10" s="57" t="n"/>
+      <c r="F10" s="57" t="n"/>
+      <c r="G10" s="57" t="n"/>
+      <c r="H10" s="57" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1606,12 +2005,12 @@
           <t>Demand Reduction — Community Outreach</t>
         </is>
       </c>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
+      <c r="C11" s="57" t="n"/>
+      <c r="D11" s="57" t="n"/>
+      <c r="E11" s="57" t="n"/>
+      <c r="F11" s="57" t="n"/>
+      <c r="G11" s="57" t="n"/>
+      <c r="H11" s="57" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1624,12 +2023,12 @@
           <t>Admin/HRM — Personnel &amp; Administration</t>
         </is>
       </c>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
+      <c r="C12" s="57" t="n"/>
+      <c r="D12" s="57" t="n"/>
+      <c r="E12" s="57" t="n"/>
+      <c r="F12" s="57" t="n"/>
+      <c r="G12" s="57" t="n"/>
+      <c r="H12" s="57" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1642,12 +2041,12 @@
           <t>Training — Capacity Building &amp; Certifications</t>
         </is>
       </c>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
+      <c r="C13" s="57" t="n"/>
+      <c r="D13" s="57" t="n"/>
+      <c r="E13" s="57" t="n"/>
+      <c r="F13" s="57" t="n"/>
+      <c r="G13" s="57" t="n"/>
+      <c r="H13" s="57" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1660,12 +2059,12 @@
           <t>Oversight — Compliance &amp; Governance</t>
         </is>
       </c>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
+      <c r="C14" s="57" t="n"/>
+      <c r="D14" s="57" t="n"/>
+      <c r="E14" s="57" t="n"/>
+      <c r="F14" s="57" t="n"/>
+      <c r="G14" s="57" t="n"/>
+      <c r="H14" s="57" t="n"/>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
@@ -1685,12 +2084,12 @@
           <t>Executive Dashboard — Full Operational Picture</t>
         </is>
       </c>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="n"/>
+      <c r="C17" s="57" t="n"/>
+      <c r="D17" s="57" t="n"/>
+      <c r="E17" s="57" t="n"/>
+      <c r="F17" s="57" t="n"/>
+      <c r="G17" s="57" t="n"/>
+      <c r="H17" s="57" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1703,12 +2102,12 @@
           <t>FCSI Dashboard — Focused Crime Suppression Initiative</t>
         </is>
       </c>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n"/>
-      <c r="F18" s="7" t="n"/>
-      <c r="G18" s="7" t="n"/>
-      <c r="H18" s="7" t="n"/>
+      <c r="C18" s="57" t="n"/>
+      <c r="D18" s="57" t="n"/>
+      <c r="E18" s="57" t="n"/>
+      <c r="F18" s="57" t="n"/>
+      <c r="G18" s="57" t="n"/>
+      <c r="H18" s="57" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1721,12 +2120,12 @@
           <t>Central Statistics Hub — All Modules Aggregated</t>
         </is>
       </c>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
+      <c r="C19" s="57" t="n"/>
+      <c r="D19" s="57" t="n"/>
+      <c r="E19" s="57" t="n"/>
+      <c r="F19" s="57" t="n"/>
+      <c r="G19" s="57" t="n"/>
+      <c r="H19" s="57" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1739,12 +2138,12 @@
           <t>Registry Dashboard</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="n"/>
+      <c r="C20" s="57" t="n"/>
+      <c r="D20" s="57" t="n"/>
+      <c r="E20" s="57" t="n"/>
+      <c r="F20" s="57" t="n"/>
+      <c r="G20" s="57" t="n"/>
+      <c r="H20" s="57" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -1757,12 +2156,12 @@
           <t>Investigations Dashboard</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n"/>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
+      <c r="C21" s="57" t="n"/>
+      <c r="D21" s="57" t="n"/>
+      <c r="E21" s="57" t="n"/>
+      <c r="F21" s="57" t="n"/>
+      <c r="G21" s="57" t="n"/>
+      <c r="H21" s="57" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -1775,12 +2174,12 @@
           <t>Operations Dashboard</t>
         </is>
       </c>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="n"/>
+      <c r="C22" s="57" t="n"/>
+      <c r="D22" s="57" t="n"/>
+      <c r="E22" s="57" t="n"/>
+      <c r="F22" s="57" t="n"/>
+      <c r="G22" s="57" t="n"/>
+      <c r="H22" s="57" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -1793,12 +2192,12 @@
           <t>Intelligence Dashboard</t>
         </is>
       </c>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
+      <c r="C23" s="57" t="n"/>
+      <c r="D23" s="57" t="n"/>
+      <c r="E23" s="57" t="n"/>
+      <c r="F23" s="57" t="n"/>
+      <c r="G23" s="57" t="n"/>
+      <c r="H23" s="57" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -1811,12 +2210,12 @@
           <t>Transport Dashboard</t>
         </is>
       </c>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
-      <c r="F24" s="7" t="n"/>
-      <c r="G24" s="7" t="n"/>
-      <c r="H24" s="7" t="n"/>
+      <c r="C24" s="57" t="n"/>
+      <c r="D24" s="57" t="n"/>
+      <c r="E24" s="57" t="n"/>
+      <c r="F24" s="57" t="n"/>
+      <c r="G24" s="57" t="n"/>
+      <c r="H24" s="57" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -1829,12 +2228,12 @@
           <t>Evidence &amp; Forensics Dashboard</t>
         </is>
       </c>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="7" t="n"/>
+      <c r="C25" s="57" t="n"/>
+      <c r="D25" s="57" t="n"/>
+      <c r="E25" s="57" t="n"/>
+      <c r="F25" s="57" t="n"/>
+      <c r="G25" s="57" t="n"/>
+      <c r="H25" s="57" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -1847,12 +2246,12 @@
           <t>Demand Reduction Dashboard</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="n"/>
+      <c r="C26" s="57" t="n"/>
+      <c r="D26" s="57" t="n"/>
+      <c r="E26" s="57" t="n"/>
+      <c r="F26" s="57" t="n"/>
+      <c r="G26" s="57" t="n"/>
+      <c r="H26" s="57" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -1865,12 +2264,12 @@
           <t>Oversight &amp; Compliance Dashboard</t>
         </is>
       </c>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="7" t="n"/>
+      <c r="C27" s="57" t="n"/>
+      <c r="D27" s="57" t="n"/>
+      <c r="E27" s="57" t="n"/>
+      <c r="F27" s="57" t="n"/>
+      <c r="G27" s="57" t="n"/>
+      <c r="H27" s="57" t="n"/>
     </row>
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
@@ -1890,12 +2289,12 @@
           <t>Cases Register</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="n"/>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="7" t="n"/>
-      <c r="G30" s="7" t="n"/>
-      <c r="H30" s="7" t="n"/>
+      <c r="C30" s="57" t="n"/>
+      <c r="D30" s="57" t="n"/>
+      <c r="E30" s="57" t="n"/>
+      <c r="F30" s="57" t="n"/>
+      <c r="G30" s="57" t="n"/>
+      <c r="H30" s="57" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -1908,12 +2307,12 @@
           <t>Action Items</t>
         </is>
       </c>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="7" t="n"/>
-      <c r="G31" s="7" t="n"/>
-      <c r="H31" s="7" t="n"/>
+      <c r="C31" s="57" t="n"/>
+      <c r="D31" s="57" t="n"/>
+      <c r="E31" s="57" t="n"/>
+      <c r="F31" s="57" t="n"/>
+      <c r="G31" s="57" t="n"/>
+      <c r="H31" s="57" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -1926,12 +2325,12 @@
           <t>Supervisory Reviews</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
-      <c r="E32" s="7" t="n"/>
-      <c r="F32" s="7" t="n"/>
-      <c r="G32" s="7" t="n"/>
-      <c r="H32" s="7" t="n"/>
+      <c r="C32" s="57" t="n"/>
+      <c r="D32" s="57" t="n"/>
+      <c r="E32" s="57" t="n"/>
+      <c r="F32" s="57" t="n"/>
+      <c r="G32" s="57" t="n"/>
+      <c r="H32" s="57" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -1944,12 +2343,12 @@
           <t>Investigation Diary</t>
         </is>
       </c>
-      <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="n"/>
-      <c r="E33" s="7" t="n"/>
-      <c r="F33" s="7" t="n"/>
-      <c r="G33" s="7" t="n"/>
-      <c r="H33" s="7" t="n"/>
+      <c r="C33" s="57" t="n"/>
+      <c r="D33" s="57" t="n"/>
+      <c r="E33" s="57" t="n"/>
+      <c r="F33" s="57" t="n"/>
+      <c r="G33" s="57" t="n"/>
+      <c r="H33" s="57" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -1962,12 +2361,12 @@
           <t>Radio Messages</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="n"/>
-      <c r="E34" s="7" t="n"/>
-      <c r="F34" s="7" t="n"/>
-      <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="n"/>
+      <c r="C34" s="57" t="n"/>
+      <c r="D34" s="57" t="n"/>
+      <c r="E34" s="57" t="n"/>
+      <c r="F34" s="57" t="n"/>
+      <c r="G34" s="57" t="n"/>
+      <c r="H34" s="57" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -1980,12 +2379,12 @@
           <t>Persons of Interest</t>
         </is>
       </c>
-      <c r="C35" s="7" t="n"/>
-      <c r="D35" s="7" t="n"/>
-      <c r="E35" s="7" t="n"/>
-      <c r="F35" s="7" t="n"/>
-      <c r="G35" s="7" t="n"/>
-      <c r="H35" s="7" t="n"/>
+      <c r="C35" s="57" t="n"/>
+      <c r="D35" s="57" t="n"/>
+      <c r="E35" s="57" t="n"/>
+      <c r="F35" s="57" t="n"/>
+      <c r="G35" s="57" t="n"/>
+      <c r="H35" s="57" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
@@ -1998,12 +2397,12 @@
           <t>Morning Crime Report Intake</t>
         </is>
       </c>
-      <c r="C36" s="7" t="n"/>
-      <c r="D36" s="7" t="n"/>
-      <c r="E36" s="7" t="n"/>
-      <c r="F36" s="7" t="n"/>
-      <c r="G36" s="7" t="n"/>
-      <c r="H36" s="7" t="n"/>
+      <c r="C36" s="57" t="n"/>
+      <c r="D36" s="57" t="n"/>
+      <c r="E36" s="57" t="n"/>
+      <c r="F36" s="57" t="n"/>
+      <c r="G36" s="57" t="n"/>
+      <c r="H36" s="57" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -2016,12 +2415,12 @@
           <t>Lead Register</t>
         </is>
       </c>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7" t="n"/>
-      <c r="E37" s="7" t="n"/>
-      <c r="F37" s="7" t="n"/>
-      <c r="G37" s="7" t="n"/>
-      <c r="H37" s="7" t="n"/>
+      <c r="C37" s="57" t="n"/>
+      <c r="D37" s="57" t="n"/>
+      <c r="E37" s="57" t="n"/>
+      <c r="F37" s="57" t="n"/>
+      <c r="G37" s="57" t="n"/>
+      <c r="H37" s="57" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
@@ -2034,12 +2433,12 @@
           <t>Follow-Up Recommendations</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="n"/>
-      <c r="E38" s="7" t="n"/>
-      <c r="F38" s="7" t="n"/>
-      <c r="G38" s="7" t="n"/>
-      <c r="H38" s="7" t="n"/>
+      <c r="C38" s="57" t="n"/>
+      <c r="D38" s="57" t="n"/>
+      <c r="E38" s="57" t="n"/>
+      <c r="F38" s="57" t="n"/>
+      <c r="G38" s="57" t="n"/>
+      <c r="H38" s="57" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -2052,12 +2451,12 @@
           <t>Intelligence Briefings</t>
         </is>
       </c>
-      <c r="C39" s="7" t="n"/>
-      <c r="D39" s="7" t="n"/>
-      <c r="E39" s="7" t="n"/>
-      <c r="F39" s="7" t="n"/>
-      <c r="G39" s="7" t="n"/>
-      <c r="H39" s="7" t="n"/>
+      <c r="C39" s="57" t="n"/>
+      <c r="D39" s="57" t="n"/>
+      <c r="E39" s="57" t="n"/>
+      <c r="F39" s="57" t="n"/>
+      <c r="G39" s="57" t="n"/>
+      <c r="H39" s="57" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -2070,12 +2469,12 @@
           <t>Operations Register</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="n"/>
-      <c r="E40" s="7" t="n"/>
-      <c r="F40" s="7" t="n"/>
-      <c r="G40" s="7" t="n"/>
-      <c r="H40" s="7" t="n"/>
+      <c r="C40" s="57" t="n"/>
+      <c r="D40" s="57" t="n"/>
+      <c r="E40" s="57" t="n"/>
+      <c r="F40" s="57" t="n"/>
+      <c r="G40" s="57" t="n"/>
+      <c r="H40" s="57" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -2088,12 +2487,12 @@
           <t>Evidence/Exhibits Pool</t>
         </is>
       </c>
-      <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="n"/>
-      <c r="E41" s="7" t="n"/>
-      <c r="F41" s="7" t="n"/>
-      <c r="G41" s="7" t="n"/>
-      <c r="H41" s="7" t="n"/>
+      <c r="C41" s="57" t="n"/>
+      <c r="D41" s="57" t="n"/>
+      <c r="E41" s="57" t="n"/>
+      <c r="F41" s="57" t="n"/>
+      <c r="G41" s="57" t="n"/>
+      <c r="H41" s="57" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -2106,12 +2505,12 @@
           <t>Vehicle Register</t>
         </is>
       </c>
-      <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="n"/>
-      <c r="E42" s="7" t="n"/>
-      <c r="F42" s="7" t="n"/>
-      <c r="G42" s="7" t="n"/>
-      <c r="H42" s="7" t="n"/>
+      <c r="C42" s="57" t="n"/>
+      <c r="D42" s="57" t="n"/>
+      <c r="E42" s="57" t="n"/>
+      <c r="F42" s="57" t="n"/>
+      <c r="G42" s="57" t="n"/>
+      <c r="H42" s="57" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -2124,12 +2523,12 @@
           <t>Vehicle Usage Log</t>
         </is>
       </c>
-      <c r="C43" s="7" t="n"/>
-      <c r="D43" s="7" t="n"/>
-      <c r="E43" s="7" t="n"/>
-      <c r="F43" s="7" t="n"/>
-      <c r="G43" s="7" t="n"/>
-      <c r="H43" s="7" t="n"/>
+      <c r="C43" s="57" t="n"/>
+      <c r="D43" s="57" t="n"/>
+      <c r="E43" s="57" t="n"/>
+      <c r="F43" s="57" t="n"/>
+      <c r="G43" s="57" t="n"/>
+      <c r="H43" s="57" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -2142,12 +2541,12 @@
           <t>Fuel Log</t>
         </is>
       </c>
-      <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="n"/>
-      <c r="E44" s="7" t="n"/>
-      <c r="F44" s="7" t="n"/>
-      <c r="G44" s="7" t="n"/>
-      <c r="H44" s="7" t="n"/>
+      <c r="C44" s="57" t="n"/>
+      <c r="D44" s="57" t="n"/>
+      <c r="E44" s="57" t="n"/>
+      <c r="F44" s="57" t="n"/>
+      <c r="G44" s="57" t="n"/>
+      <c r="H44" s="57" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -2160,12 +2559,12 @@
           <t>Maintenance Register</t>
         </is>
       </c>
-      <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="n"/>
-      <c r="E45" s="7" t="n"/>
-      <c r="F45" s="7" t="n"/>
-      <c r="G45" s="7" t="n"/>
-      <c r="H45" s="7" t="n"/>
+      <c r="C45" s="57" t="n"/>
+      <c r="D45" s="57" t="n"/>
+      <c r="E45" s="57" t="n"/>
+      <c r="F45" s="57" t="n"/>
+      <c r="G45" s="57" t="n"/>
+      <c r="H45" s="57" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -2178,12 +2577,12 @@
           <t>Driver Registry</t>
         </is>
       </c>
-      <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="n"/>
-      <c r="E46" s="7" t="n"/>
-      <c r="F46" s="7" t="n"/>
-      <c r="G46" s="7" t="n"/>
-      <c r="H46" s="7" t="n"/>
+      <c r="C46" s="57" t="n"/>
+      <c r="D46" s="57" t="n"/>
+      <c r="E46" s="57" t="n"/>
+      <c r="F46" s="57" t="n"/>
+      <c r="G46" s="57" t="n"/>
+      <c r="H46" s="57" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
@@ -2196,12 +2595,12 @@
           <t>Demand Reduction Lectures</t>
         </is>
       </c>
-      <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="n"/>
-      <c r="E47" s="7" t="n"/>
-      <c r="F47" s="7" t="n"/>
-      <c r="G47" s="7" t="n"/>
-      <c r="H47" s="7" t="n"/>
+      <c r="C47" s="57" t="n"/>
+      <c r="D47" s="57" t="n"/>
+      <c r="E47" s="57" t="n"/>
+      <c r="F47" s="57" t="n"/>
+      <c r="G47" s="57" t="n"/>
+      <c r="H47" s="57" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
@@ -2214,12 +2613,12 @@
           <t>Unit Plans, Targets &amp; Performance</t>
         </is>
       </c>
-      <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="n"/>
-      <c r="E48" s="7" t="n"/>
-      <c r="F48" s="7" t="n"/>
-      <c r="G48" s="7" t="n"/>
-      <c r="H48" s="7" t="n"/>
+      <c r="C48" s="57" t="n"/>
+      <c r="D48" s="57" t="n"/>
+      <c r="E48" s="57" t="n"/>
+      <c r="F48" s="57" t="n"/>
+      <c r="G48" s="57" t="n"/>
+      <c r="H48" s="57" t="n"/>
     </row>
     <row r="50" ht="26" customHeight="1">
       <c r="A50" s="10" t="inlineStr">
@@ -2239,12 +2638,12 @@
           <t>Dropdown Lists &amp; Reference Data</t>
         </is>
       </c>
-      <c r="C51" s="7" t="n"/>
-      <c r="D51" s="7" t="n"/>
-      <c r="E51" s="7" t="n"/>
-      <c r="F51" s="7" t="n"/>
-      <c r="G51" s="7" t="n"/>
-      <c r="H51" s="7" t="n"/>
+      <c r="C51" s="57" t="n"/>
+      <c r="D51" s="57" t="n"/>
+      <c r="E51" s="57" t="n"/>
+      <c r="F51" s="57" t="n"/>
+      <c r="G51" s="57" t="n"/>
+      <c r="H51" s="57" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -2257,12 +2656,12 @@
           <t>Offence Classification &amp; FNID Routing Map</t>
         </is>
       </c>
-      <c r="C52" s="7" t="n"/>
-      <c r="D52" s="7" t="n"/>
-      <c r="E52" s="7" t="n"/>
-      <c r="F52" s="7" t="n"/>
-      <c r="G52" s="7" t="n"/>
-      <c r="H52" s="7" t="n"/>
+      <c r="C52" s="57" t="n"/>
+      <c r="D52" s="57" t="n"/>
+      <c r="E52" s="57" t="n"/>
+      <c r="F52" s="57" t="n"/>
+      <c r="G52" s="57" t="n"/>
+      <c r="H52" s="57" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
@@ -2275,12 +2674,12 @@
           <t>Evidence → Forensic Agency Routing</t>
         </is>
       </c>
-      <c r="C53" s="7" t="n"/>
-      <c r="D53" s="7" t="n"/>
-      <c r="E53" s="7" t="n"/>
-      <c r="F53" s="7" t="n"/>
-      <c r="G53" s="7" t="n"/>
-      <c r="H53" s="7" t="n"/>
+      <c r="C53" s="57" t="n"/>
+      <c r="D53" s="57" t="n"/>
+      <c r="E53" s="57" t="n"/>
+      <c r="F53" s="57" t="n"/>
+      <c r="G53" s="57" t="n"/>
+      <c r="H53" s="57" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
@@ -2293,12 +2692,12 @@
           <t>Evidence → Evidential Use Mapping</t>
         </is>
       </c>
-      <c r="C54" s="7" t="n"/>
-      <c r="D54" s="7" t="n"/>
-      <c r="E54" s="7" t="n"/>
-      <c r="F54" s="7" t="n"/>
-      <c r="G54" s="7" t="n"/>
-      <c r="H54" s="7" t="n"/>
+      <c r="C54" s="57" t="n"/>
+      <c r="D54" s="57" t="n"/>
+      <c r="E54" s="57" t="n"/>
+      <c r="F54" s="57" t="n"/>
+      <c r="G54" s="57" t="n"/>
+      <c r="H54" s="57" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
@@ -2311,12 +2710,12 @@
           <t>CR1 Form Template (Printable)</t>
         </is>
       </c>
-      <c r="C55" s="7" t="n"/>
-      <c r="D55" s="7" t="n"/>
-      <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7" t="n"/>
-      <c r="G55" s="7" t="n"/>
-      <c r="H55" s="7" t="n"/>
+      <c r="C55" s="57" t="n"/>
+      <c r="D55" s="57" t="n"/>
+      <c r="E55" s="57" t="n"/>
+      <c r="F55" s="57" t="n"/>
+      <c r="G55" s="57" t="n"/>
+      <c r="H55" s="57" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
@@ -2329,12 +2728,12 @@
           <t>CR2 Form Template (Printable)</t>
         </is>
       </c>
-      <c r="C56" s="7" t="n"/>
-      <c r="D56" s="7" t="n"/>
-      <c r="E56" s="7" t="n"/>
-      <c r="F56" s="7" t="n"/>
-      <c r="G56" s="7" t="n"/>
-      <c r="H56" s="7" t="n"/>
+      <c r="C56" s="57" t="n"/>
+      <c r="D56" s="57" t="n"/>
+      <c r="E56" s="57" t="n"/>
+      <c r="F56" s="57" t="n"/>
+      <c r="G56" s="57" t="n"/>
+      <c r="H56" s="57" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -2347,12 +2746,12 @@
           <t>CR5 Form Template (Printable)</t>
         </is>
       </c>
-      <c r="C57" s="7" t="n"/>
-      <c r="D57" s="7" t="n"/>
-      <c r="E57" s="7" t="n"/>
-      <c r="F57" s="7" t="n"/>
-      <c r="G57" s="7" t="n"/>
-      <c r="H57" s="7" t="n"/>
+      <c r="C57" s="57" t="n"/>
+      <c r="D57" s="57" t="n"/>
+      <c r="E57" s="57" t="n"/>
+      <c r="F57" s="57" t="n"/>
+      <c r="G57" s="57" t="n"/>
+      <c r="H57" s="57" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
@@ -2365,12 +2764,12 @@
           <t>Case Summary Report Template</t>
         </is>
       </c>
-      <c r="C58" s="7" t="n"/>
-      <c r="D58" s="7" t="n"/>
-      <c r="E58" s="7" t="n"/>
-      <c r="F58" s="7" t="n"/>
-      <c r="G58" s="7" t="n"/>
-      <c r="H58" s="7" t="n"/>
+      <c r="C58" s="57" t="n"/>
+      <c r="D58" s="57" t="n"/>
+      <c r="E58" s="57" t="n"/>
+      <c r="F58" s="57" t="n"/>
+      <c r="G58" s="57" t="n"/>
+      <c r="H58" s="57" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
@@ -2379,20 +2778,210 @@
         </is>
       </c>
     </row>
+    <row r="63" ht="26" customHeight="1">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>NEW TABLES (Audit Patch — Gap Remediation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  &gt;&gt; tbl_Personnel</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>Personnel Register — Staff details, qualifications, postings</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="n"/>
+      <c r="D64" s="7" t="n"/>
+      <c r="E64" s="7" t="n"/>
+      <c r="F64" s="7" t="n"/>
+      <c r="G64" s="7" t="n"/>
+      <c r="H64" s="7" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  &gt;&gt; tbl_Training</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>Training Log — Courses, attendance, certifications, costs</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="n"/>
+      <c r="D65" s="7" t="n"/>
+      <c r="E65" s="7" t="n"/>
+      <c r="F65" s="7" t="n"/>
+      <c r="G65" s="7" t="n"/>
+      <c r="H65" s="7" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  &gt;&gt; tbl_CourtDates</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>Court Tracking — Hearings, outcomes, bail, sentencing</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="n"/>
+      <c r="D66" s="7" t="n"/>
+      <c r="E66" s="7" t="n"/>
+      <c r="F66" s="7" t="n"/>
+      <c r="G66" s="7" t="n"/>
+      <c r="H66" s="7" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  &gt;&gt; tbl_Arrests</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>Arrest Register — Detailed arrest records, charges, bail/remand</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="n"/>
+      <c r="D67" s="7" t="n"/>
+      <c r="E67" s="7" t="n"/>
+      <c r="F67" s="7" t="n"/>
+      <c r="G67" s="7" t="n"/>
+      <c r="H67" s="7" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  &gt;&gt; tbl_Seizures</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>Seizures Register — Individual seized items linked to ops/cases</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="n"/>
+      <c r="D68" s="7" t="n"/>
+      <c r="E68" s="7" t="n"/>
+      <c r="F68" s="7" t="n"/>
+      <c r="G68" s="7" t="n"/>
+      <c r="H68" s="7" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  &gt;&gt; tbl_Warrants</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>Warrant Register — Applications, issuance, execution, return to JP</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="n"/>
+      <c r="D69" s="7" t="n"/>
+      <c r="E69" s="7" t="n"/>
+      <c r="F69" s="7" t="n"/>
+      <c r="G69" s="7" t="n"/>
+      <c r="H69" s="7" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  &gt;&gt; tbl_Informants</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>Informant Management — Code names, handlers, reliability, payments</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="n"/>
+      <c r="D70" s="7" t="n"/>
+      <c r="E70" s="7" t="n"/>
+      <c r="F70" s="7" t="n"/>
+      <c r="G70" s="7" t="n"/>
+      <c r="H70" s="7" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  &gt;&gt; tbl_DutyRoster</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>Duty Roster — Shifts, assignments, overtime, leave tracking</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="n"/>
+      <c r="D71" s="7" t="n"/>
+      <c r="E71" s="7" t="n"/>
+      <c r="F71" s="7" t="n"/>
+      <c r="G71" s="7" t="n"/>
+      <c r="H71" s="7" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  &gt;&gt; tbl_CustodyTransfers</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>Chain of Custody Transfers — Exhibit handover audit trail</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="n"/>
+      <c r="D72" s="7" t="n"/>
+      <c r="E72" s="7" t="n"/>
+      <c r="F72" s="7" t="n"/>
+      <c r="G72" s="7" t="n"/>
+      <c r="H72" s="7" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  &gt;&gt; tbl_SceneLog</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>Scene Processing Log — Crime scene details, evidence collection</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="n"/>
+      <c r="D73" s="7" t="n"/>
+      <c r="E73" s="7" t="n"/>
+      <c r="F73" s="7" t="n"/>
+      <c r="G73" s="7" t="n"/>
+      <c r="H73" s="7" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="55">
+  <mergeCells count="66">
     <mergeCell ref="B40:H40"/>
     <mergeCell ref="B9:H9"/>
+    <mergeCell ref="B65:H65"/>
+    <mergeCell ref="B68:H68"/>
     <mergeCell ref="B55:H55"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B24:H24"/>
     <mergeCell ref="B30:H30"/>
+    <mergeCell ref="B64:H64"/>
     <mergeCell ref="B33:H33"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="B51:H51"/>
     <mergeCell ref="B20:H20"/>
+    <mergeCell ref="A61:H61"/>
     <mergeCell ref="B37:H37"/>
-    <mergeCell ref="A61:H61"/>
     <mergeCell ref="B45:H45"/>
     <mergeCell ref="B36:H36"/>
     <mergeCell ref="B32:H32"/>
@@ -2404,10 +2993,12 @@
     <mergeCell ref="B54:H54"/>
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="B25:H25"/>
+    <mergeCell ref="B72:H72"/>
     <mergeCell ref="B31:H31"/>
     <mergeCell ref="B46:H46"/>
     <mergeCell ref="A50:H50"/>
     <mergeCell ref="B22:H22"/>
+    <mergeCell ref="B66:H66"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="B18:H18"/>
     <mergeCell ref="B27:H27"/>
@@ -2419,10 +3010,12 @@
     <mergeCell ref="B12:H12"/>
     <mergeCell ref="B39:H39"/>
     <mergeCell ref="B58:H58"/>
+    <mergeCell ref="B70:H70"/>
     <mergeCell ref="B48:H48"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="B11:H11"/>
     <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B67:H67"/>
     <mergeCell ref="B23:H23"/>
     <mergeCell ref="B8:H8"/>
     <mergeCell ref="B14:H14"/>
@@ -2432,10 +3025,14 @@
     <mergeCell ref="B57:H57"/>
     <mergeCell ref="B44:H44"/>
     <mergeCell ref="B53:H53"/>
+    <mergeCell ref="A63:H63"/>
+    <mergeCell ref="B73:H73"/>
+    <mergeCell ref="B69:H69"/>
     <mergeCell ref="B38:H38"/>
     <mergeCell ref="B10:H10"/>
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="B34:H34"/>
+    <mergeCell ref="B71:H71"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6005,7 +6602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6028,6 +6625,16 @@
     <col width="22" customWidth="1" min="18" max="18"/>
     <col width="22" customWidth="1" min="19" max="19"/>
     <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
+    <col width="22" customWidth="1" min="29" max="29"/>
+    <col width="22" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6131,6 +6738,56 @@
           <t>ComplianceStatus</t>
         </is>
       </c>
+      <c r="U1" s="12" t="inlineStr">
+        <is>
+          <t>ActionStatus</t>
+        </is>
+      </c>
+      <c r="V1" s="12" t="inlineStr">
+        <is>
+          <t>ActionType</t>
+        </is>
+      </c>
+      <c r="W1" s="12" t="inlineStr">
+        <is>
+          <t>ReviewType</t>
+        </is>
+      </c>
+      <c r="X1" s="12" t="inlineStr">
+        <is>
+          <t>HearingType</t>
+        </is>
+      </c>
+      <c r="Y1" s="12" t="inlineStr">
+        <is>
+          <t>ShiftType</t>
+        </is>
+      </c>
+      <c r="Z1" s="12" t="inlineStr">
+        <is>
+          <t>WarrantType</t>
+        </is>
+      </c>
+      <c r="AA1" s="12" t="inlineStr">
+        <is>
+          <t>WarrantStatus</t>
+        </is>
+      </c>
+      <c r="AB1" s="12" t="inlineStr">
+        <is>
+          <t>BailStatus</t>
+        </is>
+      </c>
+      <c r="AC1" s="12" t="inlineStr">
+        <is>
+          <t>PersonnelStatus</t>
+        </is>
+      </c>
+      <c r="AD1" s="12" t="inlineStr">
+        <is>
+          <t>SceneType</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6233,6 +6890,56 @@
           <t>Compliant</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Interview Witness</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Supervisory Review</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Mention</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Day Shift</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Search Warrant</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Granted</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Shooting Scene</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6335,6 +7042,56 @@
           <t>Non-Compliant</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Interview Suspect</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Peer Review</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Preliminary Inquiry</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Night Shift</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Arrest Warrant</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Issued</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Denied</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>On Leave</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Drug Lab</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6432,6 +7189,56 @@
           <t>Under Review</t>
         </is>
       </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Collect Evidence</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Compliance Audit</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Trial</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Evening Shift</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Bench Warrant</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Executed</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Not Applied</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Seconded</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Stash House</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -6524,6 +7331,56 @@
           <t>Overdue</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Submit Exhibit</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Quality Check</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Sentencing</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>24-Hour Duty</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Seizure Order</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Returned to JP</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Revoked</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Suspended</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Arrest Scene</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6606,6 +7463,56 @@
           <t>N/A</t>
         </is>
       </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Conduct Search</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Command Review</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Bail Hearing</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>On Call</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Surveillance Order</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Expired</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Surety Pending</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Transferred</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Vehicle Search</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6663,6 +7570,46 @@
           <t>DSP</t>
         </is>
       </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Surveillance</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Monthly Review</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Appeal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Rest Day</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Retired</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Residential Search</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6710,6 +7657,26 @@
           <t>SSP</t>
         </is>
       </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Arrest</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Deceased</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Commercial Search</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6752,6 +7719,16 @@
           <t>ACP</t>
         </is>
       </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Court Preparation</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>Open Area</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6789,6 +7766,16 @@
           <t>DCP</t>
         </is>
       </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lab Follow-Up</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6821,6 +7808,11 @@
           <t>Commissioner</t>
         </is>
       </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Supervisory Review</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="C12" t="inlineStr">
@@ -6838,6 +7830,11 @@
           <t>Biological Sample</t>
         </is>
       </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Report Writing</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="C13" t="inlineStr">
@@ -6853,6 +7850,11 @@
       <c r="K13" t="inlineStr">
         <is>
           <t>Fingerprint</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -8151,7 +9153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC33"/>
+  <dimension ref="A1:AC45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11083,6 +12085,1038 @@
       <c r="AA33" s="14" t="n"/>
       <c r="AB33" s="14" t="n"/>
       <c r="AC33" s="14" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>KPI-0033</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>Investigations</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>Court Readiness</t>
+        </is>
+      </c>
+      <c r="D34" s="14" t="inlineStr">
+        <is>
+          <t>Court Dates Attended</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>Scheduled hearings attended</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="n"/>
+      <c r="H34" s="14" t="n"/>
+      <c r="I34" s="14" t="n"/>
+      <c r="J34" s="14" t="n"/>
+      <c r="K34" s="14" t="n"/>
+      <c r="L34" s="14" t="n"/>
+      <c r="M34" s="14" t="n"/>
+      <c r="N34" s="14">
+        <f>IF(OR(K34="",H34=""),"",K34-H34)</f>
+        <v/>
+      </c>
+      <c r="O34" s="14">
+        <f>IF(OR(L34="",I34=""),"",L34-I34)</f>
+        <v/>
+      </c>
+      <c r="P34" s="14">
+        <f>IF(OR(M34="",J34=""),"",M34-J34)</f>
+        <v/>
+      </c>
+      <c r="Q34" s="16">
+        <f>IF(OR(K34="",H34="",H34=0),"",K34/H34)</f>
+        <v/>
+      </c>
+      <c r="R34" s="16">
+        <f>IF(OR(L34="",I34="",I34=0),"",L34/I34)</f>
+        <v/>
+      </c>
+      <c r="S34" s="16">
+        <f>IF(OR(M34="",J34="",J34=0),"",M34/J34)</f>
+        <v/>
+      </c>
+      <c r="T34" s="14">
+        <f>IF(Q34="","",IF(Q34&gt;=0.9,"On Track",IF(Q34&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="U34" s="14">
+        <f>IF(R34="","",IF(R34&gt;=0.9,"On Track",IF(R34&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="V34" s="14">
+        <f>IF(S34="","",IF(S34&gt;=0.9,"On Track",IF(S34&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="W34" s="14" t="inlineStr">
+        <is>
+          <t>tbl_CourtDates</t>
+        </is>
+      </c>
+      <c r="X34" s="14" t="n"/>
+      <c r="Y34" s="14" t="n"/>
+      <c r="Z34" s="14" t="n"/>
+      <c r="AA34" s="14" t="n"/>
+      <c r="AB34" s="14" t="n"/>
+      <c r="AC34" s="14" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>KPI-0034</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>Investigations</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>Court Readiness</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>Conviction Rate</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>% of court outcomes resulting in conviction</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="n"/>
+      <c r="H35" s="14" t="n"/>
+      <c r="I35" s="14" t="n"/>
+      <c r="J35" s="14" t="n"/>
+      <c r="K35" s="14" t="n"/>
+      <c r="L35" s="14" t="n"/>
+      <c r="M35" s="14" t="n"/>
+      <c r="N35" s="14">
+        <f>IF(OR(K35="",H35=""),"",K35-H35)</f>
+        <v/>
+      </c>
+      <c r="O35" s="14">
+        <f>IF(OR(L35="",I35=""),"",L35-I35)</f>
+        <v/>
+      </c>
+      <c r="P35" s="14">
+        <f>IF(OR(M35="",J35=""),"",M35-J35)</f>
+        <v/>
+      </c>
+      <c r="Q35" s="16">
+        <f>IF(OR(K35="",H35="",H35=0),"",K35/H35)</f>
+        <v/>
+      </c>
+      <c r="R35" s="16">
+        <f>IF(OR(L35="",I35="",I35=0),"",L35/I35)</f>
+        <v/>
+      </c>
+      <c r="S35" s="16">
+        <f>IF(OR(M35="",J35="",J35=0),"",M35/J35)</f>
+        <v/>
+      </c>
+      <c r="T35" s="14">
+        <f>IF(Q35="","",IF(Q35&gt;=0.9,"On Track",IF(Q35&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="U35" s="14">
+        <f>IF(R35="","",IF(R35&gt;=0.9,"On Track",IF(R35&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="V35" s="14">
+        <f>IF(S35="","",IF(S35&gt;=0.9,"On Track",IF(S35&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="W35" s="14" t="inlineStr">
+        <is>
+          <t>tbl_CourtDates</t>
+        </is>
+      </c>
+      <c r="X35" s="14" t="n"/>
+      <c r="Y35" s="14" t="n"/>
+      <c r="Z35" s="14" t="n"/>
+      <c r="AA35" s="14" t="n"/>
+      <c r="AB35" s="14" t="n"/>
+      <c r="AC35" s="14" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>KPI-0035</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>Arrest Quality</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr">
+        <is>
+          <t>Arrest-to-Charge Rate</t>
+        </is>
+      </c>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>% of arrests with charges filed</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="G36" s="14" t="n"/>
+      <c r="H36" s="14" t="n"/>
+      <c r="I36" s="14" t="n"/>
+      <c r="J36" s="14" t="n"/>
+      <c r="K36" s="14" t="n"/>
+      <c r="L36" s="14" t="n"/>
+      <c r="M36" s="14" t="n"/>
+      <c r="N36" s="14">
+        <f>IF(OR(K36="",H36=""),"",K36-H36)</f>
+        <v/>
+      </c>
+      <c r="O36" s="14">
+        <f>IF(OR(L36="",I36=""),"",L36-I36)</f>
+        <v/>
+      </c>
+      <c r="P36" s="14">
+        <f>IF(OR(M36="",J36=""),"",M36-J36)</f>
+        <v/>
+      </c>
+      <c r="Q36" s="16">
+        <f>IF(OR(K36="",H36="",H36=0),"",K36/H36)</f>
+        <v/>
+      </c>
+      <c r="R36" s="16">
+        <f>IF(OR(L36="",I36="",I36=0),"",L36/I36)</f>
+        <v/>
+      </c>
+      <c r="S36" s="16">
+        <f>IF(OR(M36="",J36="",J36=0),"",M36/J36)</f>
+        <v/>
+      </c>
+      <c r="T36" s="14">
+        <f>IF(Q36="","",IF(Q36&gt;=0.9,"On Track",IF(Q36&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="U36" s="14">
+        <f>IF(R36="","",IF(R36&gt;=0.9,"On Track",IF(R36&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="V36" s="14">
+        <f>IF(S36="","",IF(S36&gt;=0.9,"On Track",IF(S36&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="W36" s="14" t="inlineStr">
+        <is>
+          <t>tbl_Arrests</t>
+        </is>
+      </c>
+      <c r="X36" s="14" t="n"/>
+      <c r="Y36" s="14" t="n"/>
+      <c r="Z36" s="14" t="n"/>
+      <c r="AA36" s="14" t="n"/>
+      <c r="AB36" s="14" t="n"/>
+      <c r="AC36" s="14" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>KPI-0036</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>Seizure Effectiveness</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>Items Seized per Op</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>Avg seized items per operation</t>
+        </is>
+      </c>
+      <c r="F37" s="14" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="G37" s="14" t="n"/>
+      <c r="H37" s="14" t="n"/>
+      <c r="I37" s="14" t="n"/>
+      <c r="J37" s="14" t="n"/>
+      <c r="K37" s="14" t="n"/>
+      <c r="L37" s="14" t="n"/>
+      <c r="M37" s="14" t="n"/>
+      <c r="N37" s="14">
+        <f>IF(OR(K37="",H37=""),"",K37-H37)</f>
+        <v/>
+      </c>
+      <c r="O37" s="14">
+        <f>IF(OR(L37="",I37=""),"",L37-I37)</f>
+        <v/>
+      </c>
+      <c r="P37" s="14">
+        <f>IF(OR(M37="",J37=""),"",M37-J37)</f>
+        <v/>
+      </c>
+      <c r="Q37" s="16">
+        <f>IF(OR(K37="",H37="",H37=0),"",K37/H37)</f>
+        <v/>
+      </c>
+      <c r="R37" s="16">
+        <f>IF(OR(L37="",I37="",I37=0),"",L37/I37)</f>
+        <v/>
+      </c>
+      <c r="S37" s="16">
+        <f>IF(OR(M37="",J37="",J37=0),"",M37/J37)</f>
+        <v/>
+      </c>
+      <c r="T37" s="14">
+        <f>IF(Q37="","",IF(Q37&gt;=0.9,"On Track",IF(Q37&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="U37" s="14">
+        <f>IF(R37="","",IF(R37&gt;=0.9,"On Track",IF(R37&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="V37" s="14">
+        <f>IF(S37="","",IF(S37&gt;=0.9,"On Track",IF(S37&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="W37" s="14" t="inlineStr">
+        <is>
+          <t>tbl_Seizures</t>
+        </is>
+      </c>
+      <c r="X37" s="14" t="n"/>
+      <c r="Y37" s="14" t="n"/>
+      <c r="Z37" s="14" t="n"/>
+      <c r="AA37" s="14" t="n"/>
+      <c r="AB37" s="14" t="n"/>
+      <c r="AC37" s="14" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>KPI-0037</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>Intelligence</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>Informant Management</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>Active Informants</t>
+        </is>
+      </c>
+      <c r="E38" s="14" t="inlineStr">
+        <is>
+          <t>Number of active registered informants</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="G38" s="14" t="n"/>
+      <c r="H38" s="14" t="n"/>
+      <c r="I38" s="14" t="n"/>
+      <c r="J38" s="14" t="n"/>
+      <c r="K38" s="14" t="n"/>
+      <c r="L38" s="14" t="n"/>
+      <c r="M38" s="14" t="n"/>
+      <c r="N38" s="14">
+        <f>IF(OR(K38="",H38=""),"",K38-H38)</f>
+        <v/>
+      </c>
+      <c r="O38" s="14">
+        <f>IF(OR(L38="",I38=""),"",L38-I38)</f>
+        <v/>
+      </c>
+      <c r="P38" s="14">
+        <f>IF(OR(M38="",J38=""),"",M38-J38)</f>
+        <v/>
+      </c>
+      <c r="Q38" s="16">
+        <f>IF(OR(K38="",H38="",H38=0),"",K38/H38)</f>
+        <v/>
+      </c>
+      <c r="R38" s="16">
+        <f>IF(OR(L38="",I38="",I38=0),"",L38/I38)</f>
+        <v/>
+      </c>
+      <c r="S38" s="16">
+        <f>IF(OR(M38="",J38="",J38=0),"",M38/J38)</f>
+        <v/>
+      </c>
+      <c r="T38" s="14">
+        <f>IF(Q38="","",IF(Q38&gt;=0.9,"On Track",IF(Q38&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="U38" s="14">
+        <f>IF(R38="","",IF(R38&gt;=0.9,"On Track",IF(R38&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="V38" s="14">
+        <f>IF(S38="","",IF(S38&gt;=0.9,"On Track",IF(S38&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="W38" s="14" t="inlineStr">
+        <is>
+          <t>tbl_Informants</t>
+        </is>
+      </c>
+      <c r="X38" s="14" t="n"/>
+      <c r="Y38" s="14" t="n"/>
+      <c r="Z38" s="14" t="n"/>
+      <c r="AA38" s="14" t="n"/>
+      <c r="AB38" s="14" t="n"/>
+      <c r="AC38" s="14" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>KPI-0038</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>Intelligence</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>Informant Management</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>Informant Tip Conversion %</t>
+        </is>
+      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>% of informant tips converted</t>
+        </is>
+      </c>
+      <c r="F39" s="14" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="G39" s="14" t="n"/>
+      <c r="H39" s="14" t="n"/>
+      <c r="I39" s="14" t="n"/>
+      <c r="J39" s="14" t="n"/>
+      <c r="K39" s="14" t="n"/>
+      <c r="L39" s="14" t="n"/>
+      <c r="M39" s="14" t="n"/>
+      <c r="N39" s="14">
+        <f>IF(OR(K39="",H39=""),"",K39-H39)</f>
+        <v/>
+      </c>
+      <c r="O39" s="14">
+        <f>IF(OR(L39="",I39=""),"",L39-I39)</f>
+        <v/>
+      </c>
+      <c r="P39" s="14">
+        <f>IF(OR(M39="",J39=""),"",M39-J39)</f>
+        <v/>
+      </c>
+      <c r="Q39" s="16">
+        <f>IF(OR(K39="",H39="",H39=0),"",K39/H39)</f>
+        <v/>
+      </c>
+      <c r="R39" s="16">
+        <f>IF(OR(L39="",I39="",I39=0),"",L39/I39)</f>
+        <v/>
+      </c>
+      <c r="S39" s="16">
+        <f>IF(OR(M39="",J39="",J39=0),"",M39/J39)</f>
+        <v/>
+      </c>
+      <c r="T39" s="14">
+        <f>IF(Q39="","",IF(Q39&gt;=0.9,"On Track",IF(Q39&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="U39" s="14">
+        <f>IF(R39="","",IF(R39&gt;=0.9,"On Track",IF(R39&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="V39" s="14">
+        <f>IF(S39="","",IF(S39&gt;=0.9,"On Track",IF(S39&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="W39" s="14" t="inlineStr">
+        <is>
+          <t>tbl_Informants</t>
+        </is>
+      </c>
+      <c r="X39" s="14" t="n"/>
+      <c r="Y39" s="14" t="n"/>
+      <c r="Z39" s="14" t="n"/>
+      <c r="AA39" s="14" t="n"/>
+      <c r="AB39" s="14" t="n"/>
+      <c r="AC39" s="14" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>KPI-0039</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>Admin/HRM</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>Workforce Readiness</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>Duty Roster Completion</t>
+        </is>
+      </c>
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>% of shifts filled vs required</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="G40" s="14" t="n"/>
+      <c r="H40" s="14" t="n"/>
+      <c r="I40" s="14" t="n"/>
+      <c r="J40" s="14" t="n"/>
+      <c r="K40" s="14" t="n"/>
+      <c r="L40" s="14" t="n"/>
+      <c r="M40" s="14" t="n"/>
+      <c r="N40" s="14">
+        <f>IF(OR(K40="",H40=""),"",K40-H40)</f>
+        <v/>
+      </c>
+      <c r="O40" s="14">
+        <f>IF(OR(L40="",I40=""),"",L40-I40)</f>
+        <v/>
+      </c>
+      <c r="P40" s="14">
+        <f>IF(OR(M40="",J40=""),"",M40-J40)</f>
+        <v/>
+      </c>
+      <c r="Q40" s="16">
+        <f>IF(OR(K40="",H40="",H40=0),"",K40/H40)</f>
+        <v/>
+      </c>
+      <c r="R40" s="16">
+        <f>IF(OR(L40="",I40="",I40=0),"",L40/I40)</f>
+        <v/>
+      </c>
+      <c r="S40" s="16">
+        <f>IF(OR(M40="",J40="",J40=0),"",M40/J40)</f>
+        <v/>
+      </c>
+      <c r="T40" s="14">
+        <f>IF(Q40="","",IF(Q40&gt;=0.9,"On Track",IF(Q40&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="U40" s="14">
+        <f>IF(R40="","",IF(R40&gt;=0.9,"On Track",IF(R40&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="V40" s="14">
+        <f>IF(S40="","",IF(S40&gt;=0.9,"On Track",IF(S40&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="W40" s="14" t="inlineStr">
+        <is>
+          <t>tbl_DutyRoster</t>
+        </is>
+      </c>
+      <c r="X40" s="14" t="n"/>
+      <c r="Y40" s="14" t="n"/>
+      <c r="Z40" s="14" t="n"/>
+      <c r="AA40" s="14" t="n"/>
+      <c r="AB40" s="14" t="n"/>
+      <c r="AC40" s="14" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>KPI-0040</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>Admin/HRM</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>Workforce Readiness</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>Training Compliance Rate</t>
+        </is>
+      </c>
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>% of personnel with current training</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="G41" s="14" t="n"/>
+      <c r="H41" s="14" t="n"/>
+      <c r="I41" s="14" t="n"/>
+      <c r="J41" s="14" t="n"/>
+      <c r="K41" s="14" t="n"/>
+      <c r="L41" s="14" t="n"/>
+      <c r="M41" s="14" t="n"/>
+      <c r="N41" s="14">
+        <f>IF(OR(K41="",H41=""),"",K41-H41)</f>
+        <v/>
+      </c>
+      <c r="O41" s="14">
+        <f>IF(OR(L41="",I41=""),"",L41-I41)</f>
+        <v/>
+      </c>
+      <c r="P41" s="14">
+        <f>IF(OR(M41="",J41=""),"",M41-J41)</f>
+        <v/>
+      </c>
+      <c r="Q41" s="16">
+        <f>IF(OR(K41="",H41="",H41=0),"",K41/H41)</f>
+        <v/>
+      </c>
+      <c r="R41" s="16">
+        <f>IF(OR(L41="",I41="",I41=0),"",L41/I41)</f>
+        <v/>
+      </c>
+      <c r="S41" s="16">
+        <f>IF(OR(M41="",J41="",J41=0),"",M41/J41)</f>
+        <v/>
+      </c>
+      <c r="T41" s="14">
+        <f>IF(Q41="","",IF(Q41&gt;=0.9,"On Track",IF(Q41&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="U41" s="14">
+        <f>IF(R41="","",IF(R41&gt;=0.9,"On Track",IF(R41&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="V41" s="14">
+        <f>IF(S41="","",IF(S41&gt;=0.9,"On Track",IF(S41&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="W41" s="14" t="inlineStr">
+        <is>
+          <t>tbl_Personnel</t>
+        </is>
+      </c>
+      <c r="X41" s="14" t="n"/>
+      <c r="Y41" s="14" t="n"/>
+      <c r="Z41" s="14" t="n"/>
+      <c r="AA41" s="14" t="n"/>
+      <c r="AB41" s="14" t="n"/>
+      <c r="AC41" s="14" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>KPI-0041</t>
+        </is>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>Capacity Building</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr">
+        <is>
+          <t>Training Hours Delivered</t>
+        </is>
+      </c>
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>Total hours of training delivered</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="G42" s="14" t="n"/>
+      <c r="H42" s="14" t="n"/>
+      <c r="I42" s="14" t="n"/>
+      <c r="J42" s="14" t="n"/>
+      <c r="K42" s="14" t="n"/>
+      <c r="L42" s="14" t="n"/>
+      <c r="M42" s="14" t="n"/>
+      <c r="N42" s="14">
+        <f>IF(OR(K42="",H42=""),"",K42-H42)</f>
+        <v/>
+      </c>
+      <c r="O42" s="14">
+        <f>IF(OR(L42="",I42=""),"",L42-I42)</f>
+        <v/>
+      </c>
+      <c r="P42" s="14">
+        <f>IF(OR(M42="",J42=""),"",M42-J42)</f>
+        <v/>
+      </c>
+      <c r="Q42" s="16">
+        <f>IF(OR(K42="",H42="",H42=0),"",K42/H42)</f>
+        <v/>
+      </c>
+      <c r="R42" s="16">
+        <f>IF(OR(L42="",I42="",I42=0),"",L42/I42)</f>
+        <v/>
+      </c>
+      <c r="S42" s="16">
+        <f>IF(OR(M42="",J42="",J42=0),"",M42/J42)</f>
+        <v/>
+      </c>
+      <c r="T42" s="14">
+        <f>IF(Q42="","",IF(Q42&gt;=0.9,"On Track",IF(Q42&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="U42" s="14">
+        <f>IF(R42="","",IF(R42&gt;=0.9,"On Track",IF(R42&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="V42" s="14">
+        <f>IF(S42="","",IF(S42&gt;=0.9,"On Track",IF(S42&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="W42" s="14" t="inlineStr">
+        <is>
+          <t>tbl_Training</t>
+        </is>
+      </c>
+      <c r="X42" s="14" t="n"/>
+      <c r="Y42" s="14" t="n"/>
+      <c r="Z42" s="14" t="n"/>
+      <c r="AA42" s="14" t="n"/>
+      <c r="AB42" s="14" t="n"/>
+      <c r="AC42" s="14" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>KPI-0042</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>Capacity Building</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>Training Cost (JMD)</t>
+        </is>
+      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>Total training expenditure</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="G43" s="14" t="n"/>
+      <c r="H43" s="14" t="n"/>
+      <c r="I43" s="14" t="n"/>
+      <c r="J43" s="14" t="n"/>
+      <c r="K43" s="14" t="n"/>
+      <c r="L43" s="14" t="n"/>
+      <c r="M43" s="14" t="n"/>
+      <c r="N43" s="14">
+        <f>IF(OR(K43="",H43=""),"",K43-H43)</f>
+        <v/>
+      </c>
+      <c r="O43" s="14">
+        <f>IF(OR(L43="",I43=""),"",L43-I43)</f>
+        <v/>
+      </c>
+      <c r="P43" s="14">
+        <f>IF(OR(M43="",J43=""),"",M43-J43)</f>
+        <v/>
+      </c>
+      <c r="Q43" s="16">
+        <f>IF(OR(K43="",H43="",H43=0),"",K43/H43)</f>
+        <v/>
+      </c>
+      <c r="R43" s="16">
+        <f>IF(OR(L43="",I43="",I43=0),"",L43/I43)</f>
+        <v/>
+      </c>
+      <c r="S43" s="16">
+        <f>IF(OR(M43="",J43="",J43=0),"",M43/J43)</f>
+        <v/>
+      </c>
+      <c r="T43" s="14">
+        <f>IF(Q43="","",IF(Q43&gt;=0.9,"On Track",IF(Q43&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="U43" s="14">
+        <f>IF(R43="","",IF(R43&gt;=0.9,"On Track",IF(R43&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="V43" s="14">
+        <f>IF(S43="","",IF(S43&gt;=0.9,"On Track",IF(S43&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="W43" s="14" t="inlineStr">
+        <is>
+          <t>tbl_Training</t>
+        </is>
+      </c>
+      <c r="X43" s="14" t="n"/>
+      <c r="Y43" s="14" t="n"/>
+      <c r="Z43" s="14" t="n"/>
+      <c r="AA43" s="14" t="n"/>
+      <c r="AB43" s="14" t="n"/>
+      <c r="AC43" s="14" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>KPI-0043</t>
+        </is>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>Oversight</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>Evidence Integrity</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr">
+        <is>
+          <t>Custody Transfers Logged</t>
+        </is>
+      </c>
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>Total chain-of-custody transfers</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="G44" s="14" t="n"/>
+      <c r="H44" s="14" t="n"/>
+      <c r="I44" s="14" t="n"/>
+      <c r="J44" s="14" t="n"/>
+      <c r="K44" s="14" t="n"/>
+      <c r="L44" s="14" t="n"/>
+      <c r="M44" s="14" t="n"/>
+      <c r="N44" s="14">
+        <f>IF(OR(K44="",H44=""),"",K44-H44)</f>
+        <v/>
+      </c>
+      <c r="O44" s="14">
+        <f>IF(OR(L44="",I44=""),"",L44-I44)</f>
+        <v/>
+      </c>
+      <c r="P44" s="14">
+        <f>IF(OR(M44="",J44=""),"",M44-J44)</f>
+        <v/>
+      </c>
+      <c r="Q44" s="16">
+        <f>IF(OR(K44="",H44="",H44=0),"",K44/H44)</f>
+        <v/>
+      </c>
+      <c r="R44" s="16">
+        <f>IF(OR(L44="",I44="",I44=0),"",L44/I44)</f>
+        <v/>
+      </c>
+      <c r="S44" s="16">
+        <f>IF(OR(M44="",J44="",J44=0),"",M44/J44)</f>
+        <v/>
+      </c>
+      <c r="T44" s="14">
+        <f>IF(Q44="","",IF(Q44&gt;=0.9,"On Track",IF(Q44&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="U44" s="14">
+        <f>IF(R44="","",IF(R44&gt;=0.9,"On Track",IF(R44&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="V44" s="14">
+        <f>IF(S44="","",IF(S44&gt;=0.9,"On Track",IF(S44&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="W44" s="14" t="inlineStr">
+        <is>
+          <t>tbl_CustodyTransfers</t>
+        </is>
+      </c>
+      <c r="X44" s="14" t="n"/>
+      <c r="Y44" s="14" t="n"/>
+      <c r="Z44" s="14" t="n"/>
+      <c r="AA44" s="14" t="n"/>
+      <c r="AB44" s="14" t="n"/>
+      <c r="AC44" s="14" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>KPI-0044</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>Oversight</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>Evidence Integrity</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>Scene Processing Compliance</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>Scenes processed per shooting case</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="G45" s="14" t="n"/>
+      <c r="H45" s="14" t="n"/>
+      <c r="I45" s="14" t="n"/>
+      <c r="J45" s="14" t="n"/>
+      <c r="K45" s="14" t="n"/>
+      <c r="L45" s="14" t="n"/>
+      <c r="M45" s="14" t="n"/>
+      <c r="N45" s="14">
+        <f>IF(OR(K45="",H45=""),"",K45-H45)</f>
+        <v/>
+      </c>
+      <c r="O45" s="14">
+        <f>IF(OR(L45="",I45=""),"",L45-I45)</f>
+        <v/>
+      </c>
+      <c r="P45" s="14">
+        <f>IF(OR(M45="",J45=""),"",M45-J45)</f>
+        <v/>
+      </c>
+      <c r="Q45" s="16">
+        <f>IF(OR(K45="",H45="",H45=0),"",K45/H45)</f>
+        <v/>
+      </c>
+      <c r="R45" s="16">
+        <f>IF(OR(L45="",I45="",I45=0),"",L45/I45)</f>
+        <v/>
+      </c>
+      <c r="S45" s="16">
+        <f>IF(OR(M45="",J45="",J45=0),"",M45/J45)</f>
+        <v/>
+      </c>
+      <c r="T45" s="14">
+        <f>IF(Q45="","",IF(Q45&gt;=0.9,"On Track",IF(Q45&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="U45" s="14">
+        <f>IF(R45="","",IF(R45&gt;=0.9,"On Track",IF(R45&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="V45" s="14">
+        <f>IF(S45="","",IF(S45&gt;=0.9,"On Track",IF(S45&gt;=0.7,"At Risk","Off Track")))</f>
+        <v/>
+      </c>
+      <c r="W45" s="14" t="inlineStr">
+        <is>
+          <t>tbl_SceneLog</t>
+        </is>
+      </c>
+      <c r="X45" s="14" t="n"/>
+      <c r="Y45" s="14" t="n"/>
+      <c r="Z45" s="14" t="n"/>
+      <c r="AA45" s="14" t="n"/>
+      <c r="AB45" s="14" t="n"/>
+      <c r="AC45" s="14" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="T2:T1000">
@@ -11395,8 +13429,8 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A18:H18"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A18:H18"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A11:H11"/>
@@ -14714,8 +16748,8 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A18:H18"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A18:H18"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A11:H11"/>
@@ -14743,7 +16777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L65"/>
+  <dimension ref="A1:M93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -16350,16 +18384,985 @@
         <v/>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="20" t="inlineStr">
+        <is>
+          <t>12-MONTH TREND ANALYSIS (Current Year)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="58" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B68" s="21" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="C68" s="21" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D68" s="21" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="E68" s="21" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="F68" s="21" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="G68" s="21" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="H68" s="21" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="I68" s="21" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="J68" s="21" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="K68" s="21" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="L68" s="21" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="M68" s="21" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="28" t="inlineStr">
+        <is>
+          <t>Cases Registered</t>
+        </is>
+      </c>
+      <c r="B69" s="22">
+        <f>COUNTIFS(tbl_Cases[Month],1,tbl_Cases[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="C69" s="22">
+        <f>COUNTIFS(tbl_Cases[Month],2,tbl_Cases[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="D69" s="22">
+        <f>COUNTIFS(tbl_Cases[Month],3,tbl_Cases[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="E69" s="22">
+        <f>COUNTIFS(tbl_Cases[Month],4,tbl_Cases[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="F69" s="22">
+        <f>COUNTIFS(tbl_Cases[Month],5,tbl_Cases[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="G69" s="22">
+        <f>COUNTIFS(tbl_Cases[Month],6,tbl_Cases[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="H69" s="22">
+        <f>COUNTIFS(tbl_Cases[Month],7,tbl_Cases[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="I69" s="22">
+        <f>COUNTIFS(tbl_Cases[Month],8,tbl_Cases[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="J69" s="22">
+        <f>COUNTIFS(tbl_Cases[Month],9,tbl_Cases[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="K69" s="22">
+        <f>COUNTIFS(tbl_Cases[Month],10,tbl_Cases[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="L69" s="22">
+        <f>COUNTIFS(tbl_Cases[Month],11,tbl_Cases[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="M69" s="22">
+        <f>COUNTIFS(tbl_Cases[Month],12,tbl_Cases[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="28" t="inlineStr">
+        <is>
+          <t>Cases Closed</t>
+        </is>
+      </c>
+      <c r="B70" s="22">
+        <f>COUNTIFS(tbl_Cases[CaseStatus],"Closed*",tbl_Cases[Month],1,tbl_Cases[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="C70" s="22">
+        <f>COUNTIFS(tbl_Cases[CaseStatus],"Closed*",tbl_Cases[Month],2,tbl_Cases[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="D70" s="22">
+        <f>COUNTIFS(tbl_Cases[CaseStatus],"Closed*",tbl_Cases[Month],3,tbl_Cases[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="E70" s="22">
+        <f>COUNTIFS(tbl_Cases[CaseStatus],"Closed*",tbl_Cases[Month],4,tbl_Cases[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="F70" s="22">
+        <f>COUNTIFS(tbl_Cases[CaseStatus],"Closed*",tbl_Cases[Month],5,tbl_Cases[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="G70" s="22">
+        <f>COUNTIFS(tbl_Cases[CaseStatus],"Closed*",tbl_Cases[Month],6,tbl_Cases[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="H70" s="22">
+        <f>COUNTIFS(tbl_Cases[CaseStatus],"Closed*",tbl_Cases[Month],7,tbl_Cases[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="I70" s="22">
+        <f>COUNTIFS(tbl_Cases[CaseStatus],"Closed*",tbl_Cases[Month],8,tbl_Cases[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="J70" s="22">
+        <f>COUNTIFS(tbl_Cases[CaseStatus],"Closed*",tbl_Cases[Month],9,tbl_Cases[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="K70" s="22">
+        <f>COUNTIFS(tbl_Cases[CaseStatus],"Closed*",tbl_Cases[Month],10,tbl_Cases[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="L70" s="22">
+        <f>COUNTIFS(tbl_Cases[CaseStatus],"Closed*",tbl_Cases[Month],11,tbl_Cases[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="M70" s="22">
+        <f>COUNTIFS(tbl_Cases[CaseStatus],"Closed*",tbl_Cases[Month],12,tbl_Cases[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="28" t="inlineStr">
+        <is>
+          <t>Leads Received</t>
+        </is>
+      </c>
+      <c r="B71" s="22">
+        <f>COUNTIFS(tbl_Leads[Month],1,tbl_Leads[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="C71" s="22">
+        <f>COUNTIFS(tbl_Leads[Month],2,tbl_Leads[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="D71" s="22">
+        <f>COUNTIFS(tbl_Leads[Month],3,tbl_Leads[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="E71" s="22">
+        <f>COUNTIFS(tbl_Leads[Month],4,tbl_Leads[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="F71" s="22">
+        <f>COUNTIFS(tbl_Leads[Month],5,tbl_Leads[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="G71" s="22">
+        <f>COUNTIFS(tbl_Leads[Month],6,tbl_Leads[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="H71" s="22">
+        <f>COUNTIFS(tbl_Leads[Month],7,tbl_Leads[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="I71" s="22">
+        <f>COUNTIFS(tbl_Leads[Month],8,tbl_Leads[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="J71" s="22">
+        <f>COUNTIFS(tbl_Leads[Month],9,tbl_Leads[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="K71" s="22">
+        <f>COUNTIFS(tbl_Leads[Month],10,tbl_Leads[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="L71" s="22">
+        <f>COUNTIFS(tbl_Leads[Month],11,tbl_Leads[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="M71" s="22">
+        <f>COUNTIFS(tbl_Leads[Month],12,tbl_Leads[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="28" t="inlineStr">
+        <is>
+          <t>Operations Conducted</t>
+        </is>
+      </c>
+      <c r="B72" s="22">
+        <f>COUNTIFS(tbl_Operations[Month],1,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="C72" s="22">
+        <f>COUNTIFS(tbl_Operations[Month],2,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="D72" s="22">
+        <f>COUNTIFS(tbl_Operations[Month],3,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="E72" s="22">
+        <f>COUNTIFS(tbl_Operations[Month],4,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="F72" s="22">
+        <f>COUNTIFS(tbl_Operations[Month],5,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="G72" s="22">
+        <f>COUNTIFS(tbl_Operations[Month],6,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="H72" s="22">
+        <f>COUNTIFS(tbl_Operations[Month],7,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="I72" s="22">
+        <f>COUNTIFS(tbl_Operations[Month],8,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="J72" s="22">
+        <f>COUNTIFS(tbl_Operations[Month],9,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="K72" s="22">
+        <f>COUNTIFS(tbl_Operations[Month],10,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="L72" s="22">
+        <f>COUNTIFS(tbl_Operations[Month],11,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="M72" s="22">
+        <f>COUNTIFS(tbl_Operations[Month],12,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="28" t="inlineStr">
+        <is>
+          <t>FCSI Operations</t>
+        </is>
+      </c>
+      <c r="B73" s="22">
+        <f>COUNTIFS(tbl_Operations[FCSI_Flag],"Yes",tbl_Operations[Month],1,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="C73" s="22">
+        <f>COUNTIFS(tbl_Operations[FCSI_Flag],"Yes",tbl_Operations[Month],2,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="D73" s="22">
+        <f>COUNTIFS(tbl_Operations[FCSI_Flag],"Yes",tbl_Operations[Month],3,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="E73" s="22">
+        <f>COUNTIFS(tbl_Operations[FCSI_Flag],"Yes",tbl_Operations[Month],4,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="F73" s="22">
+        <f>COUNTIFS(tbl_Operations[FCSI_Flag],"Yes",tbl_Operations[Month],5,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="G73" s="22">
+        <f>COUNTIFS(tbl_Operations[FCSI_Flag],"Yes",tbl_Operations[Month],6,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="H73" s="22">
+        <f>COUNTIFS(tbl_Operations[FCSI_Flag],"Yes",tbl_Operations[Month],7,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="I73" s="22">
+        <f>COUNTIFS(tbl_Operations[FCSI_Flag],"Yes",tbl_Operations[Month],8,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="J73" s="22">
+        <f>COUNTIFS(tbl_Operations[FCSI_Flag],"Yes",tbl_Operations[Month],9,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="K73" s="22">
+        <f>COUNTIFS(tbl_Operations[FCSI_Flag],"Yes",tbl_Operations[Month],10,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="L73" s="22">
+        <f>COUNTIFS(tbl_Operations[FCSI_Flag],"Yes",tbl_Operations[Month],11,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="M73" s="22">
+        <f>COUNTIFS(tbl_Operations[FCSI_Flag],"Yes",tbl_Operations[Month],12,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="28" t="inlineStr">
+        <is>
+          <t>Firearms Seized</t>
+        </is>
+      </c>
+      <c r="B74" s="22">
+        <f>SUMIFS(tbl_Operations[FirearmsSeized],tbl_Operations[Month],1,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="C74" s="22">
+        <f>SUMIFS(tbl_Operations[FirearmsSeized],tbl_Operations[Month],2,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="D74" s="22">
+        <f>SUMIFS(tbl_Operations[FirearmsSeized],tbl_Operations[Month],3,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="E74" s="22">
+        <f>SUMIFS(tbl_Operations[FirearmsSeized],tbl_Operations[Month],4,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="F74" s="22">
+        <f>SUMIFS(tbl_Operations[FirearmsSeized],tbl_Operations[Month],5,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="G74" s="22">
+        <f>SUMIFS(tbl_Operations[FirearmsSeized],tbl_Operations[Month],6,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="H74" s="22">
+        <f>SUMIFS(tbl_Operations[FirearmsSeized],tbl_Operations[Month],7,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="I74" s="22">
+        <f>SUMIFS(tbl_Operations[FirearmsSeized],tbl_Operations[Month],8,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="J74" s="22">
+        <f>SUMIFS(tbl_Operations[FirearmsSeized],tbl_Operations[Month],9,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="K74" s="22">
+        <f>SUMIFS(tbl_Operations[FirearmsSeized],tbl_Operations[Month],10,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="L74" s="22">
+        <f>SUMIFS(tbl_Operations[FirearmsSeized],tbl_Operations[Month],11,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="M74" s="22">
+        <f>SUMIFS(tbl_Operations[FirearmsSeized],tbl_Operations[Month],12,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="28" t="inlineStr">
+        <is>
+          <t>Narcotics Seized (kg)</t>
+        </is>
+      </c>
+      <c r="B75" s="22">
+        <f>SUMIFS(tbl_Operations[NarcoticsSeized_kg],tbl_Operations[Month],1,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="C75" s="22">
+        <f>SUMIFS(tbl_Operations[NarcoticsSeized_kg],tbl_Operations[Month],2,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="D75" s="22">
+        <f>SUMIFS(tbl_Operations[NarcoticsSeized_kg],tbl_Operations[Month],3,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="E75" s="22">
+        <f>SUMIFS(tbl_Operations[NarcoticsSeized_kg],tbl_Operations[Month],4,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="F75" s="22">
+        <f>SUMIFS(tbl_Operations[NarcoticsSeized_kg],tbl_Operations[Month],5,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="G75" s="22">
+        <f>SUMIFS(tbl_Operations[NarcoticsSeized_kg],tbl_Operations[Month],6,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="H75" s="22">
+        <f>SUMIFS(tbl_Operations[NarcoticsSeized_kg],tbl_Operations[Month],7,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="I75" s="22">
+        <f>SUMIFS(tbl_Operations[NarcoticsSeized_kg],tbl_Operations[Month],8,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="J75" s="22">
+        <f>SUMIFS(tbl_Operations[NarcoticsSeized_kg],tbl_Operations[Month],9,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="K75" s="22">
+        <f>SUMIFS(tbl_Operations[NarcoticsSeized_kg],tbl_Operations[Month],10,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="L75" s="22">
+        <f>SUMIFS(tbl_Operations[NarcoticsSeized_kg],tbl_Operations[Month],11,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="M75" s="22">
+        <f>SUMIFS(tbl_Operations[NarcoticsSeized_kg],tbl_Operations[Month],12,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="28" t="inlineStr">
+        <is>
+          <t>Arrests Made</t>
+        </is>
+      </c>
+      <c r="B76" s="22">
+        <f>SUMIFS(tbl_Operations[Arrests],tbl_Operations[Month],1,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="C76" s="22">
+        <f>SUMIFS(tbl_Operations[Arrests],tbl_Operations[Month],2,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="D76" s="22">
+        <f>SUMIFS(tbl_Operations[Arrests],tbl_Operations[Month],3,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="E76" s="22">
+        <f>SUMIFS(tbl_Operations[Arrests],tbl_Operations[Month],4,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="F76" s="22">
+        <f>SUMIFS(tbl_Operations[Arrests],tbl_Operations[Month],5,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="G76" s="22">
+        <f>SUMIFS(tbl_Operations[Arrests],tbl_Operations[Month],6,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="H76" s="22">
+        <f>SUMIFS(tbl_Operations[Arrests],tbl_Operations[Month],7,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="I76" s="22">
+        <f>SUMIFS(tbl_Operations[Arrests],tbl_Operations[Month],8,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="J76" s="22">
+        <f>SUMIFS(tbl_Operations[Arrests],tbl_Operations[Month],9,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="K76" s="22">
+        <f>SUMIFS(tbl_Operations[Arrests],tbl_Operations[Month],10,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="L76" s="22">
+        <f>SUMIFS(tbl_Operations[Arrests],tbl_Operations[Month],11,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="M76" s="22">
+        <f>SUMIFS(tbl_Operations[Arrests],tbl_Operations[Month],12,tbl_Operations[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="28" t="inlineStr">
+        <is>
+          <t>Exhibits Collected</t>
+        </is>
+      </c>
+      <c r="B77" s="22">
+        <f>COUNTIFS(tbl_Exhibits[Month],1,tbl_Exhibits[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="C77" s="22">
+        <f>COUNTIFS(tbl_Exhibits[Month],2,tbl_Exhibits[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="D77" s="22">
+        <f>COUNTIFS(tbl_Exhibits[Month],3,tbl_Exhibits[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="E77" s="22">
+        <f>COUNTIFS(tbl_Exhibits[Month],4,tbl_Exhibits[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="F77" s="22">
+        <f>COUNTIFS(tbl_Exhibits[Month],5,tbl_Exhibits[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="G77" s="22">
+        <f>COUNTIFS(tbl_Exhibits[Month],6,tbl_Exhibits[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="H77" s="22">
+        <f>COUNTIFS(tbl_Exhibits[Month],7,tbl_Exhibits[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="I77" s="22">
+        <f>COUNTIFS(tbl_Exhibits[Month],8,tbl_Exhibits[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="J77" s="22">
+        <f>COUNTIFS(tbl_Exhibits[Month],9,tbl_Exhibits[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="K77" s="22">
+        <f>COUNTIFS(tbl_Exhibits[Month],10,tbl_Exhibits[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="L77" s="22">
+        <f>COUNTIFS(tbl_Exhibits[Month],11,tbl_Exhibits[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="M77" s="22">
+        <f>COUNTIFS(tbl_Exhibits[Month],12,tbl_Exhibits[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="28" t="inlineStr">
+        <is>
+          <t>Lectures Delivered</t>
+        </is>
+      </c>
+      <c r="B78" s="22">
+        <f>COUNTIFS(tbl_DemandReduction[Month],1,tbl_DemandReduction[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="C78" s="22">
+        <f>COUNTIFS(tbl_DemandReduction[Month],2,tbl_DemandReduction[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="D78" s="22">
+        <f>COUNTIFS(tbl_DemandReduction[Month],3,tbl_DemandReduction[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="E78" s="22">
+        <f>COUNTIFS(tbl_DemandReduction[Month],4,tbl_DemandReduction[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="F78" s="22">
+        <f>COUNTIFS(tbl_DemandReduction[Month],5,tbl_DemandReduction[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="G78" s="22">
+        <f>COUNTIFS(tbl_DemandReduction[Month],6,tbl_DemandReduction[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="H78" s="22">
+        <f>COUNTIFS(tbl_DemandReduction[Month],7,tbl_DemandReduction[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="I78" s="22">
+        <f>COUNTIFS(tbl_DemandReduction[Month],8,tbl_DemandReduction[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="J78" s="22">
+        <f>COUNTIFS(tbl_DemandReduction[Month],9,tbl_DemandReduction[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="K78" s="22">
+        <f>COUNTIFS(tbl_DemandReduction[Month],10,tbl_DemandReduction[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="L78" s="22">
+        <f>COUNTIFS(tbl_DemandReduction[Month],11,tbl_DemandReduction[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="M78" s="22">
+        <f>COUNTIFS(tbl_DemandReduction[Month],12,tbl_DemandReduction[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="28" t="inlineStr">
+        <is>
+          <t>Attendance (Demand Red)</t>
+        </is>
+      </c>
+      <c r="B79" s="22">
+        <f>SUMIFS(tbl_DemandReduction[Attendance],tbl_DemandReduction[Month],1,tbl_DemandReduction[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="C79" s="22">
+        <f>SUMIFS(tbl_DemandReduction[Attendance],tbl_DemandReduction[Month],2,tbl_DemandReduction[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="D79" s="22">
+        <f>SUMIFS(tbl_DemandReduction[Attendance],tbl_DemandReduction[Month],3,tbl_DemandReduction[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="E79" s="22">
+        <f>SUMIFS(tbl_DemandReduction[Attendance],tbl_DemandReduction[Month],4,tbl_DemandReduction[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="F79" s="22">
+        <f>SUMIFS(tbl_DemandReduction[Attendance],tbl_DemandReduction[Month],5,tbl_DemandReduction[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="G79" s="22">
+        <f>SUMIFS(tbl_DemandReduction[Attendance],tbl_DemandReduction[Month],6,tbl_DemandReduction[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="H79" s="22">
+        <f>SUMIFS(tbl_DemandReduction[Attendance],tbl_DemandReduction[Month],7,tbl_DemandReduction[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="I79" s="22">
+        <f>SUMIFS(tbl_DemandReduction[Attendance],tbl_DemandReduction[Month],8,tbl_DemandReduction[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="J79" s="22">
+        <f>SUMIFS(tbl_DemandReduction[Attendance],tbl_DemandReduction[Month],9,tbl_DemandReduction[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="K79" s="22">
+        <f>SUMIFS(tbl_DemandReduction[Attendance],tbl_DemandReduction[Month],10,tbl_DemandReduction[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="L79" s="22">
+        <f>SUMIFS(tbl_DemandReduction[Attendance],tbl_DemandReduction[Month],11,tbl_DemandReduction[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="M79" s="22">
+        <f>SUMIFS(tbl_DemandReduction[Attendance],tbl_DemandReduction[Month],12,tbl_DemandReduction[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="28" t="inlineStr">
+        <is>
+          <t>Vehicle Trips</t>
+        </is>
+      </c>
+      <c r="B80" s="22">
+        <f>COUNTIFS(tbl_VehicleUsage[Month],1,tbl_VehicleUsage[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="C80" s="22">
+        <f>COUNTIFS(tbl_VehicleUsage[Month],2,tbl_VehicleUsage[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="D80" s="22">
+        <f>COUNTIFS(tbl_VehicleUsage[Month],3,tbl_VehicleUsage[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="E80" s="22">
+        <f>COUNTIFS(tbl_VehicleUsage[Month],4,tbl_VehicleUsage[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="F80" s="22">
+        <f>COUNTIFS(tbl_VehicleUsage[Month],5,tbl_VehicleUsage[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="G80" s="22">
+        <f>COUNTIFS(tbl_VehicleUsage[Month],6,tbl_VehicleUsage[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="H80" s="22">
+        <f>COUNTIFS(tbl_VehicleUsage[Month],7,tbl_VehicleUsage[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="I80" s="22">
+        <f>COUNTIFS(tbl_VehicleUsage[Month],8,tbl_VehicleUsage[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="J80" s="22">
+        <f>COUNTIFS(tbl_VehicleUsage[Month],9,tbl_VehicleUsage[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="K80" s="22">
+        <f>COUNTIFS(tbl_VehicleUsage[Month],10,tbl_VehicleUsage[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="L80" s="22">
+        <f>COUNTIFS(tbl_VehicleUsage[Month],11,tbl_VehicleUsage[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="M80" s="22">
+        <f>COUNTIFS(tbl_VehicleUsage[Month],12,tbl_VehicleUsage[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="20" t="inlineStr">
+        <is>
+          <t>AGING &amp; SLA ANALYSIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="25" t="inlineStr">
+        <is>
+          <t>Avg Case Age (days)</t>
+        </is>
+      </c>
+      <c r="B83" s="44">
+        <f>IFERROR(AVERAGE(IF(tbl_Cases[CaseStatus]&lt;&gt;"Closed*",TODAY()-tbl_Cases[DateReceived])),"—")</f>
+        <v/>
+      </c>
+      <c r="D83" s="25" t="inlineStr">
+        <is>
+          <t>Oldest Open Case (days)</t>
+        </is>
+      </c>
+      <c r="E83" s="44">
+        <f>IFERROR(MAX(IF(tbl_Cases[CaseStatus]&lt;&gt;"Closed*",TODAY()-tbl_Cases[DateReceived])),"—")</f>
+        <v/>
+      </c>
+      <c r="G83" s="25" t="inlineStr">
+        <is>
+          <t>Avg Lead Age (days)</t>
+        </is>
+      </c>
+      <c r="H83" s="44">
+        <f>IFERROR(AVERAGE(IF(tbl_Leads[Outcome]="Pending",TODAY()-tbl_Leads[DateReceived])),"—")</f>
+        <v/>
+      </c>
+      <c r="J83" s="25" t="inlineStr">
+        <is>
+          <t>Avg Forensic Turnaround</t>
+        </is>
+      </c>
+      <c r="K83" s="44">
+        <f>IFERROR(AVERAGE(tbl_Exhibits[TurnaroundDays]),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="25" t="inlineStr">
+        <is>
+          <t>Overdue Actions (count)</t>
+        </is>
+      </c>
+      <c r="B85" s="44">
+        <f>COUNTIFS(tbl_Actions[DueDate],"&lt;"&amp;TODAY(),tbl_Actions[CompletedDate],"")</f>
+        <v/>
+      </c>
+      <c r="D85" s="25" t="inlineStr">
+        <is>
+          <t>Overdue Forensic Returns</t>
+        </is>
+      </c>
+      <c r="E85" s="44">
+        <f>COUNTIFS(tbl_Exhibits[ExpectedReturn],"&lt;"&amp;TODAY(),tbl_Exhibits[ActualReturnDate],"")</f>
+        <v/>
+      </c>
+      <c r="G85" s="25" t="inlineStr">
+        <is>
+          <t>Cases &gt; 90 days Open</t>
+        </is>
+      </c>
+      <c r="H85" s="44">
+        <f>COUNTIFS(tbl_Cases[DateReceived],"&lt;"&amp;TODAY()-90,tbl_Cases[CaseStatus],"&lt;&gt;Closed*")</f>
+        <v/>
+      </c>
+      <c r="J85" s="25" t="inlineStr">
+        <is>
+          <t>Leads Pending &gt; 7 days</t>
+        </is>
+      </c>
+      <c r="K85" s="44">
+        <f>COUNTIFS(tbl_Leads[DateReceived],"&lt;"&amp;TODAY()-7,tbl_Leads[TriageDecision],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="20" t="inlineStr">
+        <is>
+          <t>COURT &amp; LEGAL STATUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="50" t="inlineStr">
+        <is>
+          <t>Court Dates Total</t>
+        </is>
+      </c>
+      <c r="B88" s="50" t="inlineStr">
+        <is>
+          <t>Upcoming (7d)</t>
+        </is>
+      </c>
+      <c r="C88" s="50" t="inlineStr">
+        <is>
+          <t>Warrants Active</t>
+        </is>
+      </c>
+      <c r="D88" s="50" t="inlineStr">
+        <is>
+          <t>Warrants Expired</t>
+        </is>
+      </c>
+      <c r="E88" s="50" t="inlineStr">
+        <is>
+          <t>Total Arrests</t>
+        </is>
+      </c>
+      <c r="F88" s="50" t="inlineStr">
+        <is>
+          <t>Seizure Items</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="26">
+        <f>COUNTA(tbl_CourtDates[CourtID])-COUNTBLANK(tbl_CourtDates[CourtID])</f>
+        <v/>
+      </c>
+      <c r="B89" s="26">
+        <f>COUNTIFS(tbl_CourtDates[HearingDate],"&gt;="&amp;TODAY(),tbl_CourtDates[HearingDate],"&lt;="&amp;TODAY()+7)</f>
+        <v/>
+      </c>
+      <c r="C89" s="26">
+        <f>COUNTIFS(tbl_Warrants[ValidUntil],"&gt;="&amp;TODAY(),tbl_Warrants[ExecutionDate],"")</f>
+        <v/>
+      </c>
+      <c r="D89" s="26">
+        <f>COUNTIF(tbl_Warrants[Status],"Expired")</f>
+        <v/>
+      </c>
+      <c r="E89" s="26">
+        <f>COUNTA(tbl_Arrests[ArrestID])-COUNTBLANK(tbl_Arrests[ArrestID])</f>
+        <v/>
+      </c>
+      <c r="F89" s="26">
+        <f>COUNTA(tbl_Seizures[SeizureID])-COUNTBLANK(tbl_Seizures[SeizureID])</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="20" t="inlineStr">
+        <is>
+          <t>PERSONNEL, TRAINING &amp; INFORMANTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="59" t="inlineStr">
+        <is>
+          <t>Personnel</t>
+        </is>
+      </c>
+      <c r="B92" s="59" t="inlineStr">
+        <is>
+          <t>Active Staff</t>
+        </is>
+      </c>
+      <c r="C92" s="59" t="inlineStr">
+        <is>
+          <t>Training Sessions</t>
+        </is>
+      </c>
+      <c r="D92" s="59" t="inlineStr">
+        <is>
+          <t>Training Overdue</t>
+        </is>
+      </c>
+      <c r="E92" s="59" t="inlineStr">
+        <is>
+          <t>Active Informants</t>
+        </is>
+      </c>
+      <c r="F92" s="59" t="inlineStr">
+        <is>
+          <t>Scenes Processed</t>
+        </is>
+      </c>
+      <c r="G92" s="59" t="inlineStr">
+        <is>
+          <t>Custody Transfers</t>
+        </is>
+      </c>
+      <c r="H92" s="59" t="inlineStr">
+        <is>
+          <t>Duty Entries</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="26">
+        <f>COUNTA(tbl_Personnel[PersonnelID])-COUNTBLANK(tbl_Personnel[PersonnelID])</f>
+        <v/>
+      </c>
+      <c r="B93" s="26">
+        <f>COUNTIF(tbl_Personnel[Status],"Active")</f>
+        <v/>
+      </c>
+      <c r="C93" s="26">
+        <f>COUNTA(tbl_Training[TrainingID])-COUNTBLANK(tbl_Training[TrainingID])</f>
+        <v/>
+      </c>
+      <c r="D93" s="26">
+        <f>COUNTIFS(tbl_Personnel[NextTrainingDue],"&lt;"&amp;TODAY())</f>
+        <v/>
+      </c>
+      <c r="E93" s="26">
+        <f>COUNTIF(tbl_Informants[Status],"Active")</f>
+        <v/>
+      </c>
+      <c r="F93" s="26">
+        <f>COUNTA(tbl_SceneLog[SceneID])-COUNTBLANK(tbl_SceneLog[SceneID])</f>
+        <v/>
+      </c>
+      <c r="G93" s="26">
+        <f>COUNTA(tbl_CustodyTransfers[TransferID])-COUNTBLANK(tbl_CustodyTransfers[TransferID])</f>
+        <v/>
+      </c>
+      <c r="H93" s="26">
+        <f>COUNTA(tbl_DutyRoster[RosterID])-COUNTBLANK(tbl_DutyRoster[RosterID])</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="14">
     <mergeCell ref="A20:L20"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A16:L16"/>
+    <mergeCell ref="A87:L87"/>
+    <mergeCell ref="A82:L82"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A28:L28"/>
     <mergeCell ref="A32:L32"/>
     <mergeCell ref="A8:L8"/>
+    <mergeCell ref="A67:L67"/>
+    <mergeCell ref="A91:L91"/>
     <mergeCell ref="A12:L12"/>
     <mergeCell ref="A4:L4"/>
   </mergeCells>
@@ -16385,7 +19388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -17074,16 +20077,464 @@
         <v/>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="43" t="inlineStr">
+        <is>
+          <t>COURT &amp; LEGAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>Total Court Dates</t>
+        </is>
+      </c>
+      <c r="B33" s="44">
+        <f>COUNTA(tbl_CourtDates[CourtID])-COUNTBLANK(tbl_CourtDates[CourtID])</f>
+        <v/>
+      </c>
+      <c r="C33" s="25" t="inlineStr">
+        <is>
+          <t>Upcoming (7 days)</t>
+        </is>
+      </c>
+      <c r="D33" s="44">
+        <f>COUNTIFS(tbl_CourtDates[HearingDate],"&gt;="&amp;TODAY(),tbl_CourtDates[HearingDate],"&lt;="&amp;TODAY()+7)</f>
+        <v/>
+      </c>
+      <c r="E33" s="25" t="inlineStr">
+        <is>
+          <t>Adjournments</t>
+        </is>
+      </c>
+      <c r="F33" s="44">
+        <f>COUNTIFS(tbl_CourtDates[AdjournmentReason],"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="G33" s="25" t="inlineStr">
+        <is>
+          <t>Convictions</t>
+        </is>
+      </c>
+      <c r="H33" s="44">
+        <f>COUNTIF(tbl_CourtDates[Verdict],"Guilty")</f>
+        <v/>
+      </c>
+      <c r="I33" s="25" t="inlineStr">
+        <is>
+          <t>Acquittals</t>
+        </is>
+      </c>
+      <c r="J33" s="44">
+        <f>COUNTIF(tbl_CourtDates[Verdict],"Not Guilty")</f>
+        <v/>
+      </c>
+      <c r="K33" s="25" t="inlineStr">
+        <is>
+          <t>Bail Granted</t>
+        </is>
+      </c>
+      <c r="L33" s="44">
+        <f>COUNTIF(tbl_CourtDates[BailStatus],"Granted")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>ARRESTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>Total Arrests</t>
+        </is>
+      </c>
+      <c r="B37" s="44">
+        <f>COUNTA(tbl_Arrests[ArrestID])-COUNTBLANK(tbl_Arrests[ArrestID])</f>
+        <v/>
+      </c>
+      <c r="C37" s="25" t="inlineStr">
+        <is>
+          <t>Arrests This Month</t>
+        </is>
+      </c>
+      <c r="D37" s="44">
+        <f>COUNTIFS(tbl_Arrests[Month],MONTH(TODAY()),tbl_Arrests[Year],YEAR(TODAY()))</f>
+        <v/>
+      </c>
+      <c r="E37" s="25" t="inlineStr">
+        <is>
+          <t>Bail Granted</t>
+        </is>
+      </c>
+      <c r="F37" s="44">
+        <f>COUNTIF(tbl_Arrests[BailGranted],"Yes")</f>
+        <v/>
+      </c>
+      <c r="G37" s="25" t="inlineStr">
+        <is>
+          <t>Remanded</t>
+        </is>
+      </c>
+      <c r="H37" s="44">
+        <f>COUNTIFS(tbl_Arrests[RemandFacility],"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="I37" s="25" t="inlineStr">
+        <is>
+          <t>Cautions Given</t>
+        </is>
+      </c>
+      <c r="J37" s="44">
+        <f>COUNTIF(tbl_Arrests[CautionGiven],"Yes")</f>
+        <v/>
+      </c>
+      <c r="K37" s="25" t="inlineStr">
+        <is>
+          <t>Rights Read</t>
+        </is>
+      </c>
+      <c r="L37" s="44">
+        <f>COUNTIF(tbl_Arrests[RightsRead],"Yes")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>SEIZURES (DETAILED)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="25" t="inlineStr">
+        <is>
+          <t>Total Seized Items</t>
+        </is>
+      </c>
+      <c r="B41" s="44">
+        <f>COUNTA(tbl_Seizures[SeizureID])-COUNTBLANK(tbl_Seizures[SeizureID])</f>
+        <v/>
+      </c>
+      <c r="C41" s="25" t="inlineStr">
+        <is>
+          <t>Firearms Seized</t>
+        </is>
+      </c>
+      <c r="D41" s="44">
+        <f>COUNTIF(tbl_Seizures[ItemType],"Firearm")</f>
+        <v/>
+      </c>
+      <c r="E41" s="25" t="inlineStr">
+        <is>
+          <t>Ammunition Seized</t>
+        </is>
+      </c>
+      <c r="F41" s="44">
+        <f>COUNTIF(tbl_Seizures[ItemType],"Ammunition")</f>
+        <v/>
+      </c>
+      <c r="G41" s="25" t="inlineStr">
+        <is>
+          <t>Narcotics Items</t>
+        </is>
+      </c>
+      <c r="H41" s="44">
+        <f>COUNTIFS(tbl_Seizures[ItemType],"Narcotics*")</f>
+        <v/>
+      </c>
+      <c r="I41" s="25" t="inlineStr">
+        <is>
+          <t>Cash/Currency Items</t>
+        </is>
+      </c>
+      <c r="J41" s="44">
+        <f>COUNTIF(tbl_Seizures[ItemType],"Cash/Currency")</f>
+        <v/>
+      </c>
+      <c r="K41" s="25" t="inlineStr">
+        <is>
+          <t>Linked to Exhibits</t>
+        </is>
+      </c>
+      <c r="L41" s="44">
+        <f>COUNTIFS(tbl_Seizures[LinkedExhibitID],"&lt;&gt;")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>WARRANTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="25" t="inlineStr">
+        <is>
+          <t>Total Warrants</t>
+        </is>
+      </c>
+      <c r="B45" s="44">
+        <f>COUNTA(tbl_Warrants[WarrantID])-COUNTBLANK(tbl_Warrants[WarrantID])</f>
+        <v/>
+      </c>
+      <c r="C45" s="25" t="inlineStr">
+        <is>
+          <t>Issued</t>
+        </is>
+      </c>
+      <c r="D45" s="44">
+        <f>COUNTIF(tbl_Warrants[Status],"Issued")</f>
+        <v/>
+      </c>
+      <c r="E45" s="25" t="inlineStr">
+        <is>
+          <t>Executed</t>
+        </is>
+      </c>
+      <c r="F45" s="44">
+        <f>COUNTIF(tbl_Warrants[Status],"Executed")</f>
+        <v/>
+      </c>
+      <c r="G45" s="25" t="inlineStr">
+        <is>
+          <t>Expired (Unexecuted)</t>
+        </is>
+      </c>
+      <c r="H45" s="44">
+        <f>COUNTIF(tbl_Warrants[Status],"Expired")</f>
+        <v/>
+      </c>
+      <c r="I45" s="25" t="inlineStr">
+        <is>
+          <t>Returned to JP</t>
+        </is>
+      </c>
+      <c r="J45" s="44">
+        <f>COUNTIFS(tbl_Warrants[ReturnToJP_Date],"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="K45" s="25" t="inlineStr">
+        <is>
+          <t>Active (Not Expired)</t>
+        </is>
+      </c>
+      <c r="L45" s="44">
+        <f>COUNTIFS(tbl_Warrants[ValidUntil],"&gt;="&amp;TODAY(),tbl_Warrants[ExecutionDate],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="60" t="inlineStr">
+        <is>
+          <t>PERSONNEL &amp; ROSTER</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="25" t="inlineStr">
+        <is>
+          <t>Total Personnel</t>
+        </is>
+      </c>
+      <c r="B49" s="44">
+        <f>COUNTA(tbl_Personnel[PersonnelID])-COUNTBLANK(tbl_Personnel[PersonnelID])</f>
+        <v/>
+      </c>
+      <c r="C49" s="25" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="D49" s="44">
+        <f>COUNTIF(tbl_Personnel[Status],"Active")</f>
+        <v/>
+      </c>
+      <c r="E49" s="25" t="inlineStr">
+        <is>
+          <t>On Leave</t>
+        </is>
+      </c>
+      <c r="F49" s="44">
+        <f>COUNTIF(tbl_Personnel[Status],"On Leave")</f>
+        <v/>
+      </c>
+      <c r="G49" s="25" t="inlineStr">
+        <is>
+          <t>Training Overdue</t>
+        </is>
+      </c>
+      <c r="H49" s="44">
+        <f>COUNTIFS(tbl_Personnel[NextTrainingDue],"&lt;"&amp;TODAY())</f>
+        <v/>
+      </c>
+      <c r="I49" s="25" t="inlineStr">
+        <is>
+          <t>Duty Entries</t>
+        </is>
+      </c>
+      <c r="J49" s="44">
+        <f>COUNTA(tbl_DutyRoster[RosterID])-COUNTBLANK(tbl_DutyRoster[RosterID])</f>
+        <v/>
+      </c>
+      <c r="K49" s="25" t="inlineStr">
+        <is>
+          <t>Training Sessions</t>
+        </is>
+      </c>
+      <c r="L49" s="44">
+        <f>COUNTA(tbl_Training[TrainingID])-COUNTBLANK(tbl_Training[TrainingID])</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="45" t="inlineStr">
+        <is>
+          <t>INFORMANTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="25" t="inlineStr">
+        <is>
+          <t>Registered Informants</t>
+        </is>
+      </c>
+      <c r="B53" s="44">
+        <f>COUNTA(tbl_Informants[InformantID])-COUNTBLANK(tbl_Informants[InformantID])</f>
+        <v/>
+      </c>
+      <c r="C53" s="25" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="D53" s="44">
+        <f>COUNTIF(tbl_Informants[Status],"Active")</f>
+        <v/>
+      </c>
+      <c r="E53" s="25" t="inlineStr">
+        <is>
+          <t>Total Tips Provided</t>
+        </is>
+      </c>
+      <c r="F53" s="44">
+        <f>SUM(tbl_Informants[TotalTipsProvided])</f>
+        <v/>
+      </c>
+      <c r="G53" s="25" t="inlineStr">
+        <is>
+          <t>Tips→Cases</t>
+        </is>
+      </c>
+      <c r="H53" s="44">
+        <f>SUM(tbl_Informants[TipsConvertedToCase])</f>
+        <v/>
+      </c>
+      <c r="I53" s="25" t="inlineStr">
+        <is>
+          <t>Tips→Ops</t>
+        </is>
+      </c>
+      <c r="J53" s="44">
+        <f>SUM(tbl_Informants[TipsConvertedToOp])</f>
+        <v/>
+      </c>
+      <c r="K53" s="25" t="inlineStr">
+        <is>
+          <t>Contact Overdue</t>
+        </is>
+      </c>
+      <c r="L53" s="44">
+        <f>COUNTIFS(tbl_Informants[NextContactDue],"&lt;"&amp;TODAY())</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>SCENE PROCESSING &amp; CUSTODY</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="25" t="inlineStr">
+        <is>
+          <t>Scenes Processed</t>
+        </is>
+      </c>
+      <c r="B57" s="44">
+        <f>COUNTA(tbl_SceneLog[SceneID])-COUNTBLANK(tbl_SceneLog[SceneID])</f>
+        <v/>
+      </c>
+      <c r="C57" s="25" t="inlineStr">
+        <is>
+          <t>GSR Collected</t>
+        </is>
+      </c>
+      <c r="D57" s="44">
+        <f>COUNTIF(tbl_SceneLog[GSR_Collected],"Yes")</f>
+        <v/>
+      </c>
+      <c r="E57" s="25" t="inlineStr">
+        <is>
+          <t>Shell Casings Found</t>
+        </is>
+      </c>
+      <c r="F57" s="44">
+        <f>SUM(tbl_SceneLog[ShellCasingCount])</f>
+        <v/>
+      </c>
+      <c r="G57" s="25" t="inlineStr">
+        <is>
+          <t>Fingerprints Lifted</t>
+        </is>
+      </c>
+      <c r="H57" s="44">
+        <f>COUNTIF(tbl_SceneLog[FingerprintsLifted],"Yes")</f>
+        <v/>
+      </c>
+      <c r="I57" s="25" t="inlineStr">
+        <is>
+          <t>Custody Transfers</t>
+        </is>
+      </c>
+      <c r="J57" s="44">
+        <f>COUNTA(tbl_CustodyTransfers[TransferID])-COUNTBLANK(tbl_CustodyTransfers[TransferID])</f>
+        <v/>
+      </c>
+      <c r="K57" s="25" t="inlineStr">
+        <is>
+          <t>Weapons Found at Scene</t>
+        </is>
+      </c>
+      <c r="L57" s="44">
+        <f>COUNTIF(tbl_SceneLog[WeaponsFound],"Yes")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="15">
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A29:L29"/>
+    <mergeCell ref="A52:L52"/>
     <mergeCell ref="A19:L19"/>
     <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A32:L32"/>
+    <mergeCell ref="A36:L36"/>
     <mergeCell ref="A14:L14"/>
+    <mergeCell ref="A44:L44"/>
+    <mergeCell ref="A40:L40"/>
     <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A56:L56"/>
     <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A48:L48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19182,6 +22633,10 @@
         </is>
       </c>
       <c r="B4" s="54" t="inlineStr"/>
+      <c r="C4" s="61" t="n"/>
+      <c r="D4" s="61" t="n"/>
+      <c r="E4" s="61" t="n"/>
+      <c r="F4" s="61" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="53" t="inlineStr">
@@ -19190,6 +22645,10 @@
         </is>
       </c>
       <c r="B5" s="54" t="inlineStr"/>
+      <c r="C5" s="61" t="n"/>
+      <c r="D5" s="61" t="n"/>
+      <c r="E5" s="61" t="n"/>
+      <c r="F5" s="61" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="53" t="inlineStr">
@@ -19198,6 +22657,10 @@
         </is>
       </c>
       <c r="B6" s="54" t="inlineStr"/>
+      <c r="C6" s="61" t="n"/>
+      <c r="D6" s="61" t="n"/>
+      <c r="E6" s="61" t="n"/>
+      <c r="F6" s="61" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="53" t="inlineStr">
@@ -19206,6 +22669,10 @@
         </is>
       </c>
       <c r="B7" s="54" t="inlineStr"/>
+      <c r="C7" s="61" t="n"/>
+      <c r="D7" s="61" t="n"/>
+      <c r="E7" s="61" t="n"/>
+      <c r="F7" s="61" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="53" t="inlineStr">
@@ -19218,6 +22685,10 @@
           <t>FNID Area 3</t>
         </is>
       </c>
+      <c r="C8" s="61" t="n"/>
+      <c r="D8" s="61" t="n"/>
+      <c r="E8" s="61" t="n"/>
+      <c r="F8" s="61" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="53" t="inlineStr">
@@ -19226,6 +22697,10 @@
         </is>
       </c>
       <c r="B9" s="54" t="inlineStr"/>
+      <c r="C9" s="61" t="n"/>
+      <c r="D9" s="61" t="n"/>
+      <c r="E9" s="61" t="n"/>
+      <c r="F9" s="61" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="53" t="inlineStr">
@@ -19234,6 +22709,10 @@
         </is>
       </c>
       <c r="B10" s="54" t="inlineStr"/>
+      <c r="C10" s="61" t="n"/>
+      <c r="D10" s="61" t="n"/>
+      <c r="E10" s="61" t="n"/>
+      <c r="F10" s="61" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="53" t="inlineStr">
@@ -19242,6 +22721,10 @@
         </is>
       </c>
       <c r="B11" s="54" t="inlineStr"/>
+      <c r="C11" s="61" t="n"/>
+      <c r="D11" s="61" t="n"/>
+      <c r="E11" s="61" t="n"/>
+      <c r="F11" s="61" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="55" t="inlineStr">
@@ -19257,6 +22740,10 @@
         </is>
       </c>
       <c r="B14" s="54" t="inlineStr"/>
+      <c r="C14" s="61" t="n"/>
+      <c r="D14" s="61" t="n"/>
+      <c r="E14" s="61" t="n"/>
+      <c r="F14" s="61" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="53" t="inlineStr">
@@ -19265,6 +22752,10 @@
         </is>
       </c>
       <c r="B15" s="54" t="inlineStr"/>
+      <c r="C15" s="61" t="n"/>
+      <c r="D15" s="61" t="n"/>
+      <c r="E15" s="61" t="n"/>
+      <c r="F15" s="61" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="53" t="inlineStr">
@@ -19273,6 +22764,10 @@
         </is>
       </c>
       <c r="B16" s="54" t="inlineStr"/>
+      <c r="C16" s="61" t="n"/>
+      <c r="D16" s="61" t="n"/>
+      <c r="E16" s="61" t="n"/>
+      <c r="F16" s="61" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="53" t="inlineStr">
@@ -19281,6 +22776,10 @@
         </is>
       </c>
       <c r="B17" s="54" t="inlineStr"/>
+      <c r="C17" s="61" t="n"/>
+      <c r="D17" s="61" t="n"/>
+      <c r="E17" s="61" t="n"/>
+      <c r="F17" s="61" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="55" t="inlineStr">
@@ -19296,6 +22795,10 @@
         </is>
       </c>
       <c r="B20" s="54" t="inlineStr"/>
+      <c r="C20" s="61" t="n"/>
+      <c r="D20" s="61" t="n"/>
+      <c r="E20" s="61" t="n"/>
+      <c r="F20" s="61" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="53" t="inlineStr">
@@ -19304,6 +22807,10 @@
         </is>
       </c>
       <c r="B21" s="54" t="inlineStr"/>
+      <c r="C21" s="61" t="n"/>
+      <c r="D21" s="61" t="n"/>
+      <c r="E21" s="61" t="n"/>
+      <c r="F21" s="61" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="53" t="inlineStr">
@@ -19312,6 +22819,10 @@
         </is>
       </c>
       <c r="B22" s="54" t="inlineStr"/>
+      <c r="C22" s="61" t="n"/>
+      <c r="D22" s="61" t="n"/>
+      <c r="E22" s="61" t="n"/>
+      <c r="F22" s="61" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="53" t="inlineStr">
@@ -19320,6 +22831,10 @@
         </is>
       </c>
       <c r="B23" s="54" t="inlineStr"/>
+      <c r="C23" s="61" t="n"/>
+      <c r="D23" s="61" t="n"/>
+      <c r="E23" s="61" t="n"/>
+      <c r="F23" s="61" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="53" t="inlineStr">
@@ -19328,6 +22843,10 @@
         </is>
       </c>
       <c r="B24" s="54" t="inlineStr"/>
+      <c r="C24" s="61" t="n"/>
+      <c r="D24" s="61" t="n"/>
+      <c r="E24" s="61" t="n"/>
+      <c r="F24" s="61" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="55" t="inlineStr">
@@ -19350,6 +22869,10 @@
         </is>
       </c>
       <c r="B34" s="54" t="inlineStr"/>
+      <c r="C34" s="61" t="n"/>
+      <c r="D34" s="61" t="n"/>
+      <c r="E34" s="61" t="n"/>
+      <c r="F34" s="61" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="53" t="inlineStr">
@@ -19358,6 +22881,10 @@
         </is>
       </c>
       <c r="B35" s="54" t="inlineStr"/>
+      <c r="C35" s="61" t="n"/>
+      <c r="D35" s="61" t="n"/>
+      <c r="E35" s="61" t="n"/>
+      <c r="F35" s="61" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="53" t="inlineStr">
@@ -19366,6 +22893,10 @@
         </is>
       </c>
       <c r="B36" s="54" t="inlineStr"/>
+      <c r="C36" s="61" t="n"/>
+      <c r="D36" s="61" t="n"/>
+      <c r="E36" s="61" t="n"/>
+      <c r="F36" s="61" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="53" t="inlineStr">
@@ -19374,6 +22905,10 @@
         </is>
       </c>
       <c r="B37" s="54" t="inlineStr"/>
+      <c r="C37" s="61" t="n"/>
+      <c r="D37" s="61" t="n"/>
+      <c r="E37" s="61" t="n"/>
+      <c r="F37" s="61" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="55" t="inlineStr">
@@ -19389,6 +22924,10 @@
         </is>
       </c>
       <c r="B40" s="54" t="inlineStr"/>
+      <c r="C40" s="61" t="n"/>
+      <c r="D40" s="61" t="n"/>
+      <c r="E40" s="61" t="n"/>
+      <c r="F40" s="61" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="53" t="inlineStr">
@@ -19397,6 +22936,10 @@
         </is>
       </c>
       <c r="B41" s="54" t="inlineStr"/>
+      <c r="C41" s="61" t="n"/>
+      <c r="D41" s="61" t="n"/>
+      <c r="E41" s="61" t="n"/>
+      <c r="F41" s="61" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="53" t="inlineStr">
@@ -19405,6 +22948,10 @@
         </is>
       </c>
       <c r="B43" s="54" t="inlineStr"/>
+      <c r="C43" s="61" t="n"/>
+      <c r="D43" s="61" t="n"/>
+      <c r="E43" s="61" t="n"/>
+      <c r="F43" s="61" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="53" t="inlineStr">
@@ -19413,6 +22960,10 @@
         </is>
       </c>
       <c r="B44" s="54" t="inlineStr"/>
+      <c r="C44" s="61" t="n"/>
+      <c r="D44" s="61" t="n"/>
+      <c r="E44" s="61" t="n"/>
+      <c r="F44" s="61" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="53" t="inlineStr">
@@ -19421,6 +22972,10 @@
         </is>
       </c>
       <c r="B45" s="54" t="inlineStr"/>
+      <c r="C45" s="61" t="n"/>
+      <c r="D45" s="61" t="n"/>
+      <c r="E45" s="61" t="n"/>
+      <c r="F45" s="61" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="33">
@@ -19502,6 +23057,10 @@
         </is>
       </c>
       <c r="B4" s="56" t="n"/>
+      <c r="C4" s="61" t="n"/>
+      <c r="D4" s="61" t="n"/>
+      <c r="E4" s="61" t="n"/>
+      <c r="F4" s="61" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="53" t="inlineStr">
@@ -19510,6 +23069,10 @@
         </is>
       </c>
       <c r="B5" s="56" t="n"/>
+      <c r="C5" s="61" t="n"/>
+      <c r="D5" s="61" t="n"/>
+      <c r="E5" s="61" t="n"/>
+      <c r="F5" s="61" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="53" t="inlineStr">
@@ -19518,6 +23081,10 @@
         </is>
       </c>
       <c r="B6" s="56" t="n"/>
+      <c r="C6" s="61" t="n"/>
+      <c r="D6" s="61" t="n"/>
+      <c r="E6" s="61" t="n"/>
+      <c r="F6" s="61" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="53" t="inlineStr">
@@ -19526,6 +23093,10 @@
         </is>
       </c>
       <c r="B7" s="56" t="n"/>
+      <c r="C7" s="61" t="n"/>
+      <c r="D7" s="61" t="n"/>
+      <c r="E7" s="61" t="n"/>
+      <c r="F7" s="61" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="53" t="inlineStr">
@@ -19534,6 +23105,10 @@
         </is>
       </c>
       <c r="B8" s="56" t="n"/>
+      <c r="C8" s="61" t="n"/>
+      <c r="D8" s="61" t="n"/>
+      <c r="E8" s="61" t="n"/>
+      <c r="F8" s="61" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="53" t="inlineStr">
@@ -19542,6 +23117,10 @@
         </is>
       </c>
       <c r="B9" s="56" t="n"/>
+      <c r="C9" s="61" t="n"/>
+      <c r="D9" s="61" t="n"/>
+      <c r="E9" s="61" t="n"/>
+      <c r="F9" s="61" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="55" t="inlineStr">
@@ -19557,6 +23136,10 @@
         </is>
       </c>
       <c r="B12" s="56" t="n"/>
+      <c r="C12" s="61" t="n"/>
+      <c r="D12" s="61" t="n"/>
+      <c r="E12" s="61" t="n"/>
+      <c r="F12" s="61" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="53" t="inlineStr">
@@ -19565,6 +23148,10 @@
         </is>
       </c>
       <c r="B15" s="56" t="n"/>
+      <c r="C15" s="61" t="n"/>
+      <c r="D15" s="61" t="n"/>
+      <c r="E15" s="61" t="n"/>
+      <c r="F15" s="61" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="53" t="inlineStr">
@@ -19573,6 +23160,10 @@
         </is>
       </c>
       <c r="B17" s="56" t="n"/>
+      <c r="C17" s="61" t="n"/>
+      <c r="D17" s="61" t="n"/>
+      <c r="E17" s="61" t="n"/>
+      <c r="F17" s="61" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="53" t="inlineStr">
@@ -19581,6 +23172,10 @@
         </is>
       </c>
       <c r="B19" s="56" t="n"/>
+      <c r="C19" s="61" t="n"/>
+      <c r="D19" s="61" t="n"/>
+      <c r="E19" s="61" t="n"/>
+      <c r="F19" s="61" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="55" t="inlineStr">
@@ -19596,6 +23191,10 @@
         </is>
       </c>
       <c r="B22" s="56" t="n"/>
+      <c r="C22" s="61" t="n"/>
+      <c r="D22" s="61" t="n"/>
+      <c r="E22" s="61" t="n"/>
+      <c r="F22" s="61" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="53" t="inlineStr">
@@ -19604,6 +23203,10 @@
         </is>
       </c>
       <c r="B23" s="56" t="n"/>
+      <c r="C23" s="61" t="n"/>
+      <c r="D23" s="61" t="n"/>
+      <c r="E23" s="61" t="n"/>
+      <c r="F23" s="61" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="53" t="inlineStr">
@@ -19612,6 +23215,10 @@
         </is>
       </c>
       <c r="B24" s="56" t="n"/>
+      <c r="C24" s="61" t="n"/>
+      <c r="D24" s="61" t="n"/>
+      <c r="E24" s="61" t="n"/>
+      <c r="F24" s="61" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="55" t="inlineStr">
@@ -19634,6 +23241,10 @@
         </is>
       </c>
       <c r="B31" s="56" t="n"/>
+      <c r="C31" s="61" t="n"/>
+      <c r="D31" s="61" t="n"/>
+      <c r="E31" s="61" t="n"/>
+      <c r="F31" s="61" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="53" t="inlineStr">
@@ -19642,6 +23253,10 @@
         </is>
       </c>
       <c r="B32" s="56" t="n"/>
+      <c r="C32" s="61" t="n"/>
+      <c r="D32" s="61" t="n"/>
+      <c r="E32" s="61" t="n"/>
+      <c r="F32" s="61" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="53" t="inlineStr">
@@ -19650,6 +23265,10 @@
         </is>
       </c>
       <c r="B33" s="56" t="n"/>
+      <c r="C33" s="61" t="n"/>
+      <c r="D33" s="61" t="n"/>
+      <c r="E33" s="61" t="n"/>
+      <c r="F33" s="61" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="55" t="inlineStr">
@@ -19665,6 +23284,10 @@
         </is>
       </c>
       <c r="B37" s="56" t="n"/>
+      <c r="C37" s="61" t="n"/>
+      <c r="D37" s="61" t="n"/>
+      <c r="E37" s="61" t="n"/>
+      <c r="F37" s="61" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="53" t="inlineStr">
@@ -19673,6 +23296,10 @@
         </is>
       </c>
       <c r="B38" s="56" t="n"/>
+      <c r="C38" s="61" t="n"/>
+      <c r="D38" s="61" t="n"/>
+      <c r="E38" s="61" t="n"/>
+      <c r="F38" s="61" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="53" t="inlineStr">
@@ -19681,6 +23308,10 @@
         </is>
       </c>
       <c r="B39" s="56" t="n"/>
+      <c r="C39" s="61" t="n"/>
+      <c r="D39" s="61" t="n"/>
+      <c r="E39" s="61" t="n"/>
+      <c r="F39" s="61" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="26">
@@ -19754,6 +23385,10 @@
         </is>
       </c>
       <c r="B4" s="56" t="n"/>
+      <c r="C4" s="61" t="n"/>
+      <c r="D4" s="61" t="n"/>
+      <c r="E4" s="61" t="n"/>
+      <c r="F4" s="61" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="53" t="inlineStr">
@@ -19762,6 +23397,10 @@
         </is>
       </c>
       <c r="B5" s="56" t="n"/>
+      <c r="C5" s="61" t="n"/>
+      <c r="D5" s="61" t="n"/>
+      <c r="E5" s="61" t="n"/>
+      <c r="F5" s="61" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="53" t="inlineStr">
@@ -19770,6 +23409,10 @@
         </is>
       </c>
       <c r="B6" s="56" t="n"/>
+      <c r="C6" s="61" t="n"/>
+      <c r="D6" s="61" t="n"/>
+      <c r="E6" s="61" t="n"/>
+      <c r="F6" s="61" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="53" t="inlineStr">
@@ -19778,6 +23421,10 @@
         </is>
       </c>
       <c r="B7" s="56" t="n"/>
+      <c r="C7" s="61" t="n"/>
+      <c r="D7" s="61" t="n"/>
+      <c r="E7" s="61" t="n"/>
+      <c r="F7" s="61" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="53" t="inlineStr">
@@ -19786,6 +23433,10 @@
         </is>
       </c>
       <c r="B8" s="56" t="n"/>
+      <c r="C8" s="61" t="n"/>
+      <c r="D8" s="61" t="n"/>
+      <c r="E8" s="61" t="n"/>
+      <c r="F8" s="61" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="53" t="inlineStr">
@@ -19794,6 +23445,10 @@
         </is>
       </c>
       <c r="B9" s="56" t="n"/>
+      <c r="C9" s="61" t="n"/>
+      <c r="D9" s="61" t="n"/>
+      <c r="E9" s="61" t="n"/>
+      <c r="F9" s="61" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="53" t="inlineStr">
@@ -19802,6 +23457,10 @@
         </is>
       </c>
       <c r="B10" s="56" t="n"/>
+      <c r="C10" s="61" t="n"/>
+      <c r="D10" s="61" t="n"/>
+      <c r="E10" s="61" t="n"/>
+      <c r="F10" s="61" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="55" t="inlineStr">
@@ -19817,6 +23476,10 @@
         </is>
       </c>
       <c r="B13" s="56" t="n"/>
+      <c r="C13" s="61" t="n"/>
+      <c r="D13" s="61" t="n"/>
+      <c r="E13" s="61" t="n"/>
+      <c r="F13" s="61" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="53" t="inlineStr">
@@ -19825,6 +23488,10 @@
         </is>
       </c>
       <c r="B14" s="56" t="n"/>
+      <c r="C14" s="61" t="n"/>
+      <c r="D14" s="61" t="n"/>
+      <c r="E14" s="61" t="n"/>
+      <c r="F14" s="61" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="53" t="inlineStr">
@@ -19833,6 +23500,10 @@
         </is>
       </c>
       <c r="B15" s="56" t="n"/>
+      <c r="C15" s="61" t="n"/>
+      <c r="D15" s="61" t="n"/>
+      <c r="E15" s="61" t="n"/>
+      <c r="F15" s="61" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="53" t="inlineStr">
@@ -19841,6 +23512,10 @@
         </is>
       </c>
       <c r="B16" s="56" t="n"/>
+      <c r="C16" s="61" t="n"/>
+      <c r="D16" s="61" t="n"/>
+      <c r="E16" s="61" t="n"/>
+      <c r="F16" s="61" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="53" t="inlineStr">
@@ -19849,6 +23524,10 @@
         </is>
       </c>
       <c r="B17" s="56" t="n"/>
+      <c r="C17" s="61" t="n"/>
+      <c r="D17" s="61" t="n"/>
+      <c r="E17" s="61" t="n"/>
+      <c r="F17" s="61" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="55" t="inlineStr">
@@ -19864,6 +23543,10 @@
         </is>
       </c>
       <c r="B20" s="56" t="n"/>
+      <c r="C20" s="61" t="n"/>
+      <c r="D20" s="61" t="n"/>
+      <c r="E20" s="61" t="n"/>
+      <c r="F20" s="61" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="53" t="inlineStr">
@@ -19872,6 +23555,10 @@
         </is>
       </c>
       <c r="B21" s="56" t="n"/>
+      <c r="C21" s="61" t="n"/>
+      <c r="D21" s="61" t="n"/>
+      <c r="E21" s="61" t="n"/>
+      <c r="F21" s="61" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="53" t="inlineStr">
@@ -19880,6 +23567,10 @@
         </is>
       </c>
       <c r="B22" s="56" t="n"/>
+      <c r="C22" s="61" t="n"/>
+      <c r="D22" s="61" t="n"/>
+      <c r="E22" s="61" t="n"/>
+      <c r="F22" s="61" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="55" t="inlineStr">
@@ -19902,6 +23593,10 @@
         </is>
       </c>
       <c r="B29" s="56" t="n"/>
+      <c r="C29" s="61" t="n"/>
+      <c r="D29" s="61" t="n"/>
+      <c r="E29" s="61" t="n"/>
+      <c r="F29" s="61" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="53" t="inlineStr">
@@ -19910,6 +23605,10 @@
         </is>
       </c>
       <c r="B30" s="56" t="n"/>
+      <c r="C30" s="61" t="n"/>
+      <c r="D30" s="61" t="n"/>
+      <c r="E30" s="61" t="n"/>
+      <c r="F30" s="61" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="53" t="inlineStr">
@@ -19918,6 +23617,10 @@
         </is>
       </c>
       <c r="B31" s="56" t="n"/>
+      <c r="C31" s="61" t="n"/>
+      <c r="D31" s="61" t="n"/>
+      <c r="E31" s="61" t="n"/>
+      <c r="F31" s="61" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="53" t="inlineStr">
@@ -19926,6 +23629,10 @@
         </is>
       </c>
       <c r="B32" s="56" t="n"/>
+      <c r="C32" s="61" t="n"/>
+      <c r="D32" s="61" t="n"/>
+      <c r="E32" s="61" t="n"/>
+      <c r="F32" s="61" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="25">
@@ -19991,6 +23698,10 @@
         </is>
       </c>
       <c r="B3" s="56" t="n"/>
+      <c r="C3" s="61" t="n"/>
+      <c r="D3" s="61" t="n"/>
+      <c r="E3" s="61" t="n"/>
+      <c r="F3" s="61" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="53" t="inlineStr">
@@ -19999,6 +23710,10 @@
         </is>
       </c>
       <c r="B4" s="56" t="n"/>
+      <c r="C4" s="61" t="n"/>
+      <c r="D4" s="61" t="n"/>
+      <c r="E4" s="61" t="n"/>
+      <c r="F4" s="61" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="53" t="inlineStr">
@@ -20007,6 +23722,10 @@
         </is>
       </c>
       <c r="B5" s="56" t="n"/>
+      <c r="C5" s="61" t="n"/>
+      <c r="D5" s="61" t="n"/>
+      <c r="E5" s="61" t="n"/>
+      <c r="F5" s="61" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="53" t="inlineStr">
@@ -20015,6 +23734,10 @@
         </is>
       </c>
       <c r="B6" s="56" t="n"/>
+      <c r="C6" s="61" t="n"/>
+      <c r="D6" s="61" t="n"/>
+      <c r="E6" s="61" t="n"/>
+      <c r="F6" s="61" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="53" t="inlineStr">
@@ -20023,6 +23746,10 @@
         </is>
       </c>
       <c r="B7" s="56" t="n"/>
+      <c r="C7" s="61" t="n"/>
+      <c r="D7" s="61" t="n"/>
+      <c r="E7" s="61" t="n"/>
+      <c r="F7" s="61" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="53" t="inlineStr">
@@ -20031,6 +23758,10 @@
         </is>
       </c>
       <c r="B8" s="56" t="n"/>
+      <c r="C8" s="61" t="n"/>
+      <c r="D8" s="61" t="n"/>
+      <c r="E8" s="61" t="n"/>
+      <c r="F8" s="61" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="53" t="inlineStr">
@@ -20039,6 +23770,10 @@
         </is>
       </c>
       <c r="B9" s="56" t="n"/>
+      <c r="C9" s="61" t="n"/>
+      <c r="D9" s="61" t="n"/>
+      <c r="E9" s="61" t="n"/>
+      <c r="F9" s="61" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="53" t="inlineStr">
@@ -20047,6 +23782,10 @@
         </is>
       </c>
       <c r="B10" s="56" t="n"/>
+      <c r="C10" s="61" t="n"/>
+      <c r="D10" s="61" t="n"/>
+      <c r="E10" s="61" t="n"/>
+      <c r="F10" s="61" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="53" t="inlineStr">
@@ -20055,6 +23794,10 @@
         </is>
       </c>
       <c r="B11" s="56" t="n"/>
+      <c r="C11" s="61" t="n"/>
+      <c r="D11" s="61" t="n"/>
+      <c r="E11" s="61" t="n"/>
+      <c r="F11" s="61" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="53" t="inlineStr">
@@ -20063,6 +23806,10 @@
         </is>
       </c>
       <c r="B12" s="56" t="n"/>
+      <c r="C12" s="61" t="n"/>
+      <c r="D12" s="61" t="n"/>
+      <c r="E12" s="61" t="n"/>
+      <c r="F12" s="61" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="55" t="inlineStr">
@@ -20106,6 +23853,10 @@
         </is>
       </c>
       <c r="B29" s="56" t="n"/>
+      <c r="C29" s="61" t="n"/>
+      <c r="D29" s="61" t="n"/>
+      <c r="E29" s="61" t="n"/>
+      <c r="F29" s="61" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="53" t="inlineStr">
@@ -20114,6 +23865,10 @@
         </is>
       </c>
       <c r="B30" s="56" t="n"/>
+      <c r="C30" s="61" t="n"/>
+      <c r="D30" s="61" t="n"/>
+      <c r="E30" s="61" t="n"/>
+      <c r="F30" s="61" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -20140,6 +23895,333 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>PersonnelID</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>FullName</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>BadgeNo</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>Station</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>DateOfEnlistment</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>DatePostedToFNID</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>CurrentRole</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>Specialization</t>
+        </is>
+      </c>
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="L1" s="13" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="M1" s="13" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="N1" s="13" t="inlineStr">
+        <is>
+          <t>EmergencyContact</t>
+        </is>
+      </c>
+      <c r="O1" s="13" t="inlineStr">
+        <is>
+          <t>QualificationsHeld</t>
+        </is>
+      </c>
+      <c r="P1" s="13" t="inlineStr">
+        <is>
+          <t>LastTrainingDate</t>
+        </is>
+      </c>
+      <c r="Q1" s="13" t="inlineStr">
+        <is>
+          <t>NextTrainingDue</t>
+        </is>
+      </c>
+      <c r="R1" s="13" t="inlineStr">
+        <is>
+          <t>PerformanceRating</t>
+        </is>
+      </c>
+      <c r="S1" s="13" t="inlineStr">
+        <is>
+          <t>DisciplinaryFlag</t>
+        </is>
+      </c>
+      <c r="T1" s="13" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="U1" s="13" t="inlineStr">
+        <is>
+          <t>CreatedBy</t>
+        </is>
+      </c>
+      <c r="V1" s="13" t="inlineStr">
+        <is>
+          <t>CreatedDate</t>
+        </is>
+      </c>
+      <c r="W1" s="13" t="inlineStr">
+        <is>
+          <t>LastUpdatedBy</t>
+        </is>
+      </c>
+      <c r="X1" s="13" t="inlineStr">
+        <is>
+          <t>LastUpdatedDate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14">
+        <f>IF(B2="","","STAFF-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B2" s="14" t="n"/>
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="14" t="n"/>
+      <c r="G2" s="14" t="n"/>
+      <c r="H2" s="14" t="n"/>
+      <c r="I2" s="14" t="n"/>
+      <c r="J2" s="14" t="n"/>
+      <c r="K2" s="14" t="n"/>
+      <c r="L2" s="14" t="n"/>
+      <c r="M2" s="14" t="n"/>
+      <c r="N2" s="14" t="n"/>
+      <c r="O2" s="14" t="n"/>
+      <c r="P2" s="14" t="n"/>
+      <c r="Q2" s="14" t="n"/>
+      <c r="R2" s="14" t="n"/>
+      <c r="S2" s="14" t="n"/>
+      <c r="T2" s="14" t="n"/>
+      <c r="U2" s="14" t="n"/>
+      <c r="V2" s="14" t="n"/>
+      <c r="W2" s="14" t="n"/>
+      <c r="X2" s="14" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="14">
+        <f>IF(B3="","","STAFF-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="14" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="14" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="14" t="n"/>
+      <c r="L3" s="14" t="n"/>
+      <c r="M3" s="14" t="n"/>
+      <c r="N3" s="14" t="n"/>
+      <c r="O3" s="14" t="n"/>
+      <c r="P3" s="14" t="n"/>
+      <c r="Q3" s="14" t="n"/>
+      <c r="R3" s="14" t="n"/>
+      <c r="S3" s="14" t="n"/>
+      <c r="T3" s="14" t="n"/>
+      <c r="U3" s="14" t="n"/>
+      <c r="V3" s="14" t="n"/>
+      <c r="W3" s="14" t="n"/>
+      <c r="X3" s="14" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="14">
+        <f>IF(B4="","","STAFF-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="14" t="n"/>
+      <c r="H4" s="14" t="n"/>
+      <c r="I4" s="14" t="n"/>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="14" t="n"/>
+      <c r="L4" s="14" t="n"/>
+      <c r="M4" s="14" t="n"/>
+      <c r="N4" s="14" t="n"/>
+      <c r="O4" s="14" t="n"/>
+      <c r="P4" s="14" t="n"/>
+      <c r="Q4" s="14" t="n"/>
+      <c r="R4" s="14" t="n"/>
+      <c r="S4" s="14" t="n"/>
+      <c r="T4" s="14" t="n"/>
+      <c r="U4" s="14" t="n"/>
+      <c r="V4" s="14" t="n"/>
+      <c r="W4" s="14" t="n"/>
+      <c r="X4" s="14" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="14">
+        <f>IF(B5="","","STAFF-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B5" s="14" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="n"/>
+      <c r="E5" s="14" t="n"/>
+      <c r="F5" s="14" t="n"/>
+      <c r="G5" s="14" t="n"/>
+      <c r="H5" s="14" t="n"/>
+      <c r="I5" s="14" t="n"/>
+      <c r="J5" s="14" t="n"/>
+      <c r="K5" s="14" t="n"/>
+      <c r="L5" s="14" t="n"/>
+      <c r="M5" s="14" t="n"/>
+      <c r="N5" s="14" t="n"/>
+      <c r="O5" s="14" t="n"/>
+      <c r="P5" s="14" t="n"/>
+      <c r="Q5" s="14" t="n"/>
+      <c r="R5" s="14" t="n"/>
+      <c r="S5" s="14" t="n"/>
+      <c r="T5" s="14" t="n"/>
+      <c r="U5" s="14" t="n"/>
+      <c r="V5" s="14" t="n"/>
+      <c r="W5" s="14" t="n"/>
+      <c r="X5" s="14" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14">
+        <f>IF(B6="","","STAFF-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B6" s="14" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14" t="n"/>
+      <c r="E6" s="14" t="n"/>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="14" t="n"/>
+      <c r="H6" s="14" t="n"/>
+      <c r="I6" s="14" t="n"/>
+      <c r="J6" s="14" t="n"/>
+      <c r="K6" s="14" t="n"/>
+      <c r="L6" s="14" t="n"/>
+      <c r="M6" s="14" t="n"/>
+      <c r="N6" s="14" t="n"/>
+      <c r="O6" s="14" t="n"/>
+      <c r="P6" s="14" t="n"/>
+      <c r="Q6" s="14" t="n"/>
+      <c r="R6" s="14" t="n"/>
+      <c r="S6" s="14" t="n"/>
+      <c r="T6" s="14" t="n"/>
+      <c r="U6" s="14" t="n"/>
+      <c r="V6" s="14" t="n"/>
+      <c r="W6" s="14" t="n"/>
+      <c r="X6" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="Q2:Q1000">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>=AND(Q2&lt;&gt;"",Q2&lt;TODAY())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$Q$2:$Q$11</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$E$2:$E$11</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$AC$2:$AC$8</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -20482,6 +24564,3551 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00548235"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="8" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>TrainingID</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>CourseTitle</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>TrainingType</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>Duration_Hrs</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>Attendees</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>AttendeeNames</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>CertificateIssued</t>
+        </is>
+      </c>
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>ExpiryDate</t>
+        </is>
+      </c>
+      <c r="L1" s="13" t="inlineStr">
+        <is>
+          <t>LinkedUnit</t>
+        </is>
+      </c>
+      <c r="M1" s="13" t="inlineStr">
+        <is>
+          <t>CostJMD</t>
+        </is>
+      </c>
+      <c r="N1" s="13" t="inlineStr">
+        <is>
+          <t>FundingSource</t>
+        </is>
+      </c>
+      <c r="O1" s="13" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="P1" s="13" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="Q1" s="13" t="inlineStr">
+        <is>
+          <t>CreatedBy</t>
+        </is>
+      </c>
+      <c r="R1" s="13" t="inlineStr">
+        <is>
+          <t>CreatedDate</t>
+        </is>
+      </c>
+      <c r="S1" s="13" t="inlineStr">
+        <is>
+          <t>LastUpdatedBy</t>
+        </is>
+      </c>
+      <c r="T1" s="13" t="inlineStr">
+        <is>
+          <t>LastUpdatedDate</t>
+        </is>
+      </c>
+      <c r="U1" s="13" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="V1" s="13" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="W1" s="13" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="X1" s="13" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14">
+        <f>IF(B2="","","TRN-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B2" s="14" t="n"/>
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="14" t="n"/>
+      <c r="G2" s="14" t="n"/>
+      <c r="H2" s="14" t="n"/>
+      <c r="I2" s="14" t="n"/>
+      <c r="J2" s="14" t="n"/>
+      <c r="K2" s="14" t="n"/>
+      <c r="L2" s="14" t="n"/>
+      <c r="M2" s="14" t="n"/>
+      <c r="N2" s="14" t="n"/>
+      <c r="O2" s="14" t="n"/>
+      <c r="P2" s="14" t="n"/>
+      <c r="Q2" s="14" t="n"/>
+      <c r="R2" s="14" t="n"/>
+      <c r="S2" s="14" t="n"/>
+      <c r="T2" s="14" t="n"/>
+      <c r="U2" s="14">
+        <f>IF(B2="","",WEEKNUM(B2))</f>
+        <v/>
+      </c>
+      <c r="V2" s="14">
+        <f>IF(B2="","",MONTH(B2))</f>
+        <v/>
+      </c>
+      <c r="W2" s="14">
+        <f>IF(B2="","",ROUNDUP(MONTH(B2)/3,0))</f>
+        <v/>
+      </c>
+      <c r="X2" s="14">
+        <f>IF(B2="","",YEAR(B2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14">
+        <f>IF(B3="","","TRN-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="14" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="14" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="14" t="n"/>
+      <c r="L3" s="14" t="n"/>
+      <c r="M3" s="14" t="n"/>
+      <c r="N3" s="14" t="n"/>
+      <c r="O3" s="14" t="n"/>
+      <c r="P3" s="14" t="n"/>
+      <c r="Q3" s="14" t="n"/>
+      <c r="R3" s="14" t="n"/>
+      <c r="S3" s="14" t="n"/>
+      <c r="T3" s="14" t="n"/>
+      <c r="U3" s="14">
+        <f>IF(B3="","",WEEKNUM(B3))</f>
+        <v/>
+      </c>
+      <c r="V3" s="14">
+        <f>IF(B3="","",MONTH(B3))</f>
+        <v/>
+      </c>
+      <c r="W3" s="14">
+        <f>IF(B3="","",ROUNDUP(MONTH(B3)/3,0))</f>
+        <v/>
+      </c>
+      <c r="X3" s="14">
+        <f>IF(B3="","",YEAR(B3))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14">
+        <f>IF(B4="","","TRN-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="14" t="n"/>
+      <c r="H4" s="14" t="n"/>
+      <c r="I4" s="14" t="n"/>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="14" t="n"/>
+      <c r="L4" s="14" t="n"/>
+      <c r="M4" s="14" t="n"/>
+      <c r="N4" s="14" t="n"/>
+      <c r="O4" s="14" t="n"/>
+      <c r="P4" s="14" t="n"/>
+      <c r="Q4" s="14" t="n"/>
+      <c r="R4" s="14" t="n"/>
+      <c r="S4" s="14" t="n"/>
+      <c r="T4" s="14" t="n"/>
+      <c r="U4" s="14">
+        <f>IF(B4="","",WEEKNUM(B4))</f>
+        <v/>
+      </c>
+      <c r="V4" s="14">
+        <f>IF(B4="","",MONTH(B4))</f>
+        <v/>
+      </c>
+      <c r="W4" s="14">
+        <f>IF(B4="","",ROUNDUP(MONTH(B4)/3,0))</f>
+        <v/>
+      </c>
+      <c r="X4" s="14">
+        <f>IF(B4="","",YEAR(B4))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14">
+        <f>IF(B5="","","TRN-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B5" s="14" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="n"/>
+      <c r="E5" s="14" t="n"/>
+      <c r="F5" s="14" t="n"/>
+      <c r="G5" s="14" t="n"/>
+      <c r="H5" s="14" t="n"/>
+      <c r="I5" s="14" t="n"/>
+      <c r="J5" s="14" t="n"/>
+      <c r="K5" s="14" t="n"/>
+      <c r="L5" s="14" t="n"/>
+      <c r="M5" s="14" t="n"/>
+      <c r="N5" s="14" t="n"/>
+      <c r="O5" s="14" t="n"/>
+      <c r="P5" s="14" t="n"/>
+      <c r="Q5" s="14" t="n"/>
+      <c r="R5" s="14" t="n"/>
+      <c r="S5" s="14" t="n"/>
+      <c r="T5" s="14" t="n"/>
+      <c r="U5" s="14">
+        <f>IF(B5="","",WEEKNUM(B5))</f>
+        <v/>
+      </c>
+      <c r="V5" s="14">
+        <f>IF(B5="","",MONTH(B5))</f>
+        <v/>
+      </c>
+      <c r="W5" s="14">
+        <f>IF(B5="","",ROUNDUP(MONTH(B5)/3,0))</f>
+        <v/>
+      </c>
+      <c r="X5" s="14">
+        <f>IF(B5="","",YEAR(B5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14">
+        <f>IF(B6="","","TRN-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B6" s="14" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14" t="n"/>
+      <c r="E6" s="14" t="n"/>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="14" t="n"/>
+      <c r="H6" s="14" t="n"/>
+      <c r="I6" s="14" t="n"/>
+      <c r="J6" s="14" t="n"/>
+      <c r="K6" s="14" t="n"/>
+      <c r="L6" s="14" t="n"/>
+      <c r="M6" s="14" t="n"/>
+      <c r="N6" s="14" t="n"/>
+      <c r="O6" s="14" t="n"/>
+      <c r="P6" s="14" t="n"/>
+      <c r="Q6" s="14" t="n"/>
+      <c r="R6" s="14" t="n"/>
+      <c r="S6" s="14" t="n"/>
+      <c r="T6" s="14" t="n"/>
+      <c r="U6" s="14">
+        <f>IF(B6="","",WEEKNUM(B6))</f>
+        <v/>
+      </c>
+      <c r="V6" s="14">
+        <f>IF(B6="","",MONTH(B6))</f>
+        <v/>
+      </c>
+      <c r="W6" s="14">
+        <f>IF(B6="","",ROUNDUP(MONTH(B6)/3,0))</f>
+        <v/>
+      </c>
+      <c r="X6" s="14">
+        <f>IF(B6="","",YEAR(B6))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$E$2:$E$11</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$I$2:$I$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F3864"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AG6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="24" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col width="8" customWidth="1" min="33" max="33"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>CourtID</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>LinkedCaseID</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>CourtName</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>CourtType</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>HearingDate</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>HearingTime</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>HearingType</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>JudgeMagistrate</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>Prosecutor</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>DefenseAttorney</t>
+        </is>
+      </c>
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>Defendant</t>
+        </is>
+      </c>
+      <c r="L1" s="13" t="inlineStr">
+        <is>
+          <t>ChargesSummary</t>
+        </is>
+      </c>
+      <c r="M1" s="13" t="inlineStr">
+        <is>
+          <t>WitnessesRequired</t>
+        </is>
+      </c>
+      <c r="N1" s="13" t="inlineStr">
+        <is>
+          <t>WitnessesAttended</t>
+        </is>
+      </c>
+      <c r="O1" s="13" t="inlineStr">
+        <is>
+          <t>ExhibitsRequired</t>
+        </is>
+      </c>
+      <c r="P1" s="13" t="inlineStr">
+        <is>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="Q1" s="13" t="inlineStr">
+        <is>
+          <t>AdjournmentReason</t>
+        </is>
+      </c>
+      <c r="R1" s="13" t="inlineStr">
+        <is>
+          <t>NextHearingDate</t>
+        </is>
+      </c>
+      <c r="S1" s="13" t="inlineStr">
+        <is>
+          <t>BailStatus</t>
+        </is>
+      </c>
+      <c r="T1" s="13" t="inlineStr">
+        <is>
+          <t>BailAmount</t>
+        </is>
+      </c>
+      <c r="U1" s="13" t="inlineStr">
+        <is>
+          <t>RemandStatus</t>
+        </is>
+      </c>
+      <c r="V1" s="13" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="W1" s="13" t="inlineStr">
+        <is>
+          <t>Sentence</t>
+        </is>
+      </c>
+      <c r="X1" s="13" t="inlineStr">
+        <is>
+          <t>SentenceDate</t>
+        </is>
+      </c>
+      <c r="Y1" s="13" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="Z1" s="13" t="inlineStr">
+        <is>
+          <t>CreatedBy</t>
+        </is>
+      </c>
+      <c r="AA1" s="13" t="inlineStr">
+        <is>
+          <t>CreatedDate</t>
+        </is>
+      </c>
+      <c r="AB1" s="13" t="inlineStr">
+        <is>
+          <t>LastUpdatedBy</t>
+        </is>
+      </c>
+      <c r="AC1" s="13" t="inlineStr">
+        <is>
+          <t>LastUpdatedDate</t>
+        </is>
+      </c>
+      <c r="AD1" s="13" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="AE1" s="13" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="AF1" s="13" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="AG1" s="13" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14">
+        <f>IF(B2="","","CRT-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B2" s="14" t="n"/>
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="14" t="n"/>
+      <c r="G2" s="14" t="n"/>
+      <c r="H2" s="14" t="n"/>
+      <c r="I2" s="14" t="n"/>
+      <c r="J2" s="14" t="n"/>
+      <c r="K2" s="14" t="n"/>
+      <c r="L2" s="14" t="n"/>
+      <c r="M2" s="14" t="n"/>
+      <c r="N2" s="14" t="n"/>
+      <c r="O2" s="14" t="n"/>
+      <c r="P2" s="14" t="n"/>
+      <c r="Q2" s="14" t="n"/>
+      <c r="R2" s="14" t="n"/>
+      <c r="S2" s="14" t="n"/>
+      <c r="T2" s="14" t="n"/>
+      <c r="U2" s="14" t="n"/>
+      <c r="V2" s="14" t="n"/>
+      <c r="W2" s="14" t="n"/>
+      <c r="X2" s="14" t="n"/>
+      <c r="Y2" s="14" t="n"/>
+      <c r="Z2" s="14" t="n"/>
+      <c r="AA2" s="14" t="n"/>
+      <c r="AB2" s="14" t="n"/>
+      <c r="AC2" s="14" t="n"/>
+      <c r="AD2" s="14">
+        <f>IF(E2="","",WEEKNUM(E2))</f>
+        <v/>
+      </c>
+      <c r="AE2" s="14">
+        <f>IF(E2="","",MONTH(E2))</f>
+        <v/>
+      </c>
+      <c r="AF2" s="14">
+        <f>IF(E2="","",ROUNDUP(MONTH(E2)/3,0))</f>
+        <v/>
+      </c>
+      <c r="AG2" s="14">
+        <f>IF(E2="","",YEAR(E2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14">
+        <f>IF(B3="","","CRT-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="14" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="14" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="14" t="n"/>
+      <c r="L3" s="14" t="n"/>
+      <c r="M3" s="14" t="n"/>
+      <c r="N3" s="14" t="n"/>
+      <c r="O3" s="14" t="n"/>
+      <c r="P3" s="14" t="n"/>
+      <c r="Q3" s="14" t="n"/>
+      <c r="R3" s="14" t="n"/>
+      <c r="S3" s="14" t="n"/>
+      <c r="T3" s="14" t="n"/>
+      <c r="U3" s="14" t="n"/>
+      <c r="V3" s="14" t="n"/>
+      <c r="W3" s="14" t="n"/>
+      <c r="X3" s="14" t="n"/>
+      <c r="Y3" s="14" t="n"/>
+      <c r="Z3" s="14" t="n"/>
+      <c r="AA3" s="14" t="n"/>
+      <c r="AB3" s="14" t="n"/>
+      <c r="AC3" s="14" t="n"/>
+      <c r="AD3" s="14">
+        <f>IF(E3="","",WEEKNUM(E3))</f>
+        <v/>
+      </c>
+      <c r="AE3" s="14">
+        <f>IF(E3="","",MONTH(E3))</f>
+        <v/>
+      </c>
+      <c r="AF3" s="14">
+        <f>IF(E3="","",ROUNDUP(MONTH(E3)/3,0))</f>
+        <v/>
+      </c>
+      <c r="AG3" s="14">
+        <f>IF(E3="","",YEAR(E3))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14">
+        <f>IF(B4="","","CRT-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="14" t="n"/>
+      <c r="H4" s="14" t="n"/>
+      <c r="I4" s="14" t="n"/>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="14" t="n"/>
+      <c r="L4" s="14" t="n"/>
+      <c r="M4" s="14" t="n"/>
+      <c r="N4" s="14" t="n"/>
+      <c r="O4" s="14" t="n"/>
+      <c r="P4" s="14" t="n"/>
+      <c r="Q4" s="14" t="n"/>
+      <c r="R4" s="14" t="n"/>
+      <c r="S4" s="14" t="n"/>
+      <c r="T4" s="14" t="n"/>
+      <c r="U4" s="14" t="n"/>
+      <c r="V4" s="14" t="n"/>
+      <c r="W4" s="14" t="n"/>
+      <c r="X4" s="14" t="n"/>
+      <c r="Y4" s="14" t="n"/>
+      <c r="Z4" s="14" t="n"/>
+      <c r="AA4" s="14" t="n"/>
+      <c r="AB4" s="14" t="n"/>
+      <c r="AC4" s="14" t="n"/>
+      <c r="AD4" s="14">
+        <f>IF(E4="","",WEEKNUM(E4))</f>
+        <v/>
+      </c>
+      <c r="AE4" s="14">
+        <f>IF(E4="","",MONTH(E4))</f>
+        <v/>
+      </c>
+      <c r="AF4" s="14">
+        <f>IF(E4="","",ROUNDUP(MONTH(E4)/3,0))</f>
+        <v/>
+      </c>
+      <c r="AG4" s="14">
+        <f>IF(E4="","",YEAR(E4))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14">
+        <f>IF(B5="","","CRT-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B5" s="14" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="n"/>
+      <c r="E5" s="14" t="n"/>
+      <c r="F5" s="14" t="n"/>
+      <c r="G5" s="14" t="n"/>
+      <c r="H5" s="14" t="n"/>
+      <c r="I5" s="14" t="n"/>
+      <c r="J5" s="14" t="n"/>
+      <c r="K5" s="14" t="n"/>
+      <c r="L5" s="14" t="n"/>
+      <c r="M5" s="14" t="n"/>
+      <c r="N5" s="14" t="n"/>
+      <c r="O5" s="14" t="n"/>
+      <c r="P5" s="14" t="n"/>
+      <c r="Q5" s="14" t="n"/>
+      <c r="R5" s="14" t="n"/>
+      <c r="S5" s="14" t="n"/>
+      <c r="T5" s="14" t="n"/>
+      <c r="U5" s="14" t="n"/>
+      <c r="V5" s="14" t="n"/>
+      <c r="W5" s="14" t="n"/>
+      <c r="X5" s="14" t="n"/>
+      <c r="Y5" s="14" t="n"/>
+      <c r="Z5" s="14" t="n"/>
+      <c r="AA5" s="14" t="n"/>
+      <c r="AB5" s="14" t="n"/>
+      <c r="AC5" s="14" t="n"/>
+      <c r="AD5" s="14">
+        <f>IF(E5="","",WEEKNUM(E5))</f>
+        <v/>
+      </c>
+      <c r="AE5" s="14">
+        <f>IF(E5="","",MONTH(E5))</f>
+        <v/>
+      </c>
+      <c r="AF5" s="14">
+        <f>IF(E5="","",ROUNDUP(MONTH(E5)/3,0))</f>
+        <v/>
+      </c>
+      <c r="AG5" s="14">
+        <f>IF(E5="","",YEAR(E5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14">
+        <f>IF(B6="","","CRT-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B6" s="14" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14" t="n"/>
+      <c r="E6" s="14" t="n"/>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="14" t="n"/>
+      <c r="H6" s="14" t="n"/>
+      <c r="I6" s="14" t="n"/>
+      <c r="J6" s="14" t="n"/>
+      <c r="K6" s="14" t="n"/>
+      <c r="L6" s="14" t="n"/>
+      <c r="M6" s="14" t="n"/>
+      <c r="N6" s="14" t="n"/>
+      <c r="O6" s="14" t="n"/>
+      <c r="P6" s="14" t="n"/>
+      <c r="Q6" s="14" t="n"/>
+      <c r="R6" s="14" t="n"/>
+      <c r="S6" s="14" t="n"/>
+      <c r="T6" s="14" t="n"/>
+      <c r="U6" s="14" t="n"/>
+      <c r="V6" s="14" t="n"/>
+      <c r="W6" s="14" t="n"/>
+      <c r="X6" s="14" t="n"/>
+      <c r="Y6" s="14" t="n"/>
+      <c r="Z6" s="14" t="n"/>
+      <c r="AA6" s="14" t="n"/>
+      <c r="AB6" s="14" t="n"/>
+      <c r="AC6" s="14" t="n"/>
+      <c r="AD6" s="14">
+        <f>IF(E6="","",WEEKNUM(E6))</f>
+        <v/>
+      </c>
+      <c r="AE6" s="14">
+        <f>IF(E6="","",MONTH(E6))</f>
+        <v/>
+      </c>
+      <c r="AF6" s="14">
+        <f>IF(E6="","",ROUNDUP(MONTH(E6)/3,0))</f>
+        <v/>
+      </c>
+      <c r="AG6" s="14">
+        <f>IF(E6="","",YEAR(E6))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="E2:E1000">
+    <cfRule type="expression" priority="1" dxfId="1">
+      <formula>=AND(E2&lt;&gt;"",E2&gt;=TODAY(),E2&lt;=TODAY()+7)</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>=AND(E2&lt;&gt;"",E2&lt;TODAY(),P2="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$X$2:$X$8</formula1>
+    </dataValidation>
+    <dataValidation sqref="S2:S1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$AB$2:$AB$6</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C00000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AG6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="24" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="29" max="29"/>
+    <col width="8" customWidth="1" min="30" max="30"/>
+    <col width="8" customWidth="1" min="31" max="31"/>
+    <col width="8" customWidth="1" min="32" max="32"/>
+    <col width="8" customWidth="1" min="33" max="33"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>ArrestID</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>LinkedOpsID</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>LinkedCaseID</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>ArrestDate</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>ArrestTime</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>ArrestLocation</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>Parish</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>Station</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>SuspectName</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>SuspectDOB</t>
+        </is>
+      </c>
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>SuspectAddress</t>
+        </is>
+      </c>
+      <c r="L1" s="13" t="inlineStr">
+        <is>
+          <t>SuspectGender</t>
+        </is>
+      </c>
+      <c r="M1" s="13" t="inlineStr">
+        <is>
+          <t>ChargeDescription</t>
+        </is>
+      </c>
+      <c r="N1" s="13" t="inlineStr">
+        <is>
+          <t>OffenceType</t>
+        </is>
+      </c>
+      <c r="O1" s="13" t="inlineStr">
+        <is>
+          <t>ArrestingOfficer</t>
+        </is>
+      </c>
+      <c r="P1" s="13" t="inlineStr">
+        <is>
+          <t>ArrestingOfficerBadge</t>
+        </is>
+      </c>
+      <c r="Q1" s="13" t="inlineStr">
+        <is>
+          <t>CautionGiven</t>
+        </is>
+      </c>
+      <c r="R1" s="13" t="inlineStr">
+        <is>
+          <t>RightsRead</t>
+        </is>
+      </c>
+      <c r="S1" s="13" t="inlineStr">
+        <is>
+          <t>BailGranted</t>
+        </is>
+      </c>
+      <c r="T1" s="13" t="inlineStr">
+        <is>
+          <t>BailAmount</t>
+        </is>
+      </c>
+      <c r="U1" s="13" t="inlineStr">
+        <is>
+          <t>RemandFacility</t>
+        </is>
+      </c>
+      <c r="V1" s="13" t="inlineStr">
+        <is>
+          <t>RemandDate</t>
+        </is>
+      </c>
+      <c r="W1" s="13" t="inlineStr">
+        <is>
+          <t>CourtDate</t>
+        </is>
+      </c>
+      <c r="X1" s="13" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="Y1" s="13" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="Z1" s="13" t="inlineStr">
+        <is>
+          <t>CreatedBy</t>
+        </is>
+      </c>
+      <c r="AA1" s="13" t="inlineStr">
+        <is>
+          <t>CreatedDate</t>
+        </is>
+      </c>
+      <c r="AB1" s="13" t="inlineStr">
+        <is>
+          <t>LastUpdatedBy</t>
+        </is>
+      </c>
+      <c r="AC1" s="13" t="inlineStr">
+        <is>
+          <t>LastUpdatedDate</t>
+        </is>
+      </c>
+      <c r="AD1" s="13" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="AE1" s="13" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="AF1" s="13" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="AG1" s="13" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14">
+        <f>IF(B2="","","ARR-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B2" s="14" t="n"/>
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="14" t="n"/>
+      <c r="G2" s="14" t="n"/>
+      <c r="H2" s="14" t="n"/>
+      <c r="I2" s="14" t="n"/>
+      <c r="J2" s="14" t="n"/>
+      <c r="K2" s="14" t="n"/>
+      <c r="L2" s="14" t="n"/>
+      <c r="M2" s="14" t="n"/>
+      <c r="N2" s="14" t="n"/>
+      <c r="O2" s="14" t="n"/>
+      <c r="P2" s="14" t="n"/>
+      <c r="Q2" s="14" t="n"/>
+      <c r="R2" s="14" t="n"/>
+      <c r="S2" s="14" t="n"/>
+      <c r="T2" s="14" t="n"/>
+      <c r="U2" s="14" t="n"/>
+      <c r="V2" s="14" t="n"/>
+      <c r="W2" s="14" t="n"/>
+      <c r="X2" s="14" t="n"/>
+      <c r="Y2" s="14" t="n"/>
+      <c r="Z2" s="14" t="n"/>
+      <c r="AA2" s="14" t="n"/>
+      <c r="AB2" s="14" t="n"/>
+      <c r="AC2" s="14" t="n"/>
+      <c r="AD2" s="14">
+        <f>IF(D2="","",WEEKNUM(D2))</f>
+        <v/>
+      </c>
+      <c r="AE2" s="14">
+        <f>IF(D2="","",MONTH(D2))</f>
+        <v/>
+      </c>
+      <c r="AF2" s="14">
+        <f>IF(D2="","",ROUNDUP(MONTH(D2)/3,0))</f>
+        <v/>
+      </c>
+      <c r="AG2" s="14">
+        <f>IF(D2="","",YEAR(D2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14">
+        <f>IF(B3="","","ARR-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="14" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="14" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="14" t="n"/>
+      <c r="L3" s="14" t="n"/>
+      <c r="M3" s="14" t="n"/>
+      <c r="N3" s="14" t="n"/>
+      <c r="O3" s="14" t="n"/>
+      <c r="P3" s="14" t="n"/>
+      <c r="Q3" s="14" t="n"/>
+      <c r="R3" s="14" t="n"/>
+      <c r="S3" s="14" t="n"/>
+      <c r="T3" s="14" t="n"/>
+      <c r="U3" s="14" t="n"/>
+      <c r="V3" s="14" t="n"/>
+      <c r="W3" s="14" t="n"/>
+      <c r="X3" s="14" t="n"/>
+      <c r="Y3" s="14" t="n"/>
+      <c r="Z3" s="14" t="n"/>
+      <c r="AA3" s="14" t="n"/>
+      <c r="AB3" s="14" t="n"/>
+      <c r="AC3" s="14" t="n"/>
+      <c r="AD3" s="14">
+        <f>IF(D3="","",WEEKNUM(D3))</f>
+        <v/>
+      </c>
+      <c r="AE3" s="14">
+        <f>IF(D3="","",MONTH(D3))</f>
+        <v/>
+      </c>
+      <c r="AF3" s="14">
+        <f>IF(D3="","",ROUNDUP(MONTH(D3)/3,0))</f>
+        <v/>
+      </c>
+      <c r="AG3" s="14">
+        <f>IF(D3="","",YEAR(D3))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14">
+        <f>IF(B4="","","ARR-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="14" t="n"/>
+      <c r="H4" s="14" t="n"/>
+      <c r="I4" s="14" t="n"/>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="14" t="n"/>
+      <c r="L4" s="14" t="n"/>
+      <c r="M4" s="14" t="n"/>
+      <c r="N4" s="14" t="n"/>
+      <c r="O4" s="14" t="n"/>
+      <c r="P4" s="14" t="n"/>
+      <c r="Q4" s="14" t="n"/>
+      <c r="R4" s="14" t="n"/>
+      <c r="S4" s="14" t="n"/>
+      <c r="T4" s="14" t="n"/>
+      <c r="U4" s="14" t="n"/>
+      <c r="V4" s="14" t="n"/>
+      <c r="W4" s="14" t="n"/>
+      <c r="X4" s="14" t="n"/>
+      <c r="Y4" s="14" t="n"/>
+      <c r="Z4" s="14" t="n"/>
+      <c r="AA4" s="14" t="n"/>
+      <c r="AB4" s="14" t="n"/>
+      <c r="AC4" s="14" t="n"/>
+      <c r="AD4" s="14">
+        <f>IF(D4="","",WEEKNUM(D4))</f>
+        <v/>
+      </c>
+      <c r="AE4" s="14">
+        <f>IF(D4="","",MONTH(D4))</f>
+        <v/>
+      </c>
+      <c r="AF4" s="14">
+        <f>IF(D4="","",ROUNDUP(MONTH(D4)/3,0))</f>
+        <v/>
+      </c>
+      <c r="AG4" s="14">
+        <f>IF(D4="","",YEAR(D4))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14">
+        <f>IF(B5="","","ARR-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B5" s="14" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="n"/>
+      <c r="E5" s="14" t="n"/>
+      <c r="F5" s="14" t="n"/>
+      <c r="G5" s="14" t="n"/>
+      <c r="H5" s="14" t="n"/>
+      <c r="I5" s="14" t="n"/>
+      <c r="J5" s="14" t="n"/>
+      <c r="K5" s="14" t="n"/>
+      <c r="L5" s="14" t="n"/>
+      <c r="M5" s="14" t="n"/>
+      <c r="N5" s="14" t="n"/>
+      <c r="O5" s="14" t="n"/>
+      <c r="P5" s="14" t="n"/>
+      <c r="Q5" s="14" t="n"/>
+      <c r="R5" s="14" t="n"/>
+      <c r="S5" s="14" t="n"/>
+      <c r="T5" s="14" t="n"/>
+      <c r="U5" s="14" t="n"/>
+      <c r="V5" s="14" t="n"/>
+      <c r="W5" s="14" t="n"/>
+      <c r="X5" s="14" t="n"/>
+      <c r="Y5" s="14" t="n"/>
+      <c r="Z5" s="14" t="n"/>
+      <c r="AA5" s="14" t="n"/>
+      <c r="AB5" s="14" t="n"/>
+      <c r="AC5" s="14" t="n"/>
+      <c r="AD5" s="14">
+        <f>IF(D5="","",WEEKNUM(D5))</f>
+        <v/>
+      </c>
+      <c r="AE5" s="14">
+        <f>IF(D5="","",MONTH(D5))</f>
+        <v/>
+      </c>
+      <c r="AF5" s="14">
+        <f>IF(D5="","",ROUNDUP(MONTH(D5)/3,0))</f>
+        <v/>
+      </c>
+      <c r="AG5" s="14">
+        <f>IF(D5="","",YEAR(D5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14">
+        <f>IF(B6="","","ARR-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B6" s="14" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14" t="n"/>
+      <c r="E6" s="14" t="n"/>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="14" t="n"/>
+      <c r="H6" s="14" t="n"/>
+      <c r="I6" s="14" t="n"/>
+      <c r="J6" s="14" t="n"/>
+      <c r="K6" s="14" t="n"/>
+      <c r="L6" s="14" t="n"/>
+      <c r="M6" s="14" t="n"/>
+      <c r="N6" s="14" t="n"/>
+      <c r="O6" s="14" t="n"/>
+      <c r="P6" s="14" t="n"/>
+      <c r="Q6" s="14" t="n"/>
+      <c r="R6" s="14" t="n"/>
+      <c r="S6" s="14" t="n"/>
+      <c r="T6" s="14" t="n"/>
+      <c r="U6" s="14" t="n"/>
+      <c r="V6" s="14" t="n"/>
+      <c r="W6" s="14" t="n"/>
+      <c r="X6" s="14" t="n"/>
+      <c r="Y6" s="14" t="n"/>
+      <c r="Z6" s="14" t="n"/>
+      <c r="AA6" s="14" t="n"/>
+      <c r="AB6" s="14" t="n"/>
+      <c r="AC6" s="14" t="n"/>
+      <c r="AD6" s="14">
+        <f>IF(D6="","",WEEKNUM(D6))</f>
+        <v/>
+      </c>
+      <c r="AE6" s="14">
+        <f>IF(D6="","",MONTH(D6))</f>
+        <v/>
+      </c>
+      <c r="AF6" s="14">
+        <f>IF(D6="","",ROUNDUP(MONTH(D6)/3,0))</f>
+        <v/>
+      </c>
+      <c r="AG6" s="14">
+        <f>IF(D6="","",YEAR(D6))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="5">
+    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$D$2:$D$16</formula1>
+    </dataValidation>
+    <dataValidation sqref="N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$C$2:$C$22</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q2:Q1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$I$2:$I$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="R2:R1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$I$2:$I$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="S2:S1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$I$2:$I$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C00000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AC6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="8" customWidth="1" min="27" max="27"/>
+    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="8" customWidth="1" min="29" max="29"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>SeizureID</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>LinkedOpsID</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>LinkedCaseID</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>LinkedArrestID</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>SeizureDate</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>SeizureLocation</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>Parish</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>ItemType</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>ItemDescription</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>UnitMeasure</t>
+        </is>
+      </c>
+      <c r="L1" s="13" t="inlineStr">
+        <is>
+          <t>SerialNumber</t>
+        </is>
+      </c>
+      <c r="M1" s="13" t="inlineStr">
+        <is>
+          <t>Make</t>
+        </is>
+      </c>
+      <c r="N1" s="13" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="O1" s="13" t="inlineStr">
+        <is>
+          <t>Calibre</t>
+        </is>
+      </c>
+      <c r="P1" s="13" t="inlineStr">
+        <is>
+          <t>EstimatedValue</t>
+        </is>
+      </c>
+      <c r="Q1" s="13" t="inlineStr">
+        <is>
+          <t>LinkedExhibitID</t>
+        </is>
+      </c>
+      <c r="R1" s="13" t="inlineStr">
+        <is>
+          <t>PhotoRef</t>
+        </is>
+      </c>
+      <c r="S1" s="13" t="inlineStr">
+        <is>
+          <t>SeizedBy</t>
+        </is>
+      </c>
+      <c r="T1" s="13" t="inlineStr">
+        <is>
+          <t>WitnessPresent</t>
+        </is>
+      </c>
+      <c r="U1" s="13" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="V1" s="13" t="inlineStr">
+        <is>
+          <t>CreatedBy</t>
+        </is>
+      </c>
+      <c r="W1" s="13" t="inlineStr">
+        <is>
+          <t>CreatedDate</t>
+        </is>
+      </c>
+      <c r="X1" s="13" t="inlineStr">
+        <is>
+          <t>LastUpdatedBy</t>
+        </is>
+      </c>
+      <c r="Y1" s="13" t="inlineStr">
+        <is>
+          <t>LastUpdatedDate</t>
+        </is>
+      </c>
+      <c r="Z1" s="13" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="AA1" s="13" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="AB1" s="13" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="AC1" s="13" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14">
+        <f>IF(B2="","","SEZ-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B2" s="14" t="n"/>
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="14" t="n"/>
+      <c r="G2" s="14" t="n"/>
+      <c r="H2" s="14" t="n"/>
+      <c r="I2" s="14" t="n"/>
+      <c r="J2" s="14" t="n"/>
+      <c r="K2" s="14" t="n"/>
+      <c r="L2" s="14" t="n"/>
+      <c r="M2" s="14" t="n"/>
+      <c r="N2" s="14" t="n"/>
+      <c r="O2" s="14" t="n"/>
+      <c r="P2" s="14" t="n"/>
+      <c r="Q2" s="14" t="n"/>
+      <c r="R2" s="14" t="n"/>
+      <c r="S2" s="14" t="n"/>
+      <c r="T2" s="14" t="n"/>
+      <c r="U2" s="14" t="n"/>
+      <c r="V2" s="14" t="n"/>
+      <c r="W2" s="14" t="n"/>
+      <c r="X2" s="14" t="n"/>
+      <c r="Y2" s="14" t="n"/>
+      <c r="Z2" s="14">
+        <f>IF(E2="","",WEEKNUM(E2))</f>
+        <v/>
+      </c>
+      <c r="AA2" s="14">
+        <f>IF(E2="","",MONTH(E2))</f>
+        <v/>
+      </c>
+      <c r="AB2" s="14">
+        <f>IF(E2="","",ROUNDUP(MONTH(E2)/3,0))</f>
+        <v/>
+      </c>
+      <c r="AC2" s="14">
+        <f>IF(E2="","",YEAR(E2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14">
+        <f>IF(B3="","","SEZ-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="14" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="14" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="14" t="n"/>
+      <c r="L3" s="14" t="n"/>
+      <c r="M3" s="14" t="n"/>
+      <c r="N3" s="14" t="n"/>
+      <c r="O3" s="14" t="n"/>
+      <c r="P3" s="14" t="n"/>
+      <c r="Q3" s="14" t="n"/>
+      <c r="R3" s="14" t="n"/>
+      <c r="S3" s="14" t="n"/>
+      <c r="T3" s="14" t="n"/>
+      <c r="U3" s="14" t="n"/>
+      <c r="V3" s="14" t="n"/>
+      <c r="W3" s="14" t="n"/>
+      <c r="X3" s="14" t="n"/>
+      <c r="Y3" s="14" t="n"/>
+      <c r="Z3" s="14">
+        <f>IF(E3="","",WEEKNUM(E3))</f>
+        <v/>
+      </c>
+      <c r="AA3" s="14">
+        <f>IF(E3="","",MONTH(E3))</f>
+        <v/>
+      </c>
+      <c r="AB3" s="14">
+        <f>IF(E3="","",ROUNDUP(MONTH(E3)/3,0))</f>
+        <v/>
+      </c>
+      <c r="AC3" s="14">
+        <f>IF(E3="","",YEAR(E3))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14">
+        <f>IF(B4="","","SEZ-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="14" t="n"/>
+      <c r="H4" s="14" t="n"/>
+      <c r="I4" s="14" t="n"/>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="14" t="n"/>
+      <c r="L4" s="14" t="n"/>
+      <c r="M4" s="14" t="n"/>
+      <c r="N4" s="14" t="n"/>
+      <c r="O4" s="14" t="n"/>
+      <c r="P4" s="14" t="n"/>
+      <c r="Q4" s="14" t="n"/>
+      <c r="R4" s="14" t="n"/>
+      <c r="S4" s="14" t="n"/>
+      <c r="T4" s="14" t="n"/>
+      <c r="U4" s="14" t="n"/>
+      <c r="V4" s="14" t="n"/>
+      <c r="W4" s="14" t="n"/>
+      <c r="X4" s="14" t="n"/>
+      <c r="Y4" s="14" t="n"/>
+      <c r="Z4" s="14">
+        <f>IF(E4="","",WEEKNUM(E4))</f>
+        <v/>
+      </c>
+      <c r="AA4" s="14">
+        <f>IF(E4="","",MONTH(E4))</f>
+        <v/>
+      </c>
+      <c r="AB4" s="14">
+        <f>IF(E4="","",ROUNDUP(MONTH(E4)/3,0))</f>
+        <v/>
+      </c>
+      <c r="AC4" s="14">
+        <f>IF(E4="","",YEAR(E4))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14">
+        <f>IF(B5="","","SEZ-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B5" s="14" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="n"/>
+      <c r="E5" s="14" t="n"/>
+      <c r="F5" s="14" t="n"/>
+      <c r="G5" s="14" t="n"/>
+      <c r="H5" s="14" t="n"/>
+      <c r="I5" s="14" t="n"/>
+      <c r="J5" s="14" t="n"/>
+      <c r="K5" s="14" t="n"/>
+      <c r="L5" s="14" t="n"/>
+      <c r="M5" s="14" t="n"/>
+      <c r="N5" s="14" t="n"/>
+      <c r="O5" s="14" t="n"/>
+      <c r="P5" s="14" t="n"/>
+      <c r="Q5" s="14" t="n"/>
+      <c r="R5" s="14" t="n"/>
+      <c r="S5" s="14" t="n"/>
+      <c r="T5" s="14" t="n"/>
+      <c r="U5" s="14" t="n"/>
+      <c r="V5" s="14" t="n"/>
+      <c r="W5" s="14" t="n"/>
+      <c r="X5" s="14" t="n"/>
+      <c r="Y5" s="14" t="n"/>
+      <c r="Z5" s="14">
+        <f>IF(E5="","",WEEKNUM(E5))</f>
+        <v/>
+      </c>
+      <c r="AA5" s="14">
+        <f>IF(E5="","",MONTH(E5))</f>
+        <v/>
+      </c>
+      <c r="AB5" s="14">
+        <f>IF(E5="","",ROUNDUP(MONTH(E5)/3,0))</f>
+        <v/>
+      </c>
+      <c r="AC5" s="14">
+        <f>IF(E5="","",YEAR(E5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14">
+        <f>IF(B6="","","SEZ-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B6" s="14" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14" t="n"/>
+      <c r="E6" s="14" t="n"/>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="14" t="n"/>
+      <c r="H6" s="14" t="n"/>
+      <c r="I6" s="14" t="n"/>
+      <c r="J6" s="14" t="n"/>
+      <c r="K6" s="14" t="n"/>
+      <c r="L6" s="14" t="n"/>
+      <c r="M6" s="14" t="n"/>
+      <c r="N6" s="14" t="n"/>
+      <c r="O6" s="14" t="n"/>
+      <c r="P6" s="14" t="n"/>
+      <c r="Q6" s="14" t="n"/>
+      <c r="R6" s="14" t="n"/>
+      <c r="S6" s="14" t="n"/>
+      <c r="T6" s="14" t="n"/>
+      <c r="U6" s="14" t="n"/>
+      <c r="V6" s="14" t="n"/>
+      <c r="W6" s="14" t="n"/>
+      <c r="X6" s="14" t="n"/>
+      <c r="Y6" s="14" t="n"/>
+      <c r="Z6" s="14">
+        <f>IF(E6="","",WEEKNUM(E6))</f>
+        <v/>
+      </c>
+      <c r="AA6" s="14">
+        <f>IF(E6="","",MONTH(E6))</f>
+        <v/>
+      </c>
+      <c r="AB6" s="14">
+        <f>IF(E6="","",ROUNDUP(MONTH(E6)/3,0))</f>
+        <v/>
+      </c>
+      <c r="AC6" s="14">
+        <f>IF(E6="","",YEAR(E6))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$D$2:$D$16</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$K$2:$K$16</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C00000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Y6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>WarrantID</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>WarrantType</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>LinkedCaseID</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>LinkedLeadID</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>LinkedOpsID</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>ApplicationDate</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>IssuedDate</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>IssuedBy</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>JP_Name</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>Court</t>
+        </is>
+      </c>
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>TargetName</t>
+        </is>
+      </c>
+      <c r="L1" s="13" t="inlineStr">
+        <is>
+          <t>TargetAddress</t>
+        </is>
+      </c>
+      <c r="M1" s="13" t="inlineStr">
+        <is>
+          <t>Parish</t>
+        </is>
+      </c>
+      <c r="N1" s="13" t="inlineStr">
+        <is>
+          <t>ValidUntil</t>
+        </is>
+      </c>
+      <c r="O1" s="13" t="inlineStr">
+        <is>
+          <t>ExecutionDate</t>
+        </is>
+      </c>
+      <c r="P1" s="13" t="inlineStr">
+        <is>
+          <t>ExecutedBy</t>
+        </is>
+      </c>
+      <c r="Q1" s="13" t="inlineStr">
+        <is>
+          <t>ExecutionOutcome</t>
+        </is>
+      </c>
+      <c r="R1" s="13" t="inlineStr">
+        <is>
+          <t>ReturnToJP_Date</t>
+        </is>
+      </c>
+      <c r="S1" s="13" t="inlineStr">
+        <is>
+          <t>ReturnToJP_By</t>
+        </is>
+      </c>
+      <c r="T1" s="13" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="U1" s="13" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="V1" s="13" t="inlineStr">
+        <is>
+          <t>CreatedBy</t>
+        </is>
+      </c>
+      <c r="W1" s="13" t="inlineStr">
+        <is>
+          <t>CreatedDate</t>
+        </is>
+      </c>
+      <c r="X1" s="13" t="inlineStr">
+        <is>
+          <t>LastUpdatedBy</t>
+        </is>
+      </c>
+      <c r="Y1" s="13" t="inlineStr">
+        <is>
+          <t>LastUpdatedDate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14">
+        <f>IF(B2="","","WAR-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B2" s="14" t="n"/>
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="14" t="n"/>
+      <c r="G2" s="14" t="n"/>
+      <c r="H2" s="14" t="n"/>
+      <c r="I2" s="14" t="n"/>
+      <c r="J2" s="14" t="n"/>
+      <c r="K2" s="14" t="n"/>
+      <c r="L2" s="14" t="n"/>
+      <c r="M2" s="14" t="n"/>
+      <c r="N2" s="14" t="n"/>
+      <c r="O2" s="14" t="n"/>
+      <c r="P2" s="14" t="n"/>
+      <c r="Q2" s="14" t="n"/>
+      <c r="R2" s="14" t="n"/>
+      <c r="S2" s="14" t="n"/>
+      <c r="T2" s="14" t="n"/>
+      <c r="U2" s="14" t="n"/>
+      <c r="V2" s="14" t="n"/>
+      <c r="W2" s="14" t="n"/>
+      <c r="X2" s="14" t="n"/>
+      <c r="Y2" s="14" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="14">
+        <f>IF(B3="","","WAR-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="14" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="14" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="14" t="n"/>
+      <c r="L3" s="14" t="n"/>
+      <c r="M3" s="14" t="n"/>
+      <c r="N3" s="14" t="n"/>
+      <c r="O3" s="14" t="n"/>
+      <c r="P3" s="14" t="n"/>
+      <c r="Q3" s="14" t="n"/>
+      <c r="R3" s="14" t="n"/>
+      <c r="S3" s="14" t="n"/>
+      <c r="T3" s="14" t="n"/>
+      <c r="U3" s="14" t="n"/>
+      <c r="V3" s="14" t="n"/>
+      <c r="W3" s="14" t="n"/>
+      <c r="X3" s="14" t="n"/>
+      <c r="Y3" s="14" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="14">
+        <f>IF(B4="","","WAR-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="14" t="n"/>
+      <c r="H4" s="14" t="n"/>
+      <c r="I4" s="14" t="n"/>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="14" t="n"/>
+      <c r="L4" s="14" t="n"/>
+      <c r="M4" s="14" t="n"/>
+      <c r="N4" s="14" t="n"/>
+      <c r="O4" s="14" t="n"/>
+      <c r="P4" s="14" t="n"/>
+      <c r="Q4" s="14" t="n"/>
+      <c r="R4" s="14" t="n"/>
+      <c r="S4" s="14" t="n"/>
+      <c r="T4" s="14" t="n"/>
+      <c r="U4" s="14" t="n"/>
+      <c r="V4" s="14" t="n"/>
+      <c r="W4" s="14" t="n"/>
+      <c r="X4" s="14" t="n"/>
+      <c r="Y4" s="14" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="14">
+        <f>IF(B5="","","WAR-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B5" s="14" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="n"/>
+      <c r="E5" s="14" t="n"/>
+      <c r="F5" s="14" t="n"/>
+      <c r="G5" s="14" t="n"/>
+      <c r="H5" s="14" t="n"/>
+      <c r="I5" s="14" t="n"/>
+      <c r="J5" s="14" t="n"/>
+      <c r="K5" s="14" t="n"/>
+      <c r="L5" s="14" t="n"/>
+      <c r="M5" s="14" t="n"/>
+      <c r="N5" s="14" t="n"/>
+      <c r="O5" s="14" t="n"/>
+      <c r="P5" s="14" t="n"/>
+      <c r="Q5" s="14" t="n"/>
+      <c r="R5" s="14" t="n"/>
+      <c r="S5" s="14" t="n"/>
+      <c r="T5" s="14" t="n"/>
+      <c r="U5" s="14" t="n"/>
+      <c r="V5" s="14" t="n"/>
+      <c r="W5" s="14" t="n"/>
+      <c r="X5" s="14" t="n"/>
+      <c r="Y5" s="14" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14">
+        <f>IF(B6="","","WAR-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B6" s="14" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14" t="n"/>
+      <c r="E6" s="14" t="n"/>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="14" t="n"/>
+      <c r="H6" s="14" t="n"/>
+      <c r="I6" s="14" t="n"/>
+      <c r="J6" s="14" t="n"/>
+      <c r="K6" s="14" t="n"/>
+      <c r="L6" s="14" t="n"/>
+      <c r="M6" s="14" t="n"/>
+      <c r="N6" s="14" t="n"/>
+      <c r="O6" s="14" t="n"/>
+      <c r="P6" s="14" t="n"/>
+      <c r="Q6" s="14" t="n"/>
+      <c r="R6" s="14" t="n"/>
+      <c r="S6" s="14" t="n"/>
+      <c r="T6" s="14" t="n"/>
+      <c r="U6" s="14" t="n"/>
+      <c r="V6" s="14" t="n"/>
+      <c r="W6" s="14" t="n"/>
+      <c r="X6" s="14" t="n"/>
+      <c r="Y6" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="N2:N1000">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>=AND(N2&lt;&gt;"",N2&lt;TODAY(),O2="")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$D$2:$D$16</formula1>
+    </dataValidation>
+    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$Z$2:$Z$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="T2:T1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$AA$2:$AA$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00BF8F00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Y6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>InformantID</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>CodeName</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>Handler</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>HandlerBadge</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>RegistrationDate</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>Credibility</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>Parish</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>Area_Coverage</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>TotalTipsProvided</t>
+        </is>
+      </c>
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>TipsConvertedToCase</t>
+        </is>
+      </c>
+      <c r="L1" s="13" t="inlineStr">
+        <is>
+          <t>TipsConvertedToOp</t>
+        </is>
+      </c>
+      <c r="M1" s="13" t="inlineStr">
+        <is>
+          <t>ConversionRate</t>
+        </is>
+      </c>
+      <c r="N1" s="13" t="inlineStr">
+        <is>
+          <t>LastContactDate</t>
+        </is>
+      </c>
+      <c r="O1" s="13" t="inlineStr">
+        <is>
+          <t>NextContactDue</t>
+        </is>
+      </c>
+      <c r="P1" s="13" t="inlineStr">
+        <is>
+          <t>PaymentsToDate</t>
+        </is>
+      </c>
+      <c r="Q1" s="13" t="inlineStr">
+        <is>
+          <t>LastPaymentDate</t>
+        </is>
+      </c>
+      <c r="R1" s="13" t="inlineStr">
+        <is>
+          <t>LastPaymentAmount</t>
+        </is>
+      </c>
+      <c r="S1" s="13" t="inlineStr">
+        <is>
+          <t>RiskToInformant</t>
+        </is>
+      </c>
+      <c r="T1" s="13" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="U1" s="13" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="V1" s="13" t="inlineStr">
+        <is>
+          <t>CreatedBy</t>
+        </is>
+      </c>
+      <c r="W1" s="13" t="inlineStr">
+        <is>
+          <t>CreatedDate</t>
+        </is>
+      </c>
+      <c r="X1" s="13" t="inlineStr">
+        <is>
+          <t>LastUpdatedBy</t>
+        </is>
+      </c>
+      <c r="Y1" s="13" t="inlineStr">
+        <is>
+          <t>LastUpdatedDate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14">
+        <f>IF(B2="","","INF-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B2" s="14" t="n"/>
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="14" t="n"/>
+      <c r="G2" s="14" t="n"/>
+      <c r="H2" s="14" t="n"/>
+      <c r="I2" s="14" t="n"/>
+      <c r="J2" s="14" t="n"/>
+      <c r="K2" s="14" t="n"/>
+      <c r="L2" s="14" t="n"/>
+      <c r="M2" s="16">
+        <f>IF(OR(J2="",J2=0),"",((K2+L2)/J2))</f>
+        <v/>
+      </c>
+      <c r="N2" s="14" t="n"/>
+      <c r="O2" s="14" t="n"/>
+      <c r="P2" s="14" t="n"/>
+      <c r="Q2" s="14" t="n"/>
+      <c r="R2" s="14" t="n"/>
+      <c r="S2" s="14" t="n"/>
+      <c r="T2" s="14" t="n"/>
+      <c r="U2" s="14" t="n"/>
+      <c r="V2" s="14" t="n"/>
+      <c r="W2" s="14" t="n"/>
+      <c r="X2" s="14" t="n"/>
+      <c r="Y2" s="14" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="14">
+        <f>IF(B3="","","INF-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="14" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="14" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="14" t="n"/>
+      <c r="L3" s="14" t="n"/>
+      <c r="M3" s="16">
+        <f>IF(OR(J3="",J3=0),"",((K3+L3)/J3))</f>
+        <v/>
+      </c>
+      <c r="N3" s="14" t="n"/>
+      <c r="O3" s="14" t="n"/>
+      <c r="P3" s="14" t="n"/>
+      <c r="Q3" s="14" t="n"/>
+      <c r="R3" s="14" t="n"/>
+      <c r="S3" s="14" t="n"/>
+      <c r="T3" s="14" t="n"/>
+      <c r="U3" s="14" t="n"/>
+      <c r="V3" s="14" t="n"/>
+      <c r="W3" s="14" t="n"/>
+      <c r="X3" s="14" t="n"/>
+      <c r="Y3" s="14" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="14">
+        <f>IF(B4="","","INF-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="14" t="n"/>
+      <c r="H4" s="14" t="n"/>
+      <c r="I4" s="14" t="n"/>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="14" t="n"/>
+      <c r="L4" s="14" t="n"/>
+      <c r="M4" s="16">
+        <f>IF(OR(J4="",J4=0),"",((K4+L4)/J4))</f>
+        <v/>
+      </c>
+      <c r="N4" s="14" t="n"/>
+      <c r="O4" s="14" t="n"/>
+      <c r="P4" s="14" t="n"/>
+      <c r="Q4" s="14" t="n"/>
+      <c r="R4" s="14" t="n"/>
+      <c r="S4" s="14" t="n"/>
+      <c r="T4" s="14" t="n"/>
+      <c r="U4" s="14" t="n"/>
+      <c r="V4" s="14" t="n"/>
+      <c r="W4" s="14" t="n"/>
+      <c r="X4" s="14" t="n"/>
+      <c r="Y4" s="14" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="14">
+        <f>IF(B5="","","INF-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B5" s="14" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="n"/>
+      <c r="E5" s="14" t="n"/>
+      <c r="F5" s="14" t="n"/>
+      <c r="G5" s="14" t="n"/>
+      <c r="H5" s="14" t="n"/>
+      <c r="I5" s="14" t="n"/>
+      <c r="J5" s="14" t="n"/>
+      <c r="K5" s="14" t="n"/>
+      <c r="L5" s="14" t="n"/>
+      <c r="M5" s="16">
+        <f>IF(OR(J5="",J5=0),"",((K5+L5)/J5))</f>
+        <v/>
+      </c>
+      <c r="N5" s="14" t="n"/>
+      <c r="O5" s="14" t="n"/>
+      <c r="P5" s="14" t="n"/>
+      <c r="Q5" s="14" t="n"/>
+      <c r="R5" s="14" t="n"/>
+      <c r="S5" s="14" t="n"/>
+      <c r="T5" s="14" t="n"/>
+      <c r="U5" s="14" t="n"/>
+      <c r="V5" s="14" t="n"/>
+      <c r="W5" s="14" t="n"/>
+      <c r="X5" s="14" t="n"/>
+      <c r="Y5" s="14" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14">
+        <f>IF(B6="","","INF-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B6" s="14" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14" t="n"/>
+      <c r="E6" s="14" t="n"/>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="14" t="n"/>
+      <c r="H6" s="14" t="n"/>
+      <c r="I6" s="14" t="n"/>
+      <c r="J6" s="14" t="n"/>
+      <c r="K6" s="14" t="n"/>
+      <c r="L6" s="14" t="n"/>
+      <c r="M6" s="16">
+        <f>IF(OR(J6="",J6=0),"",((K6+L6)/J6))</f>
+        <v/>
+      </c>
+      <c r="N6" s="14" t="n"/>
+      <c r="O6" s="14" t="n"/>
+      <c r="P6" s="14" t="n"/>
+      <c r="Q6" s="14" t="n"/>
+      <c r="R6" s="14" t="n"/>
+      <c r="S6" s="14" t="n"/>
+      <c r="T6" s="14" t="n"/>
+      <c r="U6" s="14" t="n"/>
+      <c r="V6" s="14" t="n"/>
+      <c r="W6" s="14" t="n"/>
+      <c r="X6" s="14" t="n"/>
+      <c r="Y6" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="O2:O1000">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>=AND(O2&lt;&gt;"",O2&lt;TODAY())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$E$2:$E$11</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$J$2:$J$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$D$2:$D$16</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="8" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>RosterID</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>ShiftType</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>StartTime</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>EndTime</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>OfficerName</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>BadgeNo</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>Station</t>
+        </is>
+      </c>
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>Assignment</t>
+        </is>
+      </c>
+      <c r="L1" s="13" t="inlineStr">
+        <is>
+          <t>PostLocation</t>
+        </is>
+      </c>
+      <c r="M1" s="13" t="inlineStr">
+        <is>
+          <t>Supervisor</t>
+        </is>
+      </c>
+      <c r="N1" s="13" t="inlineStr">
+        <is>
+          <t>OvertimeHrs</t>
+        </is>
+      </c>
+      <c r="O1" s="13" t="inlineStr">
+        <is>
+          <t>LeaveType</t>
+        </is>
+      </c>
+      <c r="P1" s="13" t="inlineStr">
+        <is>
+          <t>Replacement</t>
+        </is>
+      </c>
+      <c r="Q1" s="13" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="R1" s="13" t="inlineStr">
+        <is>
+          <t>CreatedBy</t>
+        </is>
+      </c>
+      <c r="S1" s="13" t="inlineStr">
+        <is>
+          <t>CreatedDate</t>
+        </is>
+      </c>
+      <c r="T1" s="13" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="U1" s="13" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="V1" s="13" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="W1" s="13" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14">
+        <f>IF(B2="","","DUTY-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B2" s="14" t="n"/>
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="14" t="n"/>
+      <c r="G2" s="14" t="n"/>
+      <c r="H2" s="14" t="n"/>
+      <c r="I2" s="14" t="n"/>
+      <c r="J2" s="14" t="n"/>
+      <c r="K2" s="14" t="n"/>
+      <c r="L2" s="14" t="n"/>
+      <c r="M2" s="14" t="n"/>
+      <c r="N2" s="14" t="n"/>
+      <c r="O2" s="14" t="n"/>
+      <c r="P2" s="14" t="n"/>
+      <c r="Q2" s="14" t="n"/>
+      <c r="R2" s="14" t="n"/>
+      <c r="S2" s="14" t="n"/>
+      <c r="T2" s="14">
+        <f>IF(B2="","",WEEKNUM(B2))</f>
+        <v/>
+      </c>
+      <c r="U2" s="14">
+        <f>IF(B2="","",MONTH(B2))</f>
+        <v/>
+      </c>
+      <c r="V2" s="14">
+        <f>IF(B2="","",ROUNDUP(MONTH(B2)/3,0))</f>
+        <v/>
+      </c>
+      <c r="W2" s="14">
+        <f>IF(B2="","",YEAR(B2))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14">
+        <f>IF(B3="","","DUTY-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="14" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="14" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="14" t="n"/>
+      <c r="L3" s="14" t="n"/>
+      <c r="M3" s="14" t="n"/>
+      <c r="N3" s="14" t="n"/>
+      <c r="O3" s="14" t="n"/>
+      <c r="P3" s="14" t="n"/>
+      <c r="Q3" s="14" t="n"/>
+      <c r="R3" s="14" t="n"/>
+      <c r="S3" s="14" t="n"/>
+      <c r="T3" s="14">
+        <f>IF(B3="","",WEEKNUM(B3))</f>
+        <v/>
+      </c>
+      <c r="U3" s="14">
+        <f>IF(B3="","",MONTH(B3))</f>
+        <v/>
+      </c>
+      <c r="V3" s="14">
+        <f>IF(B3="","",ROUNDUP(MONTH(B3)/3,0))</f>
+        <v/>
+      </c>
+      <c r="W3" s="14">
+        <f>IF(B3="","",YEAR(B3))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14">
+        <f>IF(B4="","","DUTY-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="14" t="n"/>
+      <c r="H4" s="14" t="n"/>
+      <c r="I4" s="14" t="n"/>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="14" t="n"/>
+      <c r="L4" s="14" t="n"/>
+      <c r="M4" s="14" t="n"/>
+      <c r="N4" s="14" t="n"/>
+      <c r="O4" s="14" t="n"/>
+      <c r="P4" s="14" t="n"/>
+      <c r="Q4" s="14" t="n"/>
+      <c r="R4" s="14" t="n"/>
+      <c r="S4" s="14" t="n"/>
+      <c r="T4" s="14">
+        <f>IF(B4="","",WEEKNUM(B4))</f>
+        <v/>
+      </c>
+      <c r="U4" s="14">
+        <f>IF(B4="","",MONTH(B4))</f>
+        <v/>
+      </c>
+      <c r="V4" s="14">
+        <f>IF(B4="","",ROUNDUP(MONTH(B4)/3,0))</f>
+        <v/>
+      </c>
+      <c r="W4" s="14">
+        <f>IF(B4="","",YEAR(B4))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14">
+        <f>IF(B5="","","DUTY-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B5" s="14" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="n"/>
+      <c r="E5" s="14" t="n"/>
+      <c r="F5" s="14" t="n"/>
+      <c r="G5" s="14" t="n"/>
+      <c r="H5" s="14" t="n"/>
+      <c r="I5" s="14" t="n"/>
+      <c r="J5" s="14" t="n"/>
+      <c r="K5" s="14" t="n"/>
+      <c r="L5" s="14" t="n"/>
+      <c r="M5" s="14" t="n"/>
+      <c r="N5" s="14" t="n"/>
+      <c r="O5" s="14" t="n"/>
+      <c r="P5" s="14" t="n"/>
+      <c r="Q5" s="14" t="n"/>
+      <c r="R5" s="14" t="n"/>
+      <c r="S5" s="14" t="n"/>
+      <c r="T5" s="14">
+        <f>IF(B5="","",WEEKNUM(B5))</f>
+        <v/>
+      </c>
+      <c r="U5" s="14">
+        <f>IF(B5="","",MONTH(B5))</f>
+        <v/>
+      </c>
+      <c r="V5" s="14">
+        <f>IF(B5="","",ROUNDUP(MONTH(B5)/3,0))</f>
+        <v/>
+      </c>
+      <c r="W5" s="14">
+        <f>IF(B5="","",YEAR(B5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14">
+        <f>IF(B6="","","DUTY-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B6" s="14" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14" t="n"/>
+      <c r="E6" s="14" t="n"/>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="14" t="n"/>
+      <c r="H6" s="14" t="n"/>
+      <c r="I6" s="14" t="n"/>
+      <c r="J6" s="14" t="n"/>
+      <c r="K6" s="14" t="n"/>
+      <c r="L6" s="14" t="n"/>
+      <c r="M6" s="14" t="n"/>
+      <c r="N6" s="14" t="n"/>
+      <c r="O6" s="14" t="n"/>
+      <c r="P6" s="14" t="n"/>
+      <c r="Q6" s="14" t="n"/>
+      <c r="R6" s="14" t="n"/>
+      <c r="S6" s="14" t="n"/>
+      <c r="T6" s="14">
+        <f>IF(B6="","",WEEKNUM(B6))</f>
+        <v/>
+      </c>
+      <c r="U6" s="14">
+        <f>IF(B6="","",MONTH(B6))</f>
+        <v/>
+      </c>
+      <c r="V6" s="14">
+        <f>IF(B6="","",ROUNDUP(MONTH(B6)/3,0))</f>
+        <v/>
+      </c>
+      <c r="W6" s="14">
+        <f>IF(B6="","",YEAR(B6))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$Q$2:$Q$11</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$E$2:$E$11</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$Y$2:$Y$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00538135"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>TransferID</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>ExhibitID</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>LinkedCaseID</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>TransferDate</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>TransferTime</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>ReleasedBy</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>ReleasedByRank</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>ReleasedByBadge</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>ReceivedBy</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>ReceivedByRank</t>
+        </is>
+      </c>
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>ReceivedByBadge</t>
+        </is>
+      </c>
+      <c r="L1" s="13" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="M1" s="13" t="inlineStr">
+        <is>
+          <t>FromLocation</t>
+        </is>
+      </c>
+      <c r="N1" s="13" t="inlineStr">
+        <is>
+          <t>ToLocation</t>
+        </is>
+      </c>
+      <c r="O1" s="13" t="inlineStr">
+        <is>
+          <t>ConditionAtTransfer</t>
+        </is>
+      </c>
+      <c r="P1" s="13" t="inlineStr">
+        <is>
+          <t>WitnessName</t>
+        </is>
+      </c>
+      <c r="Q1" s="13" t="inlineStr">
+        <is>
+          <t>WitnessBadge</t>
+        </is>
+      </c>
+      <c r="R1" s="13" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="S1" s="13" t="inlineStr">
+        <is>
+          <t>CreatedBy</t>
+        </is>
+      </c>
+      <c r="T1" s="13" t="inlineStr">
+        <is>
+          <t>CreatedDate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14">
+        <f>IF(B2="","","COC-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B2" s="14" t="n"/>
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="14" t="n"/>
+      <c r="G2" s="14" t="n"/>
+      <c r="H2" s="14" t="n"/>
+      <c r="I2" s="14" t="n"/>
+      <c r="J2" s="14" t="n"/>
+      <c r="K2" s="14" t="n"/>
+      <c r="L2" s="14" t="n"/>
+      <c r="M2" s="14" t="n"/>
+      <c r="N2" s="14" t="n"/>
+      <c r="O2" s="14" t="n"/>
+      <c r="P2" s="14" t="n"/>
+      <c r="Q2" s="14" t="n"/>
+      <c r="R2" s="14" t="n"/>
+      <c r="S2" s="14" t="n"/>
+      <c r="T2" s="14" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="14">
+        <f>IF(B3="","","COC-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="14" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="14" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="14" t="n"/>
+      <c r="L3" s="14" t="n"/>
+      <c r="M3" s="14" t="n"/>
+      <c r="N3" s="14" t="n"/>
+      <c r="O3" s="14" t="n"/>
+      <c r="P3" s="14" t="n"/>
+      <c r="Q3" s="14" t="n"/>
+      <c r="R3" s="14" t="n"/>
+      <c r="S3" s="14" t="n"/>
+      <c r="T3" s="14" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="14">
+        <f>IF(B4="","","COC-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="14" t="n"/>
+      <c r="H4" s="14" t="n"/>
+      <c r="I4" s="14" t="n"/>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="14" t="n"/>
+      <c r="L4" s="14" t="n"/>
+      <c r="M4" s="14" t="n"/>
+      <c r="N4" s="14" t="n"/>
+      <c r="O4" s="14" t="n"/>
+      <c r="P4" s="14" t="n"/>
+      <c r="Q4" s="14" t="n"/>
+      <c r="R4" s="14" t="n"/>
+      <c r="S4" s="14" t="n"/>
+      <c r="T4" s="14" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="14">
+        <f>IF(B5="","","COC-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B5" s="14" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="n"/>
+      <c r="E5" s="14" t="n"/>
+      <c r="F5" s="14" t="n"/>
+      <c r="G5" s="14" t="n"/>
+      <c r="H5" s="14" t="n"/>
+      <c r="I5" s="14" t="n"/>
+      <c r="J5" s="14" t="n"/>
+      <c r="K5" s="14" t="n"/>
+      <c r="L5" s="14" t="n"/>
+      <c r="M5" s="14" t="n"/>
+      <c r="N5" s="14" t="n"/>
+      <c r="O5" s="14" t="n"/>
+      <c r="P5" s="14" t="n"/>
+      <c r="Q5" s="14" t="n"/>
+      <c r="R5" s="14" t="n"/>
+      <c r="S5" s="14" t="n"/>
+      <c r="T5" s="14" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14">
+        <f>IF(B6="","","COC-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B6" s="14" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14" t="n"/>
+      <c r="E6" s="14" t="n"/>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="14" t="n"/>
+      <c r="H6" s="14" t="n"/>
+      <c r="I6" s="14" t="n"/>
+      <c r="J6" s="14" t="n"/>
+      <c r="K6" s="14" t="n"/>
+      <c r="L6" s="14" t="n"/>
+      <c r="M6" s="14" t="n"/>
+      <c r="N6" s="14" t="n"/>
+      <c r="O6" s="14" t="n"/>
+      <c r="P6" s="14" t="n"/>
+      <c r="Q6" s="14" t="n"/>
+      <c r="R6" s="14" t="n"/>
+      <c r="S6" s="14" t="n"/>
+      <c r="T6" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F3864"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AG6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="24" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="28" customWidth="1" min="28" max="28"/>
+    <col width="24" customWidth="1" min="29" max="29"/>
+    <col width="14" customWidth="1" min="30" max="30"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="14" customWidth="1" min="32" max="32"/>
+    <col width="14" customWidth="1" min="33" max="33"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>SceneID</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>LinkedCaseID</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>LinkedOpsID</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>Parish</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>GPS_Coordinates</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>SceneType</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>SceneOfficer</t>
+        </is>
+      </c>
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="L1" s="13" t="inlineStr">
+        <is>
+          <t>BadgeNo</t>
+        </is>
+      </c>
+      <c r="M1" s="13" t="inlineStr">
+        <is>
+          <t>PhotosTaken</t>
+        </is>
+      </c>
+      <c r="N1" s="13" t="inlineStr">
+        <is>
+          <t>VideoRecorded</t>
+        </is>
+      </c>
+      <c r="O1" s="13" t="inlineStr">
+        <is>
+          <t>SketchDrawn</t>
+        </is>
+      </c>
+      <c r="P1" s="13" t="inlineStr">
+        <is>
+          <t>GSR_Collected</t>
+        </is>
+      </c>
+      <c r="Q1" s="13" t="inlineStr">
+        <is>
+          <t>ShellCasingsFound</t>
+        </is>
+      </c>
+      <c r="R1" s="13" t="inlineStr">
+        <is>
+          <t>ShellCasingCount</t>
+        </is>
+      </c>
+      <c r="S1" s="13" t="inlineStr">
+        <is>
+          <t>BloodSamplesCollected</t>
+        </is>
+      </c>
+      <c r="T1" s="13" t="inlineStr">
+        <is>
+          <t>FingerprintsLifted</t>
+        </is>
+      </c>
+      <c r="U1" s="13" t="inlineStr">
+        <is>
+          <t>WeaponsFound</t>
+        </is>
+      </c>
+      <c r="V1" s="13" t="inlineStr">
+        <is>
+          <t>WeaponDetails</t>
+        </is>
+      </c>
+      <c r="W1" s="13" t="inlineStr">
+        <is>
+          <t>WitnessesAtScene</t>
+        </is>
+      </c>
+      <c r="X1" s="13" t="inlineStr">
+        <is>
+          <t>WeatherConditions</t>
+        </is>
+      </c>
+      <c r="Y1" s="13" t="inlineStr">
+        <is>
+          <t>Lighting</t>
+        </is>
+      </c>
+      <c r="Z1" s="13" t="inlineStr">
+        <is>
+          <t>SceneSealedTime</t>
+        </is>
+      </c>
+      <c r="AA1" s="13" t="inlineStr">
+        <is>
+          <t>SceneReleasedTime</t>
+        </is>
+      </c>
+      <c r="AB1" s="13" t="inlineStr">
+        <is>
+          <t>OtherEvidenceNotes</t>
+        </is>
+      </c>
+      <c r="AC1" s="13" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="AD1" s="13" t="inlineStr">
+        <is>
+          <t>CreatedBy</t>
+        </is>
+      </c>
+      <c r="AE1" s="13" t="inlineStr">
+        <is>
+          <t>CreatedDate</t>
+        </is>
+      </c>
+      <c r="AF1" s="13" t="inlineStr">
+        <is>
+          <t>LastUpdatedBy</t>
+        </is>
+      </c>
+      <c r="AG1" s="13" t="inlineStr">
+        <is>
+          <t>LastUpdatedDate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14">
+        <f>IF(B2="","","SCN-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B2" s="14" t="n"/>
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="14" t="n"/>
+      <c r="G2" s="14" t="n"/>
+      <c r="H2" s="14" t="n"/>
+      <c r="I2" s="14" t="n"/>
+      <c r="J2" s="14" t="n"/>
+      <c r="K2" s="14" t="n"/>
+      <c r="L2" s="14" t="n"/>
+      <c r="M2" s="14" t="n"/>
+      <c r="N2" s="14" t="n"/>
+      <c r="O2" s="14" t="n"/>
+      <c r="P2" s="14" t="n"/>
+      <c r="Q2" s="14" t="n"/>
+      <c r="R2" s="14" t="n"/>
+      <c r="S2" s="14" t="n"/>
+      <c r="T2" s="14" t="n"/>
+      <c r="U2" s="14" t="n"/>
+      <c r="V2" s="14" t="n"/>
+      <c r="W2" s="14" t="n"/>
+      <c r="X2" s="14" t="n"/>
+      <c r="Y2" s="14" t="n"/>
+      <c r="Z2" s="14" t="n"/>
+      <c r="AA2" s="14" t="n"/>
+      <c r="AB2" s="14" t="n"/>
+      <c r="AC2" s="14" t="n"/>
+      <c r="AD2" s="14" t="n"/>
+      <c r="AE2" s="14" t="n"/>
+      <c r="AF2" s="14" t="n"/>
+      <c r="AG2" s="14" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="14">
+        <f>IF(B3="","","SCN-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B3" s="14" t="n"/>
+      <c r="C3" s="14" t="n"/>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="14" t="n"/>
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="14" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="14" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="14" t="n"/>
+      <c r="L3" s="14" t="n"/>
+      <c r="M3" s="14" t="n"/>
+      <c r="N3" s="14" t="n"/>
+      <c r="O3" s="14" t="n"/>
+      <c r="P3" s="14" t="n"/>
+      <c r="Q3" s="14" t="n"/>
+      <c r="R3" s="14" t="n"/>
+      <c r="S3" s="14" t="n"/>
+      <c r="T3" s="14" t="n"/>
+      <c r="U3" s="14" t="n"/>
+      <c r="V3" s="14" t="n"/>
+      <c r="W3" s="14" t="n"/>
+      <c r="X3" s="14" t="n"/>
+      <c r="Y3" s="14" t="n"/>
+      <c r="Z3" s="14" t="n"/>
+      <c r="AA3" s="14" t="n"/>
+      <c r="AB3" s="14" t="n"/>
+      <c r="AC3" s="14" t="n"/>
+      <c r="AD3" s="14" t="n"/>
+      <c r="AE3" s="14" t="n"/>
+      <c r="AF3" s="14" t="n"/>
+      <c r="AG3" s="14" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="14">
+        <f>IF(B4="","","SCN-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B4" s="14" t="n"/>
+      <c r="C4" s="14" t="n"/>
+      <c r="D4" s="14" t="n"/>
+      <c r="E4" s="14" t="n"/>
+      <c r="F4" s="14" t="n"/>
+      <c r="G4" s="14" t="n"/>
+      <c r="H4" s="14" t="n"/>
+      <c r="I4" s="14" t="n"/>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="14" t="n"/>
+      <c r="L4" s="14" t="n"/>
+      <c r="M4" s="14" t="n"/>
+      <c r="N4" s="14" t="n"/>
+      <c r="O4" s="14" t="n"/>
+      <c r="P4" s="14" t="n"/>
+      <c r="Q4" s="14" t="n"/>
+      <c r="R4" s="14" t="n"/>
+      <c r="S4" s="14" t="n"/>
+      <c r="T4" s="14" t="n"/>
+      <c r="U4" s="14" t="n"/>
+      <c r="V4" s="14" t="n"/>
+      <c r="W4" s="14" t="n"/>
+      <c r="X4" s="14" t="n"/>
+      <c r="Y4" s="14" t="n"/>
+      <c r="Z4" s="14" t="n"/>
+      <c r="AA4" s="14" t="n"/>
+      <c r="AB4" s="14" t="n"/>
+      <c r="AC4" s="14" t="n"/>
+      <c r="AD4" s="14" t="n"/>
+      <c r="AE4" s="14" t="n"/>
+      <c r="AF4" s="14" t="n"/>
+      <c r="AG4" s="14" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="14">
+        <f>IF(B5="","","SCN-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B5" s="14" t="n"/>
+      <c r="C5" s="14" t="n"/>
+      <c r="D5" s="14" t="n"/>
+      <c r="E5" s="14" t="n"/>
+      <c r="F5" s="14" t="n"/>
+      <c r="G5" s="14" t="n"/>
+      <c r="H5" s="14" t="n"/>
+      <c r="I5" s="14" t="n"/>
+      <c r="J5" s="14" t="n"/>
+      <c r="K5" s="14" t="n"/>
+      <c r="L5" s="14" t="n"/>
+      <c r="M5" s="14" t="n"/>
+      <c r="N5" s="14" t="n"/>
+      <c r="O5" s="14" t="n"/>
+      <c r="P5" s="14" t="n"/>
+      <c r="Q5" s="14" t="n"/>
+      <c r="R5" s="14" t="n"/>
+      <c r="S5" s="14" t="n"/>
+      <c r="T5" s="14" t="n"/>
+      <c r="U5" s="14" t="n"/>
+      <c r="V5" s="14" t="n"/>
+      <c r="W5" s="14" t="n"/>
+      <c r="X5" s="14" t="n"/>
+      <c r="Y5" s="14" t="n"/>
+      <c r="Z5" s="14" t="n"/>
+      <c r="AA5" s="14" t="n"/>
+      <c r="AB5" s="14" t="n"/>
+      <c r="AC5" s="14" t="n"/>
+      <c r="AD5" s="14" t="n"/>
+      <c r="AE5" s="14" t="n"/>
+      <c r="AF5" s="14" t="n"/>
+      <c r="AG5" s="14" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14">
+        <f>IF(B6="","","SCN-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B6" s="14" t="n"/>
+      <c r="C6" s="14" t="n"/>
+      <c r="D6" s="14" t="n"/>
+      <c r="E6" s="14" t="n"/>
+      <c r="F6" s="14" t="n"/>
+      <c r="G6" s="14" t="n"/>
+      <c r="H6" s="14" t="n"/>
+      <c r="I6" s="14" t="n"/>
+      <c r="J6" s="14" t="n"/>
+      <c r="K6" s="14" t="n"/>
+      <c r="L6" s="14" t="n"/>
+      <c r="M6" s="14" t="n"/>
+      <c r="N6" s="14" t="n"/>
+      <c r="O6" s="14" t="n"/>
+      <c r="P6" s="14" t="n"/>
+      <c r="Q6" s="14" t="n"/>
+      <c r="R6" s="14" t="n"/>
+      <c r="S6" s="14" t="n"/>
+      <c r="T6" s="14" t="n"/>
+      <c r="U6" s="14" t="n"/>
+      <c r="V6" s="14" t="n"/>
+      <c r="W6" s="14" t="n"/>
+      <c r="X6" s="14" t="n"/>
+      <c r="Y6" s="14" t="n"/>
+      <c r="Z6" s="14" t="n"/>
+      <c r="AA6" s="14" t="n"/>
+      <c r="AB6" s="14" t="n"/>
+      <c r="AC6" s="14" t="n"/>
+      <c r="AD6" s="14" t="n"/>
+      <c r="AE6" s="14" t="n"/>
+      <c r="AF6" s="14" t="n"/>
+      <c r="AG6" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <dataValidations count="6">
+    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$D$2:$D$16</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$I$2:$I$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$I$2:$I$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="O2:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$I$2:$I$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="P2:P1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$I$2:$I$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$AD$2:$AD$10</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -21344,6 +28971,17 @@
       <formula>=AND(G2&lt;&gt;"",G2&lt;TODAY(),H2="")</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$V$2:$V$13</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$U$2:$U$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$E$2:$E$11</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -21545,6 +29183,14 @@
       <c r="N6" s="14" t="n"/>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$W$2:$W$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Please select from the list." type="list">
+      <formula1>=Lookups!$U$2:$U$7</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/FNID_Area3_Operational_Workbook.xlsx
+++ b/FNID_Area3_Operational_Workbook.xlsx
@@ -16,12 +16,13 @@
     <sheet name="tbl_NarcoticSeizures" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="tbl_OtherSeizures" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="tbl_Arrests" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="tbl_ChainOfCustody" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="tbl_CaseFiles" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="tbl_Witnesses" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="tbl_Informants" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="tbl_Personnel" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="tbl_Vehicles" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="tbl_CaseRegistry" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="tbl_ChainOfCustody" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="tbl_CaseFiles" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="tbl_Witnesses" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="tbl_Informants" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="tbl_Personnel" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="tbl_Vehicles" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'tbl_IntelLog'!$A$1:$W$1</definedName>
@@ -30,12 +31,13 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'tbl_NarcoticSeizures'!$A$1:$AE$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'tbl_OtherSeizures'!$A$1:$U$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'tbl_Arrests'!$A$1:$AJ$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'tbl_ChainOfCustody'!$A$1:$S$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'tbl_CaseFiles'!$A$1:$AI$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'tbl_Witnesses'!$A$1:$V$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'tbl_Informants'!$A$1:$R$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'tbl_Personnel'!$A$1:$P$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'tbl_Vehicles'!$A$1:$O$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'tbl_CaseRegistry'!$A$1:$AY$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'tbl_ChainOfCustody'!$A$1:$S$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'tbl_CaseFiles'!$A$1:$AI$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'tbl_Witnesses'!$A$1:$V$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'tbl_Informants'!$A$1:$R$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'tbl_Personnel'!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'tbl_Vehicles'!$A$1:$O$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -143,7 +145,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -163,6 +165,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
       </patternFill>
     </fill>
     <fill>
@@ -204,7 +211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -228,6 +235,7 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -249,16 +257,20 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -407,7 +419,38 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="tbl_Informants" displayName="tbl_Informants" ref="A1:R6" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="tbl_Witnesses" displayName="tbl_Witnesses" ref="A1:V6" headerRowCount="1">
+  <autoFilter ref="A1:V6"/>
+  <tableColumns count="22">
+    <tableColumn id="1" name="WitnessID"/>
+    <tableColumn id="2" name="LinkedCaseFileID"/>
+    <tableColumn id="3" name="WitnessName"/>
+    <tableColumn id="4" name="ContactNumber"/>
+    <tableColumn id="5" name="Address"/>
+    <tableColumn id="6" name="Parish"/>
+    <tableColumn id="7" name="WitnessType"/>
+    <tableColumn id="8" name="StatementTaken"/>
+    <tableColumn id="9" name="StatementDate"/>
+    <tableColumn id="10" name="CautionGiven"/>
+    <tableColumn id="11" name="WillingToTestify"/>
+    <tableColumn id="12" name="ProtectionRequired"/>
+    <tableColumn id="13" name="WitnessProtectionReferred"/>
+    <tableColumn id="14" name="SummonsIssued"/>
+    <tableColumn id="15" name="SummonsServed"/>
+    <tableColumn id="16" name="SummonsServedDate"/>
+    <tableColumn id="17" name="Vulnerable"/>
+    <tableColumn id="18" name="IntimidationReported"/>
+    <tableColumn id="19" name="CourtAppearanceDate"/>
+    <tableColumn id="20" name="Notes"/>
+    <tableColumn id="21" name="CreatedBy"/>
+    <tableColumn id="22" name="CreatedDate"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="tbl_Informants" displayName="tbl_Informants" ref="A1:R6" headerRowCount="1">
   <autoFilter ref="A1:R6"/>
   <tableColumns count="18">
     <tableColumn id="1" name="InformantCode"/>
@@ -433,8 +476,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="tbl_Personnel" displayName="tbl_Personnel" ref="A1:P6" headerRowCount="1">
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="tbl_Personnel" displayName="tbl_Personnel" ref="A1:P6" headerRowCount="1">
   <autoFilter ref="A1:P6"/>
   <tableColumns count="16">
     <tableColumn id="1" name="PersonnelID"/>
@@ -458,8 +501,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="tbl_Vehicles" displayName="tbl_Vehicles" ref="A1:O6" headerRowCount="1">
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="tbl_Vehicles" displayName="tbl_Vehicles" ref="A1:O6" headerRowCount="1">
   <autoFilter ref="A1:O6"/>
   <tableColumns count="15">
     <tableColumn id="1" name="VehicleID"/>
@@ -688,7 +731,67 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="tbl_ChainOfCustody" displayName="tbl_ChainOfCustody" ref="A1:S6" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="tbl_CaseRegistry" displayName="tbl_CaseRegistry" ref="A1:AY6" headerRowCount="1">
+  <autoFilter ref="A1:AY6"/>
+  <tableColumns count="51">
+    <tableColumn id="1" name="CaseRegID"/>
+    <tableColumn id="2" name="CaseFileNumber"/>
+    <tableColumn id="3" name="DateOpened"/>
+    <tableColumn id="4" name="CaseClassification"/>
+    <tableColumn id="5" name="CasePriority"/>
+    <tableColumn id="6" name="CaseStatus"/>
+    <tableColumn id="7" name="InvestigationType"/>
+    <tableColumn id="8" name="PrimaryOffence"/>
+    <tableColumn id="9" name="ActSection"/>
+    <tableColumn id="10" name="LinkedIntelIDs"/>
+    <tableColumn id="11" name="LinkedOpsIDs"/>
+    <tableColumn id="12" name="LinkedArrestIDs"/>
+    <tableColumn id="13" name="LinkedFirearmSeizureIDs"/>
+    <tableColumn id="14" name="LinkedNarcoticSeizureIDs"/>
+    <tableColumn id="15" name="LinkedDPPCaseFileID"/>
+    <tableColumn id="16" name="InvestigatingOfficer"/>
+    <tableColumn id="17" name="InvestigatingOfficerRank"/>
+    <tableColumn id="18" name="Supervisor"/>
+    <tableColumn id="19" name="DateAssigned"/>
+    <tableColumn id="20" name="Parish"/>
+    <tableColumn id="21" name="Division"/>
+    <tableColumn id="22" name="TargetPerson"/>
+    <tableColumn id="23" name="TargetOrganisation"/>
+    <tableColumn id="24" name="GangAffiliation"/>
+    <tableColumn id="25" name="SceneExamComplete"/>
+    <tableColumn id="26" name="WitnessStatementsTaken"/>
+    <tableColumn id="27" name="ForensicEvidenceSubmitted"/>
+    <tableColumn id="28" name="ForensicResultsReceived"/>
+    <tableColumn id="29" name="SurveillanceConducted"/>
+    <tableColumn id="30" name="PhoneRecordsObtained"/>
+    <tableColumn id="31" name="FinancialRecordsObtained"/>
+    <tableColumn id="32" name="CCTVFootageObtained"/>
+    <tableColumn id="33" name="DigitalForensicsComplete"/>
+    <tableColumn id="34" name="InvestigationProgress"/>
+    <tableColumn id="35" name="LastActivityDate"/>
+    <tableColumn id="36" name="NextActionRequired"/>
+    <tableColumn id="37" name="NextActionDeadline"/>
+    <tableColumn id="38" name="LastReviewDate"/>
+    <tableColumn id="39" name="ReviewedBy"/>
+    <tableColumn id="40" name="ReviewNotes"/>
+    <tableColumn id="41" name="Escalated"/>
+    <tableColumn id="42" name="EscalatedTo"/>
+    <tableColumn id="43" name="EscalationReason"/>
+    <tableColumn id="44" name="ColdCaseReviewDate"/>
+    <tableColumn id="45" name="ColdCaseReviewedBy"/>
+    <tableColumn id="46" name="ResolutionDate"/>
+    <tableColumn id="47" name="ResolutionSummary"/>
+    <tableColumn id="48" name="DaysOpen"/>
+    <tableColumn id="49" name="Notes"/>
+    <tableColumn id="50" name="CreatedBy"/>
+    <tableColumn id="51" name="CreatedDate"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="tbl_ChainOfCustody" displayName="tbl_ChainOfCustody" ref="A1:S6" headerRowCount="1">
   <autoFilter ref="A1:S6"/>
   <tableColumns count="19">
     <tableColumn id="1" name="TransferID"/>
@@ -715,8 +818,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="tbl_CaseFiles" displayName="tbl_CaseFiles" ref="A1:AI6" headerRowCount="1">
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="tbl_CaseFiles" displayName="tbl_CaseFiles" ref="A1:AI6" headerRowCount="1">
   <autoFilter ref="A1:AI6"/>
   <tableColumns count="35">
     <tableColumn id="1" name="CaseFileID"/>
@@ -754,37 +857,6 @@
     <tableColumn id="33" name="Notes"/>
     <tableColumn id="34" name="CreatedBy"/>
     <tableColumn id="35" name="CreatedDate"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="tbl_Witnesses" displayName="tbl_Witnesses" ref="A1:V6" headerRowCount="1">
-  <autoFilter ref="A1:V6"/>
-  <tableColumns count="22">
-    <tableColumn id="1" name="WitnessID"/>
-    <tableColumn id="2" name="LinkedCaseFileID"/>
-    <tableColumn id="3" name="WitnessName"/>
-    <tableColumn id="4" name="ContactNumber"/>
-    <tableColumn id="5" name="Address"/>
-    <tableColumn id="6" name="Parish"/>
-    <tableColumn id="7" name="WitnessType"/>
-    <tableColumn id="8" name="StatementTaken"/>
-    <tableColumn id="9" name="StatementDate"/>
-    <tableColumn id="10" name="CautionGiven"/>
-    <tableColumn id="11" name="WillingToTestify"/>
-    <tableColumn id="12" name="ProtectionRequired"/>
-    <tableColumn id="13" name="WitnessProtectionReferred"/>
-    <tableColumn id="14" name="SummonsIssued"/>
-    <tableColumn id="15" name="SummonsServed"/>
-    <tableColumn id="16" name="SummonsServedDate"/>
-    <tableColumn id="17" name="Vulnerable"/>
-    <tableColumn id="18" name="IntimidationReported"/>
-    <tableColumn id="19" name="CourtAppearanceDate"/>
-    <tableColumn id="20" name="Notes"/>
-    <tableColumn id="21" name="CreatedBy"/>
-    <tableColumn id="22" name="CreatedDate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1080,7 +1152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1255,146 +1327,894 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>STAGE 5: EVIDENCE &amp; FORENSICS</t>
+          <t>STAGE 5: CASE REGISTRY &amp; INVESTIGATIONS</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &gt;&gt; tbl_ChainOfCustody</t>
+          <t xml:space="preserve">  &gt;&gt; tbl_CaseRegistry</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Exhibit Chain of Custody — every handover logged</t>
+          <t>Master Case File Registry — every case, investigation milestones, progress tracking</t>
         </is>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>STAGE 6: DPP &amp; COURT</t>
+          <t>STAGE 6: EVIDENCE &amp; FORENSICS</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">  &gt;&gt; tbl_ChainOfCustody</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Exhibit Chain of Custody — every handover logged</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>STAGE 7: DPP &amp; COURT</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">  &gt;&gt; tbl_CaseFiles</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>Case File Tracker — DPP submission pipeline, completeness scoring</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  &gt;&gt; tbl_Witnesses</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Witness &amp; Statement Register — testimony, protection, summons</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>SUPPORT</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
+          <t xml:space="preserve">  &gt;&gt; tbl_Witnesses</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Witness &amp; Statement Register — testimony, protection, summons</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>SUPPORT</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
           <t xml:space="preserve">  &gt;&gt; tbl_Personnel</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>Personnel Register — staff, qualifications, polygraph</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  &gt;&gt; tbl_Vehicles</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>Vehicle/Fleet Log — status, service, fitness</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  &gt;&gt; Lookups</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>Reference Data — Jamaica-specific lookups</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="13" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
         <is>
           <t>LEGAL FRAMEWORK: Firearms (Prohibition, Restriction and Regulation) Act 2022 | Dangerous Drugs Act (as amended 2015) | Gun Court Act 1974 | Proceeds of Crime Act 2007 | Bail Act 2023 | Constabulary Force Act s.15 (48-Hour Rule)</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="14" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t>CONFIDENTIAL — FOR OFFICIAL USE ONLY | FNID Area 3 | Search warrants under Section 91, Firearms Act 2022</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="30">
     <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A30:H30"/>
     <mergeCell ref="A24:H24"/>
-    <mergeCell ref="B33:H33"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A6:H6"/>
+    <mergeCell ref="B36:H36"/>
     <mergeCell ref="B32:H32"/>
+    <mergeCell ref="B35:H35"/>
     <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A41:H41"/>
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="B25:H25"/>
-    <mergeCell ref="A37:H37"/>
     <mergeCell ref="A27:H27"/>
+    <mergeCell ref="B31:H31"/>
     <mergeCell ref="B22:H22"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A21:H21"/>
     <mergeCell ref="B18:H18"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B11:H11"/>
+    <mergeCell ref="A40:H40"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="B14:H14"/>
     <mergeCell ref="B17:H17"/>
-    <mergeCell ref="A38:H38"/>
-    <mergeCell ref="B34:H34"/>
     <mergeCell ref="A13:H13"/>
-    <mergeCell ref="B29:H29"/>
     <mergeCell ref="B10:H10"/>
     <mergeCell ref="B19:H19"/>
-    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="B37:H37"/>
     <mergeCell ref="B28:H28"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002E75B6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AY6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="10" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="10" customWidth="1" min="31" max="31"/>
+    <col width="10" customWidth="1" min="32" max="32"/>
+    <col width="10" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="28" customWidth="1" min="36" max="36"/>
+    <col width="14" customWidth="1" min="37" max="37"/>
+    <col width="12" customWidth="1" min="38" max="38"/>
+    <col width="16" customWidth="1" min="39" max="39"/>
+    <col width="28" customWidth="1" min="40" max="40"/>
+    <col width="10" customWidth="1" min="41" max="41"/>
+    <col width="18" customWidth="1" min="42" max="42"/>
+    <col width="24" customWidth="1" min="43" max="43"/>
+    <col width="12" customWidth="1" min="44" max="44"/>
+    <col width="16" customWidth="1" min="45" max="45"/>
+    <col width="12" customWidth="1" min="46" max="46"/>
+    <col width="30" customWidth="1" min="47" max="47"/>
+    <col width="10" customWidth="1" min="48" max="48"/>
+    <col width="28" customWidth="1" min="49" max="49"/>
+    <col width="14" customWidth="1" min="50" max="50"/>
+    <col width="12" customWidth="1" min="51" max="51"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="32" t="inlineStr">
+        <is>
+          <t>CaseRegID</t>
+        </is>
+      </c>
+      <c r="B1" s="32" t="inlineStr">
+        <is>
+          <t>CaseFileNumber</t>
+        </is>
+      </c>
+      <c r="C1" s="32" t="inlineStr">
+        <is>
+          <t>DateOpened</t>
+        </is>
+      </c>
+      <c r="D1" s="32" t="inlineStr">
+        <is>
+          <t>CaseClassification</t>
+        </is>
+      </c>
+      <c r="E1" s="32" t="inlineStr">
+        <is>
+          <t>CasePriority</t>
+        </is>
+      </c>
+      <c r="F1" s="32" t="inlineStr">
+        <is>
+          <t>CaseStatus</t>
+        </is>
+      </c>
+      <c r="G1" s="32" t="inlineStr">
+        <is>
+          <t>InvestigationType</t>
+        </is>
+      </c>
+      <c r="H1" s="32" t="inlineStr">
+        <is>
+          <t>PrimaryOffence</t>
+        </is>
+      </c>
+      <c r="I1" s="32" t="inlineStr">
+        <is>
+          <t>ActSection</t>
+        </is>
+      </c>
+      <c r="J1" s="32" t="inlineStr">
+        <is>
+          <t>LinkedIntelIDs</t>
+        </is>
+      </c>
+      <c r="K1" s="32" t="inlineStr">
+        <is>
+          <t>LinkedOpsIDs</t>
+        </is>
+      </c>
+      <c r="L1" s="32" t="inlineStr">
+        <is>
+          <t>LinkedArrestIDs</t>
+        </is>
+      </c>
+      <c r="M1" s="32" t="inlineStr">
+        <is>
+          <t>LinkedFirearmSeizureIDs</t>
+        </is>
+      </c>
+      <c r="N1" s="32" t="inlineStr">
+        <is>
+          <t>LinkedNarcoticSeizureIDs</t>
+        </is>
+      </c>
+      <c r="O1" s="32" t="inlineStr">
+        <is>
+          <t>LinkedDPPCaseFileID</t>
+        </is>
+      </c>
+      <c r="P1" s="32" t="inlineStr">
+        <is>
+          <t>InvestigatingOfficer</t>
+        </is>
+      </c>
+      <c r="Q1" s="32" t="inlineStr">
+        <is>
+          <t>InvestigatingOfficerRank</t>
+        </is>
+      </c>
+      <c r="R1" s="32" t="inlineStr">
+        <is>
+          <t>Supervisor</t>
+        </is>
+      </c>
+      <c r="S1" s="32" t="inlineStr">
+        <is>
+          <t>DateAssigned</t>
+        </is>
+      </c>
+      <c r="T1" s="32" t="inlineStr">
+        <is>
+          <t>Parish</t>
+        </is>
+      </c>
+      <c r="U1" s="32" t="inlineStr">
+        <is>
+          <t>Division</t>
+        </is>
+      </c>
+      <c r="V1" s="32" t="inlineStr">
+        <is>
+          <t>TargetPerson</t>
+        </is>
+      </c>
+      <c r="W1" s="32" t="inlineStr">
+        <is>
+          <t>TargetOrganisation</t>
+        </is>
+      </c>
+      <c r="X1" s="32" t="inlineStr">
+        <is>
+          <t>GangAffiliation</t>
+        </is>
+      </c>
+      <c r="Y1" s="32" t="inlineStr">
+        <is>
+          <t>SceneExamComplete</t>
+        </is>
+      </c>
+      <c r="Z1" s="32" t="inlineStr">
+        <is>
+          <t>WitnessStatementsTaken</t>
+        </is>
+      </c>
+      <c r="AA1" s="32" t="inlineStr">
+        <is>
+          <t>ForensicEvidenceSubmitted</t>
+        </is>
+      </c>
+      <c r="AB1" s="32" t="inlineStr">
+        <is>
+          <t>ForensicResultsReceived</t>
+        </is>
+      </c>
+      <c r="AC1" s="32" t="inlineStr">
+        <is>
+          <t>SurveillanceConducted</t>
+        </is>
+      </c>
+      <c r="AD1" s="32" t="inlineStr">
+        <is>
+          <t>PhoneRecordsObtained</t>
+        </is>
+      </c>
+      <c r="AE1" s="32" t="inlineStr">
+        <is>
+          <t>FinancialRecordsObtained</t>
+        </is>
+      </c>
+      <c r="AF1" s="32" t="inlineStr">
+        <is>
+          <t>CCTVFootageObtained</t>
+        </is>
+      </c>
+      <c r="AG1" s="32" t="inlineStr">
+        <is>
+          <t>DigitalForensicsComplete</t>
+        </is>
+      </c>
+      <c r="AH1" s="32" t="inlineStr">
+        <is>
+          <t>InvestigationProgress</t>
+        </is>
+      </c>
+      <c r="AI1" s="32" t="inlineStr">
+        <is>
+          <t>LastActivityDate</t>
+        </is>
+      </c>
+      <c r="AJ1" s="32" t="inlineStr">
+        <is>
+          <t>NextActionRequired</t>
+        </is>
+      </c>
+      <c r="AK1" s="32" t="inlineStr">
+        <is>
+          <t>NextActionDeadline</t>
+        </is>
+      </c>
+      <c r="AL1" s="32" t="inlineStr">
+        <is>
+          <t>LastReviewDate</t>
+        </is>
+      </c>
+      <c r="AM1" s="32" t="inlineStr">
+        <is>
+          <t>ReviewedBy</t>
+        </is>
+      </c>
+      <c r="AN1" s="32" t="inlineStr">
+        <is>
+          <t>ReviewNotes</t>
+        </is>
+      </c>
+      <c r="AO1" s="32" t="inlineStr">
+        <is>
+          <t>Escalated</t>
+        </is>
+      </c>
+      <c r="AP1" s="32" t="inlineStr">
+        <is>
+          <t>EscalatedTo</t>
+        </is>
+      </c>
+      <c r="AQ1" s="32" t="inlineStr">
+        <is>
+          <t>EscalationReason</t>
+        </is>
+      </c>
+      <c r="AR1" s="32" t="inlineStr">
+        <is>
+          <t>ColdCaseReviewDate</t>
+        </is>
+      </c>
+      <c r="AS1" s="32" t="inlineStr">
+        <is>
+          <t>ColdCaseReviewedBy</t>
+        </is>
+      </c>
+      <c r="AT1" s="32" t="inlineStr">
+        <is>
+          <t>ResolutionDate</t>
+        </is>
+      </c>
+      <c r="AU1" s="32" t="inlineStr">
+        <is>
+          <t>ResolutionSummary</t>
+        </is>
+      </c>
+      <c r="AV1" s="32" t="inlineStr">
+        <is>
+          <t>DaysOpen</t>
+        </is>
+      </c>
+      <c r="AW1" s="32" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="AX1" s="32" t="inlineStr">
+        <is>
+          <t>CreatedBy</t>
+        </is>
+      </c>
+      <c r="AY1" s="32" t="inlineStr">
+        <is>
+          <t>CreatedDate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="33">
+        <f>IF(C2="","","CR-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B2" s="33" t="n"/>
+      <c r="C2" s="33" t="n"/>
+      <c r="D2" s="33" t="n"/>
+      <c r="E2" s="33" t="n"/>
+      <c r="F2" s="33" t="n"/>
+      <c r="G2" s="33" t="n"/>
+      <c r="H2" s="33" t="n"/>
+      <c r="I2" s="33" t="n"/>
+      <c r="J2" s="33" t="n"/>
+      <c r="K2" s="33" t="n"/>
+      <c r="L2" s="33" t="n"/>
+      <c r="M2" s="33" t="n"/>
+      <c r="N2" s="33" t="n"/>
+      <c r="O2" s="33" t="n"/>
+      <c r="P2" s="33" t="n"/>
+      <c r="Q2" s="33" t="n"/>
+      <c r="R2" s="33" t="n"/>
+      <c r="S2" s="33" t="n"/>
+      <c r="T2" s="33" t="n"/>
+      <c r="U2" s="33" t="n"/>
+      <c r="V2" s="33" t="n"/>
+      <c r="W2" s="33" t="n"/>
+      <c r="X2" s="33" t="n"/>
+      <c r="Y2" s="33" t="n"/>
+      <c r="Z2" s="33" t="n"/>
+      <c r="AA2" s="33" t="n"/>
+      <c r="AB2" s="33" t="n"/>
+      <c r="AC2" s="33" t="n"/>
+      <c r="AD2" s="33" t="n"/>
+      <c r="AE2" s="33" t="n"/>
+      <c r="AF2" s="33" t="n"/>
+      <c r="AG2" s="33" t="n"/>
+      <c r="AH2" s="35">
+        <f>IF(C2="","",((Z2="Yes")+(AA2="Yes")+(AB2="Yes")+(AC2="Yes")+(AD2="Yes")+(AE2="Yes")+(AF2="Yes")+(AG2="Yes")+(AH2="Yes"))/9)</f>
+        <v/>
+      </c>
+      <c r="AI2" s="33" t="n"/>
+      <c r="AJ2" s="33" t="n"/>
+      <c r="AK2" s="33" t="n"/>
+      <c r="AL2" s="33" t="n"/>
+      <c r="AM2" s="33" t="n"/>
+      <c r="AN2" s="33" t="n"/>
+      <c r="AO2" s="33" t="n"/>
+      <c r="AP2" s="33" t="n"/>
+      <c r="AQ2" s="33" t="n"/>
+      <c r="AR2" s="33" t="n"/>
+      <c r="AS2" s="33" t="n"/>
+      <c r="AT2" s="33" t="n"/>
+      <c r="AU2" s="33" t="n"/>
+      <c r="AV2" s="33">
+        <f>IF(C2="","",IF(ISBLANK(AR2),TODAY()-C2,AR2-C2))</f>
+        <v/>
+      </c>
+      <c r="AW2" s="33" t="n"/>
+      <c r="AX2" s="33" t="n"/>
+      <c r="AY2" s="33" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="33">
+        <f>IF(C3="","","CR-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B3" s="33" t="n"/>
+      <c r="C3" s="33" t="n"/>
+      <c r="D3" s="33" t="n"/>
+      <c r="E3" s="33" t="n"/>
+      <c r="F3" s="33" t="n"/>
+      <c r="G3" s="33" t="n"/>
+      <c r="H3" s="33" t="n"/>
+      <c r="I3" s="33" t="n"/>
+      <c r="J3" s="33" t="n"/>
+      <c r="K3" s="33" t="n"/>
+      <c r="L3" s="33" t="n"/>
+      <c r="M3" s="33" t="n"/>
+      <c r="N3" s="33" t="n"/>
+      <c r="O3" s="33" t="n"/>
+      <c r="P3" s="33" t="n"/>
+      <c r="Q3" s="33" t="n"/>
+      <c r="R3" s="33" t="n"/>
+      <c r="S3" s="33" t="n"/>
+      <c r="T3" s="33" t="n"/>
+      <c r="U3" s="33" t="n"/>
+      <c r="V3" s="33" t="n"/>
+      <c r="W3" s="33" t="n"/>
+      <c r="X3" s="33" t="n"/>
+      <c r="Y3" s="33" t="n"/>
+      <c r="Z3" s="33" t="n"/>
+      <c r="AA3" s="33" t="n"/>
+      <c r="AB3" s="33" t="n"/>
+      <c r="AC3" s="33" t="n"/>
+      <c r="AD3" s="33" t="n"/>
+      <c r="AE3" s="33" t="n"/>
+      <c r="AF3" s="33" t="n"/>
+      <c r="AG3" s="33" t="n"/>
+      <c r="AH3" s="35">
+        <f>IF(C3="","",((Z3="Yes")+(AA3="Yes")+(AB3="Yes")+(AC3="Yes")+(AD3="Yes")+(AE3="Yes")+(AF3="Yes")+(AG3="Yes")+(AH3="Yes"))/9)</f>
+        <v/>
+      </c>
+      <c r="AI3" s="33" t="n"/>
+      <c r="AJ3" s="33" t="n"/>
+      <c r="AK3" s="33" t="n"/>
+      <c r="AL3" s="33" t="n"/>
+      <c r="AM3" s="33" t="n"/>
+      <c r="AN3" s="33" t="n"/>
+      <c r="AO3" s="33" t="n"/>
+      <c r="AP3" s="33" t="n"/>
+      <c r="AQ3" s="33" t="n"/>
+      <c r="AR3" s="33" t="n"/>
+      <c r="AS3" s="33" t="n"/>
+      <c r="AT3" s="33" t="n"/>
+      <c r="AU3" s="33" t="n"/>
+      <c r="AV3" s="33">
+        <f>IF(C3="","",IF(ISBLANK(AR3),TODAY()-C3,AR3-C3))</f>
+        <v/>
+      </c>
+      <c r="AW3" s="33" t="n"/>
+      <c r="AX3" s="33" t="n"/>
+      <c r="AY3" s="33" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="33">
+        <f>IF(C4="","","CR-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B4" s="33" t="n"/>
+      <c r="C4" s="33" t="n"/>
+      <c r="D4" s="33" t="n"/>
+      <c r="E4" s="33" t="n"/>
+      <c r="F4" s="33" t="n"/>
+      <c r="G4" s="33" t="n"/>
+      <c r="H4" s="33" t="n"/>
+      <c r="I4" s="33" t="n"/>
+      <c r="J4" s="33" t="n"/>
+      <c r="K4" s="33" t="n"/>
+      <c r="L4" s="33" t="n"/>
+      <c r="M4" s="33" t="n"/>
+      <c r="N4" s="33" t="n"/>
+      <c r="O4" s="33" t="n"/>
+      <c r="P4" s="33" t="n"/>
+      <c r="Q4" s="33" t="n"/>
+      <c r="R4" s="33" t="n"/>
+      <c r="S4" s="33" t="n"/>
+      <c r="T4" s="33" t="n"/>
+      <c r="U4" s="33" t="n"/>
+      <c r="V4" s="33" t="n"/>
+      <c r="W4" s="33" t="n"/>
+      <c r="X4" s="33" t="n"/>
+      <c r="Y4" s="33" t="n"/>
+      <c r="Z4" s="33" t="n"/>
+      <c r="AA4" s="33" t="n"/>
+      <c r="AB4" s="33" t="n"/>
+      <c r="AC4" s="33" t="n"/>
+      <c r="AD4" s="33" t="n"/>
+      <c r="AE4" s="33" t="n"/>
+      <c r="AF4" s="33" t="n"/>
+      <c r="AG4" s="33" t="n"/>
+      <c r="AH4" s="35">
+        <f>IF(C4="","",((Z4="Yes")+(AA4="Yes")+(AB4="Yes")+(AC4="Yes")+(AD4="Yes")+(AE4="Yes")+(AF4="Yes")+(AG4="Yes")+(AH4="Yes"))/9)</f>
+        <v/>
+      </c>
+      <c r="AI4" s="33" t="n"/>
+      <c r="AJ4" s="33" t="n"/>
+      <c r="AK4" s="33" t="n"/>
+      <c r="AL4" s="33" t="n"/>
+      <c r="AM4" s="33" t="n"/>
+      <c r="AN4" s="33" t="n"/>
+      <c r="AO4" s="33" t="n"/>
+      <c r="AP4" s="33" t="n"/>
+      <c r="AQ4" s="33" t="n"/>
+      <c r="AR4" s="33" t="n"/>
+      <c r="AS4" s="33" t="n"/>
+      <c r="AT4" s="33" t="n"/>
+      <c r="AU4" s="33" t="n"/>
+      <c r="AV4" s="33">
+        <f>IF(C4="","",IF(ISBLANK(AR4),TODAY()-C4,AR4-C4))</f>
+        <v/>
+      </c>
+      <c r="AW4" s="33" t="n"/>
+      <c r="AX4" s="33" t="n"/>
+      <c r="AY4" s="33" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="33">
+        <f>IF(C5="","","CR-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B5" s="33" t="n"/>
+      <c r="C5" s="33" t="n"/>
+      <c r="D5" s="33" t="n"/>
+      <c r="E5" s="33" t="n"/>
+      <c r="F5" s="33" t="n"/>
+      <c r="G5" s="33" t="n"/>
+      <c r="H5" s="33" t="n"/>
+      <c r="I5" s="33" t="n"/>
+      <c r="J5" s="33" t="n"/>
+      <c r="K5" s="33" t="n"/>
+      <c r="L5" s="33" t="n"/>
+      <c r="M5" s="33" t="n"/>
+      <c r="N5" s="33" t="n"/>
+      <c r="O5" s="33" t="n"/>
+      <c r="P5" s="33" t="n"/>
+      <c r="Q5" s="33" t="n"/>
+      <c r="R5" s="33" t="n"/>
+      <c r="S5" s="33" t="n"/>
+      <c r="T5" s="33" t="n"/>
+      <c r="U5" s="33" t="n"/>
+      <c r="V5" s="33" t="n"/>
+      <c r="W5" s="33" t="n"/>
+      <c r="X5" s="33" t="n"/>
+      <c r="Y5" s="33" t="n"/>
+      <c r="Z5" s="33" t="n"/>
+      <c r="AA5" s="33" t="n"/>
+      <c r="AB5" s="33" t="n"/>
+      <c r="AC5" s="33" t="n"/>
+      <c r="AD5" s="33" t="n"/>
+      <c r="AE5" s="33" t="n"/>
+      <c r="AF5" s="33" t="n"/>
+      <c r="AG5" s="33" t="n"/>
+      <c r="AH5" s="35">
+        <f>IF(C5="","",((Z5="Yes")+(AA5="Yes")+(AB5="Yes")+(AC5="Yes")+(AD5="Yes")+(AE5="Yes")+(AF5="Yes")+(AG5="Yes")+(AH5="Yes"))/9)</f>
+        <v/>
+      </c>
+      <c r="AI5" s="33" t="n"/>
+      <c r="AJ5" s="33" t="n"/>
+      <c r="AK5" s="33" t="n"/>
+      <c r="AL5" s="33" t="n"/>
+      <c r="AM5" s="33" t="n"/>
+      <c r="AN5" s="33" t="n"/>
+      <c r="AO5" s="33" t="n"/>
+      <c r="AP5" s="33" t="n"/>
+      <c r="AQ5" s="33" t="n"/>
+      <c r="AR5" s="33" t="n"/>
+      <c r="AS5" s="33" t="n"/>
+      <c r="AT5" s="33" t="n"/>
+      <c r="AU5" s="33" t="n"/>
+      <c r="AV5" s="33">
+        <f>IF(C5="","",IF(ISBLANK(AR5),TODAY()-C5,AR5-C5))</f>
+        <v/>
+      </c>
+      <c r="AW5" s="33" t="n"/>
+      <c r="AX5" s="33" t="n"/>
+      <c r="AY5" s="33" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="33">
+        <f>IF(C6="","","CR-"&amp;TEXT(ROW()-1,"0000"))</f>
+        <v/>
+      </c>
+      <c r="B6" s="33" t="n"/>
+      <c r="C6" s="33" t="n"/>
+      <c r="D6" s="33" t="n"/>
+      <c r="E6" s="33" t="n"/>
+      <c r="F6" s="33" t="n"/>
+      <c r="G6" s="33" t="n"/>
+      <c r="H6" s="33" t="n"/>
+      <c r="I6" s="33" t="n"/>
+      <c r="J6" s="33" t="n"/>
+      <c r="K6" s="33" t="n"/>
+      <c r="L6" s="33" t="n"/>
+      <c r="M6" s="33" t="n"/>
+      <c r="N6" s="33" t="n"/>
+      <c r="O6" s="33" t="n"/>
+      <c r="P6" s="33" t="n"/>
+      <c r="Q6" s="33" t="n"/>
+      <c r="R6" s="33" t="n"/>
+      <c r="S6" s="33" t="n"/>
+      <c r="T6" s="33" t="n"/>
+      <c r="U6" s="33" t="n"/>
+      <c r="V6" s="33" t="n"/>
+      <c r="W6" s="33" t="n"/>
+      <c r="X6" s="33" t="n"/>
+      <c r="Y6" s="33" t="n"/>
+      <c r="Z6" s="33" t="n"/>
+      <c r="AA6" s="33" t="n"/>
+      <c r="AB6" s="33" t="n"/>
+      <c r="AC6" s="33" t="n"/>
+      <c r="AD6" s="33" t="n"/>
+      <c r="AE6" s="33" t="n"/>
+      <c r="AF6" s="33" t="n"/>
+      <c r="AG6" s="33" t="n"/>
+      <c r="AH6" s="35">
+        <f>IF(C6="","",((Z6="Yes")+(AA6="Yes")+(AB6="Yes")+(AC6="Yes")+(AD6="Yes")+(AE6="Yes")+(AF6="Yes")+(AG6="Yes")+(AH6="Yes"))/9)</f>
+        <v/>
+      </c>
+      <c r="AI6" s="33" t="n"/>
+      <c r="AJ6" s="33" t="n"/>
+      <c r="AK6" s="33" t="n"/>
+      <c r="AL6" s="33" t="n"/>
+      <c r="AM6" s="33" t="n"/>
+      <c r="AN6" s="33" t="n"/>
+      <c r="AO6" s="33" t="n"/>
+      <c r="AP6" s="33" t="n"/>
+      <c r="AQ6" s="33" t="n"/>
+      <c r="AR6" s="33" t="n"/>
+      <c r="AS6" s="33" t="n"/>
+      <c r="AT6" s="33" t="n"/>
+      <c r="AU6" s="33" t="n"/>
+      <c r="AV6" s="33">
+        <f>IF(C6="","",IF(ISBLANK(AR6),TODAY()-C6,AR6-C6))</f>
+        <v/>
+      </c>
+      <c r="AW6" s="33" t="n"/>
+      <c r="AX6" s="33" t="n"/>
+      <c r="AY6" s="33" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:AY1"/>
+  <conditionalFormatting sqref="F2:F1000">
+    <cfRule type="cellIs" priority="1" operator="beginsWith" dxfId="1">
+      <formula>"Open"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="beginsWith" dxfId="0">
+      <formula>"Cold Case"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="beginsWith" dxfId="3">
+      <formula>"Closed — Convicted"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E1000">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
+      <formula>"Critical"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="1">
+      <formula>"High"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AH2:AH1000">
+    <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="0">
+      <formula>0.33</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="between" dxfId="1">
+      <formula>0.33</formula>
+      <formula>0.66</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="greaterThanOrEqual" dxfId="3">
+      <formula>0.66</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL2:AL1000">
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="0">
+      <formula>"Yes"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK2:AK1000">
+    <cfRule type="expression" priority="10" dxfId="0">
+      <formula>=AND(AK2&lt;&gt;"",AK2&lt;TODAY())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="15">
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid" error="Select from dropdown" type="list">
+      <formula1>=Lookups!$X$2:$X$10</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid" error="Select from dropdown" type="list">
+      <formula1>=Lookups!$B$2:$B$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid" error="Select from dropdown" type="list">
+      <formula1>=Lookups!$Y$2:$Y$14</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid" error="Select from dropdown" type="list">
+      <formula1>=Lookups!$Z$2:$Z$15</formula1>
+    </dataValidation>
+    <dataValidation sqref="T2:T1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid" error="Select from dropdown" type="list">
+      <formula1>=Lookups!$P$2:$P$15</formula1>
+    </dataValidation>
+    <dataValidation sqref="Z2:Z1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid" error="Select from dropdown" type="list">
+      <formula1>=Lookups!$Q$2:$Q$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="AA2:AA1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid" error="Select from dropdown" type="list">
+      <formula1>=Lookups!$Q$2:$Q$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="AB2:AB1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid" error="Select from dropdown" type="list">
+      <formula1>=Lookups!$Q$2:$Q$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="AC2:AC1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid" error="Select from dropdown" type="list">
+      <formula1>=Lookups!$Q$2:$Q$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="AD2:AD1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid" error="Select from dropdown" type="list">
+      <formula1>=Lookups!$Q$2:$Q$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="AE2:AE1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid" error="Select from dropdown" type="list">
+      <formula1>=Lookups!$Q$2:$Q$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="AF2:AF1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid" error="Select from dropdown" type="list">
+      <formula1>=Lookups!$Q$2:$Q$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="AG2:AG1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid" error="Select from dropdown" type="list">
+      <formula1>=Lookups!$Q$2:$Q$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="AH2:AH1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid" error="Select from dropdown" type="list">
+      <formula1>=Lookups!$Q$2:$Q$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="AL2:AL1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid" error="Select from dropdown" type="list">
+      <formula1>=Lookups!$Q$2:$Q$3</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00538135"/>
@@ -1426,221 +2246,221 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>TransferID</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="32" t="inlineStr">
         <is>
           <t>ExhibitRef</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="32" t="inlineStr">
         <is>
           <t>ExhibitType</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="32" t="inlineStr">
         <is>
           <t>ExhibitDescription</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="32" t="inlineStr">
         <is>
           <t>LinkedCaseID</t>
         </is>
       </c>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" s="32" t="inlineStr">
         <is>
           <t>TransferDate</t>
         </is>
       </c>
-      <c r="G1" s="29" t="inlineStr">
+      <c r="G1" s="32" t="inlineStr">
         <is>
           <t>TransferTime</t>
         </is>
       </c>
-      <c r="H1" s="29" t="inlineStr">
+      <c r="H1" s="32" t="inlineStr">
         <is>
           <t>ReleasedBy</t>
         </is>
       </c>
-      <c r="I1" s="29" t="inlineStr">
+      <c r="I1" s="32" t="inlineStr">
         <is>
           <t>ReleasedByRank</t>
         </is>
       </c>
-      <c r="J1" s="29" t="inlineStr">
+      <c r="J1" s="32" t="inlineStr">
         <is>
           <t>ReceivedBy</t>
         </is>
       </c>
-      <c r="K1" s="29" t="inlineStr">
+      <c r="K1" s="32" t="inlineStr">
         <is>
           <t>ReceivedByRank</t>
         </is>
       </c>
-      <c r="L1" s="29" t="inlineStr">
+      <c r="L1" s="32" t="inlineStr">
         <is>
           <t>Location_From</t>
         </is>
       </c>
-      <c r="M1" s="29" t="inlineStr">
+      <c r="M1" s="32" t="inlineStr">
         <is>
           <t>Location_To</t>
         </is>
       </c>
-      <c r="N1" s="29" t="inlineStr">
+      <c r="N1" s="32" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
       </c>
-      <c r="O1" s="29" t="inlineStr">
+      <c r="O1" s="32" t="inlineStr">
         <is>
           <t>ForensicRecoveryBag</t>
         </is>
       </c>
-      <c r="P1" s="29" t="inlineStr">
+      <c r="P1" s="32" t="inlineStr">
         <is>
           <t>ConditionOnTransfer</t>
         </is>
       </c>
-      <c r="Q1" s="29" t="inlineStr">
+      <c r="Q1" s="32" t="inlineStr">
         <is>
           <t>SignedReceiptObtained</t>
         </is>
       </c>
-      <c r="R1" s="29" t="inlineStr">
+      <c r="R1" s="32" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="S1" s="29" t="inlineStr">
+      <c r="S1" s="32" t="inlineStr">
         <is>
           <t>CreatedDate</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30">
+      <c r="A2" s="33">
         <f>IF(F2="","","COC-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B2" s="30" t="n"/>
-      <c r="C2" s="30" t="n"/>
-      <c r="D2" s="30" t="n"/>
-      <c r="E2" s="30" t="n"/>
-      <c r="F2" s="30" t="n"/>
-      <c r="G2" s="30" t="n"/>
-      <c r="H2" s="30" t="n"/>
-      <c r="I2" s="30" t="n"/>
-      <c r="J2" s="30" t="n"/>
-      <c r="K2" s="30" t="n"/>
-      <c r="L2" s="30" t="n"/>
-      <c r="M2" s="30" t="n"/>
-      <c r="N2" s="30" t="n"/>
-      <c r="O2" s="30" t="n"/>
-      <c r="P2" s="30" t="n"/>
-      <c r="Q2" s="30" t="n"/>
-      <c r="R2" s="30" t="n"/>
-      <c r="S2" s="30" t="n"/>
+      <c r="B2" s="33" t="n"/>
+      <c r="C2" s="33" t="n"/>
+      <c r="D2" s="33" t="n"/>
+      <c r="E2" s="33" t="n"/>
+      <c r="F2" s="33" t="n"/>
+      <c r="G2" s="33" t="n"/>
+      <c r="H2" s="33" t="n"/>
+      <c r="I2" s="33" t="n"/>
+      <c r="J2" s="33" t="n"/>
+      <c r="K2" s="33" t="n"/>
+      <c r="L2" s="33" t="n"/>
+      <c r="M2" s="33" t="n"/>
+      <c r="N2" s="33" t="n"/>
+      <c r="O2" s="33" t="n"/>
+      <c r="P2" s="33" t="n"/>
+      <c r="Q2" s="33" t="n"/>
+      <c r="R2" s="33" t="n"/>
+      <c r="S2" s="33" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="30">
+      <c r="A3" s="33">
         <f>IF(F3="","","COC-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B3" s="30" t="n"/>
-      <c r="C3" s="30" t="n"/>
-      <c r="D3" s="30" t="n"/>
-      <c r="E3" s="30" t="n"/>
-      <c r="F3" s="30" t="n"/>
-      <c r="G3" s="30" t="n"/>
-      <c r="H3" s="30" t="n"/>
-      <c r="I3" s="30" t="n"/>
-      <c r="J3" s="30" t="n"/>
-      <c r="K3" s="30" t="n"/>
-      <c r="L3" s="30" t="n"/>
-      <c r="M3" s="30" t="n"/>
-      <c r="N3" s="30" t="n"/>
-      <c r="O3" s="30" t="n"/>
-      <c r="P3" s="30" t="n"/>
-      <c r="Q3" s="30" t="n"/>
-      <c r="R3" s="30" t="n"/>
-      <c r="S3" s="30" t="n"/>
+      <c r="B3" s="33" t="n"/>
+      <c r="C3" s="33" t="n"/>
+      <c r="D3" s="33" t="n"/>
+      <c r="E3" s="33" t="n"/>
+      <c r="F3" s="33" t="n"/>
+      <c r="G3" s="33" t="n"/>
+      <c r="H3" s="33" t="n"/>
+      <c r="I3" s="33" t="n"/>
+      <c r="J3" s="33" t="n"/>
+      <c r="K3" s="33" t="n"/>
+      <c r="L3" s="33" t="n"/>
+      <c r="M3" s="33" t="n"/>
+      <c r="N3" s="33" t="n"/>
+      <c r="O3" s="33" t="n"/>
+      <c r="P3" s="33" t="n"/>
+      <c r="Q3" s="33" t="n"/>
+      <c r="R3" s="33" t="n"/>
+      <c r="S3" s="33" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="30">
+      <c r="A4" s="33">
         <f>IF(F4="","","COC-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B4" s="30" t="n"/>
-      <c r="C4" s="30" t="n"/>
-      <c r="D4" s="30" t="n"/>
-      <c r="E4" s="30" t="n"/>
-      <c r="F4" s="30" t="n"/>
-      <c r="G4" s="30" t="n"/>
-      <c r="H4" s="30" t="n"/>
-      <c r="I4" s="30" t="n"/>
-      <c r="J4" s="30" t="n"/>
-      <c r="K4" s="30" t="n"/>
-      <c r="L4" s="30" t="n"/>
-      <c r="M4" s="30" t="n"/>
-      <c r="N4" s="30" t="n"/>
-      <c r="O4" s="30" t="n"/>
-      <c r="P4" s="30" t="n"/>
-      <c r="Q4" s="30" t="n"/>
-      <c r="R4" s="30" t="n"/>
-      <c r="S4" s="30" t="n"/>
+      <c r="B4" s="33" t="n"/>
+      <c r="C4" s="33" t="n"/>
+      <c r="D4" s="33" t="n"/>
+      <c r="E4" s="33" t="n"/>
+      <c r="F4" s="33" t="n"/>
+      <c r="G4" s="33" t="n"/>
+      <c r="H4" s="33" t="n"/>
+      <c r="I4" s="33" t="n"/>
+      <c r="J4" s="33" t="n"/>
+      <c r="K4" s="33" t="n"/>
+      <c r="L4" s="33" t="n"/>
+      <c r="M4" s="33" t="n"/>
+      <c r="N4" s="33" t="n"/>
+      <c r="O4" s="33" t="n"/>
+      <c r="P4" s="33" t="n"/>
+      <c r="Q4" s="33" t="n"/>
+      <c r="R4" s="33" t="n"/>
+      <c r="S4" s="33" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="30">
+      <c r="A5" s="33">
         <f>IF(F5="","","COC-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B5" s="30" t="n"/>
-      <c r="C5" s="30" t="n"/>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="30" t="n"/>
-      <c r="F5" s="30" t="n"/>
-      <c r="G5" s="30" t="n"/>
-      <c r="H5" s="30" t="n"/>
-      <c r="I5" s="30" t="n"/>
-      <c r="J5" s="30" t="n"/>
-      <c r="K5" s="30" t="n"/>
-      <c r="L5" s="30" t="n"/>
-      <c r="M5" s="30" t="n"/>
-      <c r="N5" s="30" t="n"/>
-      <c r="O5" s="30" t="n"/>
-      <c r="P5" s="30" t="n"/>
-      <c r="Q5" s="30" t="n"/>
-      <c r="R5" s="30" t="n"/>
-      <c r="S5" s="30" t="n"/>
+      <c r="B5" s="33" t="n"/>
+      <c r="C5" s="33" t="n"/>
+      <c r="D5" s="33" t="n"/>
+      <c r="E5" s="33" t="n"/>
+      <c r="F5" s="33" t="n"/>
+      <c r="G5" s="33" t="n"/>
+      <c r="H5" s="33" t="n"/>
+      <c r="I5" s="33" t="n"/>
+      <c r="J5" s="33" t="n"/>
+      <c r="K5" s="33" t="n"/>
+      <c r="L5" s="33" t="n"/>
+      <c r="M5" s="33" t="n"/>
+      <c r="N5" s="33" t="n"/>
+      <c r="O5" s="33" t="n"/>
+      <c r="P5" s="33" t="n"/>
+      <c r="Q5" s="33" t="n"/>
+      <c r="R5" s="33" t="n"/>
+      <c r="S5" s="33" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="30">
+      <c r="A6" s="33">
         <f>IF(F6="","","COC-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B6" s="30" t="n"/>
-      <c r="C6" s="30" t="n"/>
-      <c r="D6" s="30" t="n"/>
-      <c r="E6" s="30" t="n"/>
-      <c r="F6" s="30" t="n"/>
-      <c r="G6" s="30" t="n"/>
-      <c r="H6" s="30" t="n"/>
-      <c r="I6" s="30" t="n"/>
-      <c r="J6" s="30" t="n"/>
-      <c r="K6" s="30" t="n"/>
-      <c r="L6" s="30" t="n"/>
-      <c r="M6" s="30" t="n"/>
-      <c r="N6" s="30" t="n"/>
-      <c r="O6" s="30" t="n"/>
-      <c r="P6" s="30" t="n"/>
-      <c r="Q6" s="30" t="n"/>
-      <c r="R6" s="30" t="n"/>
-      <c r="S6" s="30" t="n"/>
+      <c r="B6" s="33" t="n"/>
+      <c r="C6" s="33" t="n"/>
+      <c r="D6" s="33" t="n"/>
+      <c r="E6" s="33" t="n"/>
+      <c r="F6" s="33" t="n"/>
+      <c r="G6" s="33" t="n"/>
+      <c r="H6" s="33" t="n"/>
+      <c r="I6" s="33" t="n"/>
+      <c r="J6" s="33" t="n"/>
+      <c r="K6" s="33" t="n"/>
+      <c r="L6" s="33" t="n"/>
+      <c r="M6" s="33" t="n"/>
+      <c r="N6" s="33" t="n"/>
+      <c r="O6" s="33" t="n"/>
+      <c r="P6" s="33" t="n"/>
+      <c r="Q6" s="33" t="n"/>
+      <c r="R6" s="33" t="n"/>
+      <c r="S6" s="33" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:S1"/>
@@ -1659,7 +2479,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007030A0"/>
@@ -1707,411 +2527,411 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>CaseFileID</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="32" t="inlineStr">
         <is>
           <t>LinkedOpsID</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="32" t="inlineStr">
         <is>
           <t>CaseType</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="32" t="inlineStr">
         <is>
           <t>PrimaryOffence</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="32" t="inlineStr">
         <is>
           <t>ActSection</t>
         </is>
       </c>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" s="32" t="inlineStr">
         <is>
           <t>InvestigatingOfficer</t>
         </is>
       </c>
-      <c r="G1" s="29" t="inlineStr">
+      <c r="G1" s="32" t="inlineStr">
         <is>
           <t>Supervisor</t>
         </is>
       </c>
-      <c r="H1" s="29" t="inlineStr">
+      <c r="H1" s="32" t="inlineStr">
         <is>
           <t>ArrestIDs</t>
         </is>
       </c>
-      <c r="I1" s="29" t="inlineStr">
+      <c r="I1" s="32" t="inlineStr">
         <is>
           <t>FirearmSeizureIDs</t>
         </is>
       </c>
-      <c r="J1" s="29" t="inlineStr">
+      <c r="J1" s="32" t="inlineStr">
         <is>
           <t>NarcoticSeizureIDs</t>
         </is>
       </c>
-      <c r="K1" s="29" t="inlineStr">
+      <c r="K1" s="32" t="inlineStr">
         <is>
           <t>OtherSeizureIDs</t>
         </is>
       </c>
-      <c r="L1" s="29" t="inlineStr">
+      <c r="L1" s="32" t="inlineStr">
         <is>
           <t>StatementsComplete</t>
         </is>
       </c>
-      <c r="M1" s="29" t="inlineStr">
+      <c r="M1" s="32" t="inlineStr">
         <is>
           <t>ForensicCertObtained</t>
         </is>
       </c>
-      <c r="N1" s="29" t="inlineStr">
+      <c r="N1" s="32" t="inlineStr">
         <is>
           <t>BallisticCertObtained</t>
         </is>
       </c>
-      <c r="O1" s="29" t="inlineStr">
+      <c r="O1" s="32" t="inlineStr">
         <is>
           <t>PostMortemObtained</t>
         </is>
       </c>
-      <c r="P1" s="29" t="inlineStr">
+      <c r="P1" s="32" t="inlineStr">
         <is>
           <t>DisclosureComplete</t>
         </is>
       </c>
-      <c r="Q1" s="29" t="inlineStr">
+      <c r="Q1" s="32" t="inlineStr">
         <is>
           <t>FileInTriplicate</t>
         </is>
       </c>
-      <c r="R1" s="29" t="inlineStr">
+      <c r="R1" s="32" t="inlineStr">
         <is>
           <t>DPPSubmitDate</t>
         </is>
       </c>
-      <c r="S1" s="29" t="inlineStr">
+      <c r="S1" s="32" t="inlineStr">
         <is>
           <t>DPPStatus</t>
         </is>
       </c>
-      <c r="T1" s="29" t="inlineStr">
+      <c r="T1" s="32" t="inlineStr">
         <is>
           <t>CrownCounselAssigned</t>
         </is>
       </c>
-      <c r="U1" s="29" t="inlineStr">
+      <c r="U1" s="32" t="inlineStr">
         <is>
           <t>DPPRulingDate</t>
         </is>
       </c>
-      <c r="V1" s="29" t="inlineStr">
+      <c r="V1" s="32" t="inlineStr">
         <is>
           <t>DPPRuling</t>
         </is>
       </c>
-      <c r="W1" s="29" t="inlineStr">
+      <c r="W1" s="32" t="inlineStr">
         <is>
           <t>ChargesApproved</t>
         </is>
       </c>
-      <c r="X1" s="29" t="inlineStr">
+      <c r="X1" s="32" t="inlineStr">
         <is>
           <t>CourtType</t>
         </is>
       </c>
-      <c r="Y1" s="29" t="inlineStr">
+      <c r="Y1" s="32" t="inlineStr">
         <is>
           <t>FirstHearingDate</t>
         </is>
       </c>
-      <c r="Z1" s="29" t="inlineStr">
+      <c r="Z1" s="32" t="inlineStr">
         <is>
           <t>NextHearingDate</t>
         </is>
       </c>
-      <c r="AA1" s="29" t="inlineStr">
+      <c r="AA1" s="32" t="inlineStr">
         <is>
           <t>CourtOutcome</t>
         </is>
       </c>
-      <c r="AB1" s="29" t="inlineStr">
+      <c r="AB1" s="32" t="inlineStr">
         <is>
           <t>SentenceIfConvicted</t>
         </is>
       </c>
-      <c r="AC1" s="29" t="inlineStr">
+      <c r="AC1" s="32" t="inlineStr">
         <is>
           <t>POCAStatus</t>
         </is>
       </c>
-      <c r="AD1" s="29" t="inlineStr">
+      <c r="AD1" s="32" t="inlineStr">
         <is>
           <t>POCAAmount_JMD</t>
         </is>
       </c>
-      <c r="AE1" s="29" t="inlineStr">
+      <c r="AE1" s="32" t="inlineStr">
         <is>
           <t>DaysInPipeline</t>
         </is>
       </c>
-      <c r="AF1" s="29" t="inlineStr">
+      <c r="AF1" s="32" t="inlineStr">
         <is>
           <t>FileCompletenessScore</t>
         </is>
       </c>
-      <c r="AG1" s="29" t="inlineStr">
+      <c r="AG1" s="32" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="AH1" s="29" t="inlineStr">
+      <c r="AH1" s="32" t="inlineStr">
         <is>
           <t>CreatedBy</t>
         </is>
       </c>
-      <c r="AI1" s="29" t="inlineStr">
+      <c r="AI1" s="32" t="inlineStr">
         <is>
           <t>CreatedDate</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30">
+      <c r="A2" s="33">
         <f>IF(D2="","","CF-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B2" s="30" t="n"/>
-      <c r="C2" s="30" t="n"/>
-      <c r="D2" s="30" t="n"/>
-      <c r="E2" s="30" t="n"/>
-      <c r="F2" s="30" t="n"/>
-      <c r="G2" s="30" t="n"/>
-      <c r="H2" s="30" t="n"/>
-      <c r="I2" s="30" t="n"/>
-      <c r="J2" s="30" t="n"/>
-      <c r="K2" s="30" t="n"/>
-      <c r="L2" s="30" t="n"/>
-      <c r="M2" s="30" t="n"/>
-      <c r="N2" s="30" t="n"/>
-      <c r="O2" s="30" t="n"/>
-      <c r="P2" s="30" t="n"/>
-      <c r="Q2" s="30" t="n"/>
-      <c r="R2" s="30" t="n"/>
-      <c r="S2" s="30" t="n"/>
-      <c r="T2" s="30" t="n"/>
-      <c r="U2" s="30" t="n"/>
-      <c r="V2" s="30" t="n"/>
-      <c r="W2" s="30" t="n"/>
-      <c r="X2" s="30" t="n"/>
-      <c r="Y2" s="30" t="n"/>
-      <c r="Z2" s="30" t="n"/>
-      <c r="AA2" s="30" t="n"/>
-      <c r="AB2" s="30" t="n"/>
-      <c r="AC2" s="30" t="n"/>
-      <c r="AD2" s="30" t="n"/>
-      <c r="AE2" s="30">
+      <c r="B2" s="33" t="n"/>
+      <c r="C2" s="33" t="n"/>
+      <c r="D2" s="33" t="n"/>
+      <c r="E2" s="33" t="n"/>
+      <c r="F2" s="33" t="n"/>
+      <c r="G2" s="33" t="n"/>
+      <c r="H2" s="33" t="n"/>
+      <c r="I2" s="33" t="n"/>
+      <c r="J2" s="33" t="n"/>
+      <c r="K2" s="33" t="n"/>
+      <c r="L2" s="33" t="n"/>
+      <c r="M2" s="33" t="n"/>
+      <c r="N2" s="33" t="n"/>
+      <c r="O2" s="33" t="n"/>
+      <c r="P2" s="33" t="n"/>
+      <c r="Q2" s="33" t="n"/>
+      <c r="R2" s="33" t="n"/>
+      <c r="S2" s="33" t="n"/>
+      <c r="T2" s="33" t="n"/>
+      <c r="U2" s="33" t="n"/>
+      <c r="V2" s="33" t="n"/>
+      <c r="W2" s="33" t="n"/>
+      <c r="X2" s="33" t="n"/>
+      <c r="Y2" s="33" t="n"/>
+      <c r="Z2" s="33" t="n"/>
+      <c r="AA2" s="33" t="n"/>
+      <c r="AB2" s="33" t="n"/>
+      <c r="AC2" s="33" t="n"/>
+      <c r="AD2" s="33" t="n"/>
+      <c r="AE2" s="33">
         <f>IF(R2="","",TODAY()-R2)</f>
         <v/>
       </c>
-      <c r="AF2" s="32">
+      <c r="AF2" s="35">
         <f>IF(D2="","",((L2="Yes")+(M2="Yes")+(N2="Yes")+(O2="Yes")+(P2="Yes")+(Q2="Yes"))/6)</f>
         <v/>
       </c>
-      <c r="AG2" s="30" t="n"/>
-      <c r="AH2" s="30" t="n"/>
-      <c r="AI2" s="30" t="n"/>
+      <c r="AG2" s="33" t="n"/>
+      <c r="AH2" s="33" t="n"/>
+      <c r="AI2" s="33" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="30">
+      <c r="A3" s="33">
         <f>IF(D3="","","CF-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B3" s="30" t="n"/>
-      <c r="C3" s="30" t="n"/>
-      <c r="D3" s="30" t="n"/>
-      <c r="E3" s="30" t="n"/>
-      <c r="F3" s="30" t="n"/>
-      <c r="G3" s="30" t="n"/>
-      <c r="H3" s="30" t="n"/>
-      <c r="I3" s="30" t="n"/>
-      <c r="J3" s="30" t="n"/>
-      <c r="K3" s="30" t="n"/>
-      <c r="L3" s="30" t="n"/>
-      <c r="M3" s="30" t="n"/>
-      <c r="N3" s="30" t="n"/>
-      <c r="O3" s="30" t="n"/>
-      <c r="P3" s="30" t="n"/>
-      <c r="Q3" s="30" t="n"/>
-      <c r="R3" s="30" t="n"/>
-      <c r="S3" s="30" t="n"/>
-      <c r="T3" s="30" t="n"/>
-      <c r="U3" s="30" t="n"/>
-      <c r="V3" s="30" t="n"/>
-      <c r="W3" s="30" t="n"/>
-      <c r="X3" s="30" t="n"/>
-      <c r="Y3" s="30" t="n"/>
-      <c r="Z3" s="30" t="n"/>
-      <c r="AA3" s="30" t="n"/>
-      <c r="AB3" s="30" t="n"/>
-      <c r="AC3" s="30" t="n"/>
-      <c r="AD3" s="30" t="n"/>
-      <c r="AE3" s="30">
+      <c r="B3" s="33" t="n"/>
+      <c r="C3" s="33" t="n"/>
+      <c r="D3" s="33" t="n"/>
+      <c r="E3" s="33" t="n"/>
+      <c r="F3" s="33" t="n"/>
+      <c r="G3" s="33" t="n"/>
+      <c r="H3" s="33" t="n"/>
+      <c r="I3" s="33" t="n"/>
+      <c r="J3" s="33" t="n"/>
+      <c r="K3" s="33" t="n"/>
+      <c r="L3" s="33" t="n"/>
+      <c r="M3" s="33" t="n"/>
+      <c r="N3" s="33" t="n"/>
+      <c r="O3" s="33" t="n"/>
+      <c r="P3" s="33" t="n"/>
+      <c r="Q3" s="33" t="n"/>
+      <c r="R3" s="33" t="n"/>
+      <c r="S3" s="33" t="n"/>
+      <c r="T3" s="33" t="n"/>
+      <c r="U3" s="33" t="n"/>
+      <c r="V3" s="33" t="n"/>
+      <c r="W3" s="33" t="n"/>
+      <c r="X3" s="33" t="n"/>
+      <c r="Y3" s="33" t="n"/>
+      <c r="Z3" s="33" t="n"/>
+      <c r="AA3" s="33" t="n"/>
+      <c r="AB3" s="33" t="n"/>
+      <c r="AC3" s="33" t="n"/>
+      <c r="AD3" s="33" t="n"/>
+      <c r="AE3" s="33">
         <f>IF(R3="","",TODAY()-R3)</f>
         <v/>
       </c>
-      <c r="AF3" s="32">
+      <c r="AF3" s="35">
         <f>IF(D3="","",((L3="Yes")+(M3="Yes")+(N3="Yes")+(O3="Yes")+(P3="Yes")+(Q3="Yes"))/6)</f>
         <v/>
       </c>
-      <c r="AG3" s="30" t="n"/>
-      <c r="AH3" s="30" t="n"/>
-      <c r="AI3" s="30" t="n"/>
+      <c r="AG3" s="33" t="n"/>
+      <c r="AH3" s="33" t="n"/>
+      <c r="AI3" s="33" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="30">
+      <c r="A4" s="33">
         <f>IF(D4="","","CF-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B4" s="30" t="n"/>
-      <c r="C4" s="30" t="n"/>
-      <c r="D4" s="30" t="n"/>
-      <c r="E4" s="30" t="n"/>
-      <c r="F4" s="30" t="n"/>
-      <c r="G4" s="30" t="n"/>
-      <c r="H4" s="30" t="n"/>
-      <c r="I4" s="30" t="n"/>
-      <c r="J4" s="30" t="n"/>
-      <c r="K4" s="30" t="n"/>
-      <c r="L4" s="30" t="n"/>
-      <c r="M4" s="30" t="n"/>
-      <c r="N4" s="30" t="n"/>
-      <c r="O4" s="30" t="n"/>
-      <c r="P4" s="30" t="n"/>
-      <c r="Q4" s="30" t="n"/>
-      <c r="R4" s="30" t="n"/>
-      <c r="S4" s="30" t="n"/>
-      <c r="T4" s="30" t="n"/>
-      <c r="U4" s="30" t="n"/>
-      <c r="V4" s="30" t="n"/>
-      <c r="W4" s="30" t="n"/>
-      <c r="X4" s="30" t="n"/>
-      <c r="Y4" s="30" t="n"/>
-      <c r="Z4" s="30" t="n"/>
-      <c r="AA4" s="30" t="n"/>
-      <c r="AB4" s="30" t="n"/>
-      <c r="AC4" s="30" t="n"/>
-      <c r="AD4" s="30" t="n"/>
-      <c r="AE4" s="30">
+      <c r="B4" s="33" t="n"/>
+      <c r="C4" s="33" t="n"/>
+      <c r="D4" s="33" t="n"/>
+      <c r="E4" s="33" t="n"/>
+      <c r="F4" s="33" t="n"/>
+      <c r="G4" s="33" t="n"/>
+      <c r="H4" s="33" t="n"/>
+      <c r="I4" s="33" t="n"/>
+      <c r="J4" s="33" t="n"/>
+      <c r="K4" s="33" t="n"/>
+      <c r="L4" s="33" t="n"/>
+      <c r="M4" s="33" t="n"/>
+      <c r="N4" s="33" t="n"/>
+      <c r="O4" s="33" t="n"/>
+      <c r="P4" s="33" t="n"/>
+      <c r="Q4" s="33" t="n"/>
+      <c r="R4" s="33" t="n"/>
+      <c r="S4" s="33" t="n"/>
+      <c r="T4" s="33" t="n"/>
+      <c r="U4" s="33" t="n"/>
+      <c r="V4" s="33" t="n"/>
+      <c r="W4" s="33" t="n"/>
+      <c r="X4" s="33" t="n"/>
+      <c r="Y4" s="33" t="n"/>
+      <c r="Z4" s="33" t="n"/>
+      <c r="AA4" s="33" t="n"/>
+      <c r="AB4" s="33" t="n"/>
+      <c r="AC4" s="33" t="n"/>
+      <c r="AD4" s="33" t="n"/>
+      <c r="AE4" s="33">
         <f>IF(R4="","",TODAY()-R4)</f>
         <v/>
       </c>
-      <c r="AF4" s="32">
+      <c r="AF4" s="35">
         <f>IF(D4="","",((L4="Yes")+(M4="Yes")+(N4="Yes")+(O4="Yes")+(P4="Yes")+(Q4="Yes"))/6)</f>
         <v/>
       </c>
-      <c r="AG4" s="30" t="n"/>
-      <c r="AH4" s="30" t="n"/>
-      <c r="AI4" s="30" t="n"/>
+      <c r="AG4" s="33" t="n"/>
+      <c r="AH4" s="33" t="n"/>
+      <c r="AI4" s="33" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="30">
+      <c r="A5" s="33">
         <f>IF(D5="","","CF-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B5" s="30" t="n"/>
-      <c r="C5" s="30" t="n"/>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="30" t="n"/>
-      <c r="F5" s="30" t="n"/>
-      <c r="G5" s="30" t="n"/>
-      <c r="H5" s="30" t="n"/>
-      <c r="I5" s="30" t="n"/>
-      <c r="J5" s="30" t="n"/>
-      <c r="K5" s="30" t="n"/>
-      <c r="L5" s="30" t="n"/>
-      <c r="M5" s="30" t="n"/>
-      <c r="N5" s="30" t="n"/>
-      <c r="O5" s="30" t="n"/>
-      <c r="P5" s="30" t="n"/>
-      <c r="Q5" s="30" t="n"/>
-      <c r="R5" s="30" t="n"/>
-      <c r="S5" s="30" t="n"/>
-      <c r="T5" s="30" t="n"/>
-      <c r="U5" s="30" t="n"/>
-      <c r="V5" s="30" t="n"/>
-      <c r="W5" s="30" t="n"/>
-      <c r="X5" s="30" t="n"/>
-      <c r="Y5" s="30" t="n"/>
-      <c r="Z5" s="30" t="n"/>
-      <c r="AA5" s="30" t="n"/>
-      <c r="AB5" s="30" t="n"/>
-      <c r="AC5" s="30" t="n"/>
-      <c r="AD5" s="30" t="n"/>
-      <c r="AE5" s="30">
+      <c r="B5" s="33" t="n"/>
+      <c r="C5" s="33" t="n"/>
+      <c r="D5" s="33" t="n"/>
+      <c r="E5" s="33" t="n"/>
+      <c r="F5" s="33" t="n"/>
+      <c r="G5" s="33" t="n"/>
+      <c r="H5" s="33" t="n"/>
+      <c r="I5" s="33" t="n"/>
+      <c r="J5" s="33" t="n"/>
+      <c r="K5" s="33" t="n"/>
+      <c r="L5" s="33" t="n"/>
+      <c r="M5" s="33" t="n"/>
+      <c r="N5" s="33" t="n"/>
+      <c r="O5" s="33" t="n"/>
+      <c r="P5" s="33" t="n"/>
+      <c r="Q5" s="33" t="n"/>
+      <c r="R5" s="33" t="n"/>
+      <c r="S5" s="33" t="n"/>
+      <c r="T5" s="33" t="n"/>
+      <c r="U5" s="33" t="n"/>
+      <c r="V5" s="33" t="n"/>
+      <c r="W5" s="33" t="n"/>
+      <c r="X5" s="33" t="n"/>
+      <c r="Y5" s="33" t="n"/>
+      <c r="Z5" s="33" t="n"/>
+      <c r="AA5" s="33" t="n"/>
+      <c r="AB5" s="33" t="n"/>
+      <c r="AC5" s="33" t="n"/>
+      <c r="AD5" s="33" t="n"/>
+      <c r="AE5" s="33">
         <f>IF(R5="","",TODAY()-R5)</f>
         <v/>
       </c>
-      <c r="AF5" s="32">
+      <c r="AF5" s="35">
         <f>IF(D5="","",((L5="Yes")+(M5="Yes")+(N5="Yes")+(O5="Yes")+(P5="Yes")+(Q5="Yes"))/6)</f>
         <v/>
       </c>
-      <c r="AG5" s="30" t="n"/>
-      <c r="AH5" s="30" t="n"/>
-      <c r="AI5" s="30" t="n"/>
+      <c r="AG5" s="33" t="n"/>
+      <c r="AH5" s="33" t="n"/>
+      <c r="AI5" s="33" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="30">
+      <c r="A6" s="33">
         <f>IF(D6="","","CF-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B6" s="30" t="n"/>
-      <c r="C6" s="30" t="n"/>
-      <c r="D6" s="30" t="n"/>
-      <c r="E6" s="30" t="n"/>
-      <c r="F6" s="30" t="n"/>
-      <c r="G6" s="30" t="n"/>
-      <c r="H6" s="30" t="n"/>
-      <c r="I6" s="30" t="n"/>
-      <c r="J6" s="30" t="n"/>
-      <c r="K6" s="30" t="n"/>
-      <c r="L6" s="30" t="n"/>
-      <c r="M6" s="30" t="n"/>
-      <c r="N6" s="30" t="n"/>
-      <c r="O6" s="30" t="n"/>
-      <c r="P6" s="30" t="n"/>
-      <c r="Q6" s="30" t="n"/>
-      <c r="R6" s="30" t="n"/>
-      <c r="S6" s="30" t="n"/>
-      <c r="T6" s="30" t="n"/>
-      <c r="U6" s="30" t="n"/>
-      <c r="V6" s="30" t="n"/>
-      <c r="W6" s="30" t="n"/>
-      <c r="X6" s="30" t="n"/>
-      <c r="Y6" s="30" t="n"/>
-      <c r="Z6" s="30" t="n"/>
-      <c r="AA6" s="30" t="n"/>
-      <c r="AB6" s="30" t="n"/>
-      <c r="AC6" s="30" t="n"/>
-      <c r="AD6" s="30" t="n"/>
-      <c r="AE6" s="30">
+      <c r="B6" s="33" t="n"/>
+      <c r="C6" s="33" t="n"/>
+      <c r="D6" s="33" t="n"/>
+      <c r="E6" s="33" t="n"/>
+      <c r="F6" s="33" t="n"/>
+      <c r="G6" s="33" t="n"/>
+      <c r="H6" s="33" t="n"/>
+      <c r="I6" s="33" t="n"/>
+      <c r="J6" s="33" t="n"/>
+      <c r="K6" s="33" t="n"/>
+      <c r="L6" s="33" t="n"/>
+      <c r="M6" s="33" t="n"/>
+      <c r="N6" s="33" t="n"/>
+      <c r="O6" s="33" t="n"/>
+      <c r="P6" s="33" t="n"/>
+      <c r="Q6" s="33" t="n"/>
+      <c r="R6" s="33" t="n"/>
+      <c r="S6" s="33" t="n"/>
+      <c r="T6" s="33" t="n"/>
+      <c r="U6" s="33" t="n"/>
+      <c r="V6" s="33" t="n"/>
+      <c r="W6" s="33" t="n"/>
+      <c r="X6" s="33" t="n"/>
+      <c r="Y6" s="33" t="n"/>
+      <c r="Z6" s="33" t="n"/>
+      <c r="AA6" s="33" t="n"/>
+      <c r="AB6" s="33" t="n"/>
+      <c r="AC6" s="33" t="n"/>
+      <c r="AD6" s="33" t="n"/>
+      <c r="AE6" s="33">
         <f>IF(R6="","",TODAY()-R6)</f>
         <v/>
       </c>
-      <c r="AF6" s="32">
+      <c r="AF6" s="35">
         <f>IF(D6="","",((L6="Yes")+(M6="Yes")+(N6="Yes")+(O6="Yes")+(P6="Yes")+(Q6="Yes"))/6)</f>
         <v/>
       </c>
-      <c r="AG6" s="30" t="n"/>
-      <c r="AH6" s="30" t="n"/>
-      <c r="AI6" s="30" t="n"/>
+      <c r="AG6" s="33" t="n"/>
+      <c r="AH6" s="33" t="n"/>
+      <c r="AI6" s="33" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AI1"/>
@@ -2148,7 +2968,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007030A0"/>
@@ -2183,251 +3003,251 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>WitnessID</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="32" t="inlineStr">
         <is>
           <t>LinkedCaseFileID</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="32" t="inlineStr">
         <is>
           <t>WitnessName</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="32" t="inlineStr">
         <is>
           <t>ContactNumber</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="32" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" s="32" t="inlineStr">
         <is>
           <t>Parish</t>
         </is>
       </c>
-      <c r="G1" s="29" t="inlineStr">
+      <c r="G1" s="32" t="inlineStr">
         <is>
           <t>WitnessType</t>
         </is>
       </c>
-      <c r="H1" s="29" t="inlineStr">
+      <c r="H1" s="32" t="inlineStr">
         <is>
           <t>StatementTaken</t>
         </is>
       </c>
-      <c r="I1" s="29" t="inlineStr">
+      <c r="I1" s="32" t="inlineStr">
         <is>
           <t>StatementDate</t>
         </is>
       </c>
-      <c r="J1" s="29" t="inlineStr">
+      <c r="J1" s="32" t="inlineStr">
         <is>
           <t>CautionGiven</t>
         </is>
       </c>
-      <c r="K1" s="29" t="inlineStr">
+      <c r="K1" s="32" t="inlineStr">
         <is>
           <t>WillingToTestify</t>
         </is>
       </c>
-      <c r="L1" s="29" t="inlineStr">
+      <c r="L1" s="32" t="inlineStr">
         <is>
           <t>ProtectionRequired</t>
         </is>
       </c>
-      <c r="M1" s="29" t="inlineStr">
+      <c r="M1" s="32" t="inlineStr">
         <is>
           <t>WitnessProtectionReferred</t>
         </is>
       </c>
-      <c r="N1" s="29" t="inlineStr">
+      <c r="N1" s="32" t="inlineStr">
         <is>
           <t>SummonsIssued</t>
         </is>
       </c>
-      <c r="O1" s="29" t="inlineStr">
+      <c r="O1" s="32" t="inlineStr">
         <is>
           <t>SummonsServed</t>
         </is>
       </c>
-      <c r="P1" s="29" t="inlineStr">
+      <c r="P1" s="32" t="inlineStr">
         <is>
           <t>SummonsServedDate</t>
         </is>
       </c>
-      <c r="Q1" s="29" t="inlineStr">
+      <c r="Q1" s="32" t="inlineStr">
         <is>
           <t>Vulnerable</t>
         </is>
       </c>
-      <c r="R1" s="29" t="inlineStr">
+      <c r="R1" s="32" t="inlineStr">
         <is>
           <t>IntimidationReported</t>
         </is>
       </c>
-      <c r="S1" s="29" t="inlineStr">
+      <c r="S1" s="32" t="inlineStr">
         <is>
           <t>CourtAppearanceDate</t>
         </is>
       </c>
-      <c r="T1" s="29" t="inlineStr">
+      <c r="T1" s="32" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="U1" s="29" t="inlineStr">
+      <c r="U1" s="32" t="inlineStr">
         <is>
           <t>CreatedBy</t>
         </is>
       </c>
-      <c r="V1" s="29" t="inlineStr">
+      <c r="V1" s="32" t="inlineStr">
         <is>
           <t>CreatedDate</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30">
+      <c r="A2" s="33">
         <f>IF(C2="","","WIT-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B2" s="30" t="n"/>
-      <c r="C2" s="30" t="n"/>
-      <c r="D2" s="30" t="n"/>
-      <c r="E2" s="30" t="n"/>
-      <c r="F2" s="30" t="n"/>
-      <c r="G2" s="30" t="n"/>
-      <c r="H2" s="30" t="n"/>
-      <c r="I2" s="30" t="n"/>
-      <c r="J2" s="30" t="n"/>
-      <c r="K2" s="30" t="n"/>
-      <c r="L2" s="30" t="n"/>
-      <c r="M2" s="30" t="n"/>
-      <c r="N2" s="30" t="n"/>
-      <c r="O2" s="30" t="n"/>
-      <c r="P2" s="30" t="n"/>
-      <c r="Q2" s="30" t="n"/>
-      <c r="R2" s="30" t="n"/>
-      <c r="S2" s="30" t="n"/>
-      <c r="T2" s="30" t="n"/>
-      <c r="U2" s="30" t="n"/>
-      <c r="V2" s="30" t="n"/>
+      <c r="B2" s="33" t="n"/>
+      <c r="C2" s="33" t="n"/>
+      <c r="D2" s="33" t="n"/>
+      <c r="E2" s="33" t="n"/>
+      <c r="F2" s="33" t="n"/>
+      <c r="G2" s="33" t="n"/>
+      <c r="H2" s="33" t="n"/>
+      <c r="I2" s="33" t="n"/>
+      <c r="J2" s="33" t="n"/>
+      <c r="K2" s="33" t="n"/>
+      <c r="L2" s="33" t="n"/>
+      <c r="M2" s="33" t="n"/>
+      <c r="N2" s="33" t="n"/>
+      <c r="O2" s="33" t="n"/>
+      <c r="P2" s="33" t="n"/>
+      <c r="Q2" s="33" t="n"/>
+      <c r="R2" s="33" t="n"/>
+      <c r="S2" s="33" t="n"/>
+      <c r="T2" s="33" t="n"/>
+      <c r="U2" s="33" t="n"/>
+      <c r="V2" s="33" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="30">
+      <c r="A3" s="33">
         <f>IF(C3="","","WIT-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B3" s="30" t="n"/>
-      <c r="C3" s="30" t="n"/>
-      <c r="D3" s="30" t="n"/>
-      <c r="E3" s="30" t="n"/>
-      <c r="F3" s="30" t="n"/>
-      <c r="G3" s="30" t="n"/>
-      <c r="H3" s="30" t="n"/>
-      <c r="I3" s="30" t="n"/>
-      <c r="J3" s="30" t="n"/>
-      <c r="K3" s="30" t="n"/>
-      <c r="L3" s="30" t="n"/>
-      <c r="M3" s="30" t="n"/>
-      <c r="N3" s="30" t="n"/>
-      <c r="O3" s="30" t="n"/>
-      <c r="P3" s="30" t="n"/>
-      <c r="Q3" s="30" t="n"/>
-      <c r="R3" s="30" t="n"/>
-      <c r="S3" s="30" t="n"/>
-      <c r="T3" s="30" t="n"/>
-      <c r="U3" s="30" t="n"/>
-      <c r="V3" s="30" t="n"/>
+      <c r="B3" s="33" t="n"/>
+      <c r="C3" s="33" t="n"/>
+      <c r="D3" s="33" t="n"/>
+      <c r="E3" s="33" t="n"/>
+      <c r="F3" s="33" t="n"/>
+      <c r="G3" s="33" t="n"/>
+      <c r="H3" s="33" t="n"/>
+      <c r="I3" s="33" t="n"/>
+      <c r="J3" s="33" t="n"/>
+      <c r="K3" s="33" t="n"/>
+      <c r="L3" s="33" t="n"/>
+      <c r="M3" s="33" t="n"/>
+      <c r="N3" s="33" t="n"/>
+      <c r="O3" s="33" t="n"/>
+      <c r="P3" s="33" t="n"/>
+      <c r="Q3" s="33" t="n"/>
+      <c r="R3" s="33" t="n"/>
+      <c r="S3" s="33" t="n"/>
+      <c r="T3" s="33" t="n"/>
+      <c r="U3" s="33" t="n"/>
+      <c r="V3" s="33" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="30">
+      <c r="A4" s="33">
         <f>IF(C4="","","WIT-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B4" s="30" t="n"/>
-      <c r="C4" s="30" t="n"/>
-      <c r="D4" s="30" t="n"/>
-      <c r="E4" s="30" t="n"/>
-      <c r="F4" s="30" t="n"/>
-      <c r="G4" s="30" t="n"/>
-      <c r="H4" s="30" t="n"/>
-      <c r="I4" s="30" t="n"/>
-      <c r="J4" s="30" t="n"/>
-      <c r="K4" s="30" t="n"/>
-      <c r="L4" s="30" t="n"/>
-      <c r="M4" s="30" t="n"/>
-      <c r="N4" s="30" t="n"/>
-      <c r="O4" s="30" t="n"/>
-      <c r="P4" s="30" t="n"/>
-      <c r="Q4" s="30" t="n"/>
-      <c r="R4" s="30" t="n"/>
-      <c r="S4" s="30" t="n"/>
-      <c r="T4" s="30" t="n"/>
-      <c r="U4" s="30" t="n"/>
-      <c r="V4" s="30" t="n"/>
+      <c r="B4" s="33" t="n"/>
+      <c r="C4" s="33" t="n"/>
+      <c r="D4" s="33" t="n"/>
+      <c r="E4" s="33" t="n"/>
+      <c r="F4" s="33" t="n"/>
+      <c r="G4" s="33" t="n"/>
+      <c r="H4" s="33" t="n"/>
+      <c r="I4" s="33" t="n"/>
+      <c r="J4" s="33" t="n"/>
+      <c r="K4" s="33" t="n"/>
+      <c r="L4" s="33" t="n"/>
+      <c r="M4" s="33" t="n"/>
+      <c r="N4" s="33" t="n"/>
+      <c r="O4" s="33" t="n"/>
+      <c r="P4" s="33" t="n"/>
+      <c r="Q4" s="33" t="n"/>
+      <c r="R4" s="33" t="n"/>
+      <c r="S4" s="33" t="n"/>
+      <c r="T4" s="33" t="n"/>
+      <c r="U4" s="33" t="n"/>
+      <c r="V4" s="33" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="30">
+      <c r="A5" s="33">
         <f>IF(C5="","","WIT-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B5" s="30" t="n"/>
-      <c r="C5" s="30" t="n"/>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="30" t="n"/>
-      <c r="F5" s="30" t="n"/>
-      <c r="G5" s="30" t="n"/>
-      <c r="H5" s="30" t="n"/>
-      <c r="I5" s="30" t="n"/>
-      <c r="J5" s="30" t="n"/>
-      <c r="K5" s="30" t="n"/>
-      <c r="L5" s="30" t="n"/>
-      <c r="M5" s="30" t="n"/>
-      <c r="N5" s="30" t="n"/>
-      <c r="O5" s="30" t="n"/>
-      <c r="P5" s="30" t="n"/>
-      <c r="Q5" s="30" t="n"/>
-      <c r="R5" s="30" t="n"/>
-      <c r="S5" s="30" t="n"/>
-      <c r="T5" s="30" t="n"/>
-      <c r="U5" s="30" t="n"/>
-      <c r="V5" s="30" t="n"/>
+      <c r="B5" s="33" t="n"/>
+      <c r="C5" s="33" t="n"/>
+      <c r="D5" s="33" t="n"/>
+      <c r="E5" s="33" t="n"/>
+      <c r="F5" s="33" t="n"/>
+      <c r="G5" s="33" t="n"/>
+      <c r="H5" s="33" t="n"/>
+      <c r="I5" s="33" t="n"/>
+      <c r="J5" s="33" t="n"/>
+      <c r="K5" s="33" t="n"/>
+      <c r="L5" s="33" t="n"/>
+      <c r="M5" s="33" t="n"/>
+      <c r="N5" s="33" t="n"/>
+      <c r="O5" s="33" t="n"/>
+      <c r="P5" s="33" t="n"/>
+      <c r="Q5" s="33" t="n"/>
+      <c r="R5" s="33" t="n"/>
+      <c r="S5" s="33" t="n"/>
+      <c r="T5" s="33" t="n"/>
+      <c r="U5" s="33" t="n"/>
+      <c r="V5" s="33" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="30">
+      <c r="A6" s="33">
         <f>IF(C6="","","WIT-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B6" s="30" t="n"/>
-      <c r="C6" s="30" t="n"/>
-      <c r="D6" s="30" t="n"/>
-      <c r="E6" s="30" t="n"/>
-      <c r="F6" s="30" t="n"/>
-      <c r="G6" s="30" t="n"/>
-      <c r="H6" s="30" t="n"/>
-      <c r="I6" s="30" t="n"/>
-      <c r="J6" s="30" t="n"/>
-      <c r="K6" s="30" t="n"/>
-      <c r="L6" s="30" t="n"/>
-      <c r="M6" s="30" t="n"/>
-      <c r="N6" s="30" t="n"/>
-      <c r="O6" s="30" t="n"/>
-      <c r="P6" s="30" t="n"/>
-      <c r="Q6" s="30" t="n"/>
-      <c r="R6" s="30" t="n"/>
-      <c r="S6" s="30" t="n"/>
-      <c r="T6" s="30" t="n"/>
-      <c r="U6" s="30" t="n"/>
-      <c r="V6" s="30" t="n"/>
+      <c r="B6" s="33" t="n"/>
+      <c r="C6" s="33" t="n"/>
+      <c r="D6" s="33" t="n"/>
+      <c r="E6" s="33" t="n"/>
+      <c r="F6" s="33" t="n"/>
+      <c r="G6" s="33" t="n"/>
+      <c r="H6" s="33" t="n"/>
+      <c r="I6" s="33" t="n"/>
+      <c r="J6" s="33" t="n"/>
+      <c r="K6" s="33" t="n"/>
+      <c r="L6" s="33" t="n"/>
+      <c r="M6" s="33" t="n"/>
+      <c r="N6" s="33" t="n"/>
+      <c r="O6" s="33" t="n"/>
+      <c r="P6" s="33" t="n"/>
+      <c r="Q6" s="33" t="n"/>
+      <c r="R6" s="33" t="n"/>
+      <c r="S6" s="33" t="n"/>
+      <c r="T6" s="33" t="n"/>
+      <c r="U6" s="33" t="n"/>
+      <c r="V6" s="33" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:V1"/>
@@ -2475,7 +3295,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00BF8F00"/>
@@ -2506,196 +3326,196 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>InformantCode</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="32" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="32" t="inlineStr">
         <is>
           <t>RegisteredDate</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="32" t="inlineStr">
         <is>
           <t>Handler</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="32" t="inlineStr">
         <is>
           <t>HandlerRank</t>
         </is>
       </c>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" s="32" t="inlineStr">
         <is>
           <t>Parish</t>
         </is>
       </c>
-      <c r="G1" s="29" t="inlineStr">
+      <c r="G1" s="32" t="inlineStr">
         <is>
           <t>Territory</t>
         </is>
       </c>
-      <c r="H1" s="29" t="inlineStr">
+      <c r="H1" s="32" t="inlineStr">
         <is>
           <t>ReliabilityRating</t>
         </is>
       </c>
-      <c r="I1" s="29" t="inlineStr">
+      <c r="I1" s="32" t="inlineStr">
         <is>
           <t>TotalTips</t>
         </is>
       </c>
-      <c r="J1" s="29" t="inlineStr">
+      <c r="J1" s="32" t="inlineStr">
         <is>
           <t>TipsToOperations</t>
         </is>
       </c>
-      <c r="K1" s="29" t="inlineStr">
+      <c r="K1" s="32" t="inlineStr">
         <is>
           <t>TipsToSeizures</t>
         </is>
       </c>
-      <c r="L1" s="29" t="inlineStr">
+      <c r="L1" s="32" t="inlineStr">
         <is>
           <t>TipsToArrests</t>
         </is>
       </c>
-      <c r="M1" s="29" t="inlineStr">
+      <c r="M1" s="32" t="inlineStr">
         <is>
           <t>LastContactDate</t>
         </is>
       </c>
-      <c r="N1" s="29" t="inlineStr">
+      <c r="N1" s="32" t="inlineStr">
         <is>
           <t>NextContactDue</t>
         </is>
       </c>
-      <c r="O1" s="29" t="inlineStr">
+      <c r="O1" s="32" t="inlineStr">
         <is>
           <t>PolygraphDate</t>
         </is>
       </c>
-      <c r="P1" s="29" t="inlineStr">
+      <c r="P1" s="32" t="inlineStr">
         <is>
           <t>PolygraphResult</t>
         </is>
       </c>
-      <c r="Q1" s="29" t="inlineStr">
+      <c r="Q1" s="32" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="R1" s="29" t="inlineStr">
+      <c r="R1" s="32" t="inlineStr">
         <is>
           <t>CreatedBy</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="n"/>
-      <c r="B2" s="30" t="n"/>
-      <c r="C2" s="30" t="n"/>
-      <c r="D2" s="30" t="n"/>
-      <c r="E2" s="30" t="n"/>
-      <c r="F2" s="30" t="n"/>
-      <c r="G2" s="30" t="n"/>
-      <c r="H2" s="30" t="n"/>
-      <c r="I2" s="30" t="n"/>
-      <c r="J2" s="30" t="n"/>
-      <c r="K2" s="30" t="n"/>
-      <c r="L2" s="30" t="n"/>
-      <c r="M2" s="30" t="n"/>
-      <c r="N2" s="30" t="n"/>
-      <c r="O2" s="30" t="n"/>
-      <c r="P2" s="30" t="n"/>
-      <c r="Q2" s="30" t="n"/>
-      <c r="R2" s="30" t="n"/>
+      <c r="A2" s="33" t="n"/>
+      <c r="B2" s="33" t="n"/>
+      <c r="C2" s="33" t="n"/>
+      <c r="D2" s="33" t="n"/>
+      <c r="E2" s="33" t="n"/>
+      <c r="F2" s="33" t="n"/>
+      <c r="G2" s="33" t="n"/>
+      <c r="H2" s="33" t="n"/>
+      <c r="I2" s="33" t="n"/>
+      <c r="J2" s="33" t="n"/>
+      <c r="K2" s="33" t="n"/>
+      <c r="L2" s="33" t="n"/>
+      <c r="M2" s="33" t="n"/>
+      <c r="N2" s="33" t="n"/>
+      <c r="O2" s="33" t="n"/>
+      <c r="P2" s="33" t="n"/>
+      <c r="Q2" s="33" t="n"/>
+      <c r="R2" s="33" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="n"/>
-      <c r="B3" s="30" t="n"/>
-      <c r="C3" s="30" t="n"/>
-      <c r="D3" s="30" t="n"/>
-      <c r="E3" s="30" t="n"/>
-      <c r="F3" s="30" t="n"/>
-      <c r="G3" s="30" t="n"/>
-      <c r="H3" s="30" t="n"/>
-      <c r="I3" s="30" t="n"/>
-      <c r="J3" s="30" t="n"/>
-      <c r="K3" s="30" t="n"/>
-      <c r="L3" s="30" t="n"/>
-      <c r="M3" s="30" t="n"/>
-      <c r="N3" s="30" t="n"/>
-      <c r="O3" s="30" t="n"/>
-      <c r="P3" s="30" t="n"/>
-      <c r="Q3" s="30" t="n"/>
-      <c r="R3" s="30" t="n"/>
+      <c r="A3" s="33" t="n"/>
+      <c r="B3" s="33" t="n"/>
+      <c r="C3" s="33" t="n"/>
+      <c r="D3" s="33" t="n"/>
+      <c r="E3" s="33" t="n"/>
+      <c r="F3" s="33" t="n"/>
+      <c r="G3" s="33" t="n"/>
+      <c r="H3" s="33" t="n"/>
+      <c r="I3" s="33" t="n"/>
+      <c r="J3" s="33" t="n"/>
+      <c r="K3" s="33" t="n"/>
+      <c r="L3" s="33" t="n"/>
+      <c r="M3" s="33" t="n"/>
+      <c r="N3" s="33" t="n"/>
+      <c r="O3" s="33" t="n"/>
+      <c r="P3" s="33" t="n"/>
+      <c r="Q3" s="33" t="n"/>
+      <c r="R3" s="33" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="30" t="n"/>
-      <c r="B4" s="30" t="n"/>
-      <c r="C4" s="30" t="n"/>
-      <c r="D4" s="30" t="n"/>
-      <c r="E4" s="30" t="n"/>
-      <c r="F4" s="30" t="n"/>
-      <c r="G4" s="30" t="n"/>
-      <c r="H4" s="30" t="n"/>
-      <c r="I4" s="30" t="n"/>
-      <c r="J4" s="30" t="n"/>
-      <c r="K4" s="30" t="n"/>
-      <c r="L4" s="30" t="n"/>
-      <c r="M4" s="30" t="n"/>
-      <c r="N4" s="30" t="n"/>
-      <c r="O4" s="30" t="n"/>
-      <c r="P4" s="30" t="n"/>
-      <c r="Q4" s="30" t="n"/>
-      <c r="R4" s="30" t="n"/>
+      <c r="A4" s="33" t="n"/>
+      <c r="B4" s="33" t="n"/>
+      <c r="C4" s="33" t="n"/>
+      <c r="D4" s="33" t="n"/>
+      <c r="E4" s="33" t="n"/>
+      <c r="F4" s="33" t="n"/>
+      <c r="G4" s="33" t="n"/>
+      <c r="H4" s="33" t="n"/>
+      <c r="I4" s="33" t="n"/>
+      <c r="J4" s="33" t="n"/>
+      <c r="K4" s="33" t="n"/>
+      <c r="L4" s="33" t="n"/>
+      <c r="M4" s="33" t="n"/>
+      <c r="N4" s="33" t="n"/>
+      <c r="O4" s="33" t="n"/>
+      <c r="P4" s="33" t="n"/>
+      <c r="Q4" s="33" t="n"/>
+      <c r="R4" s="33" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="n"/>
-      <c r="B5" s="30" t="n"/>
-      <c r="C5" s="30" t="n"/>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="30" t="n"/>
-      <c r="F5" s="30" t="n"/>
-      <c r="G5" s="30" t="n"/>
-      <c r="H5" s="30" t="n"/>
-      <c r="I5" s="30" t="n"/>
-      <c r="J5" s="30" t="n"/>
-      <c r="K5" s="30" t="n"/>
-      <c r="L5" s="30" t="n"/>
-      <c r="M5" s="30" t="n"/>
-      <c r="N5" s="30" t="n"/>
-      <c r="O5" s="30" t="n"/>
-      <c r="P5" s="30" t="n"/>
-      <c r="Q5" s="30" t="n"/>
-      <c r="R5" s="30" t="n"/>
+      <c r="A5" s="33" t="n"/>
+      <c r="B5" s="33" t="n"/>
+      <c r="C5" s="33" t="n"/>
+      <c r="D5" s="33" t="n"/>
+      <c r="E5" s="33" t="n"/>
+      <c r="F5" s="33" t="n"/>
+      <c r="G5" s="33" t="n"/>
+      <c r="H5" s="33" t="n"/>
+      <c r="I5" s="33" t="n"/>
+      <c r="J5" s="33" t="n"/>
+      <c r="K5" s="33" t="n"/>
+      <c r="L5" s="33" t="n"/>
+      <c r="M5" s="33" t="n"/>
+      <c r="N5" s="33" t="n"/>
+      <c r="O5" s="33" t="n"/>
+      <c r="P5" s="33" t="n"/>
+      <c r="Q5" s="33" t="n"/>
+      <c r="R5" s="33" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="n"/>
-      <c r="B6" s="30" t="n"/>
-      <c r="C6" s="30" t="n"/>
-      <c r="D6" s="30" t="n"/>
-      <c r="E6" s="30" t="n"/>
-      <c r="F6" s="30" t="n"/>
-      <c r="G6" s="30" t="n"/>
-      <c r="H6" s="30" t="n"/>
-      <c r="I6" s="30" t="n"/>
-      <c r="J6" s="30" t="n"/>
-      <c r="K6" s="30" t="n"/>
-      <c r="L6" s="30" t="n"/>
-      <c r="M6" s="30" t="n"/>
-      <c r="N6" s="30" t="n"/>
-      <c r="O6" s="30" t="n"/>
-      <c r="P6" s="30" t="n"/>
-      <c r="Q6" s="30" t="n"/>
-      <c r="R6" s="30" t="n"/>
+      <c r="A6" s="33" t="n"/>
+      <c r="B6" s="33" t="n"/>
+      <c r="C6" s="33" t="n"/>
+      <c r="D6" s="33" t="n"/>
+      <c r="E6" s="33" t="n"/>
+      <c r="F6" s="33" t="n"/>
+      <c r="G6" s="33" t="n"/>
+      <c r="H6" s="33" t="n"/>
+      <c r="I6" s="33" t="n"/>
+      <c r="J6" s="33" t="n"/>
+      <c r="K6" s="33" t="n"/>
+      <c r="L6" s="33" t="n"/>
+      <c r="M6" s="33" t="n"/>
+      <c r="N6" s="33" t="n"/>
+      <c r="O6" s="33" t="n"/>
+      <c r="P6" s="33" t="n"/>
+      <c r="Q6" s="33" t="n"/>
+      <c r="R6" s="33" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="849B"/>
@@ -2712,7 +3532,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -2741,176 +3561,176 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>PersonnelID</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="32" t="inlineStr">
         <is>
           <t>RegNo</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="32" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="32" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="32" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" s="32" t="inlineStr">
         <is>
           <t>Assignment</t>
         </is>
       </c>
-      <c r="G1" s="29" t="inlineStr">
+      <c r="G1" s="32" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H1" s="29" t="inlineStr">
+      <c r="H1" s="32" t="inlineStr">
         <is>
           <t>PolygraphDate</t>
         </is>
       </c>
-      <c r="I1" s="29" t="inlineStr">
+      <c r="I1" s="32" t="inlineStr">
         <is>
           <t>PolygraphResult</t>
         </is>
       </c>
-      <c r="J1" s="29" t="inlineStr">
+      <c r="J1" s="32" t="inlineStr">
         <is>
           <t>FirearmsQualified</t>
         </is>
       </c>
-      <c r="K1" s="29" t="inlineStr">
+      <c r="K1" s="32" t="inlineStr">
         <is>
           <t>TacticalTraining</t>
         </is>
       </c>
-      <c r="L1" s="29" t="inlineStr">
+      <c r="L1" s="32" t="inlineStr">
         <is>
           <t>CourtTestimonyTrained</t>
         </is>
       </c>
-      <c r="M1" s="29" t="inlineStr">
+      <c r="M1" s="32" t="inlineStr">
         <is>
           <t>JoinedFNID</t>
         </is>
       </c>
-      <c r="N1" s="29" t="inlineStr">
+      <c r="N1" s="32" t="inlineStr">
         <is>
           <t>PriorPosting</t>
         </is>
       </c>
-      <c r="O1" s="29" t="inlineStr">
+      <c r="O1" s="32" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="P1" s="29" t="inlineStr">
+      <c r="P1" s="32" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="n"/>
-      <c r="B2" s="30" t="n"/>
-      <c r="C2" s="30" t="n"/>
-      <c r="D2" s="30" t="n"/>
-      <c r="E2" s="30" t="n"/>
-      <c r="F2" s="30" t="n"/>
-      <c r="G2" s="30" t="n"/>
-      <c r="H2" s="30" t="n"/>
-      <c r="I2" s="30" t="n"/>
-      <c r="J2" s="30" t="n"/>
-      <c r="K2" s="30" t="n"/>
-      <c r="L2" s="30" t="n"/>
-      <c r="M2" s="30" t="n"/>
-      <c r="N2" s="30" t="n"/>
-      <c r="O2" s="30" t="n"/>
-      <c r="P2" s="30" t="n"/>
+      <c r="A2" s="33" t="n"/>
+      <c r="B2" s="33" t="n"/>
+      <c r="C2" s="33" t="n"/>
+      <c r="D2" s="33" t="n"/>
+      <c r="E2" s="33" t="n"/>
+      <c r="F2" s="33" t="n"/>
+      <c r="G2" s="33" t="n"/>
+      <c r="H2" s="33" t="n"/>
+      <c r="I2" s="33" t="n"/>
+      <c r="J2" s="33" t="n"/>
+      <c r="K2" s="33" t="n"/>
+      <c r="L2" s="33" t="n"/>
+      <c r="M2" s="33" t="n"/>
+      <c r="N2" s="33" t="n"/>
+      <c r="O2" s="33" t="n"/>
+      <c r="P2" s="33" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="n"/>
-      <c r="B3" s="30" t="n"/>
-      <c r="C3" s="30" t="n"/>
-      <c r="D3" s="30" t="n"/>
-      <c r="E3" s="30" t="n"/>
-      <c r="F3" s="30" t="n"/>
-      <c r="G3" s="30" t="n"/>
-      <c r="H3" s="30" t="n"/>
-      <c r="I3" s="30" t="n"/>
-      <c r="J3" s="30" t="n"/>
-      <c r="K3" s="30" t="n"/>
-      <c r="L3" s="30" t="n"/>
-      <c r="M3" s="30" t="n"/>
-      <c r="N3" s="30" t="n"/>
-      <c r="O3" s="30" t="n"/>
-      <c r="P3" s="30" t="n"/>
+      <c r="A3" s="33" t="n"/>
+      <c r="B3" s="33" t="n"/>
+      <c r="C3" s="33" t="n"/>
+      <c r="D3" s="33" t="n"/>
+      <c r="E3" s="33" t="n"/>
+      <c r="F3" s="33" t="n"/>
+      <c r="G3" s="33" t="n"/>
+      <c r="H3" s="33" t="n"/>
+      <c r="I3" s="33" t="n"/>
+      <c r="J3" s="33" t="n"/>
+      <c r="K3" s="33" t="n"/>
+      <c r="L3" s="33" t="n"/>
+      <c r="M3" s="33" t="n"/>
+      <c r="N3" s="33" t="n"/>
+      <c r="O3" s="33" t="n"/>
+      <c r="P3" s="33" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="30" t="n"/>
-      <c r="B4" s="30" t="n"/>
-      <c r="C4" s="30" t="n"/>
-      <c r="D4" s="30" t="n"/>
-      <c r="E4" s="30" t="n"/>
-      <c r="F4" s="30" t="n"/>
-      <c r="G4" s="30" t="n"/>
-      <c r="H4" s="30" t="n"/>
-      <c r="I4" s="30" t="n"/>
-      <c r="J4" s="30" t="n"/>
-      <c r="K4" s="30" t="n"/>
-      <c r="L4" s="30" t="n"/>
-      <c r="M4" s="30" t="n"/>
-      <c r="N4" s="30" t="n"/>
-      <c r="O4" s="30" t="n"/>
-      <c r="P4" s="30" t="n"/>
+      <c r="A4" s="33" t="n"/>
+      <c r="B4" s="33" t="n"/>
+      <c r="C4" s="33" t="n"/>
+      <c r="D4" s="33" t="n"/>
+      <c r="E4" s="33" t="n"/>
+      <c r="F4" s="33" t="n"/>
+      <c r="G4" s="33" t="n"/>
+      <c r="H4" s="33" t="n"/>
+      <c r="I4" s="33" t="n"/>
+      <c r="J4" s="33" t="n"/>
+      <c r="K4" s="33" t="n"/>
+      <c r="L4" s="33" t="n"/>
+      <c r="M4" s="33" t="n"/>
+      <c r="N4" s="33" t="n"/>
+      <c r="O4" s="33" t="n"/>
+      <c r="P4" s="33" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="n"/>
-      <c r="B5" s="30" t="n"/>
-      <c r="C5" s="30" t="n"/>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="30" t="n"/>
-      <c r="F5" s="30" t="n"/>
-      <c r="G5" s="30" t="n"/>
-      <c r="H5" s="30" t="n"/>
-      <c r="I5" s="30" t="n"/>
-      <c r="J5" s="30" t="n"/>
-      <c r="K5" s="30" t="n"/>
-      <c r="L5" s="30" t="n"/>
-      <c r="M5" s="30" t="n"/>
-      <c r="N5" s="30" t="n"/>
-      <c r="O5" s="30" t="n"/>
-      <c r="P5" s="30" t="n"/>
+      <c r="A5" s="33" t="n"/>
+      <c r="B5" s="33" t="n"/>
+      <c r="C5" s="33" t="n"/>
+      <c r="D5" s="33" t="n"/>
+      <c r="E5" s="33" t="n"/>
+      <c r="F5" s="33" t="n"/>
+      <c r="G5" s="33" t="n"/>
+      <c r="H5" s="33" t="n"/>
+      <c r="I5" s="33" t="n"/>
+      <c r="J5" s="33" t="n"/>
+      <c r="K5" s="33" t="n"/>
+      <c r="L5" s="33" t="n"/>
+      <c r="M5" s="33" t="n"/>
+      <c r="N5" s="33" t="n"/>
+      <c r="O5" s="33" t="n"/>
+      <c r="P5" s="33" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="n"/>
-      <c r="B6" s="30" t="n"/>
-      <c r="C6" s="30" t="n"/>
-      <c r="D6" s="30" t="n"/>
-      <c r="E6" s="30" t="n"/>
-      <c r="F6" s="30" t="n"/>
-      <c r="G6" s="30" t="n"/>
-      <c r="H6" s="30" t="n"/>
-      <c r="I6" s="30" t="n"/>
-      <c r="J6" s="30" t="n"/>
-      <c r="K6" s="30" t="n"/>
-      <c r="L6" s="30" t="n"/>
-      <c r="M6" s="30" t="n"/>
-      <c r="N6" s="30" t="n"/>
-      <c r="O6" s="30" t="n"/>
-      <c r="P6" s="30" t="n"/>
+      <c r="A6" s="33" t="n"/>
+      <c r="B6" s="33" t="n"/>
+      <c r="C6" s="33" t="n"/>
+      <c r="D6" s="33" t="n"/>
+      <c r="E6" s="33" t="n"/>
+      <c r="F6" s="33" t="n"/>
+      <c r="G6" s="33" t="n"/>
+      <c r="H6" s="33" t="n"/>
+      <c r="I6" s="33" t="n"/>
+      <c r="J6" s="33" t="n"/>
+      <c r="K6" s="33" t="n"/>
+      <c r="L6" s="33" t="n"/>
+      <c r="M6" s="33" t="n"/>
+      <c r="N6" s="33" t="n"/>
+      <c r="O6" s="33" t="n"/>
+      <c r="P6" s="33" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:P1"/>
@@ -2921,7 +3741,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -2949,166 +3769,166 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>VehicleID</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="32" t="inlineStr">
         <is>
           <t>Registration</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="32" t="inlineStr">
         <is>
           <t>Make</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="32" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="32" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" s="32" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="G1" s="29" t="inlineStr">
+      <c r="G1" s="32" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H1" s="29" t="inlineStr">
+      <c r="H1" s="32" t="inlineStr">
         <is>
           <t>AssignedTo</t>
         </is>
       </c>
-      <c r="I1" s="29" t="inlineStr">
+      <c r="I1" s="32" t="inlineStr">
         <is>
           <t>FuelType</t>
         </is>
       </c>
-      <c r="J1" s="29" t="inlineStr">
+      <c r="J1" s="32" t="inlineStr">
         <is>
           <t>LastServiceDate</t>
         </is>
       </c>
-      <c r="K1" s="29" t="inlineStr">
+      <c r="K1" s="32" t="inlineStr">
         <is>
           <t>NextServiceDue</t>
         </is>
       </c>
-      <c r="L1" s="29" t="inlineStr">
+      <c r="L1" s="32" t="inlineStr">
         <is>
           <t>InsuranceExpiry</t>
         </is>
       </c>
-      <c r="M1" s="29" t="inlineStr">
+      <c r="M1" s="32" t="inlineStr">
         <is>
           <t>FitnessExpiry</t>
         </is>
       </c>
-      <c r="N1" s="29" t="inlineStr">
+      <c r="N1" s="32" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="O1" s="29" t="inlineStr">
+      <c r="O1" s="32" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30" t="n"/>
-      <c r="B2" s="30" t="n"/>
-      <c r="C2" s="30" t="n"/>
-      <c r="D2" s="30" t="n"/>
-      <c r="E2" s="30" t="n"/>
-      <c r="F2" s="30" t="n"/>
-      <c r="G2" s="30" t="n"/>
-      <c r="H2" s="30" t="n"/>
-      <c r="I2" s="30" t="n"/>
-      <c r="J2" s="30" t="n"/>
-      <c r="K2" s="30" t="n"/>
-      <c r="L2" s="30" t="n"/>
-      <c r="M2" s="30" t="n"/>
-      <c r="N2" s="30" t="n"/>
-      <c r="O2" s="30" t="n"/>
+      <c r="A2" s="33" t="n"/>
+      <c r="B2" s="33" t="n"/>
+      <c r="C2" s="33" t="n"/>
+      <c r="D2" s="33" t="n"/>
+      <c r="E2" s="33" t="n"/>
+      <c r="F2" s="33" t="n"/>
+      <c r="G2" s="33" t="n"/>
+      <c r="H2" s="33" t="n"/>
+      <c r="I2" s="33" t="n"/>
+      <c r="J2" s="33" t="n"/>
+      <c r="K2" s="33" t="n"/>
+      <c r="L2" s="33" t="n"/>
+      <c r="M2" s="33" t="n"/>
+      <c r="N2" s="33" t="n"/>
+      <c r="O2" s="33" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="30" t="n"/>
-      <c r="B3" s="30" t="n"/>
-      <c r="C3" s="30" t="n"/>
-      <c r="D3" s="30" t="n"/>
-      <c r="E3" s="30" t="n"/>
-      <c r="F3" s="30" t="n"/>
-      <c r="G3" s="30" t="n"/>
-      <c r="H3" s="30" t="n"/>
-      <c r="I3" s="30" t="n"/>
-      <c r="J3" s="30" t="n"/>
-      <c r="K3" s="30" t="n"/>
-      <c r="L3" s="30" t="n"/>
-      <c r="M3" s="30" t="n"/>
-      <c r="N3" s="30" t="n"/>
-      <c r="O3" s="30" t="n"/>
+      <c r="A3" s="33" t="n"/>
+      <c r="B3" s="33" t="n"/>
+      <c r="C3" s="33" t="n"/>
+      <c r="D3" s="33" t="n"/>
+      <c r="E3" s="33" t="n"/>
+      <c r="F3" s="33" t="n"/>
+      <c r="G3" s="33" t="n"/>
+      <c r="H3" s="33" t="n"/>
+      <c r="I3" s="33" t="n"/>
+      <c r="J3" s="33" t="n"/>
+      <c r="K3" s="33" t="n"/>
+      <c r="L3" s="33" t="n"/>
+      <c r="M3" s="33" t="n"/>
+      <c r="N3" s="33" t="n"/>
+      <c r="O3" s="33" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="30" t="n"/>
-      <c r="B4" s="30" t="n"/>
-      <c r="C4" s="30" t="n"/>
-      <c r="D4" s="30" t="n"/>
-      <c r="E4" s="30" t="n"/>
-      <c r="F4" s="30" t="n"/>
-      <c r="G4" s="30" t="n"/>
-      <c r="H4" s="30" t="n"/>
-      <c r="I4" s="30" t="n"/>
-      <c r="J4" s="30" t="n"/>
-      <c r="K4" s="30" t="n"/>
-      <c r="L4" s="30" t="n"/>
-      <c r="M4" s="30" t="n"/>
-      <c r="N4" s="30" t="n"/>
-      <c r="O4" s="30" t="n"/>
+      <c r="A4" s="33" t="n"/>
+      <c r="B4" s="33" t="n"/>
+      <c r="C4" s="33" t="n"/>
+      <c r="D4" s="33" t="n"/>
+      <c r="E4" s="33" t="n"/>
+      <c r="F4" s="33" t="n"/>
+      <c r="G4" s="33" t="n"/>
+      <c r="H4" s="33" t="n"/>
+      <c r="I4" s="33" t="n"/>
+      <c r="J4" s="33" t="n"/>
+      <c r="K4" s="33" t="n"/>
+      <c r="L4" s="33" t="n"/>
+      <c r="M4" s="33" t="n"/>
+      <c r="N4" s="33" t="n"/>
+      <c r="O4" s="33" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="n"/>
-      <c r="B5" s="30" t="n"/>
-      <c r="C5" s="30" t="n"/>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="30" t="n"/>
-      <c r="F5" s="30" t="n"/>
-      <c r="G5" s="30" t="n"/>
-      <c r="H5" s="30" t="n"/>
-      <c r="I5" s="30" t="n"/>
-      <c r="J5" s="30" t="n"/>
-      <c r="K5" s="30" t="n"/>
-      <c r="L5" s="30" t="n"/>
-      <c r="M5" s="30" t="n"/>
-      <c r="N5" s="30" t="n"/>
-      <c r="O5" s="30" t="n"/>
+      <c r="A5" s="33" t="n"/>
+      <c r="B5" s="33" t="n"/>
+      <c r="C5" s="33" t="n"/>
+      <c r="D5" s="33" t="n"/>
+      <c r="E5" s="33" t="n"/>
+      <c r="F5" s="33" t="n"/>
+      <c r="G5" s="33" t="n"/>
+      <c r="H5" s="33" t="n"/>
+      <c r="I5" s="33" t="n"/>
+      <c r="J5" s="33" t="n"/>
+      <c r="K5" s="33" t="n"/>
+      <c r="L5" s="33" t="n"/>
+      <c r="M5" s="33" t="n"/>
+      <c r="N5" s="33" t="n"/>
+      <c r="O5" s="33" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="n"/>
-      <c r="B6" s="30" t="n"/>
-      <c r="C6" s="30" t="n"/>
-      <c r="D6" s="30" t="n"/>
-      <c r="E6" s="30" t="n"/>
-      <c r="F6" s="30" t="n"/>
-      <c r="G6" s="30" t="n"/>
-      <c r="H6" s="30" t="n"/>
-      <c r="I6" s="30" t="n"/>
-      <c r="J6" s="30" t="n"/>
-      <c r="K6" s="30" t="n"/>
-      <c r="L6" s="30" t="n"/>
-      <c r="M6" s="30" t="n"/>
-      <c r="N6" s="30" t="n"/>
-      <c r="O6" s="30" t="n"/>
+      <c r="A6" s="33" t="n"/>
+      <c r="B6" s="33" t="n"/>
+      <c r="C6" s="33" t="n"/>
+      <c r="D6" s="33" t="n"/>
+      <c r="E6" s="33" t="n"/>
+      <c r="F6" s="33" t="n"/>
+      <c r="G6" s="33" t="n"/>
+      <c r="H6" s="33" t="n"/>
+      <c r="I6" s="33" t="n"/>
+      <c r="J6" s="33" t="n"/>
+      <c r="K6" s="33" t="n"/>
+      <c r="L6" s="33" t="n"/>
+      <c r="M6" s="33" t="n"/>
+      <c r="N6" s="33" t="n"/>
+      <c r="O6" s="33" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:O1"/>
@@ -3136,7 +3956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3154,608 +3974,692 @@
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>FNID AREA 3 — DAILY COMMAND DASHBOARD</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>Intelligence → Operations → Seizures → Arrests → Forensics → DPP → Court</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>INTELLIGENCE PIPELINE</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>Total Intel (YTD)</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Pending Triage</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>Critical/High</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>Firearms-Related</t>
         </is>
       </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>Narcotics-Related</t>
         </is>
       </c>
-      <c r="F5" s="18" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>Trafficking Intel</t>
         </is>
       </c>
-      <c r="G5" s="18" t="inlineStr">
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>→ Converted to Op</t>
         </is>
       </c>
-      <c r="H5" s="18" t="inlineStr">
+      <c r="H5" s="19" t="inlineStr">
         <is>
           <t>Conversion Rate</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="19">
+      <c r="A6" s="20">
         <f>COUNTA(tbl_IntelLog[IntelID])-COUNTBLANK(tbl_IntelLog[IntelID])</f>
         <v/>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="20">
         <f>COUNTBLANK(tbl_IntelLog[TriageDecision])</f>
         <v/>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="20">
         <f>COUNTIF(tbl_IntelLog[Priority],"Critical")+COUNTIF(tbl_IntelLog[Priority],"High")</f>
         <v/>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="20">
         <f>COUNTIF(tbl_IntelLog[FirearmsRelated],"Yes")</f>
         <v/>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="20">
         <f>COUNTIF(tbl_IntelLog[NarcoticsRelated],"Yes")</f>
         <v/>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="20">
         <f>COUNTIF(tbl_IntelLog[TraffickingRelated],"Yes")</f>
         <v/>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="20">
         <f>COUNTIF(tbl_IntelLog[TriageDecision],"Action*")</f>
         <v/>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="20">
         <f>IFERROR(COUNTIF(tbl_IntelLog[TriageDecision],"Action*")/(COUNTA(tbl_IntelLog[IntelID])-COUNTBLANK(tbl_IntelLog[IntelID])),"—")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>OPERATIONS</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>Total Ops (YTD)</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>Search Warrants</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>Port/Cargo</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>Vehicle Intercepts</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>Joint Ops</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>Success Rate</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>Inspector Present %</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H9" s="22" t="inlineStr">
         <is>
           <t>Body Cam Active %</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19">
+      <c r="A10" s="20">
         <f>COUNTA(tbl_Operations[OpsID])-COUNTBLANK(tbl_Operations[OpsID])</f>
         <v/>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="20">
         <f>COUNTIF(tbl_Operations[OpsType],"Search Warrant*")</f>
         <v/>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="20">
         <f>COUNTIF(tbl_Operations[OpsType],"Port*")+COUNTIF(tbl_Operations[OpsType],"Airport*")</f>
         <v/>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="20">
         <f>COUNTIF(tbl_Operations[OpsType],"Vehicle*")</f>
         <v/>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="20">
         <f>COUNTIF(tbl_Operations[OpsType],"Joint*")</f>
         <v/>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="20">
         <f>IFERROR(COUNTIF(tbl_Operations[Outcome],"Successful*")/(COUNTA(tbl_Operations[OpsID])-COUNTBLANK(tbl_Operations[OpsID])),"—")</f>
         <v/>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="20">
         <f>IFERROR(COUNTIF(tbl_Operations[InspectorPresent],"Yes")/COUNTA(tbl_Operations[InspectorPresent]),"—")</f>
         <v/>
       </c>
-      <c r="H10" s="19">
+      <c r="H10" s="20">
         <f>IFERROR(COUNTIF(tbl_Operations[BodyCamActivated],"Yes")/COUNTA(tbl_Operations[BodyCamActivated]),"—")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>FIREARMS SEIZURES</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>Firearms Seized</t>
         </is>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>Pistols</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>Rifles</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>Shotguns</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>IBIS Hits</t>
         </is>
       </c>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>eTrace Complete</t>
         </is>
       </c>
-      <c r="G13" s="21" t="inlineStr">
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>US Origin</t>
         </is>
       </c>
-      <c r="H13" s="21" t="inlineStr">
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>Ballistic Cert Done</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="19">
+      <c r="A14" s="20">
         <f>COUNTA(tbl_FirearmSeizures[SeizureID])-COUNTBLANK(tbl_FirearmSeizures[SeizureID])</f>
         <v/>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="20">
         <f>COUNTIF(tbl_FirearmSeizures[FirearmType],"Pistol*")</f>
         <v/>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="20">
         <f>COUNTIF(tbl_FirearmSeizures[FirearmType],"Rifle*")</f>
         <v/>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="20">
         <f>COUNTIF(tbl_FirearmSeizures[FirearmType],"Shotgun")</f>
         <v/>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="20">
         <f>COUNTIF(tbl_FirearmSeizures[IBIS_Status],"Hit*")</f>
         <v/>
       </c>
-      <c r="F14" s="19">
+      <c r="F14" s="20">
         <f>COUNTIF(tbl_FirearmSeizures[eTrace_Status],"Trace*")</f>
         <v/>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="20">
         <f>COUNTIF(tbl_FirearmSeizures[eTrace_Status],"Traced*US*")</f>
         <v/>
       </c>
-      <c r="H14" s="19">
+      <c r="H14" s="20">
         <f>COUNTIF(tbl_FirearmSeizures[BallisticCertStatus],"Certificate Issued")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="inlineStr">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t>NARCOTICS SEIZURES</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="A17" s="24" t="inlineStr">
         <is>
           <t>Drug Seizures</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>Cannabis Items</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>Cocaine Items</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr">
         <is>
           <t>Est Value (JMD)</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E17" s="24" t="inlineStr">
         <is>
           <t>Linked to Gun Trade</t>
         </is>
       </c>
-      <c r="F17" s="23" t="inlineStr">
+      <c r="F17" s="24" t="inlineStr">
         <is>
           <t>Est Equiv Firearms</t>
         </is>
       </c>
-      <c r="G17" s="23" t="inlineStr">
+      <c r="G17" s="24" t="inlineStr">
         <is>
           <t>Forensic Cert Done</t>
         </is>
       </c>
-      <c r="H17" s="23" t="inlineStr">
+      <c r="H17" s="24" t="inlineStr">
         <is>
           <t>Cert Overdue</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="19">
+      <c r="A18" s="20">
         <f>COUNTA(tbl_NarcoticSeizures[SeizureID])-COUNTBLANK(tbl_NarcoticSeizures[SeizureID])</f>
         <v/>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="20">
         <f>COUNTIF(tbl_NarcoticSeizures[DrugType],"Cannabis*")</f>
         <v/>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="20">
         <f>COUNTIF(tbl_NarcoticSeizures[DrugType],"Cocaine*")</f>
         <v/>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="20">
         <f>SUM(tbl_NarcoticSeizures[EstStreetValue_JMD])</f>
         <v/>
       </c>
-      <c r="E18" s="19">
+      <c r="E18" s="20">
         <f>COUNTIF(tbl_NarcoticSeizures[LinkedToGunTrade],"Yes")</f>
         <v/>
       </c>
-      <c r="F18" s="19">
+      <c r="F18" s="20">
         <f>SUM(tbl_NarcoticSeizures[EstEquivFirearms])</f>
         <v/>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="20">
         <f>COUNTIF(tbl_NarcoticSeizures[ForensicCertStatus],"Certificate Issued")</f>
         <v/>
       </c>
-      <c r="H18" s="19">
+      <c r="H18" s="20">
         <f>COUNTIF(tbl_NarcoticSeizures[ForensicCertStatus],"Certificate Overdue")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>ARRESTS &amp; 48-HOUR COMPLIANCE</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="inlineStr">
+      <c r="A21" s="22" t="inlineStr">
         <is>
           <t>Total Arrests</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>Firearms Charges</t>
         </is>
       </c>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>Drug Charges</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>48hr Met</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>48hr BREACH</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>48hr Rate</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>Bail Granted</t>
         </is>
       </c>
-      <c r="H21" s="21" t="inlineStr">
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>Remanded</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="19">
+      <c r="A22" s="20">
         <f>COUNTA(tbl_Arrests[ArrestID])-COUNTBLANK(tbl_Arrests[ArrestID])</f>
         <v/>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="20">
         <f>COUNTIF(tbl_Arrests[ActSection],"*Firearms*")</f>
         <v/>
       </c>
-      <c r="C22" s="19">
+      <c r="C22" s="20">
         <f>COUNTIF(tbl_Arrests[ActSection],"*DDA*")+COUNTIF(tbl_Arrests[ActSection],"*Dangerous*")</f>
         <v/>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="20">
         <f>COUNTIF(tbl_Arrests[48hr_Met],"Yes")</f>
         <v/>
       </c>
-      <c r="E22" s="19">
+      <c r="E22" s="20">
         <f>COUNTIF(tbl_Arrests[48hr_Met],"BREACH")</f>
         <v/>
       </c>
-      <c r="F22" s="19">
+      <c r="F22" s="20">
         <f>IFERROR(COUNTIF(tbl_Arrests[48hr_Met],"Yes")/COUNTA(tbl_Arrests[48hr_Met]),"—")</f>
         <v/>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="20">
         <f>COUNTIF(tbl_Arrests[BailStatus],"Bail Granted")</f>
         <v/>
       </c>
-      <c r="H22" s="19">
+      <c r="H22" s="20">
         <f>COUNTIF(tbl_Arrests[BailStatus],"Remanded*")</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
+        <is>
+          <t>CASE REGISTRY &amp; INVESTIGATIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>Total Cases</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t>Open — Active</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>Open — Pending</t>
+        </is>
+      </c>
+      <c r="D25" s="26" t="inlineStr">
+        <is>
+          <t>Firearms Cases</t>
+        </is>
+      </c>
+      <c r="E25" s="26" t="inlineStr">
+        <is>
+          <t>Narcotics Cases</t>
+        </is>
+      </c>
+      <c r="F25" s="26" t="inlineStr">
+        <is>
+          <t>Escalated</t>
+        </is>
+      </c>
+      <c r="G25" s="26" t="inlineStr">
+        <is>
+          <t>Cold Cases</t>
+        </is>
+      </c>
+      <c r="H25" s="26" t="inlineStr">
+        <is>
+          <t>Avg Progress</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20">
+        <f>COUNTA(tbl_CaseRegistry[CaseRegID])-COUNTBLANK(tbl_CaseRegistry[CaseRegID])</f>
+        <v/>
+      </c>
+      <c r="B26" s="20">
+        <f>COUNTIF(tbl_CaseRegistry[CaseStatus],"Open — Active*")</f>
+        <v/>
+      </c>
+      <c r="C26" s="20">
+        <f>COUNTIF(tbl_CaseRegistry[CaseStatus],"Open — Pending*")</f>
+        <v/>
+      </c>
+      <c r="D26" s="20">
+        <f>COUNTIF(tbl_CaseRegistry[CaseClassification],"Firearms")+COUNTIF(tbl_CaseRegistry[CaseClassification],"Firearms*Narcotics")</f>
+        <v/>
+      </c>
+      <c r="E26" s="20">
+        <f>COUNTIF(tbl_CaseRegistry[CaseClassification],"Narcotics")+COUNTIF(tbl_CaseRegistry[CaseClassification],"Firearms*Narcotics")</f>
+        <v/>
+      </c>
+      <c r="F26" s="20">
+        <f>COUNTIF(tbl_CaseRegistry[Escalated],"Yes")</f>
+        <v/>
+      </c>
+      <c r="G26" s="20">
+        <f>COUNTIF(tbl_CaseRegistry[CaseStatus],"Cold Case*")</f>
+        <v/>
+      </c>
+      <c r="H26" s="20">
+        <f>IFERROR(AVERAGE(tbl_CaseRegistry[InvestigationProgress]),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="27" t="inlineStr">
         <is>
           <t>DPP CASE PIPELINE</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="25" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="28" t="inlineStr">
         <is>
           <t>Total Case Files</t>
         </is>
       </c>
-      <c r="B25" s="25" t="inlineStr">
+      <c r="B29" s="28" t="inlineStr">
         <is>
           <t>Being Prepared</t>
         </is>
       </c>
-      <c r="C25" s="25" t="inlineStr">
+      <c r="C29" s="28" t="inlineStr">
         <is>
           <t>Submitted to DPP</t>
         </is>
       </c>
-      <c r="D25" s="25" t="inlineStr">
+      <c r="D29" s="28" t="inlineStr">
         <is>
           <t>Awaiting Forensic</t>
         </is>
       </c>
-      <c r="E25" s="25" t="inlineStr">
+      <c r="E29" s="28" t="inlineStr">
         <is>
           <t>Awaiting Ballistic</t>
         </is>
       </c>
-      <c r="F25" s="25" t="inlineStr">
+      <c r="F29" s="28" t="inlineStr">
         <is>
           <t>Charge Approved</t>
         </is>
       </c>
-      <c r="G25" s="25" t="inlineStr">
+      <c r="G29" s="28" t="inlineStr">
         <is>
           <t>Avg File Score</t>
         </is>
       </c>
-      <c r="H25" s="25" t="inlineStr">
+      <c r="H29" s="28" t="inlineStr">
         <is>
           <t>Avg Days Pipeline</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="19">
+    <row r="30">
+      <c r="A30" s="20">
         <f>COUNTA(tbl_CaseFiles[CaseFileID])-COUNTBLANK(tbl_CaseFiles[CaseFileID])</f>
         <v/>
       </c>
-      <c r="B26" s="19">
+      <c r="B30" s="20">
         <f>COUNTIF(tbl_CaseFiles[DPPStatus],"File Being*")</f>
         <v/>
       </c>
-      <c r="C26" s="19">
+      <c r="C30" s="20">
         <f>COUNTIF(tbl_CaseFiles[DPPStatus],"File Submitted*")</f>
         <v/>
       </c>
-      <c r="D26" s="19">
+      <c r="D30" s="20">
         <f>COUNTIF(tbl_CaseFiles[DPPStatus],"Awaiting Forensic*")</f>
         <v/>
       </c>
-      <c r="E26" s="19">
+      <c r="E30" s="20">
         <f>COUNTIF(tbl_CaseFiles[DPPStatus],"Awaiting Ballistic*")</f>
         <v/>
       </c>
-      <c r="F26" s="19">
+      <c r="F30" s="20">
         <f>COUNTIF(tbl_CaseFiles[DPPStatus],"Ruling*Charge*")</f>
         <v/>
       </c>
-      <c r="G26" s="19">
+      <c r="G30" s="20">
         <f>IFERROR(AVERAGE(tbl_CaseFiles[FileCompletenessScore]),"—")</f>
         <v/>
       </c>
-      <c r="H26" s="19">
+      <c r="H30" s="20">
         <f>IFERROR(AVERAGE(tbl_CaseFiles[DaysInPipeline]),"—")</f>
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="26" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="29" t="inlineStr">
         <is>
           <t>FORENSIC BOTTLENECK (IFSLM)</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="27" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="30" t="inlineStr">
         <is>
           <t>Ballistic Pending</t>
         </is>
       </c>
-      <c r="B29" s="27" t="inlineStr">
+      <c r="B33" s="30" t="inlineStr">
         <is>
           <t>Ballistic Overdue</t>
         </is>
       </c>
-      <c r="C29" s="27" t="inlineStr">
+      <c r="C33" s="30" t="inlineStr">
         <is>
           <t>Ballistic Complete</t>
         </is>
       </c>
-      <c r="D29" s="27" t="inlineStr">
+      <c r="D33" s="30" t="inlineStr">
         <is>
           <t>Drug Cert Pending</t>
         </is>
       </c>
-      <c r="E29" s="27" t="inlineStr">
+      <c r="E33" s="30" t="inlineStr">
         <is>
           <t>Drug Cert Overdue</t>
         </is>
       </c>
-      <c r="F29" s="27" t="inlineStr">
+      <c r="F33" s="30" t="inlineStr">
         <is>
           <t>Drug Cert Complete</t>
         </is>
       </c>
-      <c r="G29" s="27" t="inlineStr">
+      <c r="G33" s="30" t="inlineStr">
         <is>
           <t>POCA Referrals</t>
         </is>
       </c>
-      <c r="H29" s="27" t="inlineStr">
+      <c r="H33" s="30" t="inlineStr">
         <is>
           <t>POCA Forfeited</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="19">
+    <row r="34">
+      <c r="A34" s="20">
         <f>COUNTIF(tbl_FirearmSeizures[BallisticCertStatus],"Submitted*")+COUNTIF(tbl_FirearmSeizures[BallisticCertStatus],"Analysis*")</f>
         <v/>
       </c>
-      <c r="B30" s="19">
+      <c r="B34" s="20">
         <f>COUNTIF(tbl_FirearmSeizures[BallisticCertStatus],"Certificate Overdue")</f>
         <v/>
       </c>
-      <c r="C30" s="19">
+      <c r="C34" s="20">
         <f>COUNTIF(tbl_FirearmSeizures[BallisticCertStatus],"Certificate Issued")</f>
         <v/>
       </c>
-      <c r="D30" s="19">
+      <c r="D34" s="20">
         <f>COUNTIF(tbl_NarcoticSeizures[ForensicCertStatus],"Submitted*")+COUNTIF(tbl_NarcoticSeizures[ForensicCertStatus],"Analysis*")</f>
         <v/>
       </c>
-      <c r="E30" s="19">
+      <c r="E34" s="20">
         <f>COUNTIF(tbl_NarcoticSeizures[ForensicCertStatus],"Certificate Overdue")</f>
         <v/>
       </c>
-      <c r="F30" s="19">
+      <c r="F34" s="20">
         <f>COUNTIF(tbl_NarcoticSeizures[ForensicCertStatus],"Certificate Issued")</f>
         <v/>
       </c>
-      <c r="G30" s="19">
+      <c r="G34" s="20">
         <f>COUNTIF(tbl_Arrests[POCAStatus],"Referred*")</f>
         <v/>
       </c>
-      <c r="H30" s="19">
+      <c r="H34" s="20">
         <f>COUNTIF(tbl_Arrests[POCAStatus],"Forfeiture*")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A20:L20"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A16:L16"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A28:L28"/>
+    <mergeCell ref="A32:L32"/>
     <mergeCell ref="A8:L8"/>
     <mergeCell ref="A12:L12"/>
     <mergeCell ref="A4:L4"/>
@@ -3771,7 +4675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W18"/>
+  <dimension ref="A1:Z18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3797,122 +4701,140 @@
     <col width="20" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
     <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
+    <col width="21" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="28" t="inlineStr">
+      <c r="A1" s="31" t="inlineStr">
         <is>
           <t>IntelSource</t>
         </is>
       </c>
-      <c r="B1" s="28" t="inlineStr">
+      <c r="B1" s="31" t="inlineStr">
         <is>
           <t>IntelPriority</t>
         </is>
       </c>
-      <c r="C1" s="28" t="inlineStr">
+      <c r="C1" s="31" t="inlineStr">
         <is>
           <t>TriageDecision</t>
         </is>
       </c>
-      <c r="D1" s="28" t="inlineStr">
+      <c r="D1" s="31" t="inlineStr">
         <is>
           <t>OperationType</t>
         </is>
       </c>
-      <c r="E1" s="28" t="inlineStr">
+      <c r="E1" s="31" t="inlineStr">
         <is>
           <t>WarrantBasis</t>
         </is>
       </c>
-      <c r="F1" s="28" t="inlineStr">
+      <c r="F1" s="31" t="inlineStr">
         <is>
           <t>FirearmType</t>
         </is>
       </c>
-      <c r="G1" s="28" t="inlineStr">
+      <c r="G1" s="31" t="inlineStr">
         <is>
           <t>FirearmCalibre</t>
         </is>
       </c>
-      <c r="H1" s="28" t="inlineStr">
+      <c r="H1" s="31" t="inlineStr">
         <is>
           <t>DrugType</t>
         </is>
       </c>
-      <c r="I1" s="28" t="inlineStr">
+      <c r="I1" s="31" t="inlineStr">
         <is>
           <t>DrugUnit</t>
         </is>
       </c>
-      <c r="J1" s="28" t="inlineStr">
+      <c r="J1" s="31" t="inlineStr">
         <is>
           <t>FirearmsActOffence</t>
         </is>
       </c>
-      <c r="K1" s="28" t="inlineStr">
+      <c r="K1" s="31" t="inlineStr">
         <is>
           <t>DDAOffence</t>
         </is>
       </c>
-      <c r="L1" s="28" t="inlineStr">
+      <c r="L1" s="31" t="inlineStr">
         <is>
           <t>CourtType</t>
         </is>
       </c>
-      <c r="M1" s="28" t="inlineStr">
+      <c r="M1" s="31" t="inlineStr">
         <is>
           <t>BailStatus</t>
         </is>
       </c>
-      <c r="N1" s="28" t="inlineStr">
+      <c r="N1" s="31" t="inlineStr">
         <is>
           <t>DPPStatus</t>
         </is>
       </c>
-      <c r="O1" s="28" t="inlineStr">
+      <c r="O1" s="31" t="inlineStr">
         <is>
           <t>ForensicStatus</t>
         </is>
       </c>
-      <c r="P1" s="28" t="inlineStr">
+      <c r="P1" s="31" t="inlineStr">
         <is>
           <t>Parish</t>
         </is>
       </c>
-      <c r="Q1" s="28" t="inlineStr">
+      <c r="Q1" s="31" t="inlineStr">
         <is>
           <t>YesNo</t>
         </is>
       </c>
-      <c r="R1" s="28" t="inlineStr">
+      <c r="R1" s="31" t="inlineStr">
         <is>
           <t>OpOutcome</t>
         </is>
       </c>
-      <c r="S1" s="28" t="inlineStr">
+      <c r="S1" s="31" t="inlineStr">
         <is>
           <t>SeizureLocation</t>
         </is>
       </c>
-      <c r="T1" s="28" t="inlineStr">
+      <c r="T1" s="31" t="inlineStr">
         <is>
           <t>IBIS_Status</t>
         </is>
       </c>
-      <c r="U1" s="28" t="inlineStr">
+      <c r="U1" s="31" t="inlineStr">
         <is>
           <t>eTrace_Status</t>
         </is>
       </c>
-      <c r="V1" s="28" t="inlineStr">
+      <c r="V1" s="31" t="inlineStr">
         <is>
           <t>ExhibitDisposal</t>
         </is>
       </c>
-      <c r="W1" s="28" t="inlineStr">
+      <c r="W1" s="31" t="inlineStr">
         <is>
           <t>POCAStatus</t>
+        </is>
+      </c>
+      <c r="X1" s="31" t="inlineStr">
+        <is>
+          <t>CaseClassification</t>
+        </is>
+      </c>
+      <c r="Y1" s="31" t="inlineStr">
+        <is>
+          <t>CaseStatus</t>
+        </is>
+      </c>
+      <c r="Z1" s="31" t="inlineStr">
+        <is>
+          <t>InvestigationType</t>
         </is>
       </c>
     </row>
@@ -4032,6 +4954,21 @@
           <t>Not Applicable</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Firearms</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Open — Active Investigation</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Murder Investigation (Firearm)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4149,6 +5086,21 @@
           <t>Referred to FID</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Narcotics</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Open — Pending Forensics</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Illegal Possession of Firearm</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4261,6 +5213,21 @@
           <t>Restraint Order Applied</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Firearms + Narcotics</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Open — Pending Witness Statements</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Trafficking — Firearms</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4373,6 +5340,21 @@
           <t>Restraint Order Granted</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Trafficking — Firearms</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Open — Surveillance</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Trafficking — Narcotics</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4480,6 +5462,21 @@
           <t>Civil Recovery Filed</t>
         </is>
       </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Trafficking — Narcotics</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Open — Pending DPP Submission</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Shooting with Intent</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4587,6 +5584,21 @@
           <t>Forfeiture Order — Post Conviction</t>
         </is>
       </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Trafficking — Multi-Commodity</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Referred to DPP</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Drug Dealing / Distribution</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4674,6 +5686,21 @@
           <t>Consent Order</t>
         </is>
       </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>POCA / Financial</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Closed — Convicted</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Import/Export — Narcotics</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4746,6 +5773,21 @@
           <t>Dismissed</t>
         </is>
       </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Murder with Firearm</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Closed — Acquitted</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Import/Export — Firearms</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4798,6 +5840,21 @@
           <t>Commercial Premises</t>
         </is>
       </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Shooting with Intent</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Closed — No Charge (Insufficient Evidence)</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>POCA / Financial Investigation</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4850,6 +5907,16 @@
           <t>Beach/Coastal</t>
         </is>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Closed — Withdrawn</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Stockpiling (s.6)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4897,6 +5964,16 @@
           <t>Open Land/Bushes</t>
         </is>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Cold Case — Under Review</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Manufacture / Assembly</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4934,6 +6011,16 @@
           <t>Courier/Postal Facility</t>
         </is>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Cold Case — Dormant</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Courier / Parcel Intercept</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4966,6 +6053,16 @@
           <t>ZOSO Checkpoint</t>
         </is>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Merged — See Linked Case</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Guns-for-Drugs Pipeline</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4996,6 +6093,11 @@
       <c r="S15" t="inlineStr">
         <is>
           <t>Other</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Gang / Network Investigation</t>
         </is>
       </c>
     </row>
@@ -5091,261 +6193,261 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>IntelID</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="32" t="inlineStr">
         <is>
           <t>DateReceived</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="32" t="inlineStr">
         <is>
           <t>TimeReceived</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="32" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="32" t="inlineStr">
         <is>
           <t>SourceRef</t>
         </is>
       </c>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" s="32" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="G1" s="29" t="inlineStr">
+      <c r="G1" s="32" t="inlineStr">
         <is>
           <t>SubjectMatter</t>
         </is>
       </c>
-      <c r="H1" s="29" t="inlineStr">
+      <c r="H1" s="32" t="inlineStr">
         <is>
           <t>FirearmsRelated</t>
         </is>
       </c>
-      <c r="I1" s="29" t="inlineStr">
+      <c r="I1" s="32" t="inlineStr">
         <is>
           <t>NarcoticsRelated</t>
         </is>
       </c>
-      <c r="J1" s="29" t="inlineStr">
+      <c r="J1" s="32" t="inlineStr">
         <is>
           <t>TraffickingRelated</t>
         </is>
       </c>
-      <c r="K1" s="29" t="inlineStr">
+      <c r="K1" s="32" t="inlineStr">
         <is>
           <t>TargetPerson</t>
         </is>
       </c>
-      <c r="L1" s="29" t="inlineStr">
+      <c r="L1" s="32" t="inlineStr">
         <is>
           <t>TargetLocation</t>
         </is>
       </c>
-      <c r="M1" s="29" t="inlineStr">
+      <c r="M1" s="32" t="inlineStr">
         <is>
           <t>Parish</t>
         </is>
       </c>
-      <c r="N1" s="29" t="inlineStr">
+      <c r="N1" s="32" t="inlineStr">
         <is>
           <t>SubstanceOfIntel</t>
         </is>
       </c>
-      <c r="O1" s="29" t="inlineStr">
+      <c r="O1" s="32" t="inlineStr">
         <is>
           <t>TriageDecision</t>
         </is>
       </c>
-      <c r="P1" s="29" t="inlineStr">
+      <c r="P1" s="32" t="inlineStr">
         <is>
           <t>TriageBy</t>
         </is>
       </c>
-      <c r="Q1" s="29" t="inlineStr">
+      <c r="Q1" s="32" t="inlineStr">
         <is>
           <t>TriageDate</t>
         </is>
       </c>
-      <c r="R1" s="29" t="inlineStr">
+      <c r="R1" s="32" t="inlineStr">
         <is>
           <t>LinkedOpID</t>
         </is>
       </c>
-      <c r="S1" s="29" t="inlineStr">
+      <c r="S1" s="32" t="inlineStr">
         <is>
           <t>LinkedCaseID</t>
         </is>
       </c>
-      <c r="T1" s="29" t="inlineStr">
+      <c r="T1" s="32" t="inlineStr">
         <is>
           <t>Outcome</t>
         </is>
       </c>
-      <c r="U1" s="29" t="inlineStr">
+      <c r="U1" s="32" t="inlineStr">
         <is>
           <t>OutcomeNotes</t>
         </is>
       </c>
-      <c r="V1" s="29" t="inlineStr">
+      <c r="V1" s="32" t="inlineStr">
         <is>
           <t>CreatedBy</t>
         </is>
       </c>
-      <c r="W1" s="29" t="inlineStr">
+      <c r="W1" s="32" t="inlineStr">
         <is>
           <t>CreatedDate</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30">
+      <c r="A2" s="33">
         <f>IF(B2="","","INT-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B2" s="30" t="n"/>
-      <c r="C2" s="30" t="n"/>
-      <c r="D2" s="30" t="n"/>
-      <c r="E2" s="30" t="n"/>
-      <c r="F2" s="30" t="n"/>
-      <c r="G2" s="30" t="n"/>
-      <c r="H2" s="30" t="n"/>
-      <c r="I2" s="30" t="n"/>
-      <c r="J2" s="30" t="n"/>
-      <c r="K2" s="30" t="n"/>
-      <c r="L2" s="30" t="n"/>
-      <c r="M2" s="30" t="n"/>
-      <c r="N2" s="30" t="n"/>
-      <c r="O2" s="30" t="n"/>
-      <c r="P2" s="30" t="n"/>
-      <c r="Q2" s="30" t="n"/>
-      <c r="R2" s="30" t="n"/>
-      <c r="S2" s="30" t="n"/>
-      <c r="T2" s="30" t="n"/>
-      <c r="U2" s="30" t="n"/>
-      <c r="V2" s="30" t="n"/>
-      <c r="W2" s="30" t="n"/>
+      <c r="B2" s="33" t="n"/>
+      <c r="C2" s="33" t="n"/>
+      <c r="D2" s="33" t="n"/>
+      <c r="E2" s="33" t="n"/>
+      <c r="F2" s="33" t="n"/>
+      <c r="G2" s="33" t="n"/>
+      <c r="H2" s="33" t="n"/>
+      <c r="I2" s="33" t="n"/>
+      <c r="J2" s="33" t="n"/>
+      <c r="K2" s="33" t="n"/>
+      <c r="L2" s="33" t="n"/>
+      <c r="M2" s="33" t="n"/>
+      <c r="N2" s="33" t="n"/>
+      <c r="O2" s="33" t="n"/>
+      <c r="P2" s="33" t="n"/>
+      <c r="Q2" s="33" t="n"/>
+      <c r="R2" s="33" t="n"/>
+      <c r="S2" s="33" t="n"/>
+      <c r="T2" s="33" t="n"/>
+      <c r="U2" s="33" t="n"/>
+      <c r="V2" s="33" t="n"/>
+      <c r="W2" s="33" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="30">
+      <c r="A3" s="33">
         <f>IF(B3="","","INT-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B3" s="30" t="n"/>
-      <c r="C3" s="30" t="n"/>
-      <c r="D3" s="30" t="n"/>
-      <c r="E3" s="30" t="n"/>
-      <c r="F3" s="30" t="n"/>
-      <c r="G3" s="30" t="n"/>
-      <c r="H3" s="30" t="n"/>
-      <c r="I3" s="30" t="n"/>
-      <c r="J3" s="30" t="n"/>
-      <c r="K3" s="30" t="n"/>
-      <c r="L3" s="30" t="n"/>
-      <c r="M3" s="30" t="n"/>
-      <c r="N3" s="30" t="n"/>
-      <c r="O3" s="30" t="n"/>
-      <c r="P3" s="30" t="n"/>
-      <c r="Q3" s="30" t="n"/>
-      <c r="R3" s="30" t="n"/>
-      <c r="S3" s="30" t="n"/>
-      <c r="T3" s="30" t="n"/>
-      <c r="U3" s="30" t="n"/>
-      <c r="V3" s="30" t="n"/>
-      <c r="W3" s="30" t="n"/>
+      <c r="B3" s="33" t="n"/>
+      <c r="C3" s="33" t="n"/>
+      <c r="D3" s="33" t="n"/>
+      <c r="E3" s="33" t="n"/>
+      <c r="F3" s="33" t="n"/>
+      <c r="G3" s="33" t="n"/>
+      <c r="H3" s="33" t="n"/>
+      <c r="I3" s="33" t="n"/>
+      <c r="J3" s="33" t="n"/>
+      <c r="K3" s="33" t="n"/>
+      <c r="L3" s="33" t="n"/>
+      <c r="M3" s="33" t="n"/>
+      <c r="N3" s="33" t="n"/>
+      <c r="O3" s="33" t="n"/>
+      <c r="P3" s="33" t="n"/>
+      <c r="Q3" s="33" t="n"/>
+      <c r="R3" s="33" t="n"/>
+      <c r="S3" s="33" t="n"/>
+      <c r="T3" s="33" t="n"/>
+      <c r="U3" s="33" t="n"/>
+      <c r="V3" s="33" t="n"/>
+      <c r="W3" s="33" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="30">
+      <c r="A4" s="33">
         <f>IF(B4="","","INT-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B4" s="30" t="n"/>
-      <c r="C4" s="30" t="n"/>
-      <c r="D4" s="30" t="n"/>
-      <c r="E4" s="30" t="n"/>
-      <c r="F4" s="30" t="n"/>
-      <c r="G4" s="30" t="n"/>
-      <c r="H4" s="30" t="n"/>
-      <c r="I4" s="30" t="n"/>
-      <c r="J4" s="30" t="n"/>
-      <c r="K4" s="30" t="n"/>
-      <c r="L4" s="30" t="n"/>
-      <c r="M4" s="30" t="n"/>
-      <c r="N4" s="30" t="n"/>
-      <c r="O4" s="30" t="n"/>
-      <c r="P4" s="30" t="n"/>
-      <c r="Q4" s="30" t="n"/>
-      <c r="R4" s="30" t="n"/>
-      <c r="S4" s="30" t="n"/>
-      <c r="T4" s="30" t="n"/>
-      <c r="U4" s="30" t="n"/>
-      <c r="V4" s="30" t="n"/>
-      <c r="W4" s="30" t="n"/>
+      <c r="B4" s="33" t="n"/>
+      <c r="C4" s="33" t="n"/>
+      <c r="D4" s="33" t="n"/>
+      <c r="E4" s="33" t="n"/>
+      <c r="F4" s="33" t="n"/>
+      <c r="G4" s="33" t="n"/>
+      <c r="H4" s="33" t="n"/>
+      <c r="I4" s="33" t="n"/>
+      <c r="J4" s="33" t="n"/>
+      <c r="K4" s="33" t="n"/>
+      <c r="L4" s="33" t="n"/>
+      <c r="M4" s="33" t="n"/>
+      <c r="N4" s="33" t="n"/>
+      <c r="O4" s="33" t="n"/>
+      <c r="P4" s="33" t="n"/>
+      <c r="Q4" s="33" t="n"/>
+      <c r="R4" s="33" t="n"/>
+      <c r="S4" s="33" t="n"/>
+      <c r="T4" s="33" t="n"/>
+      <c r="U4" s="33" t="n"/>
+      <c r="V4" s="33" t="n"/>
+      <c r="W4" s="33" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="30">
+      <c r="A5" s="33">
         <f>IF(B5="","","INT-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B5" s="30" t="n"/>
-      <c r="C5" s="30" t="n"/>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="30" t="n"/>
-      <c r="F5" s="30" t="n"/>
-      <c r="G5" s="30" t="n"/>
-      <c r="H5" s="30" t="n"/>
-      <c r="I5" s="30" t="n"/>
-      <c r="J5" s="30" t="n"/>
-      <c r="K5" s="30" t="n"/>
-      <c r="L5" s="30" t="n"/>
-      <c r="M5" s="30" t="n"/>
-      <c r="N5" s="30" t="n"/>
-      <c r="O5" s="30" t="n"/>
-      <c r="P5" s="30" t="n"/>
-      <c r="Q5" s="30" t="n"/>
-      <c r="R5" s="30" t="n"/>
-      <c r="S5" s="30" t="n"/>
-      <c r="T5" s="30" t="n"/>
-      <c r="U5" s="30" t="n"/>
-      <c r="V5" s="30" t="n"/>
-      <c r="W5" s="30" t="n"/>
+      <c r="B5" s="33" t="n"/>
+      <c r="C5" s="33" t="n"/>
+      <c r="D5" s="33" t="n"/>
+      <c r="E5" s="33" t="n"/>
+      <c r="F5" s="33" t="n"/>
+      <c r="G5" s="33" t="n"/>
+      <c r="H5" s="33" t="n"/>
+      <c r="I5" s="33" t="n"/>
+      <c r="J5" s="33" t="n"/>
+      <c r="K5" s="33" t="n"/>
+      <c r="L5" s="33" t="n"/>
+      <c r="M5" s="33" t="n"/>
+      <c r="N5" s="33" t="n"/>
+      <c r="O5" s="33" t="n"/>
+      <c r="P5" s="33" t="n"/>
+      <c r="Q5" s="33" t="n"/>
+      <c r="R5" s="33" t="n"/>
+      <c r="S5" s="33" t="n"/>
+      <c r="T5" s="33" t="n"/>
+      <c r="U5" s="33" t="n"/>
+      <c r="V5" s="33" t="n"/>
+      <c r="W5" s="33" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="30">
+      <c r="A6" s="33">
         <f>IF(B6="","","INT-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B6" s="30" t="n"/>
-      <c r="C6" s="30" t="n"/>
-      <c r="D6" s="30" t="n"/>
-      <c r="E6" s="30" t="n"/>
-      <c r="F6" s="30" t="n"/>
-      <c r="G6" s="30" t="n"/>
-      <c r="H6" s="30" t="n"/>
-      <c r="I6" s="30" t="n"/>
-      <c r="J6" s="30" t="n"/>
-      <c r="K6" s="30" t="n"/>
-      <c r="L6" s="30" t="n"/>
-      <c r="M6" s="30" t="n"/>
-      <c r="N6" s="30" t="n"/>
-      <c r="O6" s="30" t="n"/>
-      <c r="P6" s="30" t="n"/>
-      <c r="Q6" s="30" t="n"/>
-      <c r="R6" s="30" t="n"/>
-      <c r="S6" s="30" t="n"/>
-      <c r="T6" s="30" t="n"/>
-      <c r="U6" s="30" t="n"/>
-      <c r="V6" s="30" t="n"/>
-      <c r="W6" s="30" t="n"/>
+      <c r="B6" s="33" t="n"/>
+      <c r="C6" s="33" t="n"/>
+      <c r="D6" s="33" t="n"/>
+      <c r="E6" s="33" t="n"/>
+      <c r="F6" s="33" t="n"/>
+      <c r="G6" s="33" t="n"/>
+      <c r="H6" s="33" t="n"/>
+      <c r="I6" s="33" t="n"/>
+      <c r="J6" s="33" t="n"/>
+      <c r="K6" s="33" t="n"/>
+      <c r="L6" s="33" t="n"/>
+      <c r="M6" s="33" t="n"/>
+      <c r="N6" s="33" t="n"/>
+      <c r="O6" s="33" t="n"/>
+      <c r="P6" s="33" t="n"/>
+      <c r="Q6" s="33" t="n"/>
+      <c r="R6" s="33" t="n"/>
+      <c r="S6" s="33" t="n"/>
+      <c r="T6" s="33" t="n"/>
+      <c r="U6" s="33" t="n"/>
+      <c r="V6" s="33" t="n"/>
+      <c r="W6" s="33" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:W1"/>
@@ -5433,361 +6535,361 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>OpsID</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="32" t="inlineStr">
         <is>
           <t>OpsName</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="32" t="inlineStr">
         <is>
           <t>OpsDate</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="32" t="inlineStr">
         <is>
           <t>OpsType</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="32" t="inlineStr">
         <is>
           <t>LinkedIntelID</t>
         </is>
       </c>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" s="32" t="inlineStr">
         <is>
           <t>Parish</t>
         </is>
       </c>
-      <c r="G1" s="29" t="inlineStr">
+      <c r="G1" s="32" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="H1" s="29" t="inlineStr">
+      <c r="H1" s="32" t="inlineStr">
         <is>
           <t>WarrantObtained</t>
         </is>
       </c>
-      <c r="I1" s="29" t="inlineStr">
+      <c r="I1" s="32" t="inlineStr">
         <is>
           <t>WarrantBasis</t>
         </is>
       </c>
-      <c r="J1" s="29" t="inlineStr">
+      <c r="J1" s="32" t="inlineStr">
         <is>
           <t>WarrantNumber</t>
         </is>
       </c>
-      <c r="K1" s="29" t="inlineStr">
+      <c r="K1" s="32" t="inlineStr">
         <is>
           <t>IssuingJP</t>
         </is>
       </c>
-      <c r="L1" s="29" t="inlineStr">
+      <c r="L1" s="32" t="inlineStr">
         <is>
           <t>AuthorizingOfficer</t>
         </is>
       </c>
-      <c r="M1" s="29" t="inlineStr">
+      <c r="M1" s="32" t="inlineStr">
         <is>
           <t>AuthorizingRank</t>
         </is>
       </c>
-      <c r="N1" s="29" t="inlineStr">
+      <c r="N1" s="32" t="inlineStr">
         <is>
           <t>TeamLeader</t>
         </is>
       </c>
-      <c r="O1" s="29" t="inlineStr">
+      <c r="O1" s="32" t="inlineStr">
         <is>
           <t>TeamLeaderRank</t>
         </is>
       </c>
-      <c r="P1" s="29" t="inlineStr">
+      <c r="P1" s="32" t="inlineStr">
         <is>
           <t>TeamSize</t>
         </is>
       </c>
-      <c r="Q1" s="29" t="inlineStr">
+      <c r="Q1" s="32" t="inlineStr">
         <is>
           <t>InspectorPresent</t>
         </is>
       </c>
-      <c r="R1" s="29" t="inlineStr">
+      <c r="R1" s="32" t="inlineStr">
         <is>
           <t>BodyCamActivated</t>
         </is>
       </c>
-      <c r="S1" s="29" t="inlineStr">
+      <c r="S1" s="32" t="inlineStr">
         <is>
           <t>StartTime</t>
         </is>
       </c>
-      <c r="T1" s="29" t="inlineStr">
+      <c r="T1" s="32" t="inlineStr">
         <is>
           <t>EndTime</t>
         </is>
       </c>
-      <c r="U1" s="29" t="inlineStr">
+      <c r="U1" s="32" t="inlineStr">
         <is>
           <t>Outcome</t>
         </is>
       </c>
-      <c r="V1" s="29" t="inlineStr">
+      <c r="V1" s="32" t="inlineStr">
         <is>
           <t>FirearmsSeized</t>
         </is>
       </c>
-      <c r="W1" s="29" t="inlineStr">
+      <c r="W1" s="32" t="inlineStr">
         <is>
           <t>AmmunitionSeized</t>
         </is>
       </c>
-      <c r="X1" s="29" t="inlineStr">
+      <c r="X1" s="32" t="inlineStr">
         <is>
           <t>NarcoticsSeized_kg</t>
         </is>
       </c>
-      <c r="Y1" s="29" t="inlineStr">
+      <c r="Y1" s="32" t="inlineStr">
         <is>
           <t>CashSeized_JMD</t>
         </is>
       </c>
-      <c r="Z1" s="29" t="inlineStr">
+      <c r="Z1" s="32" t="inlineStr">
         <is>
           <t>VehiclesSeized</t>
         </is>
       </c>
-      <c r="AA1" s="29" t="inlineStr">
+      <c r="AA1" s="32" t="inlineStr">
         <is>
           <t>OtherExhibits</t>
         </is>
       </c>
-      <c r="AB1" s="29" t="inlineStr">
+      <c r="AB1" s="32" t="inlineStr">
         <is>
           <t>ArrestsMade</t>
         </is>
       </c>
-      <c r="AC1" s="29" t="inlineStr">
+      <c r="AC1" s="32" t="inlineStr">
         <is>
           <t>AfterActionCompleted</t>
         </is>
       </c>
-      <c r="AD1" s="29" t="inlineStr">
+      <c r="AD1" s="32" t="inlineStr">
         <is>
           <t>AfterActionNotes</t>
         </is>
       </c>
-      <c r="AE1" s="29" t="inlineStr">
+      <c r="AE1" s="32" t="inlineStr">
         <is>
           <t>INCOMPlianceFlags</t>
         </is>
       </c>
-      <c r="AF1" s="29" t="inlineStr">
+      <c r="AF1" s="32" t="inlineStr">
         <is>
           <t>CreatedBy</t>
         </is>
       </c>
-      <c r="AG1" s="29" t="inlineStr">
+      <c r="AG1" s="32" t="inlineStr">
         <is>
           <t>CreatedDate</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30">
+      <c r="A2" s="33">
         <f>IF(C2="","","OPS-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B2" s="30" t="n"/>
-      <c r="C2" s="30" t="n"/>
-      <c r="D2" s="30" t="n"/>
-      <c r="E2" s="30" t="n"/>
-      <c r="F2" s="30" t="n"/>
-      <c r="G2" s="30" t="n"/>
-      <c r="H2" s="30" t="n"/>
-      <c r="I2" s="30" t="n"/>
-      <c r="J2" s="30" t="n"/>
-      <c r="K2" s="30" t="n"/>
-      <c r="L2" s="30" t="n"/>
-      <c r="M2" s="30" t="n"/>
-      <c r="N2" s="30" t="n"/>
-      <c r="O2" s="30" t="n"/>
-      <c r="P2" s="30" t="n"/>
-      <c r="Q2" s="30" t="n"/>
-      <c r="R2" s="30" t="n"/>
-      <c r="S2" s="30" t="n"/>
-      <c r="T2" s="30" t="n"/>
-      <c r="U2" s="30" t="n"/>
-      <c r="V2" s="30" t="n"/>
-      <c r="W2" s="30" t="n"/>
-      <c r="X2" s="30" t="n"/>
-      <c r="Y2" s="30" t="n"/>
-      <c r="Z2" s="30" t="n"/>
-      <c r="AA2" s="30" t="n"/>
-      <c r="AB2" s="30" t="n"/>
-      <c r="AC2" s="30" t="n"/>
-      <c r="AD2" s="30" t="n"/>
-      <c r="AE2" s="30" t="n"/>
-      <c r="AF2" s="30" t="n"/>
-      <c r="AG2" s="30" t="n"/>
+      <c r="B2" s="33" t="n"/>
+      <c r="C2" s="33" t="n"/>
+      <c r="D2" s="33" t="n"/>
+      <c r="E2" s="33" t="n"/>
+      <c r="F2" s="33" t="n"/>
+      <c r="G2" s="33" t="n"/>
+      <c r="H2" s="33" t="n"/>
+      <c r="I2" s="33" t="n"/>
+      <c r="J2" s="33" t="n"/>
+      <c r="K2" s="33" t="n"/>
+      <c r="L2" s="33" t="n"/>
+      <c r="M2" s="33" t="n"/>
+      <c r="N2" s="33" t="n"/>
+      <c r="O2" s="33" t="n"/>
+      <c r="P2" s="33" t="n"/>
+      <c r="Q2" s="33" t="n"/>
+      <c r="R2" s="33" t="n"/>
+      <c r="S2" s="33" t="n"/>
+      <c r="T2" s="33" t="n"/>
+      <c r="U2" s="33" t="n"/>
+      <c r="V2" s="33" t="n"/>
+      <c r="W2" s="33" t="n"/>
+      <c r="X2" s="33" t="n"/>
+      <c r="Y2" s="33" t="n"/>
+      <c r="Z2" s="33" t="n"/>
+      <c r="AA2" s="33" t="n"/>
+      <c r="AB2" s="33" t="n"/>
+      <c r="AC2" s="33" t="n"/>
+      <c r="AD2" s="33" t="n"/>
+      <c r="AE2" s="33" t="n"/>
+      <c r="AF2" s="33" t="n"/>
+      <c r="AG2" s="33" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="30">
+      <c r="A3" s="33">
         <f>IF(C3="","","OPS-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B3" s="30" t="n"/>
-      <c r="C3" s="30" t="n"/>
-      <c r="D3" s="30" t="n"/>
-      <c r="E3" s="30" t="n"/>
-      <c r="F3" s="30" t="n"/>
-      <c r="G3" s="30" t="n"/>
-      <c r="H3" s="30" t="n"/>
-      <c r="I3" s="30" t="n"/>
-      <c r="J3" s="30" t="n"/>
-      <c r="K3" s="30" t="n"/>
-      <c r="L3" s="30" t="n"/>
-      <c r="M3" s="30" t="n"/>
-      <c r="N3" s="30" t="n"/>
-      <c r="O3" s="30" t="n"/>
-      <c r="P3" s="30" t="n"/>
-      <c r="Q3" s="30" t="n"/>
-      <c r="R3" s="30" t="n"/>
-      <c r="S3" s="30" t="n"/>
-      <c r="T3" s="30" t="n"/>
-      <c r="U3" s="30" t="n"/>
-      <c r="V3" s="30" t="n"/>
-      <c r="W3" s="30" t="n"/>
-      <c r="X3" s="30" t="n"/>
-      <c r="Y3" s="30" t="n"/>
-      <c r="Z3" s="30" t="n"/>
-      <c r="AA3" s="30" t="n"/>
-      <c r="AB3" s="30" t="n"/>
-      <c r="AC3" s="30" t="n"/>
-      <c r="AD3" s="30" t="n"/>
-      <c r="AE3" s="30" t="n"/>
-      <c r="AF3" s="30" t="n"/>
-      <c r="AG3" s="30" t="n"/>
+      <c r="B3" s="33" t="n"/>
+      <c r="C3" s="33" t="n"/>
+      <c r="D3" s="33" t="n"/>
+      <c r="E3" s="33" t="n"/>
+      <c r="F3" s="33" t="n"/>
+      <c r="G3" s="33" t="n"/>
+      <c r="H3" s="33" t="n"/>
+      <c r="I3" s="33" t="n"/>
+      <c r="J3" s="33" t="n"/>
+      <c r="K3" s="33" t="n"/>
+      <c r="L3" s="33" t="n"/>
+      <c r="M3" s="33" t="n"/>
+      <c r="N3" s="33" t="n"/>
+      <c r="O3" s="33" t="n"/>
+      <c r="P3" s="33" t="n"/>
+      <c r="Q3" s="33" t="n"/>
+      <c r="R3" s="33" t="n"/>
+      <c r="S3" s="33" t="n"/>
+      <c r="T3" s="33" t="n"/>
+      <c r="U3" s="33" t="n"/>
+      <c r="V3" s="33" t="n"/>
+      <c r="W3" s="33" t="n"/>
+      <c r="X3" s="33" t="n"/>
+      <c r="Y3" s="33" t="n"/>
+      <c r="Z3" s="33" t="n"/>
+      <c r="AA3" s="33" t="n"/>
+      <c r="AB3" s="33" t="n"/>
+      <c r="AC3" s="33" t="n"/>
+      <c r="AD3" s="33" t="n"/>
+      <c r="AE3" s="33" t="n"/>
+      <c r="AF3" s="33" t="n"/>
+      <c r="AG3" s="33" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="30">
+      <c r="A4" s="33">
         <f>IF(C4="","","OPS-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B4" s="30" t="n"/>
-      <c r="C4" s="30" t="n"/>
-      <c r="D4" s="30" t="n"/>
-      <c r="E4" s="30" t="n"/>
-      <c r="F4" s="30" t="n"/>
-      <c r="G4" s="30" t="n"/>
-      <c r="H4" s="30" t="n"/>
-      <c r="I4" s="30" t="n"/>
-      <c r="J4" s="30" t="n"/>
-      <c r="K4" s="30" t="n"/>
-      <c r="L4" s="30" t="n"/>
-      <c r="M4" s="30" t="n"/>
-      <c r="N4" s="30" t="n"/>
-      <c r="O4" s="30" t="n"/>
-      <c r="P4" s="30" t="n"/>
-      <c r="Q4" s="30" t="n"/>
-      <c r="R4" s="30" t="n"/>
-      <c r="S4" s="30" t="n"/>
-      <c r="T4" s="30" t="n"/>
-      <c r="U4" s="30" t="n"/>
-      <c r="V4" s="30" t="n"/>
-      <c r="W4" s="30" t="n"/>
-      <c r="X4" s="30" t="n"/>
-      <c r="Y4" s="30" t="n"/>
-      <c r="Z4" s="30" t="n"/>
-      <c r="AA4" s="30" t="n"/>
-      <c r="AB4" s="30" t="n"/>
-      <c r="AC4" s="30" t="n"/>
-      <c r="AD4" s="30" t="n"/>
-      <c r="AE4" s="30" t="n"/>
-      <c r="AF4" s="30" t="n"/>
-      <c r="AG4" s="30" t="n"/>
+      <c r="B4" s="33" t="n"/>
+      <c r="C4" s="33" t="n"/>
+      <c r="D4" s="33" t="n"/>
+      <c r="E4" s="33" t="n"/>
+      <c r="F4" s="33" t="n"/>
+      <c r="G4" s="33" t="n"/>
+      <c r="H4" s="33" t="n"/>
+      <c r="I4" s="33" t="n"/>
+      <c r="J4" s="33" t="n"/>
+      <c r="K4" s="33" t="n"/>
+      <c r="L4" s="33" t="n"/>
+      <c r="M4" s="33" t="n"/>
+      <c r="N4" s="33" t="n"/>
+      <c r="O4" s="33" t="n"/>
+      <c r="P4" s="33" t="n"/>
+      <c r="Q4" s="33" t="n"/>
+      <c r="R4" s="33" t="n"/>
+      <c r="S4" s="33" t="n"/>
+      <c r="T4" s="33" t="n"/>
+      <c r="U4" s="33" t="n"/>
+      <c r="V4" s="33" t="n"/>
+      <c r="W4" s="33" t="n"/>
+      <c r="X4" s="33" t="n"/>
+      <c r="Y4" s="33" t="n"/>
+      <c r="Z4" s="33" t="n"/>
+      <c r="AA4" s="33" t="n"/>
+      <c r="AB4" s="33" t="n"/>
+      <c r="AC4" s="33" t="n"/>
+      <c r="AD4" s="33" t="n"/>
+      <c r="AE4" s="33" t="n"/>
+      <c r="AF4" s="33" t="n"/>
+      <c r="AG4" s="33" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="30">
+      <c r="A5" s="33">
         <f>IF(C5="","","OPS-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B5" s="30" t="n"/>
-      <c r="C5" s="30" t="n"/>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="30" t="n"/>
-      <c r="F5" s="30" t="n"/>
-      <c r="G5" s="30" t="n"/>
-      <c r="H5" s="30" t="n"/>
-      <c r="I5" s="30" t="n"/>
-      <c r="J5" s="30" t="n"/>
-      <c r="K5" s="30" t="n"/>
-      <c r="L5" s="30" t="n"/>
-      <c r="M5" s="30" t="n"/>
-      <c r="N5" s="30" t="n"/>
-      <c r="O5" s="30" t="n"/>
-      <c r="P5" s="30" t="n"/>
-      <c r="Q5" s="30" t="n"/>
-      <c r="R5" s="30" t="n"/>
-      <c r="S5" s="30" t="n"/>
-      <c r="T5" s="30" t="n"/>
-      <c r="U5" s="30" t="n"/>
-      <c r="V5" s="30" t="n"/>
-      <c r="W5" s="30" t="n"/>
-      <c r="X5" s="30" t="n"/>
-      <c r="Y5" s="30" t="n"/>
-      <c r="Z5" s="30" t="n"/>
-      <c r="AA5" s="30" t="n"/>
-      <c r="AB5" s="30" t="n"/>
-      <c r="AC5" s="30" t="n"/>
-      <c r="AD5" s="30" t="n"/>
-      <c r="AE5" s="30" t="n"/>
-      <c r="AF5" s="30" t="n"/>
-      <c r="AG5" s="30" t="n"/>
+      <c r="B5" s="33" t="n"/>
+      <c r="C5" s="33" t="n"/>
+      <c r="D5" s="33" t="n"/>
+      <c r="E5" s="33" t="n"/>
+      <c r="F5" s="33" t="n"/>
+      <c r="G5" s="33" t="n"/>
+      <c r="H5" s="33" t="n"/>
+      <c r="I5" s="33" t="n"/>
+      <c r="J5" s="33" t="n"/>
+      <c r="K5" s="33" t="n"/>
+      <c r="L5" s="33" t="n"/>
+      <c r="M5" s="33" t="n"/>
+      <c r="N5" s="33" t="n"/>
+      <c r="O5" s="33" t="n"/>
+      <c r="P5" s="33" t="n"/>
+      <c r="Q5" s="33" t="n"/>
+      <c r="R5" s="33" t="n"/>
+      <c r="S5" s="33" t="n"/>
+      <c r="T5" s="33" t="n"/>
+      <c r="U5" s="33" t="n"/>
+      <c r="V5" s="33" t="n"/>
+      <c r="W5" s="33" t="n"/>
+      <c r="X5" s="33" t="n"/>
+      <c r="Y5" s="33" t="n"/>
+      <c r="Z5" s="33" t="n"/>
+      <c r="AA5" s="33" t="n"/>
+      <c r="AB5" s="33" t="n"/>
+      <c r="AC5" s="33" t="n"/>
+      <c r="AD5" s="33" t="n"/>
+      <c r="AE5" s="33" t="n"/>
+      <c r="AF5" s="33" t="n"/>
+      <c r="AG5" s="33" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="30">
+      <c r="A6" s="33">
         <f>IF(C6="","","OPS-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B6" s="30" t="n"/>
-      <c r="C6" s="30" t="n"/>
-      <c r="D6" s="30" t="n"/>
-      <c r="E6" s="30" t="n"/>
-      <c r="F6" s="30" t="n"/>
-      <c r="G6" s="30" t="n"/>
-      <c r="H6" s="30" t="n"/>
-      <c r="I6" s="30" t="n"/>
-      <c r="J6" s="30" t="n"/>
-      <c r="K6" s="30" t="n"/>
-      <c r="L6" s="30" t="n"/>
-      <c r="M6" s="30" t="n"/>
-      <c r="N6" s="30" t="n"/>
-      <c r="O6" s="30" t="n"/>
-      <c r="P6" s="30" t="n"/>
-      <c r="Q6" s="30" t="n"/>
-      <c r="R6" s="30" t="n"/>
-      <c r="S6" s="30" t="n"/>
-      <c r="T6" s="30" t="n"/>
-      <c r="U6" s="30" t="n"/>
-      <c r="V6" s="30" t="n"/>
-      <c r="W6" s="30" t="n"/>
-      <c r="X6" s="30" t="n"/>
-      <c r="Y6" s="30" t="n"/>
-      <c r="Z6" s="30" t="n"/>
-      <c r="AA6" s="30" t="n"/>
-      <c r="AB6" s="30" t="n"/>
-      <c r="AC6" s="30" t="n"/>
-      <c r="AD6" s="30" t="n"/>
-      <c r="AE6" s="30" t="n"/>
-      <c r="AF6" s="30" t="n"/>
-      <c r="AG6" s="30" t="n"/>
+      <c r="B6" s="33" t="n"/>
+      <c r="C6" s="33" t="n"/>
+      <c r="D6" s="33" t="n"/>
+      <c r="E6" s="33" t="n"/>
+      <c r="F6" s="33" t="n"/>
+      <c r="G6" s="33" t="n"/>
+      <c r="H6" s="33" t="n"/>
+      <c r="I6" s="33" t="n"/>
+      <c r="J6" s="33" t="n"/>
+      <c r="K6" s="33" t="n"/>
+      <c r="L6" s="33" t="n"/>
+      <c r="M6" s="33" t="n"/>
+      <c r="N6" s="33" t="n"/>
+      <c r="O6" s="33" t="n"/>
+      <c r="P6" s="33" t="n"/>
+      <c r="Q6" s="33" t="n"/>
+      <c r="R6" s="33" t="n"/>
+      <c r="S6" s="33" t="n"/>
+      <c r="T6" s="33" t="n"/>
+      <c r="U6" s="33" t="n"/>
+      <c r="V6" s="33" t="n"/>
+      <c r="W6" s="33" t="n"/>
+      <c r="X6" s="33" t="n"/>
+      <c r="Y6" s="33" t="n"/>
+      <c r="Z6" s="33" t="n"/>
+      <c r="AA6" s="33" t="n"/>
+      <c r="AB6" s="33" t="n"/>
+      <c r="AC6" s="33" t="n"/>
+      <c r="AD6" s="33" t="n"/>
+      <c r="AE6" s="33" t="n"/>
+      <c r="AF6" s="33" t="n"/>
+      <c r="AG6" s="33" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AG1"/>
@@ -5886,421 +6988,421 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>SeizureID</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="32" t="inlineStr">
         <is>
           <t>LinkedOpsID</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="32" t="inlineStr">
         <is>
           <t>LinkedCaseID</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="32" t="inlineStr">
         <is>
           <t>SeizureDate</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="32" t="inlineStr">
         <is>
           <t>SeizureLocation</t>
         </is>
       </c>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" s="32" t="inlineStr">
         <is>
           <t>Parish</t>
         </is>
       </c>
-      <c r="G1" s="29" t="inlineStr">
+      <c r="G1" s="32" t="inlineStr">
         <is>
           <t>FirearmType</t>
         </is>
       </c>
-      <c r="H1" s="29" t="inlineStr">
+      <c r="H1" s="32" t="inlineStr">
         <is>
           <t>Make</t>
         </is>
       </c>
-      <c r="I1" s="29" t="inlineStr">
+      <c r="I1" s="32" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="J1" s="29" t="inlineStr">
+      <c r="J1" s="32" t="inlineStr">
         <is>
           <t>Calibre</t>
         </is>
       </c>
-      <c r="K1" s="29" t="inlineStr">
+      <c r="K1" s="32" t="inlineStr">
         <is>
           <t>SerialNumber</t>
         </is>
       </c>
-      <c r="L1" s="29" t="inlineStr">
+      <c r="L1" s="32" t="inlineStr">
         <is>
           <t>SerialStatus</t>
         </is>
       </c>
-      <c r="M1" s="29" t="inlineStr">
+      <c r="M1" s="32" t="inlineStr">
         <is>
           <t>Condition</t>
         </is>
       </c>
-      <c r="N1" s="29" t="inlineStr">
+      <c r="N1" s="32" t="inlineStr">
         <is>
           <t>Loaded</t>
         </is>
       </c>
-      <c r="O1" s="29" t="inlineStr">
+      <c r="O1" s="32" t="inlineStr">
         <is>
           <t>RoundsChamber</t>
         </is>
       </c>
-      <c r="P1" s="29" t="inlineStr">
+      <c r="P1" s="32" t="inlineStr">
         <is>
           <t>MagazineCapacity</t>
         </is>
       </c>
-      <c r="Q1" s="29" t="inlineStr">
+      <c r="Q1" s="32" t="inlineStr">
         <is>
           <t>IBIS_Submitted</t>
         </is>
       </c>
-      <c r="R1" s="29" t="inlineStr">
+      <c r="R1" s="32" t="inlineStr">
         <is>
           <t>IBIS_SubmitDate</t>
         </is>
       </c>
-      <c r="S1" s="29" t="inlineStr">
+      <c r="S1" s="32" t="inlineStr">
         <is>
           <t>IBIS_Status</t>
         </is>
       </c>
-      <c r="T1" s="29" t="inlineStr">
+      <c r="T1" s="32" t="inlineStr">
         <is>
           <t>IBIS_MatchCaseID</t>
         </is>
       </c>
-      <c r="U1" s="29" t="inlineStr">
+      <c r="U1" s="32" t="inlineStr">
         <is>
           <t>IBIS_MatchDetails</t>
         </is>
       </c>
-      <c r="V1" s="29" t="inlineStr">
+      <c r="V1" s="32" t="inlineStr">
         <is>
           <t>eTrace_Submitted</t>
         </is>
       </c>
-      <c r="W1" s="29" t="inlineStr">
+      <c r="W1" s="32" t="inlineStr">
         <is>
           <t>eTrace_Status</t>
         </is>
       </c>
-      <c r="X1" s="29" t="inlineStr">
+      <c r="X1" s="32" t="inlineStr">
         <is>
           <t>eTrace_TraceNumber</t>
         </is>
       </c>
-      <c r="Y1" s="29" t="inlineStr">
+      <c r="Y1" s="32" t="inlineStr">
         <is>
           <t>CountryOfOrigin</t>
         </is>
       </c>
-      <c r="Z1" s="29" t="inlineStr">
+      <c r="Z1" s="32" t="inlineStr">
         <is>
           <t>LastKnownPurchaser</t>
         </is>
       </c>
-      <c r="AA1" s="29" t="inlineStr">
+      <c r="AA1" s="32" t="inlineStr">
         <is>
           <t>US_State</t>
         </is>
       </c>
-      <c r="AB1" s="29" t="inlineStr">
+      <c r="AB1" s="32" t="inlineStr">
         <is>
           <t>BallisticCertStatus</t>
         </is>
       </c>
-      <c r="AC1" s="29" t="inlineStr">
+      <c r="AC1" s="32" t="inlineStr">
         <is>
           <t>BallisticCertDate</t>
         </is>
       </c>
-      <c r="AD1" s="29" t="inlineStr">
+      <c r="AD1" s="32" t="inlineStr">
         <is>
           <t>BallisticExaminer</t>
         </is>
       </c>
-      <c r="AE1" s="29" t="inlineStr">
+      <c r="AE1" s="32" t="inlineStr">
         <is>
           <t>BallisticResult</t>
         </is>
       </c>
-      <c r="AF1" s="29" t="inlineStr">
+      <c r="AF1" s="32" t="inlineStr">
         <is>
           <t>ForensicRecoveryBag</t>
         </is>
       </c>
-      <c r="AG1" s="29" t="inlineStr">
+      <c r="AG1" s="32" t="inlineStr">
         <is>
           <t>EvidencePhotographed</t>
         </is>
       </c>
-      <c r="AH1" s="29" t="inlineStr">
+      <c r="AH1" s="32" t="inlineStr">
         <is>
           <t>MarkedByCommissioner</t>
         </is>
       </c>
-      <c r="AI1" s="29" t="inlineStr">
+      <c r="AI1" s="32" t="inlineStr">
         <is>
           <t>CourtReady</t>
         </is>
       </c>
-      <c r="AJ1" s="29" t="inlineStr">
+      <c r="AJ1" s="32" t="inlineStr">
         <is>
           <t>DisposalStatus</t>
         </is>
       </c>
-      <c r="AK1" s="29" t="inlineStr">
+      <c r="AK1" s="32" t="inlineStr">
         <is>
           <t>SeizingOfficer</t>
         </is>
       </c>
-      <c r="AL1" s="29" t="inlineStr">
+      <c r="AL1" s="32" t="inlineStr">
         <is>
           <t>CreatedBy</t>
         </is>
       </c>
-      <c r="AM1" s="29" t="inlineStr">
+      <c r="AM1" s="32" t="inlineStr">
         <is>
           <t>CreatedDate</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30">
+      <c r="A2" s="33">
         <f>IF(D2="","","FS-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B2" s="30" t="n"/>
-      <c r="C2" s="30" t="n"/>
-      <c r="D2" s="30" t="n"/>
-      <c r="E2" s="30" t="n"/>
-      <c r="F2" s="30" t="n"/>
-      <c r="G2" s="30" t="n"/>
-      <c r="H2" s="30" t="n"/>
-      <c r="I2" s="30" t="n"/>
-      <c r="J2" s="30" t="n"/>
-      <c r="K2" s="30" t="n"/>
-      <c r="L2" s="30" t="n"/>
-      <c r="M2" s="30" t="n"/>
-      <c r="N2" s="30" t="n"/>
-      <c r="O2" s="30" t="n"/>
-      <c r="P2" s="30" t="n"/>
-      <c r="Q2" s="30" t="n"/>
-      <c r="R2" s="30" t="n"/>
-      <c r="S2" s="30" t="n"/>
-      <c r="T2" s="30" t="n"/>
-      <c r="U2" s="30" t="n"/>
-      <c r="V2" s="30" t="n"/>
-      <c r="W2" s="30" t="n"/>
-      <c r="X2" s="30" t="n"/>
-      <c r="Y2" s="30" t="n"/>
-      <c r="Z2" s="30" t="n"/>
-      <c r="AA2" s="30" t="n"/>
-      <c r="AB2" s="30" t="n"/>
-      <c r="AC2" s="30" t="n"/>
-      <c r="AD2" s="30" t="n"/>
-      <c r="AE2" s="30" t="n"/>
-      <c r="AF2" s="30" t="n"/>
-      <c r="AG2" s="30" t="n"/>
-      <c r="AH2" s="30" t="n"/>
-      <c r="AI2" s="30" t="n"/>
-      <c r="AJ2" s="30" t="n"/>
-      <c r="AK2" s="30" t="n"/>
-      <c r="AL2" s="30" t="n"/>
-      <c r="AM2" s="30" t="n"/>
+      <c r="B2" s="33" t="n"/>
+      <c r="C2" s="33" t="n"/>
+      <c r="D2" s="33" t="n"/>
+      <c r="E2" s="33" t="n"/>
+      <c r="F2" s="33" t="n"/>
+      <c r="G2" s="33" t="n"/>
+      <c r="H2" s="33" t="n"/>
+      <c r="I2" s="33" t="n"/>
+      <c r="J2" s="33" t="n"/>
+      <c r="K2" s="33" t="n"/>
+      <c r="L2" s="33" t="n"/>
+      <c r="M2" s="33" t="n"/>
+      <c r="N2" s="33" t="n"/>
+      <c r="O2" s="33" t="n"/>
+      <c r="P2" s="33" t="n"/>
+      <c r="Q2" s="33" t="n"/>
+      <c r="R2" s="33" t="n"/>
+      <c r="S2" s="33" t="n"/>
+      <c r="T2" s="33" t="n"/>
+      <c r="U2" s="33" t="n"/>
+      <c r="V2" s="33" t="n"/>
+      <c r="W2" s="33" t="n"/>
+      <c r="X2" s="33" t="n"/>
+      <c r="Y2" s="33" t="n"/>
+      <c r="Z2" s="33" t="n"/>
+      <c r="AA2" s="33" t="n"/>
+      <c r="AB2" s="33" t="n"/>
+      <c r="AC2" s="33" t="n"/>
+      <c r="AD2" s="33" t="n"/>
+      <c r="AE2" s="33" t="n"/>
+      <c r="AF2" s="33" t="n"/>
+      <c r="AG2" s="33" t="n"/>
+      <c r="AH2" s="33" t="n"/>
+      <c r="AI2" s="33" t="n"/>
+      <c r="AJ2" s="33" t="n"/>
+      <c r="AK2" s="33" t="n"/>
+      <c r="AL2" s="33" t="n"/>
+      <c r="AM2" s="33" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="30">
+      <c r="A3" s="33">
         <f>IF(D3="","","FS-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B3" s="30" t="n"/>
-      <c r="C3" s="30" t="n"/>
-      <c r="D3" s="30" t="n"/>
-      <c r="E3" s="30" t="n"/>
-      <c r="F3" s="30" t="n"/>
-      <c r="G3" s="30" t="n"/>
-      <c r="H3" s="30" t="n"/>
-      <c r="I3" s="30" t="n"/>
-      <c r="J3" s="30" t="n"/>
-      <c r="K3" s="30" t="n"/>
-      <c r="L3" s="30" t="n"/>
-      <c r="M3" s="30" t="n"/>
-      <c r="N3" s="30" t="n"/>
-      <c r="O3" s="30" t="n"/>
-      <c r="P3" s="30" t="n"/>
-      <c r="Q3" s="30" t="n"/>
-      <c r="R3" s="30" t="n"/>
-      <c r="S3" s="30" t="n"/>
-      <c r="T3" s="30" t="n"/>
-      <c r="U3" s="30" t="n"/>
-      <c r="V3" s="30" t="n"/>
-      <c r="W3" s="30" t="n"/>
-      <c r="X3" s="30" t="n"/>
-      <c r="Y3" s="30" t="n"/>
-      <c r="Z3" s="30" t="n"/>
-      <c r="AA3" s="30" t="n"/>
-      <c r="AB3" s="30" t="n"/>
-      <c r="AC3" s="30" t="n"/>
-      <c r="AD3" s="30" t="n"/>
-      <c r="AE3" s="30" t="n"/>
-      <c r="AF3" s="30" t="n"/>
-      <c r="AG3" s="30" t="n"/>
-      <c r="AH3" s="30" t="n"/>
-      <c r="AI3" s="30" t="n"/>
-      <c r="AJ3" s="30" t="n"/>
-      <c r="AK3" s="30" t="n"/>
-      <c r="AL3" s="30" t="n"/>
-      <c r="AM3" s="30" t="n"/>
+      <c r="B3" s="33" t="n"/>
+      <c r="C3" s="33" t="n"/>
+      <c r="D3" s="33" t="n"/>
+      <c r="E3" s="33" t="n"/>
+      <c r="F3" s="33" t="n"/>
+      <c r="G3" s="33" t="n"/>
+      <c r="H3" s="33" t="n"/>
+      <c r="I3" s="33" t="n"/>
+      <c r="J3" s="33" t="n"/>
+      <c r="K3" s="33" t="n"/>
+      <c r="L3" s="33" t="n"/>
+      <c r="M3" s="33" t="n"/>
+      <c r="N3" s="33" t="n"/>
+      <c r="O3" s="33" t="n"/>
+      <c r="P3" s="33" t="n"/>
+      <c r="Q3" s="33" t="n"/>
+      <c r="R3" s="33" t="n"/>
+      <c r="S3" s="33" t="n"/>
+      <c r="T3" s="33" t="n"/>
+      <c r="U3" s="33" t="n"/>
+      <c r="V3" s="33" t="n"/>
+      <c r="W3" s="33" t="n"/>
+      <c r="X3" s="33" t="n"/>
+      <c r="Y3" s="33" t="n"/>
+      <c r="Z3" s="33" t="n"/>
+      <c r="AA3" s="33" t="n"/>
+      <c r="AB3" s="33" t="n"/>
+      <c r="AC3" s="33" t="n"/>
+      <c r="AD3" s="33" t="n"/>
+      <c r="AE3" s="33" t="n"/>
+      <c r="AF3" s="33" t="n"/>
+      <c r="AG3" s="33" t="n"/>
+      <c r="AH3" s="33" t="n"/>
+      <c r="AI3" s="33" t="n"/>
+      <c r="AJ3" s="33" t="n"/>
+      <c r="AK3" s="33" t="n"/>
+      <c r="AL3" s="33" t="n"/>
+      <c r="AM3" s="33" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="30">
+      <c r="A4" s="33">
         <f>IF(D4="","","FS-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B4" s="30" t="n"/>
-      <c r="C4" s="30" t="n"/>
-      <c r="D4" s="30" t="n"/>
-      <c r="E4" s="30" t="n"/>
-      <c r="F4" s="30" t="n"/>
-      <c r="G4" s="30" t="n"/>
-      <c r="H4" s="30" t="n"/>
-      <c r="I4" s="30" t="n"/>
-      <c r="J4" s="30" t="n"/>
-      <c r="K4" s="30" t="n"/>
-      <c r="L4" s="30" t="n"/>
-      <c r="M4" s="30" t="n"/>
-      <c r="N4" s="30" t="n"/>
-      <c r="O4" s="30" t="n"/>
-      <c r="P4" s="30" t="n"/>
-      <c r="Q4" s="30" t="n"/>
-      <c r="R4" s="30" t="n"/>
-      <c r="S4" s="30" t="n"/>
-      <c r="T4" s="30" t="n"/>
-      <c r="U4" s="30" t="n"/>
-      <c r="V4" s="30" t="n"/>
-      <c r="W4" s="30" t="n"/>
-      <c r="X4" s="30" t="n"/>
-      <c r="Y4" s="30" t="n"/>
-      <c r="Z4" s="30" t="n"/>
-      <c r="AA4" s="30" t="n"/>
-      <c r="AB4" s="30" t="n"/>
-      <c r="AC4" s="30" t="n"/>
-      <c r="AD4" s="30" t="n"/>
-      <c r="AE4" s="30" t="n"/>
-      <c r="AF4" s="30" t="n"/>
-      <c r="AG4" s="30" t="n"/>
-      <c r="AH4" s="30" t="n"/>
-      <c r="AI4" s="30" t="n"/>
-      <c r="AJ4" s="30" t="n"/>
-      <c r="AK4" s="30" t="n"/>
-      <c r="AL4" s="30" t="n"/>
-      <c r="AM4" s="30" t="n"/>
+      <c r="B4" s="33" t="n"/>
+      <c r="C4" s="33" t="n"/>
+      <c r="D4" s="33" t="n"/>
+      <c r="E4" s="33" t="n"/>
+      <c r="F4" s="33" t="n"/>
+      <c r="G4" s="33" t="n"/>
+      <c r="H4" s="33" t="n"/>
+      <c r="I4" s="33" t="n"/>
+      <c r="J4" s="33" t="n"/>
+      <c r="K4" s="33" t="n"/>
+      <c r="L4" s="33" t="n"/>
+      <c r="M4" s="33" t="n"/>
+      <c r="N4" s="33" t="n"/>
+      <c r="O4" s="33" t="n"/>
+      <c r="P4" s="33" t="n"/>
+      <c r="Q4" s="33" t="n"/>
+      <c r="R4" s="33" t="n"/>
+      <c r="S4" s="33" t="n"/>
+      <c r="T4" s="33" t="n"/>
+      <c r="U4" s="33" t="n"/>
+      <c r="V4" s="33" t="n"/>
+      <c r="W4" s="33" t="n"/>
+      <c r="X4" s="33" t="n"/>
+      <c r="Y4" s="33" t="n"/>
+      <c r="Z4" s="33" t="n"/>
+      <c r="AA4" s="33" t="n"/>
+      <c r="AB4" s="33" t="n"/>
+      <c r="AC4" s="33" t="n"/>
+      <c r="AD4" s="33" t="n"/>
+      <c r="AE4" s="33" t="n"/>
+      <c r="AF4" s="33" t="n"/>
+      <c r="AG4" s="33" t="n"/>
+      <c r="AH4" s="33" t="n"/>
+      <c r="AI4" s="33" t="n"/>
+      <c r="AJ4" s="33" t="n"/>
+      <c r="AK4" s="33" t="n"/>
+      <c r="AL4" s="33" t="n"/>
+      <c r="AM4" s="33" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="30">
+      <c r="A5" s="33">
         <f>IF(D5="","","FS-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B5" s="30" t="n"/>
-      <c r="C5" s="30" t="n"/>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="30" t="n"/>
-      <c r="F5" s="30" t="n"/>
-      <c r="G5" s="30" t="n"/>
-      <c r="H5" s="30" t="n"/>
-      <c r="I5" s="30" t="n"/>
-      <c r="J5" s="30" t="n"/>
-      <c r="K5" s="30" t="n"/>
-      <c r="L5" s="30" t="n"/>
-      <c r="M5" s="30" t="n"/>
-      <c r="N5" s="30" t="n"/>
-      <c r="O5" s="30" t="n"/>
-      <c r="P5" s="30" t="n"/>
-      <c r="Q5" s="30" t="n"/>
-      <c r="R5" s="30" t="n"/>
-      <c r="S5" s="30" t="n"/>
-      <c r="T5" s="30" t="n"/>
-      <c r="U5" s="30" t="n"/>
-      <c r="V5" s="30" t="n"/>
-      <c r="W5" s="30" t="n"/>
-      <c r="X5" s="30" t="n"/>
-      <c r="Y5" s="30" t="n"/>
-      <c r="Z5" s="30" t="n"/>
-      <c r="AA5" s="30" t="n"/>
-      <c r="AB5" s="30" t="n"/>
-      <c r="AC5" s="30" t="n"/>
-      <c r="AD5" s="30" t="n"/>
-      <c r="AE5" s="30" t="n"/>
-      <c r="AF5" s="30" t="n"/>
-      <c r="AG5" s="30" t="n"/>
-      <c r="AH5" s="30" t="n"/>
-      <c r="AI5" s="30" t="n"/>
-      <c r="AJ5" s="30" t="n"/>
-      <c r="AK5" s="30" t="n"/>
-      <c r="AL5" s="30" t="n"/>
-      <c r="AM5" s="30" t="n"/>
+      <c r="B5" s="33" t="n"/>
+      <c r="C5" s="33" t="n"/>
+      <c r="D5" s="33" t="n"/>
+      <c r="E5" s="33" t="n"/>
+      <c r="F5" s="33" t="n"/>
+      <c r="G5" s="33" t="n"/>
+      <c r="H5" s="33" t="n"/>
+      <c r="I5" s="33" t="n"/>
+      <c r="J5" s="33" t="n"/>
+      <c r="K5" s="33" t="n"/>
+      <c r="L5" s="33" t="n"/>
+      <c r="M5" s="33" t="n"/>
+      <c r="N5" s="33" t="n"/>
+      <c r="O5" s="33" t="n"/>
+      <c r="P5" s="33" t="n"/>
+      <c r="Q5" s="33" t="n"/>
+      <c r="R5" s="33" t="n"/>
+      <c r="S5" s="33" t="n"/>
+      <c r="T5" s="33" t="n"/>
+      <c r="U5" s="33" t="n"/>
+      <c r="V5" s="33" t="n"/>
+      <c r="W5" s="33" t="n"/>
+      <c r="X5" s="33" t="n"/>
+      <c r="Y5" s="33" t="n"/>
+      <c r="Z5" s="33" t="n"/>
+      <c r="AA5" s="33" t="n"/>
+      <c r="AB5" s="33" t="n"/>
+      <c r="AC5" s="33" t="n"/>
+      <c r="AD5" s="33" t="n"/>
+      <c r="AE5" s="33" t="n"/>
+      <c r="AF5" s="33" t="n"/>
+      <c r="AG5" s="33" t="n"/>
+      <c r="AH5" s="33" t="n"/>
+      <c r="AI5" s="33" t="n"/>
+      <c r="AJ5" s="33" t="n"/>
+      <c r="AK5" s="33" t="n"/>
+      <c r="AL5" s="33" t="n"/>
+      <c r="AM5" s="33" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="30">
+      <c r="A6" s="33">
         <f>IF(D6="","","FS-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B6" s="30" t="n"/>
-      <c r="C6" s="30" t="n"/>
-      <c r="D6" s="30" t="n"/>
-      <c r="E6" s="30" t="n"/>
-      <c r="F6" s="30" t="n"/>
-      <c r="G6" s="30" t="n"/>
-      <c r="H6" s="30" t="n"/>
-      <c r="I6" s="30" t="n"/>
-      <c r="J6" s="30" t="n"/>
-      <c r="K6" s="30" t="n"/>
-      <c r="L6" s="30" t="n"/>
-      <c r="M6" s="30" t="n"/>
-      <c r="N6" s="30" t="n"/>
-      <c r="O6" s="30" t="n"/>
-      <c r="P6" s="30" t="n"/>
-      <c r="Q6" s="30" t="n"/>
-      <c r="R6" s="30" t="n"/>
-      <c r="S6" s="30" t="n"/>
-      <c r="T6" s="30" t="n"/>
-      <c r="U6" s="30" t="n"/>
-      <c r="V6" s="30" t="n"/>
-      <c r="W6" s="30" t="n"/>
-      <c r="X6" s="30" t="n"/>
-      <c r="Y6" s="30" t="n"/>
-      <c r="Z6" s="30" t="n"/>
-      <c r="AA6" s="30" t="n"/>
-      <c r="AB6" s="30" t="n"/>
-      <c r="AC6" s="30" t="n"/>
-      <c r="AD6" s="30" t="n"/>
-      <c r="AE6" s="30" t="n"/>
-      <c r="AF6" s="30" t="n"/>
-      <c r="AG6" s="30" t="n"/>
-      <c r="AH6" s="30" t="n"/>
-      <c r="AI6" s="30" t="n"/>
-      <c r="AJ6" s="30" t="n"/>
-      <c r="AK6" s="30" t="n"/>
-      <c r="AL6" s="30" t="n"/>
-      <c r="AM6" s="30" t="n"/>
+      <c r="B6" s="33" t="n"/>
+      <c r="C6" s="33" t="n"/>
+      <c r="D6" s="33" t="n"/>
+      <c r="E6" s="33" t="n"/>
+      <c r="F6" s="33" t="n"/>
+      <c r="G6" s="33" t="n"/>
+      <c r="H6" s="33" t="n"/>
+      <c r="I6" s="33" t="n"/>
+      <c r="J6" s="33" t="n"/>
+      <c r="K6" s="33" t="n"/>
+      <c r="L6" s="33" t="n"/>
+      <c r="M6" s="33" t="n"/>
+      <c r="N6" s="33" t="n"/>
+      <c r="O6" s="33" t="n"/>
+      <c r="P6" s="33" t="n"/>
+      <c r="Q6" s="33" t="n"/>
+      <c r="R6" s="33" t="n"/>
+      <c r="S6" s="33" t="n"/>
+      <c r="T6" s="33" t="n"/>
+      <c r="U6" s="33" t="n"/>
+      <c r="V6" s="33" t="n"/>
+      <c r="W6" s="33" t="n"/>
+      <c r="X6" s="33" t="n"/>
+      <c r="Y6" s="33" t="n"/>
+      <c r="Z6" s="33" t="n"/>
+      <c r="AA6" s="33" t="n"/>
+      <c r="AB6" s="33" t="n"/>
+      <c r="AC6" s="33" t="n"/>
+      <c r="AD6" s="33" t="n"/>
+      <c r="AE6" s="33" t="n"/>
+      <c r="AF6" s="33" t="n"/>
+      <c r="AG6" s="33" t="n"/>
+      <c r="AH6" s="33" t="n"/>
+      <c r="AI6" s="33" t="n"/>
+      <c r="AJ6" s="33" t="n"/>
+      <c r="AK6" s="33" t="n"/>
+      <c r="AL6" s="33" t="n"/>
+      <c r="AM6" s="33" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AM1"/>
@@ -6400,356 +7502,356 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>SeizureID</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="32" t="inlineStr">
         <is>
           <t>LinkedOpsID</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="32" t="inlineStr">
         <is>
           <t>LinkedCaseID</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="32" t="inlineStr">
         <is>
           <t>SeizureDate</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="32" t="inlineStr">
         <is>
           <t>SeizureLocation</t>
         </is>
       </c>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" s="32" t="inlineStr">
         <is>
           <t>Parish</t>
         </is>
       </c>
-      <c r="G1" s="29" t="inlineStr">
+      <c r="G1" s="32" t="inlineStr">
         <is>
           <t>DrugType</t>
         </is>
       </c>
-      <c r="H1" s="29" t="inlineStr">
+      <c r="H1" s="32" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="I1" s="29" t="inlineStr">
+      <c r="I1" s="32" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="J1" s="29" t="inlineStr">
+      <c r="J1" s="32" t="inlineStr">
         <is>
           <t>PackagingDesc</t>
         </is>
       </c>
-      <c r="K1" s="29" t="inlineStr">
+      <c r="K1" s="32" t="inlineStr">
         <is>
           <t>EstStreetValue_JMD</t>
         </is>
       </c>
-      <c r="L1" s="29" t="inlineStr">
+      <c r="L1" s="32" t="inlineStr">
         <is>
           <t>Concealment</t>
         </is>
       </c>
-      <c r="M1" s="29" t="inlineStr">
+      <c r="M1" s="32" t="inlineStr">
         <is>
           <t>FieldTestConducted</t>
         </is>
       </c>
-      <c r="N1" s="29" t="inlineStr">
+      <c r="N1" s="32" t="inlineStr">
         <is>
           <t>FieldTestResult</t>
         </is>
       </c>
-      <c r="O1" s="29" t="inlineStr">
+      <c r="O1" s="32" t="inlineStr">
         <is>
           <t>SubmittedToIFSLM</t>
         </is>
       </c>
-      <c r="P1" s="29" t="inlineStr">
+      <c r="P1" s="32" t="inlineStr">
         <is>
           <t>IFSLM_SubmitDate</t>
         </is>
       </c>
-      <c r="Q1" s="29" t="inlineStr">
+      <c r="Q1" s="32" t="inlineStr">
         <is>
           <t>IFSLM_LabNumber</t>
         </is>
       </c>
-      <c r="R1" s="29" t="inlineStr">
+      <c r="R1" s="32" t="inlineStr">
         <is>
           <t>ForensicCertStatus</t>
         </is>
       </c>
-      <c r="S1" s="29" t="inlineStr">
+      <c r="S1" s="32" t="inlineStr">
         <is>
           <t>ForensicCertDate</t>
         </is>
       </c>
-      <c r="T1" s="29" t="inlineStr">
+      <c r="T1" s="32" t="inlineStr">
         <is>
           <t>ForensicResult</t>
         </is>
       </c>
-      <c r="U1" s="29" t="inlineStr">
+      <c r="U1" s="32" t="inlineStr">
         <is>
           <t>AnalystName</t>
         </is>
       </c>
-      <c r="V1" s="29" t="inlineStr">
+      <c r="V1" s="32" t="inlineStr">
         <is>
           <t>LinkedToGunTrade</t>
         </is>
       </c>
-      <c r="W1" s="29" t="inlineStr">
+      <c r="W1" s="32" t="inlineStr">
         <is>
           <t>EstEquivFirearms</t>
         </is>
       </c>
-      <c r="X1" s="29" t="inlineStr">
+      <c r="X1" s="32" t="inlineStr">
         <is>
           <t>DisposalAuthorized</t>
         </is>
       </c>
-      <c r="Y1" s="29" t="inlineStr">
+      <c r="Y1" s="32" t="inlineStr">
         <is>
           <t>DisposalAuthorizedBy</t>
         </is>
       </c>
-      <c r="Z1" s="29" t="inlineStr">
+      <c r="Z1" s="32" t="inlineStr">
         <is>
           <t>DisposalDate</t>
         </is>
       </c>
-      <c r="AA1" s="29" t="inlineStr">
+      <c r="AA1" s="32" t="inlineStr">
         <is>
           <t>DisposalWitnesses</t>
         </is>
       </c>
-      <c r="AB1" s="29" t="inlineStr">
+      <c r="AB1" s="32" t="inlineStr">
         <is>
           <t>CourtReady</t>
         </is>
       </c>
-      <c r="AC1" s="29" t="inlineStr">
+      <c r="AC1" s="32" t="inlineStr">
         <is>
           <t>SeizingOfficer</t>
         </is>
       </c>
-      <c r="AD1" s="29" t="inlineStr">
+      <c r="AD1" s="32" t="inlineStr">
         <is>
           <t>CreatedBy</t>
         </is>
       </c>
-      <c r="AE1" s="29" t="inlineStr">
+      <c r="AE1" s="32" t="inlineStr">
         <is>
           <t>CreatedDate</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30">
+      <c r="A2" s="33">
         <f>IF(D2="","","NS-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B2" s="30" t="n"/>
-      <c r="C2" s="30" t="n"/>
-      <c r="D2" s="30" t="n"/>
-      <c r="E2" s="30" t="n"/>
-      <c r="F2" s="30" t="n"/>
-      <c r="G2" s="30" t="n"/>
-      <c r="H2" s="30" t="n"/>
-      <c r="I2" s="30" t="n"/>
-      <c r="J2" s="30" t="n"/>
-      <c r="K2" s="30" t="n"/>
-      <c r="L2" s="30" t="n"/>
-      <c r="M2" s="30" t="n"/>
-      <c r="N2" s="30" t="n"/>
-      <c r="O2" s="30" t="n"/>
-      <c r="P2" s="30" t="n"/>
-      <c r="Q2" s="30" t="n"/>
-      <c r="R2" s="30" t="n"/>
-      <c r="S2" s="30" t="n"/>
-      <c r="T2" s="30" t="n"/>
-      <c r="U2" s="30" t="n"/>
-      <c r="V2" s="30" t="n"/>
-      <c r="W2" s="30">
+      <c r="B2" s="33" t="n"/>
+      <c r="C2" s="33" t="n"/>
+      <c r="D2" s="33" t="n"/>
+      <c r="E2" s="33" t="n"/>
+      <c r="F2" s="33" t="n"/>
+      <c r="G2" s="33" t="n"/>
+      <c r="H2" s="33" t="n"/>
+      <c r="I2" s="33" t="n"/>
+      <c r="J2" s="33" t="n"/>
+      <c r="K2" s="33" t="n"/>
+      <c r="L2" s="33" t="n"/>
+      <c r="M2" s="33" t="n"/>
+      <c r="N2" s="33" t="n"/>
+      <c r="O2" s="33" t="n"/>
+      <c r="P2" s="33" t="n"/>
+      <c r="Q2" s="33" t="n"/>
+      <c r="R2" s="33" t="n"/>
+      <c r="S2" s="33" t="n"/>
+      <c r="T2" s="33" t="n"/>
+      <c r="U2" s="33" t="n"/>
+      <c r="V2" s="33" t="n"/>
+      <c r="W2" s="33">
         <f>IF(AND(V2="Yes",I2="lbs"),ROUND(H2/50,0),"")</f>
         <v/>
       </c>
-      <c r="X2" s="30" t="n"/>
-      <c r="Y2" s="30" t="n"/>
-      <c r="Z2" s="30" t="n"/>
-      <c r="AA2" s="30" t="n"/>
-      <c r="AB2" s="30" t="n"/>
-      <c r="AC2" s="30" t="n"/>
-      <c r="AD2" s="30" t="n"/>
-      <c r="AE2" s="30" t="n"/>
+      <c r="X2" s="33" t="n"/>
+      <c r="Y2" s="33" t="n"/>
+      <c r="Z2" s="33" t="n"/>
+      <c r="AA2" s="33" t="n"/>
+      <c r="AB2" s="33" t="n"/>
+      <c r="AC2" s="33" t="n"/>
+      <c r="AD2" s="33" t="n"/>
+      <c r="AE2" s="33" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="30">
+      <c r="A3" s="33">
         <f>IF(D3="","","NS-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B3" s="30" t="n"/>
-      <c r="C3" s="30" t="n"/>
-      <c r="D3" s="30" t="n"/>
-      <c r="E3" s="30" t="n"/>
-      <c r="F3" s="30" t="n"/>
-      <c r="G3" s="30" t="n"/>
-      <c r="H3" s="30" t="n"/>
-      <c r="I3" s="30" t="n"/>
-      <c r="J3" s="30" t="n"/>
-      <c r="K3" s="30" t="n"/>
-      <c r="L3" s="30" t="n"/>
-      <c r="M3" s="30" t="n"/>
-      <c r="N3" s="30" t="n"/>
-      <c r="O3" s="30" t="n"/>
-      <c r="P3" s="30" t="n"/>
-      <c r="Q3" s="30" t="n"/>
-      <c r="R3" s="30" t="n"/>
-      <c r="S3" s="30" t="n"/>
-      <c r="T3" s="30" t="n"/>
-      <c r="U3" s="30" t="n"/>
-      <c r="V3" s="30" t="n"/>
-      <c r="W3" s="30">
+      <c r="B3" s="33" t="n"/>
+      <c r="C3" s="33" t="n"/>
+      <c r="D3" s="33" t="n"/>
+      <c r="E3" s="33" t="n"/>
+      <c r="F3" s="33" t="n"/>
+      <c r="G3" s="33" t="n"/>
+      <c r="H3" s="33" t="n"/>
+      <c r="I3" s="33" t="n"/>
+      <c r="J3" s="33" t="n"/>
+      <c r="K3" s="33" t="n"/>
+      <c r="L3" s="33" t="n"/>
+      <c r="M3" s="33" t="n"/>
+      <c r="N3" s="33" t="n"/>
+      <c r="O3" s="33" t="n"/>
+      <c r="P3" s="33" t="n"/>
+      <c r="Q3" s="33" t="n"/>
+      <c r="R3" s="33" t="n"/>
+      <c r="S3" s="33" t="n"/>
+      <c r="T3" s="33" t="n"/>
+      <c r="U3" s="33" t="n"/>
+      <c r="V3" s="33" t="n"/>
+      <c r="W3" s="33">
         <f>IF(AND(V3="Yes",I3="lbs"),ROUND(H3/50,0),"")</f>
         <v/>
       </c>
-      <c r="X3" s="30" t="n"/>
-      <c r="Y3" s="30" t="n"/>
-      <c r="Z3" s="30" t="n"/>
-      <c r="AA3" s="30" t="n"/>
-      <c r="AB3" s="30" t="n"/>
-      <c r="AC3" s="30" t="n"/>
-      <c r="AD3" s="30" t="n"/>
-      <c r="AE3" s="30" t="n"/>
+      <c r="X3" s="33" t="n"/>
+      <c r="Y3" s="33" t="n"/>
+      <c r="Z3" s="33" t="n"/>
+      <c r="AA3" s="33" t="n"/>
+      <c r="AB3" s="33" t="n"/>
+      <c r="AC3" s="33" t="n"/>
+      <c r="AD3" s="33" t="n"/>
+      <c r="AE3" s="33" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="30">
+      <c r="A4" s="33">
         <f>IF(D4="","","NS-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B4" s="30" t="n"/>
-      <c r="C4" s="30" t="n"/>
-      <c r="D4" s="30" t="n"/>
-      <c r="E4" s="30" t="n"/>
-      <c r="F4" s="30" t="n"/>
-      <c r="G4" s="30" t="n"/>
-      <c r="H4" s="30" t="n"/>
-      <c r="I4" s="30" t="n"/>
-      <c r="J4" s="30" t="n"/>
-      <c r="K4" s="30" t="n"/>
-      <c r="L4" s="30" t="n"/>
-      <c r="M4" s="30" t="n"/>
-      <c r="N4" s="30" t="n"/>
-      <c r="O4" s="30" t="n"/>
-      <c r="P4" s="30" t="n"/>
-      <c r="Q4" s="30" t="n"/>
-      <c r="R4" s="30" t="n"/>
-      <c r="S4" s="30" t="n"/>
-      <c r="T4" s="30" t="n"/>
-      <c r="U4" s="30" t="n"/>
-      <c r="V4" s="30" t="n"/>
-      <c r="W4" s="30">
+      <c r="B4" s="33" t="n"/>
+      <c r="C4" s="33" t="n"/>
+      <c r="D4" s="33" t="n"/>
+      <c r="E4" s="33" t="n"/>
+      <c r="F4" s="33" t="n"/>
+      <c r="G4" s="33" t="n"/>
+      <c r="H4" s="33" t="n"/>
+      <c r="I4" s="33" t="n"/>
+      <c r="J4" s="33" t="n"/>
+      <c r="K4" s="33" t="n"/>
+      <c r="L4" s="33" t="n"/>
+      <c r="M4" s="33" t="n"/>
+      <c r="N4" s="33" t="n"/>
+      <c r="O4" s="33" t="n"/>
+      <c r="P4" s="33" t="n"/>
+      <c r="Q4" s="33" t="n"/>
+      <c r="R4" s="33" t="n"/>
+      <c r="S4" s="33" t="n"/>
+      <c r="T4" s="33" t="n"/>
+      <c r="U4" s="33" t="n"/>
+      <c r="V4" s="33" t="n"/>
+      <c r="W4" s="33">
         <f>IF(AND(V4="Yes",I4="lbs"),ROUND(H4/50,0),"")</f>
         <v/>
       </c>
-      <c r="X4" s="30" t="n"/>
-      <c r="Y4" s="30" t="n"/>
-      <c r="Z4" s="30" t="n"/>
-      <c r="AA4" s="30" t="n"/>
-      <c r="AB4" s="30" t="n"/>
-      <c r="AC4" s="30" t="n"/>
-      <c r="AD4" s="30" t="n"/>
-      <c r="AE4" s="30" t="n"/>
+      <c r="X4" s="33" t="n"/>
+      <c r="Y4" s="33" t="n"/>
+      <c r="Z4" s="33" t="n"/>
+      <c r="AA4" s="33" t="n"/>
+      <c r="AB4" s="33" t="n"/>
+      <c r="AC4" s="33" t="n"/>
+      <c r="AD4" s="33" t="n"/>
+      <c r="AE4" s="33" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="30">
+      <c r="A5" s="33">
         <f>IF(D5="","","NS-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B5" s="30" t="n"/>
-      <c r="C5" s="30" t="n"/>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="30" t="n"/>
-      <c r="F5" s="30" t="n"/>
-      <c r="G5" s="30" t="n"/>
-      <c r="H5" s="30" t="n"/>
-      <c r="I5" s="30" t="n"/>
-      <c r="J5" s="30" t="n"/>
-      <c r="K5" s="30" t="n"/>
-      <c r="L5" s="30" t="n"/>
-      <c r="M5" s="30" t="n"/>
-      <c r="N5" s="30" t="n"/>
-      <c r="O5" s="30" t="n"/>
-      <c r="P5" s="30" t="n"/>
-      <c r="Q5" s="30" t="n"/>
-      <c r="R5" s="30" t="n"/>
-      <c r="S5" s="30" t="n"/>
-      <c r="T5" s="30" t="n"/>
-      <c r="U5" s="30" t="n"/>
-      <c r="V5" s="30" t="n"/>
-      <c r="W5" s="30">
+      <c r="B5" s="33" t="n"/>
+      <c r="C5" s="33" t="n"/>
+      <c r="D5" s="33" t="n"/>
+      <c r="E5" s="33" t="n"/>
+      <c r="F5" s="33" t="n"/>
+      <c r="G5" s="33" t="n"/>
+      <c r="H5" s="33" t="n"/>
+      <c r="I5" s="33" t="n"/>
+      <c r="J5" s="33" t="n"/>
+      <c r="K5" s="33" t="n"/>
+      <c r="L5" s="33" t="n"/>
+      <c r="M5" s="33" t="n"/>
+      <c r="N5" s="33" t="n"/>
+      <c r="O5" s="33" t="n"/>
+      <c r="P5" s="33" t="n"/>
+      <c r="Q5" s="33" t="n"/>
+      <c r="R5" s="33" t="n"/>
+      <c r="S5" s="33" t="n"/>
+      <c r="T5" s="33" t="n"/>
+      <c r="U5" s="33" t="n"/>
+      <c r="V5" s="33" t="n"/>
+      <c r="W5" s="33">
         <f>IF(AND(V5="Yes",I5="lbs"),ROUND(H5/50,0),"")</f>
         <v/>
       </c>
-      <c r="X5" s="30" t="n"/>
-      <c r="Y5" s="30" t="n"/>
-      <c r="Z5" s="30" t="n"/>
-      <c r="AA5" s="30" t="n"/>
-      <c r="AB5" s="30" t="n"/>
-      <c r="AC5" s="30" t="n"/>
-      <c r="AD5" s="30" t="n"/>
-      <c r="AE5" s="30" t="n"/>
+      <c r="X5" s="33" t="n"/>
+      <c r="Y5" s="33" t="n"/>
+      <c r="Z5" s="33" t="n"/>
+      <c r="AA5" s="33" t="n"/>
+      <c r="AB5" s="33" t="n"/>
+      <c r="AC5" s="33" t="n"/>
+      <c r="AD5" s="33" t="n"/>
+      <c r="AE5" s="33" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="30">
+      <c r="A6" s="33">
         <f>IF(D6="","","NS-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B6" s="30" t="n"/>
-      <c r="C6" s="30" t="n"/>
-      <c r="D6" s="30" t="n"/>
-      <c r="E6" s="30" t="n"/>
-      <c r="F6" s="30" t="n"/>
-      <c r="G6" s="30" t="n"/>
-      <c r="H6" s="30" t="n"/>
-      <c r="I6" s="30" t="n"/>
-      <c r="J6" s="30" t="n"/>
-      <c r="K6" s="30" t="n"/>
-      <c r="L6" s="30" t="n"/>
-      <c r="M6" s="30" t="n"/>
-      <c r="N6" s="30" t="n"/>
-      <c r="O6" s="30" t="n"/>
-      <c r="P6" s="30" t="n"/>
-      <c r="Q6" s="30" t="n"/>
-      <c r="R6" s="30" t="n"/>
-      <c r="S6" s="30" t="n"/>
-      <c r="T6" s="30" t="n"/>
-      <c r="U6" s="30" t="n"/>
-      <c r="V6" s="30" t="n"/>
-      <c r="W6" s="30">
+      <c r="B6" s="33" t="n"/>
+      <c r="C6" s="33" t="n"/>
+      <c r="D6" s="33" t="n"/>
+      <c r="E6" s="33" t="n"/>
+      <c r="F6" s="33" t="n"/>
+      <c r="G6" s="33" t="n"/>
+      <c r="H6" s="33" t="n"/>
+      <c r="I6" s="33" t="n"/>
+      <c r="J6" s="33" t="n"/>
+      <c r="K6" s="33" t="n"/>
+      <c r="L6" s="33" t="n"/>
+      <c r="M6" s="33" t="n"/>
+      <c r="N6" s="33" t="n"/>
+      <c r="O6" s="33" t="n"/>
+      <c r="P6" s="33" t="n"/>
+      <c r="Q6" s="33" t="n"/>
+      <c r="R6" s="33" t="n"/>
+      <c r="S6" s="33" t="n"/>
+      <c r="T6" s="33" t="n"/>
+      <c r="U6" s="33" t="n"/>
+      <c r="V6" s="33" t="n"/>
+      <c r="W6" s="33">
         <f>IF(AND(V6="Yes",I6="lbs"),ROUND(H6/50,0),"")</f>
         <v/>
       </c>
-      <c r="X6" s="30" t="n"/>
-      <c r="Y6" s="30" t="n"/>
-      <c r="Z6" s="30" t="n"/>
-      <c r="AA6" s="30" t="n"/>
-      <c r="AB6" s="30" t="n"/>
-      <c r="AC6" s="30" t="n"/>
-      <c r="AD6" s="30" t="n"/>
-      <c r="AE6" s="30" t="n"/>
+      <c r="X6" s="33" t="n"/>
+      <c r="Y6" s="33" t="n"/>
+      <c r="Z6" s="33" t="n"/>
+      <c r="AA6" s="33" t="n"/>
+      <c r="AB6" s="33" t="n"/>
+      <c r="AC6" s="33" t="n"/>
+      <c r="AD6" s="33" t="n"/>
+      <c r="AE6" s="33" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AE1"/>
@@ -6828,241 +7930,241 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>SeizureID</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="32" t="inlineStr">
         <is>
           <t>LinkedOpsID</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="32" t="inlineStr">
         <is>
           <t>LinkedCaseID</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="32" t="inlineStr">
         <is>
           <t>SeizureDate</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="32" t="inlineStr">
         <is>
           <t>ItemType</t>
         </is>
       </c>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" s="32" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="G1" s="29" t="inlineStr">
+      <c r="G1" s="32" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="H1" s="29" t="inlineStr">
+      <c r="H1" s="32" t="inlineStr">
         <is>
           <t>Calibre</t>
         </is>
       </c>
-      <c r="I1" s="29" t="inlineStr">
+      <c r="I1" s="32" t="inlineStr">
         <is>
           <t>SerialNumber</t>
         </is>
       </c>
-      <c r="J1" s="29" t="inlineStr">
+      <c r="J1" s="32" t="inlineStr">
         <is>
           <t>SeizureLocation</t>
         </is>
       </c>
-      <c r="K1" s="29" t="inlineStr">
+      <c r="K1" s="32" t="inlineStr">
         <is>
           <t>Parish</t>
         </is>
       </c>
-      <c r="L1" s="29" t="inlineStr">
+      <c r="L1" s="32" t="inlineStr">
         <is>
           <t>ForensicSubmitted</t>
         </is>
       </c>
-      <c r="M1" s="29" t="inlineStr">
+      <c r="M1" s="32" t="inlineStr">
         <is>
           <t>ForensicStatus</t>
         </is>
       </c>
-      <c r="N1" s="29" t="inlineStr">
+      <c r="N1" s="32" t="inlineStr">
         <is>
           <t>CourtReady</t>
         </is>
       </c>
-      <c r="O1" s="29" t="inlineStr">
+      <c r="O1" s="32" t="inlineStr">
         <is>
           <t>DisposalStatus</t>
         </is>
       </c>
-      <c r="P1" s="29" t="inlineStr">
+      <c r="P1" s="32" t="inlineStr">
         <is>
           <t>EstValue_JMD</t>
         </is>
       </c>
-      <c r="Q1" s="29" t="inlineStr">
+      <c r="Q1" s="32" t="inlineStr">
         <is>
           <t>POCARelevant</t>
         </is>
       </c>
-      <c r="R1" s="29" t="inlineStr">
+      <c r="R1" s="32" t="inlineStr">
         <is>
           <t>SeizingOfficer</t>
         </is>
       </c>
-      <c r="S1" s="29" t="inlineStr">
+      <c r="S1" s="32" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="T1" s="29" t="inlineStr">
+      <c r="T1" s="32" t="inlineStr">
         <is>
           <t>CreatedBy</t>
         </is>
       </c>
-      <c r="U1" s="29" t="inlineStr">
+      <c r="U1" s="32" t="inlineStr">
         <is>
           <t>CreatedDate</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30">
+      <c r="A2" s="33">
         <f>IF(D2="","","OS-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B2" s="30" t="n"/>
-      <c r="C2" s="30" t="n"/>
-      <c r="D2" s="30" t="n"/>
-      <c r="E2" s="30" t="n"/>
-      <c r="F2" s="30" t="n"/>
-      <c r="G2" s="30" t="n"/>
-      <c r="H2" s="30" t="n"/>
-      <c r="I2" s="30" t="n"/>
-      <c r="J2" s="30" t="n"/>
-      <c r="K2" s="30" t="n"/>
-      <c r="L2" s="30" t="n"/>
-      <c r="M2" s="30" t="n"/>
-      <c r="N2" s="30" t="n"/>
-      <c r="O2" s="30" t="n"/>
-      <c r="P2" s="30" t="n"/>
-      <c r="Q2" s="30" t="n"/>
-      <c r="R2" s="30" t="n"/>
-      <c r="S2" s="30" t="n"/>
-      <c r="T2" s="30" t="n"/>
-      <c r="U2" s="30" t="n"/>
+      <c r="B2" s="33" t="n"/>
+      <c r="C2" s="33" t="n"/>
+      <c r="D2" s="33" t="n"/>
+      <c r="E2" s="33" t="n"/>
+      <c r="F2" s="33" t="n"/>
+      <c r="G2" s="33" t="n"/>
+      <c r="H2" s="33" t="n"/>
+      <c r="I2" s="33" t="n"/>
+      <c r="J2" s="33" t="n"/>
+      <c r="K2" s="33" t="n"/>
+      <c r="L2" s="33" t="n"/>
+      <c r="M2" s="33" t="n"/>
+      <c r="N2" s="33" t="n"/>
+      <c r="O2" s="33" t="n"/>
+      <c r="P2" s="33" t="n"/>
+      <c r="Q2" s="33" t="n"/>
+      <c r="R2" s="33" t="n"/>
+      <c r="S2" s="33" t="n"/>
+      <c r="T2" s="33" t="n"/>
+      <c r="U2" s="33" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="30">
+      <c r="A3" s="33">
         <f>IF(D3="","","OS-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B3" s="30" t="n"/>
-      <c r="C3" s="30" t="n"/>
-      <c r="D3" s="30" t="n"/>
-      <c r="E3" s="30" t="n"/>
-      <c r="F3" s="30" t="n"/>
-      <c r="G3" s="30" t="n"/>
-      <c r="H3" s="30" t="n"/>
-      <c r="I3" s="30" t="n"/>
-      <c r="J3" s="30" t="n"/>
-      <c r="K3" s="30" t="n"/>
-      <c r="L3" s="30" t="n"/>
-      <c r="M3" s="30" t="n"/>
-      <c r="N3" s="30" t="n"/>
-      <c r="O3" s="30" t="n"/>
-      <c r="P3" s="30" t="n"/>
-      <c r="Q3" s="30" t="n"/>
-      <c r="R3" s="30" t="n"/>
-      <c r="S3" s="30" t="n"/>
-      <c r="T3" s="30" t="n"/>
-      <c r="U3" s="30" t="n"/>
+      <c r="B3" s="33" t="n"/>
+      <c r="C3" s="33" t="n"/>
+      <c r="D3" s="33" t="n"/>
+      <c r="E3" s="33" t="n"/>
+      <c r="F3" s="33" t="n"/>
+      <c r="G3" s="33" t="n"/>
+      <c r="H3" s="33" t="n"/>
+      <c r="I3" s="33" t="n"/>
+      <c r="J3" s="33" t="n"/>
+      <c r="K3" s="33" t="n"/>
+      <c r="L3" s="33" t="n"/>
+      <c r="M3" s="33" t="n"/>
+      <c r="N3" s="33" t="n"/>
+      <c r="O3" s="33" t="n"/>
+      <c r="P3" s="33" t="n"/>
+      <c r="Q3" s="33" t="n"/>
+      <c r="R3" s="33" t="n"/>
+      <c r="S3" s="33" t="n"/>
+      <c r="T3" s="33" t="n"/>
+      <c r="U3" s="33" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="30">
+      <c r="A4" s="33">
         <f>IF(D4="","","OS-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B4" s="30" t="n"/>
-      <c r="C4" s="30" t="n"/>
-      <c r="D4" s="30" t="n"/>
-      <c r="E4" s="30" t="n"/>
-      <c r="F4" s="30" t="n"/>
-      <c r="G4" s="30" t="n"/>
-      <c r="H4" s="30" t="n"/>
-      <c r="I4" s="30" t="n"/>
-      <c r="J4" s="30" t="n"/>
-      <c r="K4" s="30" t="n"/>
-      <c r="L4" s="30" t="n"/>
-      <c r="M4" s="30" t="n"/>
-      <c r="N4" s="30" t="n"/>
-      <c r="O4" s="30" t="n"/>
-      <c r="P4" s="30" t="n"/>
-      <c r="Q4" s="30" t="n"/>
-      <c r="R4" s="30" t="n"/>
-      <c r="S4" s="30" t="n"/>
-      <c r="T4" s="30" t="n"/>
-      <c r="U4" s="30" t="n"/>
+      <c r="B4" s="33" t="n"/>
+      <c r="C4" s="33" t="n"/>
+      <c r="D4" s="33" t="n"/>
+      <c r="E4" s="33" t="n"/>
+      <c r="F4" s="33" t="n"/>
+      <c r="G4" s="33" t="n"/>
+      <c r="H4" s="33" t="n"/>
+      <c r="I4" s="33" t="n"/>
+      <c r="J4" s="33" t="n"/>
+      <c r="K4" s="33" t="n"/>
+      <c r="L4" s="33" t="n"/>
+      <c r="M4" s="33" t="n"/>
+      <c r="N4" s="33" t="n"/>
+      <c r="O4" s="33" t="n"/>
+      <c r="P4" s="33" t="n"/>
+      <c r="Q4" s="33" t="n"/>
+      <c r="R4" s="33" t="n"/>
+      <c r="S4" s="33" t="n"/>
+      <c r="T4" s="33" t="n"/>
+      <c r="U4" s="33" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="30">
+      <c r="A5" s="33">
         <f>IF(D5="","","OS-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B5" s="30" t="n"/>
-      <c r="C5" s="30" t="n"/>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="30" t="n"/>
-      <c r="F5" s="30" t="n"/>
-      <c r="G5" s="30" t="n"/>
-      <c r="H5" s="30" t="n"/>
-      <c r="I5" s="30" t="n"/>
-      <c r="J5" s="30" t="n"/>
-      <c r="K5" s="30" t="n"/>
-      <c r="L5" s="30" t="n"/>
-      <c r="M5" s="30" t="n"/>
-      <c r="N5" s="30" t="n"/>
-      <c r="O5" s="30" t="n"/>
-      <c r="P5" s="30" t="n"/>
-      <c r="Q5" s="30" t="n"/>
-      <c r="R5" s="30" t="n"/>
-      <c r="S5" s="30" t="n"/>
-      <c r="T5" s="30" t="n"/>
-      <c r="U5" s="30" t="n"/>
+      <c r="B5" s="33" t="n"/>
+      <c r="C5" s="33" t="n"/>
+      <c r="D5" s="33" t="n"/>
+      <c r="E5" s="33" t="n"/>
+      <c r="F5" s="33" t="n"/>
+      <c r="G5" s="33" t="n"/>
+      <c r="H5" s="33" t="n"/>
+      <c r="I5" s="33" t="n"/>
+      <c r="J5" s="33" t="n"/>
+      <c r="K5" s="33" t="n"/>
+      <c r="L5" s="33" t="n"/>
+      <c r="M5" s="33" t="n"/>
+      <c r="N5" s="33" t="n"/>
+      <c r="O5" s="33" t="n"/>
+      <c r="P5" s="33" t="n"/>
+      <c r="Q5" s="33" t="n"/>
+      <c r="R5" s="33" t="n"/>
+      <c r="S5" s="33" t="n"/>
+      <c r="T5" s="33" t="n"/>
+      <c r="U5" s="33" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="30">
+      <c r="A6" s="33">
         <f>IF(D6="","","OS-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B6" s="30" t="n"/>
-      <c r="C6" s="30" t="n"/>
-      <c r="D6" s="30" t="n"/>
-      <c r="E6" s="30" t="n"/>
-      <c r="F6" s="30" t="n"/>
-      <c r="G6" s="30" t="n"/>
-      <c r="H6" s="30" t="n"/>
-      <c r="I6" s="30" t="n"/>
-      <c r="J6" s="30" t="n"/>
-      <c r="K6" s="30" t="n"/>
-      <c r="L6" s="30" t="n"/>
-      <c r="M6" s="30" t="n"/>
-      <c r="N6" s="30" t="n"/>
-      <c r="O6" s="30" t="n"/>
-      <c r="P6" s="30" t="n"/>
-      <c r="Q6" s="30" t="n"/>
-      <c r="R6" s="30" t="n"/>
-      <c r="S6" s="30" t="n"/>
-      <c r="T6" s="30" t="n"/>
-      <c r="U6" s="30" t="n"/>
+      <c r="B6" s="33" t="n"/>
+      <c r="C6" s="33" t="n"/>
+      <c r="D6" s="33" t="n"/>
+      <c r="E6" s="33" t="n"/>
+      <c r="F6" s="33" t="n"/>
+      <c r="G6" s="33" t="n"/>
+      <c r="H6" s="33" t="n"/>
+      <c r="I6" s="33" t="n"/>
+      <c r="J6" s="33" t="n"/>
+      <c r="K6" s="33" t="n"/>
+      <c r="L6" s="33" t="n"/>
+      <c r="M6" s="33" t="n"/>
+      <c r="N6" s="33" t="n"/>
+      <c r="O6" s="33" t="n"/>
+      <c r="P6" s="33" t="n"/>
+      <c r="Q6" s="33" t="n"/>
+      <c r="R6" s="33" t="n"/>
+      <c r="S6" s="33" t="n"/>
+      <c r="T6" s="33" t="n"/>
+      <c r="U6" s="33" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:U1"/>
@@ -7127,421 +8229,421 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="29" t="inlineStr">
+      <c r="A1" s="32" t="inlineStr">
         <is>
           <t>ArrestID</t>
         </is>
       </c>
-      <c r="B1" s="29" t="inlineStr">
+      <c r="B1" s="32" t="inlineStr">
         <is>
           <t>LinkedOpsID</t>
         </is>
       </c>
-      <c r="C1" s="29" t="inlineStr">
+      <c r="C1" s="32" t="inlineStr">
         <is>
           <t>LinkedCaseID</t>
         </is>
       </c>
-      <c r="D1" s="29" t="inlineStr">
+      <c r="D1" s="32" t="inlineStr">
         <is>
           <t>ArrestDate</t>
         </is>
       </c>
-      <c r="E1" s="29" t="inlineStr">
+      <c r="E1" s="32" t="inlineStr">
         <is>
           <t>ArrestTime</t>
         </is>
       </c>
-      <c r="F1" s="29" t="inlineStr">
+      <c r="F1" s="32" t="inlineStr">
         <is>
           <t>ArrestLocation</t>
         </is>
       </c>
-      <c r="G1" s="29" t="inlineStr">
+      <c r="G1" s="32" t="inlineStr">
         <is>
           <t>Parish</t>
         </is>
       </c>
-      <c r="H1" s="29" t="inlineStr">
+      <c r="H1" s="32" t="inlineStr">
         <is>
           <t>SuspectName</t>
         </is>
       </c>
-      <c r="I1" s="29" t="inlineStr">
+      <c r="I1" s="32" t="inlineStr">
         <is>
           <t>DOB</t>
         </is>
       </c>
-      <c r="J1" s="29" t="inlineStr">
+      <c r="J1" s="32" t="inlineStr">
         <is>
           <t>Gender</t>
         </is>
       </c>
-      <c r="K1" s="29" t="inlineStr">
+      <c r="K1" s="32" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="L1" s="29" t="inlineStr">
+      <c r="L1" s="32" t="inlineStr">
         <is>
           <t>NationalID_TRN</t>
         </is>
       </c>
-      <c r="M1" s="29" t="inlineStr">
+      <c r="M1" s="32" t="inlineStr">
         <is>
           <t>PriorConvictions</t>
         </is>
       </c>
-      <c r="N1" s="29" t="inlineStr">
+      <c r="N1" s="32" t="inlineStr">
         <is>
           <t>CautionAdministered</t>
         </is>
       </c>
-      <c r="O1" s="29" t="inlineStr">
+      <c r="O1" s="32" t="inlineStr">
         <is>
           <t>CautionTime</t>
         </is>
       </c>
-      <c r="P1" s="29" t="inlineStr">
+      <c r="P1" s="32" t="inlineStr">
         <is>
           <t>ChargeDate</t>
         </is>
       </c>
-      <c r="Q1" s="29" t="inlineStr">
+      <c r="Q1" s="32" t="inlineStr">
         <is>
           <t>ChargeTime</t>
         </is>
       </c>
-      <c r="R1" s="29" t="inlineStr">
+      <c r="R1" s="32" t="inlineStr">
         <is>
           <t>PrimaryOffence</t>
         </is>
       </c>
-      <c r="S1" s="29" t="inlineStr">
+      <c r="S1" s="32" t="inlineStr">
         <is>
           <t>SecondaryOffence</t>
         </is>
       </c>
-      <c r="T1" s="29" t="inlineStr">
+      <c r="T1" s="32" t="inlineStr">
         <is>
           <t>ActSection</t>
         </is>
       </c>
-      <c r="U1" s="29" t="inlineStr">
+      <c r="U1" s="32" t="inlineStr">
         <is>
           <t>48hr_Deadline</t>
         </is>
       </c>
-      <c r="V1" s="29" t="inlineStr">
+      <c r="V1" s="32" t="inlineStr">
         <is>
           <t>FirstCourtAppearance</t>
         </is>
       </c>
-      <c r="W1" s="29" t="inlineStr">
+      <c r="W1" s="32" t="inlineStr">
         <is>
           <t>48hr_Met</t>
         </is>
       </c>
-      <c r="X1" s="29" t="inlineStr">
+      <c r="X1" s="32" t="inlineStr">
         <is>
           <t>CourtType</t>
         </is>
       </c>
-      <c r="Y1" s="29" t="inlineStr">
+      <c r="Y1" s="32" t="inlineStr">
         <is>
           <t>CourtLocation</t>
         </is>
       </c>
-      <c r="Z1" s="29" t="inlineStr">
+      <c r="Z1" s="32" t="inlineStr">
         <is>
           <t>BailStatus</t>
         </is>
       </c>
-      <c r="AA1" s="29" t="inlineStr">
+      <c r="AA1" s="32" t="inlineStr">
         <is>
           <t>BailAmount_JMD</t>
         </is>
       </c>
-      <c r="AB1" s="29" t="inlineStr">
+      <c r="AB1" s="32" t="inlineStr">
         <is>
           <t>BailConditions</t>
         </is>
       </c>
-      <c r="AC1" s="29" t="inlineStr">
+      <c r="AC1" s="32" t="inlineStr">
         <is>
           <t>RemandFacility</t>
         </is>
       </c>
-      <c r="AD1" s="29" t="inlineStr">
+      <c r="AD1" s="32" t="inlineStr">
         <is>
           <t>StopOrderIssued</t>
         </is>
       </c>
-      <c r="AE1" s="29" t="inlineStr">
+      <c r="AE1" s="32" t="inlineStr">
         <is>
           <t>POCAStatus</t>
         </is>
       </c>
-      <c r="AF1" s="29" t="inlineStr">
+      <c r="AF1" s="32" t="inlineStr">
         <is>
           <t>POCARef</t>
         </is>
       </c>
-      <c r="AG1" s="29" t="inlineStr">
+      <c r="AG1" s="32" t="inlineStr">
         <is>
           <t>ArrestingOfficer</t>
         </is>
       </c>
-      <c r="AH1" s="29" t="inlineStr">
+      <c r="AH1" s="32" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="AI1" s="29" t="inlineStr">
+      <c r="AI1" s="32" t="inlineStr">
         <is>
           <t>CreatedBy</t>
         </is>
       </c>
-      <c r="AJ1" s="29" t="inlineStr">
+      <c r="AJ1" s="32" t="inlineStr">
         <is>
           <t>CreatedDate</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="30">
+      <c r="A2" s="33">
         <f>IF(D2="","","ARR-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B2" s="30" t="n"/>
-      <c r="C2" s="30" t="n"/>
-      <c r="D2" s="30" t="n"/>
-      <c r="E2" s="30" t="n"/>
-      <c r="F2" s="30" t="n"/>
-      <c r="G2" s="30" t="n"/>
-      <c r="H2" s="30" t="n"/>
-      <c r="I2" s="30" t="n"/>
-      <c r="J2" s="30" t="n"/>
-      <c r="K2" s="30" t="n"/>
-      <c r="L2" s="30" t="n"/>
-      <c r="M2" s="30" t="n"/>
-      <c r="N2" s="30" t="n"/>
-      <c r="O2" s="30" t="n"/>
-      <c r="P2" s="30" t="n"/>
-      <c r="Q2" s="30" t="n"/>
-      <c r="R2" s="30" t="n"/>
-      <c r="S2" s="30" t="n"/>
-      <c r="T2" s="30" t="n"/>
-      <c r="U2" s="31">
+      <c r="B2" s="33" t="n"/>
+      <c r="C2" s="33" t="n"/>
+      <c r="D2" s="33" t="n"/>
+      <c r="E2" s="33" t="n"/>
+      <c r="F2" s="33" t="n"/>
+      <c r="G2" s="33" t="n"/>
+      <c r="H2" s="33" t="n"/>
+      <c r="I2" s="33" t="n"/>
+      <c r="J2" s="33" t="n"/>
+      <c r="K2" s="33" t="n"/>
+      <c r="L2" s="33" t="n"/>
+      <c r="M2" s="33" t="n"/>
+      <c r="N2" s="33" t="n"/>
+      <c r="O2" s="33" t="n"/>
+      <c r="P2" s="33" t="n"/>
+      <c r="Q2" s="33" t="n"/>
+      <c r="R2" s="33" t="n"/>
+      <c r="S2" s="33" t="n"/>
+      <c r="T2" s="33" t="n"/>
+      <c r="U2" s="34">
         <f>IF(D2="","",D2+2)</f>
         <v/>
       </c>
-      <c r="V2" s="30" t="n"/>
-      <c r="W2" s="30">
+      <c r="V2" s="33" t="n"/>
+      <c r="W2" s="33">
         <f>IF(OR(D2="",V2=""),"",IF(V2&lt;=U2,"Yes","BREACH"))</f>
         <v/>
       </c>
-      <c r="X2" s="30" t="n"/>
-      <c r="Y2" s="30" t="n"/>
-      <c r="Z2" s="30" t="n"/>
-      <c r="AA2" s="30" t="n"/>
-      <c r="AB2" s="30" t="n"/>
-      <c r="AC2" s="30" t="n"/>
-      <c r="AD2" s="30" t="n"/>
-      <c r="AE2" s="30" t="n"/>
-      <c r="AF2" s="30" t="n"/>
-      <c r="AG2" s="30" t="n"/>
-      <c r="AH2" s="30" t="n"/>
-      <c r="AI2" s="30" t="n"/>
-      <c r="AJ2" s="30" t="n"/>
+      <c r="X2" s="33" t="n"/>
+      <c r="Y2" s="33" t="n"/>
+      <c r="Z2" s="33" t="n"/>
+      <c r="AA2" s="33" t="n"/>
+      <c r="AB2" s="33" t="n"/>
+      <c r="AC2" s="33" t="n"/>
+      <c r="AD2" s="33" t="n"/>
+      <c r="AE2" s="33" t="n"/>
+      <c r="AF2" s="33" t="n"/>
+      <c r="AG2" s="33" t="n"/>
+      <c r="AH2" s="33" t="n"/>
+      <c r="AI2" s="33" t="n"/>
+      <c r="AJ2" s="33" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="30">
+      <c r="A3" s="33">
         <f>IF(D3="","","ARR-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B3" s="30" t="n"/>
-      <c r="C3" s="30" t="n"/>
-      <c r="D3" s="30" t="n"/>
-      <c r="E3" s="30" t="n"/>
-      <c r="F3" s="30" t="n"/>
-      <c r="G3" s="30" t="n"/>
-      <c r="H3" s="30" t="n"/>
-      <c r="I3" s="30" t="n"/>
-      <c r="J3" s="30" t="n"/>
-      <c r="K3" s="30" t="n"/>
-      <c r="L3" s="30" t="n"/>
-      <c r="M3" s="30" t="n"/>
-      <c r="N3" s="30" t="n"/>
-      <c r="O3" s="30" t="n"/>
-      <c r="P3" s="30" t="n"/>
-      <c r="Q3" s="30" t="n"/>
-      <c r="R3" s="30" t="n"/>
-      <c r="S3" s="30" t="n"/>
-      <c r="T3" s="30" t="n"/>
-      <c r="U3" s="31">
+      <c r="B3" s="33" t="n"/>
+      <c r="C3" s="33" t="n"/>
+      <c r="D3" s="33" t="n"/>
+      <c r="E3" s="33" t="n"/>
+      <c r="F3" s="33" t="n"/>
+      <c r="G3" s="33" t="n"/>
+      <c r="H3" s="33" t="n"/>
+      <c r="I3" s="33" t="n"/>
+      <c r="J3" s="33" t="n"/>
+      <c r="K3" s="33" t="n"/>
+      <c r="L3" s="33" t="n"/>
+      <c r="M3" s="33" t="n"/>
+      <c r="N3" s="33" t="n"/>
+      <c r="O3" s="33" t="n"/>
+      <c r="P3" s="33" t="n"/>
+      <c r="Q3" s="33" t="n"/>
+      <c r="R3" s="33" t="n"/>
+      <c r="S3" s="33" t="n"/>
+      <c r="T3" s="33" t="n"/>
+      <c r="U3" s="34">
         <f>IF(D3="","",D3+2)</f>
         <v/>
       </c>
-      <c r="V3" s="30" t="n"/>
-      <c r="W3" s="30">
+      <c r="V3" s="33" t="n"/>
+      <c r="W3" s="33">
         <f>IF(OR(D3="",V3=""),"",IF(V3&lt;=U3,"Yes","BREACH"))</f>
         <v/>
       </c>
-      <c r="X3" s="30" t="n"/>
-      <c r="Y3" s="30" t="n"/>
-      <c r="Z3" s="30" t="n"/>
-      <c r="AA3" s="30" t="n"/>
-      <c r="AB3" s="30" t="n"/>
-      <c r="AC3" s="30" t="n"/>
-      <c r="AD3" s="30" t="n"/>
-      <c r="AE3" s="30" t="n"/>
-      <c r="AF3" s="30" t="n"/>
-      <c r="AG3" s="30" t="n"/>
-      <c r="AH3" s="30" t="n"/>
-      <c r="AI3" s="30" t="n"/>
-      <c r="AJ3" s="30" t="n"/>
+      <c r="X3" s="33" t="n"/>
+      <c r="Y3" s="33" t="n"/>
+      <c r="Z3" s="33" t="n"/>
+      <c r="AA3" s="33" t="n"/>
+      <c r="AB3" s="33" t="n"/>
+      <c r="AC3" s="33" t="n"/>
+      <c r="AD3" s="33" t="n"/>
+      <c r="AE3" s="33" t="n"/>
+      <c r="AF3" s="33" t="n"/>
+      <c r="AG3" s="33" t="n"/>
+      <c r="AH3" s="33" t="n"/>
+      <c r="AI3" s="33" t="n"/>
+      <c r="AJ3" s="33" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="30">
+      <c r="A4" s="33">
         <f>IF(D4="","","ARR-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B4" s="30" t="n"/>
-      <c r="C4" s="30" t="n"/>
-      <c r="D4" s="30" t="n"/>
-      <c r="E4" s="30" t="n"/>
-      <c r="F4" s="30" t="n"/>
-      <c r="G4" s="30" t="n"/>
-      <c r="H4" s="30" t="n"/>
-      <c r="I4" s="30" t="n"/>
-      <c r="J4" s="30" t="n"/>
-      <c r="K4" s="30" t="n"/>
-      <c r="L4" s="30" t="n"/>
-      <c r="M4" s="30" t="n"/>
-      <c r="N4" s="30" t="n"/>
-      <c r="O4" s="30" t="n"/>
-      <c r="P4" s="30" t="n"/>
-      <c r="Q4" s="30" t="n"/>
-      <c r="R4" s="30" t="n"/>
-      <c r="S4" s="30" t="n"/>
-      <c r="T4" s="30" t="n"/>
-      <c r="U4" s="31">
+      <c r="B4" s="33" t="n"/>
+      <c r="C4" s="33" t="n"/>
+      <c r="D4" s="33" t="n"/>
+      <c r="E4" s="33" t="n"/>
+      <c r="F4" s="33" t="n"/>
+      <c r="G4" s="33" t="n"/>
+      <c r="H4" s="33" t="n"/>
+      <c r="I4" s="33" t="n"/>
+      <c r="J4" s="33" t="n"/>
+      <c r="K4" s="33" t="n"/>
+      <c r="L4" s="33" t="n"/>
+      <c r="M4" s="33" t="n"/>
+      <c r="N4" s="33" t="n"/>
+      <c r="O4" s="33" t="n"/>
+      <c r="P4" s="33" t="n"/>
+      <c r="Q4" s="33" t="n"/>
+      <c r="R4" s="33" t="n"/>
+      <c r="S4" s="33" t="n"/>
+      <c r="T4" s="33" t="n"/>
+      <c r="U4" s="34">
         <f>IF(D4="","",D4+2)</f>
         <v/>
       </c>
-      <c r="V4" s="30" t="n"/>
-      <c r="W4" s="30">
+      <c r="V4" s="33" t="n"/>
+      <c r="W4" s="33">
         <f>IF(OR(D4="",V4=""),"",IF(V4&lt;=U4,"Yes","BREACH"))</f>
         <v/>
       </c>
-      <c r="X4" s="30" t="n"/>
-      <c r="Y4" s="30" t="n"/>
-      <c r="Z4" s="30" t="n"/>
-      <c r="AA4" s="30" t="n"/>
-      <c r="AB4" s="30" t="n"/>
-      <c r="AC4" s="30" t="n"/>
-      <c r="AD4" s="30" t="n"/>
-      <c r="AE4" s="30" t="n"/>
-      <c r="AF4" s="30" t="n"/>
-      <c r="AG4" s="30" t="n"/>
-      <c r="AH4" s="30" t="n"/>
-      <c r="AI4" s="30" t="n"/>
-      <c r="AJ4" s="30" t="n"/>
+      <c r="X4" s="33" t="n"/>
+      <c r="Y4" s="33" t="n"/>
+      <c r="Z4" s="33" t="n"/>
+      <c r="AA4" s="33" t="n"/>
+      <c r="AB4" s="33" t="n"/>
+      <c r="AC4" s="33" t="n"/>
+      <c r="AD4" s="33" t="n"/>
+      <c r="AE4" s="33" t="n"/>
+      <c r="AF4" s="33" t="n"/>
+      <c r="AG4" s="33" t="n"/>
+      <c r="AH4" s="33" t="n"/>
+      <c r="AI4" s="33" t="n"/>
+      <c r="AJ4" s="33" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="30">
+      <c r="A5" s="33">
         <f>IF(D5="","","ARR-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B5" s="30" t="n"/>
-      <c r="C5" s="30" t="n"/>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="30" t="n"/>
-      <c r="F5" s="30" t="n"/>
-      <c r="G5" s="30" t="n"/>
-      <c r="H5" s="30" t="n"/>
-      <c r="I5" s="30" t="n"/>
-      <c r="J5" s="30" t="n"/>
-      <c r="K5" s="30" t="n"/>
-      <c r="L5" s="30" t="n"/>
-      <c r="M5" s="30" t="n"/>
-      <c r="N5" s="30" t="n"/>
-      <c r="O5" s="30" t="n"/>
-      <c r="P5" s="30" t="n"/>
-      <c r="Q5" s="30" t="n"/>
-      <c r="R5" s="30" t="n"/>
-      <c r="S5" s="30" t="n"/>
-      <c r="T5" s="30" t="n"/>
-      <c r="U5" s="31">
+      <c r="B5" s="33" t="n"/>
+      <c r="C5" s="33" t="n"/>
+      <c r="D5" s="33" t="n"/>
+      <c r="E5" s="33" t="n"/>
+      <c r="F5" s="33" t="n"/>
+      <c r="G5" s="33" t="n"/>
+      <c r="H5" s="33" t="n"/>
+      <c r="I5" s="33" t="n"/>
+      <c r="J5" s="33" t="n"/>
+      <c r="K5" s="33" t="n"/>
+      <c r="L5" s="33" t="n"/>
+      <c r="M5" s="33" t="n"/>
+      <c r="N5" s="33" t="n"/>
+      <c r="O5" s="33" t="n"/>
+      <c r="P5" s="33" t="n"/>
+      <c r="Q5" s="33" t="n"/>
+      <c r="R5" s="33" t="n"/>
+      <c r="S5" s="33" t="n"/>
+      <c r="T5" s="33" t="n"/>
+      <c r="U5" s="34">
         <f>IF(D5="","",D5+2)</f>
         <v/>
       </c>
-      <c r="V5" s="30" t="n"/>
-      <c r="W5" s="30">
+      <c r="V5" s="33" t="n"/>
+      <c r="W5" s="33">
         <f>IF(OR(D5="",V5=""),"",IF(V5&lt;=U5,"Yes","BREACH"))</f>
         <v/>
       </c>
-      <c r="X5" s="30" t="n"/>
-      <c r="Y5" s="30" t="n"/>
-      <c r="Z5" s="30" t="n"/>
-      <c r="AA5" s="30" t="n"/>
-      <c r="AB5" s="30" t="n"/>
-      <c r="AC5" s="30" t="n"/>
-      <c r="AD5" s="30" t="n"/>
-      <c r="AE5" s="30" t="n"/>
-      <c r="AF5" s="30" t="n"/>
-      <c r="AG5" s="30" t="n"/>
-      <c r="AH5" s="30" t="n"/>
-      <c r="AI5" s="30" t="n"/>
-      <c r="AJ5" s="30" t="n"/>
+      <c r="X5" s="33" t="n"/>
+      <c r="Y5" s="33" t="n"/>
+      <c r="Z5" s="33" t="n"/>
+      <c r="AA5" s="33" t="n"/>
+      <c r="AB5" s="33" t="n"/>
+      <c r="AC5" s="33" t="n"/>
+      <c r="AD5" s="33" t="n"/>
+      <c r="AE5" s="33" t="n"/>
+      <c r="AF5" s="33" t="n"/>
+      <c r="AG5" s="33" t="n"/>
+      <c r="AH5" s="33" t="n"/>
+      <c r="AI5" s="33" t="n"/>
+      <c r="AJ5" s="33" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="30">
+      <c r="A6" s="33">
         <f>IF(D6="","","ARR-"&amp;TEXT(ROW()-1,"0000"))</f>
         <v/>
       </c>
-      <c r="B6" s="30" t="n"/>
-      <c r="C6" s="30" t="n"/>
-      <c r="D6" s="30" t="n"/>
-      <c r="E6" s="30" t="n"/>
-      <c r="F6" s="30" t="n"/>
-      <c r="G6" s="30" t="n"/>
-      <c r="H6" s="30" t="n"/>
-      <c r="I6" s="30" t="n"/>
-      <c r="J6" s="30" t="n"/>
-      <c r="K6" s="30" t="n"/>
-      <c r="L6" s="30" t="n"/>
-      <c r="M6" s="30" t="n"/>
-      <c r="N6" s="30" t="n"/>
-      <c r="O6" s="30" t="n"/>
-      <c r="P6" s="30" t="n"/>
-      <c r="Q6" s="30" t="n"/>
-      <c r="R6" s="30" t="n"/>
-      <c r="S6" s="30" t="n"/>
-      <c r="T6" s="30" t="n"/>
-      <c r="U6" s="31">
+      <c r="B6" s="33" t="n"/>
+      <c r="C6" s="33" t="n"/>
+      <c r="D6" s="33" t="n"/>
+      <c r="E6" s="33" t="n"/>
+      <c r="F6" s="33" t="n"/>
+      <c r="G6" s="33" t="n"/>
+      <c r="H6" s="33" t="n"/>
+      <c r="I6" s="33" t="n"/>
+      <c r="J6" s="33" t="n"/>
+      <c r="K6" s="33" t="n"/>
+      <c r="L6" s="33" t="n"/>
+      <c r="M6" s="33" t="n"/>
+      <c r="N6" s="33" t="n"/>
+      <c r="O6" s="33" t="n"/>
+      <c r="P6" s="33" t="n"/>
+      <c r="Q6" s="33" t="n"/>
+      <c r="R6" s="33" t="n"/>
+      <c r="S6" s="33" t="n"/>
+      <c r="T6" s="33" t="n"/>
+      <c r="U6" s="34">
         <f>IF(D6="","",D6+2)</f>
         <v/>
       </c>
-      <c r="V6" s="30" t="n"/>
-      <c r="W6" s="30">
+      <c r="V6" s="33" t="n"/>
+      <c r="W6" s="33">
         <f>IF(OR(D6="",V6=""),"",IF(V6&lt;=U6,"Yes","BREACH"))</f>
         <v/>
       </c>
-      <c r="X6" s="30" t="n"/>
-      <c r="Y6" s="30" t="n"/>
-      <c r="Z6" s="30" t="n"/>
-      <c r="AA6" s="30" t="n"/>
-      <c r="AB6" s="30" t="n"/>
-      <c r="AC6" s="30" t="n"/>
-      <c r="AD6" s="30" t="n"/>
-      <c r="AE6" s="30" t="n"/>
-      <c r="AF6" s="30" t="n"/>
-      <c r="AG6" s="30" t="n"/>
-      <c r="AH6" s="30" t="n"/>
-      <c r="AI6" s="30" t="n"/>
-      <c r="AJ6" s="30" t="n"/>
+      <c r="X6" s="33" t="n"/>
+      <c r="Y6" s="33" t="n"/>
+      <c r="Z6" s="33" t="n"/>
+      <c r="AA6" s="33" t="n"/>
+      <c r="AB6" s="33" t="n"/>
+      <c r="AC6" s="33" t="n"/>
+      <c r="AD6" s="33" t="n"/>
+      <c r="AE6" s="33" t="n"/>
+      <c r="AF6" s="33" t="n"/>
+      <c r="AG6" s="33" t="n"/>
+      <c r="AH6" s="33" t="n"/>
+      <c r="AI6" s="33" t="n"/>
+      <c r="AJ6" s="33" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AJ1"/>

--- a/FNID_Area3_Operational_Workbook.xlsx
+++ b/FNID_Area3_Operational_Workbook.xlsx
@@ -1168,14 +1168,14 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>JAMAICA CONSTABULARY FORCE — FIREARM AND NARCOTICS INVESTIGATION DIVISION</t>
+          <t>JAMAICA CONSTABULARY FORCE - FIREARM AND NARCOTICS INVESTIGATION DIVISION</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AREA 3 (Manchester | St. Elizabeth | Clarendon) — OPERATIONAL WORKBOOK v2.0</t>
+          <t>AREA 3 (Manchester | St. Elizabeth | Clarendon) - OPERATIONAL WORKBOOK v2.1</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>INTELLIGENCE → OPERATION → SEIZURE → ARREST → FORENSICS → DPP → COURT → CONVICTION</t>
+          <t>INTELLIGENCE &gt; OPERATION &gt; SEIZURE &gt; ARREST &gt; FORENSICS &gt; DPP &gt; COURT &gt; CONVICTION</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &gt;&gt; DASH_Command</t>
+          <t xml:space="preserve">  &gt; DASH_Command</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Daily Command Dashboard — all key metrics at a glance</t>
+          <t>Daily Command Dashboard - all key metrics at a glance</t>
         </is>
       </c>
     </row>
@@ -1222,24 +1222,24 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &gt;&gt; tbl_IntelLog</t>
+          <t xml:space="preserve">  &gt; tbl_IntelLog</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Intelligence Log — Crime Stop, NIB, DEA, JCA, informant tips</t>
+          <t>Intelligence Log - Crime Stop, NIB, DEA, JCA, informant tips</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &gt;&gt; tbl_Informants</t>
+          <t xml:space="preserve">  &gt; tbl_Informants</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Informant Register — RESTRICTED ACCESS (code names only)</t>
+          <t>Informant Register - RESTRICTED ACCESS (code names only)</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &gt;&gt; tbl_Operations</t>
+          <t xml:space="preserve">  &gt; tbl_Operations</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Operation Register — warrants, teams, execution, outcomes</t>
+          <t>Operation Register - warrants, teams, execution, outcomes</t>
         </is>
       </c>
     </row>
@@ -1272,36 +1272,36 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &gt;&gt; tbl_FirearmSeizures</t>
+          <t xml:space="preserve">  &gt; tbl_FirearmSeizures</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Firearm Seizure Log — IBIS, eTrace, ballistic cert tracking</t>
+          <t>Firearm Seizure Log - IBIS, eTrace, ballistic cert tracking</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &gt;&gt; tbl_NarcoticSeizures</t>
+          <t xml:space="preserve">  &gt; tbl_NarcoticSeizures</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Narcotics Seizure Log — field test, IFSLM, forensic cert, disposal</t>
+          <t>Narcotics Seizure Log - field test, IFSLM, forensic cert, disposal</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &gt;&gt; tbl_OtherSeizures</t>
+          <t xml:space="preserve">  &gt; tbl_OtherSeizures</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Ammunition, Cash, Electronics, Vehicles — other exhibits</t>
+          <t>Ammunition, Cash, Electronics, Vehicles - other exhibits</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &gt;&gt; tbl_Arrests</t>
+          <t xml:space="preserve">  &gt; tbl_Arrests</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Arrest Register — 48hr rule, charge, caution, bail, court routing</t>
+          <t>Arrest Register - 48hr rule, charge, caution, bail, court routing</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &gt;&gt; tbl_CaseRegistry</t>
+          <t xml:space="preserve">  &gt; tbl_CaseRegistry</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Master Case File Registry — every case, investigation milestones, progress tracking</t>
+          <t>Master Case File Registry - every case, investigation milestones, progress tracking</t>
         </is>
       </c>
     </row>
@@ -1353,12 +1353,12 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &gt;&gt; tbl_ChainOfCustody</t>
+          <t xml:space="preserve">  &gt; tbl_ChainOfCustody</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Exhibit Chain of Custody — every handover logged</t>
+          <t>Exhibit Chain of Custody - every handover logged</t>
         </is>
       </c>
     </row>
@@ -1372,24 +1372,24 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &gt;&gt; tbl_CaseFiles</t>
+          <t xml:space="preserve">  &gt; tbl_CaseFiles</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Case File Tracker — DPP submission pipeline, completeness scoring</t>
+          <t>Case File Tracker - DPP submission pipeline, completeness scoring</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &gt;&gt; tbl_Witnesses</t>
+          <t xml:space="preserve">  &gt; tbl_Witnesses</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Witness &amp; Statement Register — testimony, protection, summons</t>
+          <t>Witness &amp; Statement Register - testimony, protection, summons</t>
         </is>
       </c>
     </row>
@@ -1403,36 +1403,36 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &gt;&gt; tbl_Personnel</t>
+          <t xml:space="preserve">  &gt; tbl_Personnel</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Personnel Register — staff, qualifications, polygraph</t>
+          <t>Personnel Register - staff, qualifications, polygraph</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &gt;&gt; tbl_Vehicles</t>
+          <t xml:space="preserve">  &gt; tbl_Vehicles</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Vehicle/Fleet Log — status, service, fitness</t>
+          <t>Vehicle/Fleet Log - status, service, fitness</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  &gt;&gt; Lookups</t>
+          <t xml:space="preserve">  &gt; Lookups</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Reference Data — Jamaica-specific lookups</t>
+          <t>Reference Data - Jamaica-specific lookups</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>CONFIDENTIAL — FOR OFFICIAL USE ONLY | FNID Area 3 | Search warrants under Section 91, Firearms Act 2022</t>
+          <t>CONFIDENTIAL - FOR OFFICIAL USE ONLY | FNID Area 3 | Search warrants under Section 91, Firearms Act 2022</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
       <formula>"Cold Case"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="3" operator="beginsWith" dxfId="3">
-      <formula>"Closed — Convicted"</formula>
+      <formula>"Closed - Convicted"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E1000">
@@ -3976,14 +3976,14 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>FNID AREA 3 — DAILY COMMAND DASHBOARD</t>
+          <t>FNID AREA 3 - DAILY COMMAND DASHBOARD</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Intelligence → Operations → Seizures → Arrests → Forensics → DPP → Court</t>
+          <t>Intelligence &gt; Operations &gt; Seizures &gt; Arrests &gt; Forensics &gt; DPP &gt; Court</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4027,7 @@
       </c>
       <c r="G5" s="19" t="inlineStr">
         <is>
-          <t>→ Converted to Op</t>
+          <t>Converted to Op</t>
         </is>
       </c>
       <c r="H5" s="19" t="inlineStr">
@@ -4066,7 +4066,7 @@
         <v/>
       </c>
       <c r="H6" s="20">
-        <f>IFERROR(COUNTIF(tbl_IntelLog[TriageDecision],"Action*")/(COUNTA(tbl_IntelLog[IntelID])-COUNTBLANK(tbl_IntelLog[IntelID])),"—")</f>
+        <f>IFERROR(COUNTIF(tbl_IntelLog[TriageDecision],"Action*")/(COUNTA(tbl_IntelLog[IntelID])-COUNTBLANK(tbl_IntelLog[IntelID])),"-")</f>
         <v/>
       </c>
     </row>
@@ -4141,15 +4141,15 @@
         <v/>
       </c>
       <c r="F10" s="20">
-        <f>IFERROR(COUNTIF(tbl_Operations[Outcome],"Successful*")/(COUNTA(tbl_Operations[OpsID])-COUNTBLANK(tbl_Operations[OpsID])),"—")</f>
+        <f>IFERROR(COUNTIF(tbl_Operations[Outcome],"Successful*")/(COUNTA(tbl_Operations[OpsID])-COUNTBLANK(tbl_Operations[OpsID])),"-")</f>
         <v/>
       </c>
       <c r="G10" s="20">
-        <f>IFERROR(COUNTIF(tbl_Operations[InspectorPresent],"Yes")/COUNTA(tbl_Operations[InspectorPresent]),"—")</f>
+        <f>IFERROR(COUNTIF(tbl_Operations[InspectorPresent],"Yes")/COUNTA(tbl_Operations[InspectorPresent]),"-")</f>
         <v/>
       </c>
       <c r="H10" s="20">
-        <f>IFERROR(COUNTIF(tbl_Operations[BodyCamActivated],"Yes")/COUNTA(tbl_Operations[BodyCamActivated]),"—")</f>
+        <f>IFERROR(COUNTIF(tbl_Operations[BodyCamActivated],"Yes")/COUNTA(tbl_Operations[BodyCamActivated]),"-")</f>
         <v/>
       </c>
     </row>
@@ -4390,7 +4390,7 @@
         <v/>
       </c>
       <c r="F22" s="20">
-        <f>IFERROR(COUNTIF(tbl_Arrests[48hr_Met],"Yes")/COUNTA(tbl_Arrests[48hr_Met]),"—")</f>
+        <f>IFERROR(COUNTIF(tbl_Arrests[48hr_Met],"Yes")/COUNTA(tbl_Arrests[48hr_Met]),"-")</f>
         <v/>
       </c>
       <c r="G22" s="20">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="B25" s="26" t="inlineStr">
         <is>
-          <t>Open — Active</t>
+          <t>Open - Active</t>
         </is>
       </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>Open — Pending</t>
+          <t>Open - Pending</t>
         </is>
       </c>
       <c r="D25" s="26" t="inlineStr">
@@ -4457,11 +4457,11 @@
         <v/>
       </c>
       <c r="B26" s="20">
-        <f>COUNTIF(tbl_CaseRegistry[CaseStatus],"Open — Active*")</f>
+        <f>COUNTIF(tbl_CaseRegistry[CaseStatus],"Open - Active*")</f>
         <v/>
       </c>
       <c r="C26" s="20">
-        <f>COUNTIF(tbl_CaseRegistry[CaseStatus],"Open — Pending*")</f>
+        <f>COUNTIF(tbl_CaseRegistry[CaseStatus],"Open - Pending*")</f>
         <v/>
       </c>
       <c r="D26" s="20">
@@ -4481,7 +4481,7 @@
         <v/>
       </c>
       <c r="H26" s="20">
-        <f>IFERROR(AVERAGE(tbl_CaseRegistry[InvestigationProgress]),"—")</f>
+        <f>IFERROR(AVERAGE(tbl_CaseRegistry[InvestigationProgress]),"-")</f>
         <v/>
       </c>
     </row>
@@ -4560,11 +4560,11 @@
         <v/>
       </c>
       <c r="G30" s="20">
-        <f>IFERROR(AVERAGE(tbl_CaseFiles[FileCompletenessScore]),"—")</f>
+        <f>IFERROR(AVERAGE(tbl_CaseFiles[FileCompletenessScore]),"-")</f>
         <v/>
       </c>
       <c r="H30" s="20">
-        <f>IFERROR(AVERAGE(tbl_CaseFiles[DaysInPipeline]),"—")</f>
+        <f>IFERROR(AVERAGE(tbl_CaseFiles[DaysInPipeline]),"-")</f>
         <v/>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Action — Mount Operation</t>
+          <t>Action - Mount Operation</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Section 91 — Firearms Act 2022</t>
+          <t>Section 91 - Firearms Act 2022</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pistol — Semi-Auto</t>
+          <t>Pistol - Semi-Auto</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Cannabis/Ganja — Compressed</t>
+          <t>Cannabis/Ganja - Compressed</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -4886,17 +4886,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>s.5 — Possession of Prohibited Weapon (15-25yr)</t>
+          <t>s.5 - Possession of Prohibited Weapon (15-25yr)</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Import/Export — Cannabis (DDA Part IIIA)</t>
+          <t>Import/Export - Cannabis (DDA Part IIIA)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Gun Court — High Court Division (judge alone, in camera)</t>
+          <t>Gun Court - High Court Division (judge alone, in camera)</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Successful — Seizure + Arrest</t>
+          <t>Successful - Seizure + Arrest</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Held — Active Case</t>
+          <t>Held - Active Case</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Open — Active Investigation</t>
+          <t>Open - Active Investigation</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Action — Surveillance</t>
+          <t>Action - Surveillance</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4993,12 +4993,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Section 21 — Dangerous Drugs Act</t>
+          <t>Section 21 - Dangerous Drugs Act</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pistol — Revolver</t>
+          <t>Pistol - Revolver</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Cannabis/Ganja — Loose</t>
+          <t>Cannabis/Ganja - Loose</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -5018,17 +5018,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>s.6 — Stockpiling (3+ weapons / 50+ rounds)</t>
+          <t>s.6 - Stockpiling (3+ weapons / 50+ rounds)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Import/Export — Cocaine (DDA Part IV)</t>
+          <t>Import/Export - Cocaine (DDA Part IV)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Gun Court — Circuit Court Division (jury, murder/treason)</t>
+          <t>Gun Court - Circuit Court Division (jury, murder/treason)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Successful — Seizure Only</t>
+          <t>Successful - Seizure Only</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -5068,17 +5068,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Submitted — Pending</t>
+          <t>Submitted - Pending</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Submitted — Pending</t>
+          <t>Submitted - Pending</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Held — Court Order</t>
+          <t>Held - Court Order</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Open — Pending Forensics</t>
+          <t>Open - Pending Forensics</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Action — Port Alert</t>
+          <t>Action - Port Alert</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Section 14 — POCA 2007</t>
+          <t>Section 14 - POCA 2007</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rifle — Semi-Auto</t>
+          <t>Rifle - Semi-Auto</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Cannabis/Ganja — Oil/Edibles</t>
+          <t>Cannabis/Ganja - Oil/Edibles</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -5150,17 +5150,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>s.7 — Trafficking in Prohibited Weapon (20yr min)</t>
+          <t>s.7 - Trafficking in Prohibited Weapon (20yr min)</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Import/Export — Heroin (DDA Part IV)</t>
+          <t>Import/Export - Heroin (DDA Part IV)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Gun Court — RM Division (preliminary exam)</t>
+          <t>Gun Court - RM Division (preliminary exam)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Successful — Arrest Only</t>
+          <t>Successful - Arrest Only</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Traced — US Origin</t>
+          <t>Traced - US Origin</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Destroyed — Authorized</t>
+          <t>Destroyed - Authorized</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Open — Pending Witness Statements</t>
+          <t>Open - Pending Witness Statements</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Trafficking — Firearms</t>
+          <t>Trafficking - Firearms</t>
         </is>
       </c>
     </row>
@@ -5252,12 +5252,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ZOSO — Warrantless (s.5 ZOSO Act)</t>
+          <t>ZOSO - Warrantless (s.5 ZOSO Act)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rifle — Bolt Action</t>
+          <t>Rifle - Bolt Action</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Cocaine — Powder</t>
+          <t>Cocaine - Powder</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -5277,12 +5277,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>s.8 — Possession with Intent to Traffic</t>
+          <t>s.8 - Possession with Intent to Traffic</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Dealing/Trafficking — Cannabis</t>
+          <t>Dealing/Trafficking - Cannabis</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Released — No Charge</t>
+          <t>Released - No Charge</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Partial — Intel Developed</t>
+          <t>Partial - Intel Developed</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Hit — Confirmed Match</t>
+          <t>Hit - Confirmed Match</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Traced — Non-US Origin</t>
+          <t>Traced - Non-US Origin</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -5342,17 +5342,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Trafficking — Firearms</t>
+          <t>Trafficking - Firearms</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Open — Surveillance</t>
+          <t>Open - Surveillance</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Trafficking — Narcotics</t>
+          <t>Trafficking - Narcotics</t>
         </is>
       </c>
     </row>
@@ -5374,12 +5374,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SOE — Warrantless</t>
+          <t>SOE - Warrantless</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rifle — Assault</t>
+          <t>Rifle - Assault</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Cocaine — Crack</t>
+          <t>Cocaine - Crack</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -5399,12 +5399,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>s.9 — Manufacture of Prohibited Weapon</t>
+          <t>s.9 - Manufacture of Prohibited Weapon</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Dealing/Trafficking — Cocaine</t>
+          <t>Dealing/Trafficking - Cocaine</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Released — Insufficient Evidence</t>
+          <t>Released - Insufficient Evidence</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Negative — No Finds</t>
+          <t>Negative - No Finds</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5444,17 +5444,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Hit — Unconfirmed</t>
+          <t>Hit - Unconfirmed</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Untraceable — No Serial</t>
+          <t>Untraceable - No Serial</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Forfeited — POCA</t>
+          <t>Forfeited - POCA</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Trafficking — Narcotics</t>
+          <t>Trafficking - Narcotics</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Open — Pending DPP Submission</t>
+          <t>Open - Pending DPP Submission</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>s.10 — Dealing in Prohibited Weapon</t>
+          <t>s.10 - Dealing in Prohibited Weapon</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Dealing/Trafficking — Heroin</t>
+          <t>Dealing/Trafficking - Heroin</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Ruling — Charge Approved</t>
+          <t>Ruling - Charge Approved</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Aborted — Compromised</t>
+          <t>Aborted - Compromised</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Untraceable — Obliterated</t>
+          <t>Untraceable - Obliterated</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Forfeiture Order — Post Conviction</t>
+          <t>Forfeiture Order - Post Conviction</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Trafficking — Multi-Commodity</t>
+          <t>Trafficking - Multi-Commodity</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Intel Filed — Monitor</t>
+          <t>Intel Filed - Monitor</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>s.12 — Diversion of Lawful Firearms</t>
+          <t>s.12 - Diversion of Lawful Firearms</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Possession — Cannabis (&gt;2oz)</t>
+          <t>Possession - Cannabis (&gt;2oz)</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Ruling — No Charge (Insufficient Evidence)</t>
+          <t>Ruling - No Charge (Insufficient Evidence)</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Aborted — Safety Concern</t>
+          <t>Aborted - Safety Concern</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Closed — Convicted</t>
+          <t>Closed - Convicted</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>Import/Export — Narcotics</t>
+          <t>Import/Export - Narcotics</t>
         </is>
       </c>
     </row>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Closed — Insufficient Info</t>
+          <t>Closed - Insufficient Info</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>s.29 — Unmarked Firearm</t>
+          <t>s.29 - Unmarked Firearm</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Possession — Cocaine</t>
+          <t>Possession - Cocaine</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Closed — Acquitted</t>
+          <t>Closed - Acquitted</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>Import/Export — Firearms</t>
+          <t>Import/Export - Firearms</t>
         </is>
       </c>
     </row>
@@ -5797,7 +5797,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Joint Op — JCA</t>
+          <t>Joint Op - JCA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Cultivation — Cannabis (&gt;5 plants)</t>
+          <t>Cultivation - Cannabis (&gt;5 plants)</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -5847,7 +5847,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Closed — No Charge (Insufficient Evidence)</t>
+          <t>Closed - No Charge (Insufficient Evidence)</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Joint Op — JDF</t>
+          <t>Joint Op - JDF</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Cultivation — Coca/Opium</t>
+          <t>Cultivation - Coca/Opium</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Closed — Withdrawn</t>
+          <t>Closed - Withdrawn</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Joint Op — MOCA</t>
+          <t>Joint Op - MOCA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Deemed Dealing — School Premises</t>
+          <t>Deemed Dealing - School Premises</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Cold Case — Under Review</t>
+          <t>Cold Case - Under Review</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Joint Op — DEA</t>
+          <t>Joint Op - DEA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Component — Frame/Receiver</t>
+          <t>Component - Frame/Receiver</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Deemed Dealing — Heroin &gt;1/10oz</t>
+          <t>Deemed Dealing - Heroin &gt;1/10oz</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Cold Case — Dormant</t>
+          <t>Cold Case - Dormant</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Component — Barrel</t>
+          <t>Component - Barrel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>Merged — See Linked Case</t>
+          <t>Merged - See Linked Case</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Component — Slide</t>
+          <t>Component - Slide</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">

--- a/FNID_Area3_Operational_Workbook.xlsx
+++ b/FNID_Area3_Operational_Workbook.xlsx
@@ -24,21 +24,7 @@
     <sheet name="tbl_Personnel" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="tbl_Vehicles" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'tbl_IntelLog'!$A$1:$W$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'tbl_Operations'!$A$1:$AG$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'tbl_FirearmSeizures'!$A$1:$AM$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'tbl_NarcoticSeizures'!$A$1:$AE$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'tbl_OtherSeizures'!$A$1:$U$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'tbl_Arrests'!$A$1:$AJ$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'tbl_CaseRegistry'!$A$1:$AY$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'tbl_ChainOfCustody'!$A$1:$S$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'tbl_CaseFiles'!$A$1:$AI$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'tbl_Witnesses'!$A$1:$V$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'tbl_Informants'!$A$1:$R$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'tbl_Personnel'!$A$1:$P$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'tbl_Vehicles'!$A$1:$O$1</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -2118,7 +2104,6 @@
       <c r="AY6" s="33" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AY1"/>
   <conditionalFormatting sqref="F2:F1000">
     <cfRule type="cellIs" priority="1" operator="beginsWith" dxfId="1">
       <formula>"Open"</formula>
@@ -2463,7 +2448,6 @@
       <c r="S6" s="33" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S1"/>
   <dataValidations count="2">
     <dataValidation sqref="O2:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid" error="Select from dropdown" type="list">
       <formula1>=Lookups!$Q$2:$Q$3</formula1>
@@ -2934,7 +2918,6 @@
       <c r="AI6" s="33" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AI1"/>
   <conditionalFormatting sqref="AF2:AF1000">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>0.5</formula>
@@ -3250,7 +3233,6 @@
       <c r="V6" s="33" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V1"/>
   <conditionalFormatting sqref="R2:R1000">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Yes"</formula>
@@ -3519,7 +3501,6 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="849B"/>
-  <autoFilter ref="A1:R1"/>
   <conditionalFormatting sqref="N2:N1000">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>=AND(N2&lt;&gt;"",N2&lt;TODAY())</formula>
@@ -3733,7 +3714,6 @@
       <c r="P6" s="33" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3931,7 +3911,6 @@
       <c r="O6" s="33" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O1"/>
   <conditionalFormatting sqref="K2:K1000">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>=AND(K2&lt;&gt;"",K2&lt;TODAY())</formula>
@@ -6450,7 +6429,6 @@
       <c r="W6" s="33" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W1"/>
   <conditionalFormatting sqref="F2:F1000">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Critical"</formula>
@@ -6892,7 +6870,6 @@
       <c r="AG6" s="33" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AG1"/>
   <conditionalFormatting sqref="Q2:Q1000">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"No"</formula>
@@ -7405,7 +7382,6 @@
       <c r="AM6" s="33" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM1"/>
   <conditionalFormatting sqref="AB2:AB1000">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Certificate Overdue"</formula>
@@ -7854,7 +7830,6 @@
       <c r="AE6" s="33" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AE1"/>
   <conditionalFormatting sqref="R2:R1000">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Certificate Overdue"</formula>
@@ -8167,7 +8142,6 @@
       <c r="U6" s="33" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U1"/>
   <dataValidations count="1">
     <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid" error="Select from dropdown" type="list">
       <formula1>=Lookups!$P$2:$P$15</formula1>
@@ -8646,7 +8620,6 @@
       <c r="AJ6" s="33" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ1"/>
   <conditionalFormatting sqref="W2:W1000">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"BREACH"</formula>
